--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D240773-116B-8649-8C41-AC7006DE6528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF093EE-B65D-4746-9E9C-88146D034048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>Temps joué</t>
   </si>
@@ -130,9 +130,6 @@
     <t>Karahali Souaré</t>
   </si>
   <si>
-    <t>Yoan Zouma</t>
-  </si>
-  <si>
     <t>Mattheo Haon</t>
   </si>
   <si>
@@ -176,13 +173,43 @@
   </si>
   <si>
     <t>01:08:52</t>
+  </si>
+  <si>
+    <t>Ryad Kralladi</t>
+  </si>
+  <si>
+    <t>01:10:58</t>
+  </si>
+  <si>
+    <t>01:10:25</t>
+  </si>
+  <si>
+    <t>01:11:52</t>
+  </si>
+  <si>
+    <t>01:08:58</t>
+  </si>
+  <si>
+    <t>01:11:39</t>
+  </si>
+  <si>
+    <t>01:09:18</t>
+  </si>
+  <si>
+    <t>Gibril Djahl</t>
+  </si>
+  <si>
+    <t>01:08:04</t>
+  </si>
+  <si>
+    <t>01:12:07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -195,6 +222,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -226,6 +259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -628,13 +662,13 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -693,13 +727,13 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
         <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>7.41</v>
@@ -758,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4">
         <v>6.91</v>
@@ -829,7 +863,7 @@
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5">
         <v>6.88</v>
@@ -888,13 +922,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>7.31</v>
@@ -953,13 +987,13 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7">
         <v>7.38</v>
@@ -1018,13 +1052,13 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8">
         <v>7.01</v>
@@ -1083,13 +1117,13 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9">
         <v>6.84</v>
@@ -1154,7 +1188,7 @@
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10">
         <v>6.45</v>
@@ -1199,6 +1233,591 @@
         <v>3</v>
       </c>
       <c r="V10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11">
+        <v>6.27</v>
+      </c>
+      <c r="I11">
+        <v>0.73</v>
+      </c>
+      <c r="J11">
+        <v>5.53</v>
+      </c>
+      <c r="K11">
+        <v>0.74</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>5.29</v>
+      </c>
+      <c r="Q11">
+        <v>18.64</v>
+      </c>
+      <c r="R11">
+        <v>3.44</v>
+      </c>
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>5</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12">
+        <v>7.06</v>
+      </c>
+      <c r="I12">
+        <v>0.84</v>
+      </c>
+      <c r="J12">
+        <v>6.21</v>
+      </c>
+      <c r="K12">
+        <v>0.84</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>5.96</v>
+      </c>
+      <c r="Q12">
+        <v>19.91</v>
+      </c>
+      <c r="R12">
+        <v>4.25</v>
+      </c>
+      <c r="S12">
+        <v>11</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13">
+        <v>7.07</v>
+      </c>
+      <c r="I13">
+        <v>1.24</v>
+      </c>
+      <c r="J13">
+        <v>5.83</v>
+      </c>
+      <c r="K13">
+        <v>1.23</v>
+      </c>
+      <c r="L13">
+        <v>0.01</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>5.86</v>
+      </c>
+      <c r="Q13">
+        <v>25.12</v>
+      </c>
+      <c r="R13">
+        <v>4.47</v>
+      </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>6.53</v>
+      </c>
+      <c r="I14">
+        <v>0.47</v>
+      </c>
+      <c r="J14">
+        <v>6.05</v>
+      </c>
+      <c r="K14">
+        <v>0.49</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>5.2</v>
+      </c>
+      <c r="Q14">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R14">
+        <v>4.59</v>
+      </c>
+      <c r="S14">
+        <v>15</v>
+      </c>
+      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="U14">
+        <v>7</v>
+      </c>
+      <c r="V14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>6.69</v>
+      </c>
+      <c r="I15">
+        <v>0.63</v>
+      </c>
+      <c r="J15">
+        <v>6.06</v>
+      </c>
+      <c r="K15">
+        <v>0.63</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>5.81</v>
+      </c>
+      <c r="Q15">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="R15">
+        <v>4.22</v>
+      </c>
+      <c r="S15">
+        <v>17</v>
+      </c>
+      <c r="T15">
+        <v>2</v>
+      </c>
+      <c r="U15">
+        <v>8</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16">
+        <v>7.56</v>
+      </c>
+      <c r="I16">
+        <v>1.66</v>
+      </c>
+      <c r="J16">
+        <v>5.9</v>
+      </c>
+      <c r="K16">
+        <v>1.64</v>
+      </c>
+      <c r="L16">
+        <v>0.02</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>6.28</v>
+      </c>
+      <c r="Q16">
+        <v>22.7</v>
+      </c>
+      <c r="R16">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="S16">
+        <v>22</v>
+      </c>
+      <c r="T16">
+        <v>4</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17">
+        <v>6.58</v>
+      </c>
+      <c r="I17">
+        <v>0.79</v>
+      </c>
+      <c r="J17">
+        <v>5.79</v>
+      </c>
+      <c r="K17">
+        <v>0.79</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>5.66</v>
+      </c>
+      <c r="Q17">
+        <v>19.21</v>
+      </c>
+      <c r="R17">
+        <v>3.82</v>
+      </c>
+      <c r="S17">
+        <v>14</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18">
+        <v>5.26</v>
+      </c>
+      <c r="I18">
+        <v>0.05</v>
+      </c>
+      <c r="J18">
+        <v>5.21</v>
+      </c>
+      <c r="K18">
+        <v>0.05</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>4.68</v>
+      </c>
+      <c r="Q18">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="R18">
+        <v>3.25</v>
+      </c>
+      <c r="S18">
+        <v>5</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46217</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19">
+        <v>6.96</v>
+      </c>
+      <c r="I19">
+        <v>1.18</v>
+      </c>
+      <c r="J19">
+        <v>5.78</v>
+      </c>
+      <c r="K19">
+        <v>1.17</v>
+      </c>
+      <c r="L19">
+        <v>0.01</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>5.73</v>
+      </c>
+      <c r="Q19">
+        <v>20.28</v>
+      </c>
+      <c r="R19">
+        <v>3.73</v>
+      </c>
+      <c r="S19">
+        <v>5</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+      <c r="V19">
         <v>0</v>
       </c>
     </row>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF093EE-B65D-4746-9E9C-88146D034048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE38683-E815-BB42-B126-ACE907F20474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
   <si>
     <t>Temps joué</t>
   </si>
@@ -203,6 +203,30 @@
   </si>
   <si>
     <t>01:12:07</t>
+  </si>
+  <si>
+    <t>01:23:55</t>
+  </si>
+  <si>
+    <t>01:23:17</t>
+  </si>
+  <si>
+    <t>01:20:01</t>
+  </si>
+  <si>
+    <t>01:22:55</t>
+  </si>
+  <si>
+    <t>01:21:32</t>
+  </si>
+  <si>
+    <t>01:23:18</t>
+  </si>
+  <si>
+    <t>01:23:03</t>
+  </si>
+  <si>
+    <t>01:24:10</t>
   </si>
 </sst>
 </file>
@@ -574,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -1821,6 +1845,591 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20">
+        <v>9.36</v>
+      </c>
+      <c r="I20">
+        <v>0.37</v>
+      </c>
+      <c r="J20">
+        <v>8.98</v>
+      </c>
+      <c r="K20">
+        <v>0.31</v>
+      </c>
+      <c r="L20">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>6.73</v>
+      </c>
+      <c r="Q20">
+        <v>22.01</v>
+      </c>
+      <c r="R20">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="S20">
+        <v>20</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>16</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="I21">
+        <v>0.35</v>
+      </c>
+      <c r="J21">
+        <v>9.43</v>
+      </c>
+      <c r="K21">
+        <v>0.23</v>
+      </c>
+      <c r="L21">
+        <v>0.12</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>7.02</v>
+      </c>
+      <c r="Q21">
+        <v>25.05</v>
+      </c>
+      <c r="R21">
+        <v>4.34</v>
+      </c>
+      <c r="S21">
+        <v>9</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>5</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I22">
+        <v>0.27</v>
+      </c>
+      <c r="J22">
+        <v>8.43</v>
+      </c>
+      <c r="K22">
+        <v>0.13</v>
+      </c>
+      <c r="L22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>6.45</v>
+      </c>
+      <c r="Q22">
+        <v>23.89</v>
+      </c>
+      <c r="R22">
+        <v>4.09</v>
+      </c>
+      <c r="S22">
+        <v>11</v>
+      </c>
+      <c r="T22">
+        <v>2</v>
+      </c>
+      <c r="U22">
+        <v>7</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="I23">
+        <v>0.31</v>
+      </c>
+      <c r="J23">
+        <v>8.9</v>
+      </c>
+      <c r="K23">
+        <v>0.16</v>
+      </c>
+      <c r="L23">
+        <v>0.12</v>
+      </c>
+      <c r="M23">
+        <v>0.03</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>6</v>
+      </c>
+      <c r="P23">
+        <v>6.11</v>
+      </c>
+      <c r="Q23">
+        <v>28.56</v>
+      </c>
+      <c r="R23">
+        <v>4.53</v>
+      </c>
+      <c r="S23">
+        <v>22</v>
+      </c>
+      <c r="T23">
+        <v>2</v>
+      </c>
+      <c r="U23">
+        <v>16</v>
+      </c>
+      <c r="V23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24">
+        <v>9.49</v>
+      </c>
+      <c r="I24">
+        <v>0.22</v>
+      </c>
+      <c r="J24">
+        <v>9.26</v>
+      </c>
+      <c r="K24">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.09</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>6.93</v>
+      </c>
+      <c r="Q24">
+        <v>22.44</v>
+      </c>
+      <c r="R24">
+        <v>4.09</v>
+      </c>
+      <c r="S24">
+        <v>9</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>4</v>
+      </c>
+      <c r="V24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25">
+        <v>9.69</v>
+      </c>
+      <c r="I25">
+        <v>0.37</v>
+      </c>
+      <c r="J25">
+        <v>9.31</v>
+      </c>
+      <c r="K25">
+        <v>0.23</v>
+      </c>
+      <c r="L25">
+        <v>0.15</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>6.92</v>
+      </c>
+      <c r="Q25">
+        <v>24.51</v>
+      </c>
+      <c r="R25">
+        <v>4.46</v>
+      </c>
+      <c r="S25">
+        <v>12</v>
+      </c>
+      <c r="T25">
+        <v>4</v>
+      </c>
+      <c r="U25">
+        <v>14</v>
+      </c>
+      <c r="V25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26">
+        <v>7.11</v>
+      </c>
+      <c r="I26">
+        <v>0.26</v>
+      </c>
+      <c r="J26">
+        <v>6.84</v>
+      </c>
+      <c r="K26">
+        <v>0.18</v>
+      </c>
+      <c r="L26">
+        <v>0.08</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>5.24</v>
+      </c>
+      <c r="Q26">
+        <v>23.16</v>
+      </c>
+      <c r="R26">
+        <v>3.52</v>
+      </c>
+      <c r="S26">
+        <v>10</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>9</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="I27">
+        <v>0.31</v>
+      </c>
+      <c r="J27">
+        <v>9.07</v>
+      </c>
+      <c r="K27">
+        <v>0.22</v>
+      </c>
+      <c r="L27">
+        <v>0.09</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>6.61</v>
+      </c>
+      <c r="Q27">
+        <v>25.07</v>
+      </c>
+      <c r="R27">
+        <v>4.09</v>
+      </c>
+      <c r="S27">
+        <v>22</v>
+      </c>
+      <c r="T27">
+        <v>3</v>
+      </c>
+      <c r="U27">
+        <v>20</v>
+      </c>
+      <c r="V27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28">
+        <v>9.16</v>
+      </c>
+      <c r="I28">
+        <v>0.3</v>
+      </c>
+      <c r="J28">
+        <v>8.85</v>
+      </c>
+      <c r="K28">
+        <v>0.21</v>
+      </c>
+      <c r="L28">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M28">
+        <v>0.03</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28">
+        <v>6.05</v>
+      </c>
+      <c r="Q28">
+        <v>26.5</v>
+      </c>
+      <c r="R28">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="S28">
+        <v>26</v>
+      </c>
+      <c r="T28">
+        <v>6</v>
+      </c>
+      <c r="U28">
+        <v>17</v>
+      </c>
+      <c r="V28">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE38683-E815-BB42-B126-ACE907F20474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F8F63F-0B8A-A047-A7CE-CA550A96BCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
   <si>
     <t>Temps joué</t>
   </si>
@@ -227,6 +227,33 @@
   </si>
   <si>
     <t>01:24:10</t>
+  </si>
+  <si>
+    <t>01:31:13</t>
+  </si>
+  <si>
+    <t>01:32:09</t>
+  </si>
+  <si>
+    <t>01:28:56</t>
+  </si>
+  <si>
+    <t>01:02:53</t>
+  </si>
+  <si>
+    <t>01:32:18</t>
+  </si>
+  <si>
+    <t>01:31:21</t>
+  </si>
+  <si>
+    <t>01:31:37</t>
+  </si>
+  <si>
+    <t>01:31:05</t>
+  </si>
+  <si>
+    <t>01:29:44</t>
   </si>
 </sst>
 </file>
@@ -598,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -2430,6 +2457,591 @@
         <v>12</v>
       </c>
     </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>0.17</v>
+      </c>
+      <c r="J29">
+        <v>9.82</v>
+      </c>
+      <c r="K29">
+        <v>0.16</v>
+      </c>
+      <c r="L29">
+        <v>0.01</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>6.5</v>
+      </c>
+      <c r="Q29">
+        <v>21.48</v>
+      </c>
+      <c r="R29">
+        <v>4.07</v>
+      </c>
+      <c r="S29">
+        <v>12</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>4</v>
+      </c>
+      <c r="V29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30">
+        <v>8.77</v>
+      </c>
+      <c r="I30">
+        <v>0.1</v>
+      </c>
+      <c r="J30">
+        <v>8.66</v>
+      </c>
+      <c r="K30">
+        <v>0.08</v>
+      </c>
+      <c r="L30">
+        <v>0.02</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>5.63</v>
+      </c>
+      <c r="Q30">
+        <v>22.85</v>
+      </c>
+      <c r="R30">
+        <v>3.78</v>
+      </c>
+      <c r="S30">
+        <v>10</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>9</v>
+      </c>
+      <c r="V30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="I31">
+        <v>0.18</v>
+      </c>
+      <c r="J31">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="K31">
+        <v>0.12</v>
+      </c>
+      <c r="L31">
+        <v>0.06</v>
+      </c>
+      <c r="M31">
+        <v>0.01</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31">
+        <v>6.13</v>
+      </c>
+      <c r="Q31">
+        <v>26.1</v>
+      </c>
+      <c r="R31">
+        <v>3.98</v>
+      </c>
+      <c r="S31">
+        <v>4</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>3</v>
+      </c>
+      <c r="V31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32">
+        <v>6.96</v>
+      </c>
+      <c r="I32">
+        <v>0.01</v>
+      </c>
+      <c r="J32">
+        <v>6.94</v>
+      </c>
+      <c r="K32">
+        <v>0.02</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>6.26</v>
+      </c>
+      <c r="Q32">
+        <v>16.38</v>
+      </c>
+      <c r="R32">
+        <v>3.74</v>
+      </c>
+      <c r="S32">
+        <v>2</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33">
+        <v>9.77</v>
+      </c>
+      <c r="I33">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J33">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="K33">
+        <v>0.15</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>5.61</v>
+      </c>
+      <c r="Q33">
+        <v>19.89</v>
+      </c>
+      <c r="R33">
+        <v>4.47</v>
+      </c>
+      <c r="S33">
+        <v>9</v>
+      </c>
+      <c r="T33">
+        <v>3</v>
+      </c>
+      <c r="U33">
+        <v>9</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34">
+        <v>9.4</v>
+      </c>
+      <c r="I34">
+        <v>0.34</v>
+      </c>
+      <c r="J34">
+        <v>9.06</v>
+      </c>
+      <c r="K34">
+        <v>0.19</v>
+      </c>
+      <c r="L34">
+        <v>0.06</v>
+      </c>
+      <c r="M34">
+        <v>0.09</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="P34">
+        <v>6.11</v>
+      </c>
+      <c r="Q34">
+        <v>29.74</v>
+      </c>
+      <c r="R34">
+        <v>4.74</v>
+      </c>
+      <c r="S34">
+        <v>17</v>
+      </c>
+      <c r="T34">
+        <v>5</v>
+      </c>
+      <c r="U34">
+        <v>18</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" t="s">
+        <v>70</v>
+      </c>
+      <c r="H35">
+        <v>9.75</v>
+      </c>
+      <c r="I35">
+        <v>0.66</v>
+      </c>
+      <c r="J35">
+        <v>9.08</v>
+      </c>
+      <c r="K35">
+        <v>0.6</v>
+      </c>
+      <c r="L35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>6.32</v>
+      </c>
+      <c r="Q35">
+        <v>24.83</v>
+      </c>
+      <c r="R35">
+        <v>4.24</v>
+      </c>
+      <c r="S35">
+        <v>21</v>
+      </c>
+      <c r="T35">
+        <v>3</v>
+      </c>
+      <c r="U35">
+        <v>9</v>
+      </c>
+      <c r="V35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36">
+        <v>9.33</v>
+      </c>
+      <c r="I36">
+        <v>0.13</v>
+      </c>
+      <c r="J36">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="K36">
+        <v>0.12</v>
+      </c>
+      <c r="L36">
+        <v>0.02</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
+        <v>6.09</v>
+      </c>
+      <c r="Q36">
+        <v>25.12</v>
+      </c>
+      <c r="R36">
+        <v>3.8</v>
+      </c>
+      <c r="S36">
+        <v>10</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>8</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37">
+        <v>8.81</v>
+      </c>
+      <c r="I37">
+        <v>0.08</v>
+      </c>
+      <c r="J37">
+        <v>8.73</v>
+      </c>
+      <c r="K37">
+        <v>0.05</v>
+      </c>
+      <c r="L37">
+        <v>0.03</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>5.77</v>
+      </c>
+      <c r="Q37">
+        <v>24.6</v>
+      </c>
+      <c r="R37">
+        <v>5.04</v>
+      </c>
+      <c r="S37">
+        <v>10</v>
+      </c>
+      <c r="T37">
+        <v>5</v>
+      </c>
+      <c r="U37">
+        <v>12</v>
+      </c>
+      <c r="V37">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F8F63F-0B8A-A047-A7CE-CA550A96BCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28105D79-6C02-4543-8024-D86388C34DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="82">
   <si>
     <t>Temps joué</t>
   </si>
@@ -254,6 +254,33 @@
   </si>
   <si>
     <t>01:29:44</t>
+  </si>
+  <si>
+    <t>01:28:13</t>
+  </si>
+  <si>
+    <t>01:29:54</t>
+  </si>
+  <si>
+    <t>01:25:51</t>
+  </si>
+  <si>
+    <t>01:26:06</t>
+  </si>
+  <si>
+    <t>01:30:10</t>
+  </si>
+  <si>
+    <t>01:30:57</t>
+  </si>
+  <si>
+    <t>01:25:58</t>
+  </si>
+  <si>
+    <t>01:28:12</t>
+  </si>
+  <si>
+    <t>01:27:57</t>
   </si>
 </sst>
 </file>
@@ -625,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -3042,6 +3069,656 @@
         <v>3</v>
       </c>
     </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38">
+        <v>7.03</v>
+      </c>
+      <c r="I38">
+        <v>0.12</v>
+      </c>
+      <c r="J38">
+        <v>6.9</v>
+      </c>
+      <c r="K38">
+        <v>0.12</v>
+      </c>
+      <c r="L38">
+        <v>0.01</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="Q38">
+        <v>20.81</v>
+      </c>
+      <c r="R38">
+        <v>4.47</v>
+      </c>
+      <c r="S38">
+        <v>12</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38">
+        <v>10</v>
+      </c>
+      <c r="V38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39">
+        <v>8.01</v>
+      </c>
+      <c r="I39">
+        <v>0.2</v>
+      </c>
+      <c r="J39">
+        <v>7.8</v>
+      </c>
+      <c r="K39">
+        <v>0.19</v>
+      </c>
+      <c r="L39">
+        <v>0.01</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>5.26</v>
+      </c>
+      <c r="Q39">
+        <v>23.85</v>
+      </c>
+      <c r="R39">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="S39">
+        <v>22</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39">
+        <v>20</v>
+      </c>
+      <c r="V39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" t="s">
+        <v>75</v>
+      </c>
+      <c r="H40">
+        <v>7.67</v>
+      </c>
+      <c r="I40">
+        <v>0.24</v>
+      </c>
+      <c r="J40">
+        <v>7.41</v>
+      </c>
+      <c r="K40">
+        <v>0.25</v>
+      </c>
+      <c r="L40">
+        <v>0.01</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>4.83</v>
+      </c>
+      <c r="Q40">
+        <v>21.47</v>
+      </c>
+      <c r="R40">
+        <v>4.51</v>
+      </c>
+      <c r="S40">
+        <v>40</v>
+      </c>
+      <c r="T40">
+        <v>9</v>
+      </c>
+      <c r="U40">
+        <v>29</v>
+      </c>
+      <c r="V40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="s">
+        <v>35</v>
+      </c>
+      <c r="F41" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41">
+        <v>7.23</v>
+      </c>
+      <c r="I41">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J41">
+        <v>6.95</v>
+      </c>
+      <c r="K41">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>4.97</v>
+      </c>
+      <c r="Q41">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="R41">
+        <v>4.57</v>
+      </c>
+      <c r="S41">
+        <v>8</v>
+      </c>
+      <c r="T41">
+        <v>2</v>
+      </c>
+      <c r="U41">
+        <v>6</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42">
+        <v>8.08</v>
+      </c>
+      <c r="I42">
+        <v>0.13</v>
+      </c>
+      <c r="J42">
+        <v>7.95</v>
+      </c>
+      <c r="K42">
+        <v>0.13</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>5.32</v>
+      </c>
+      <c r="Q42">
+        <v>21.15</v>
+      </c>
+      <c r="R42">
+        <v>4.45</v>
+      </c>
+      <c r="S42">
+        <v>15</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>11</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43">
+        <v>8.09</v>
+      </c>
+      <c r="I43">
+        <v>0.23</v>
+      </c>
+      <c r="J43">
+        <v>7.86</v>
+      </c>
+      <c r="K43">
+        <v>0.19</v>
+      </c>
+      <c r="L43">
+        <v>0.04</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>5.31</v>
+      </c>
+      <c r="Q43">
+        <v>23.9</v>
+      </c>
+      <c r="R43">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="S43">
+        <v>9</v>
+      </c>
+      <c r="T43">
+        <v>2</v>
+      </c>
+      <c r="U43">
+        <v>7</v>
+      </c>
+      <c r="V43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44">
+        <v>7.51</v>
+      </c>
+      <c r="I44">
+        <v>0.16</v>
+      </c>
+      <c r="J44">
+        <v>7.35</v>
+      </c>
+      <c r="K44">
+        <v>0.15</v>
+      </c>
+      <c r="L44">
+        <v>0.01</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>4.92</v>
+      </c>
+      <c r="Q44">
+        <v>20.88</v>
+      </c>
+      <c r="R44">
+        <v>4.71</v>
+      </c>
+      <c r="S44">
+        <v>10</v>
+      </c>
+      <c r="T44">
+        <v>3</v>
+      </c>
+      <c r="U44">
+        <v>10</v>
+      </c>
+      <c r="V44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="I45">
+        <v>0.25</v>
+      </c>
+      <c r="J45">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="K45">
+        <v>0.25</v>
+      </c>
+      <c r="L45">
+        <v>0.01</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>5.71</v>
+      </c>
+      <c r="Q45">
+        <v>22.7</v>
+      </c>
+      <c r="R45">
+        <v>4.7</v>
+      </c>
+      <c r="S45">
+        <v>17</v>
+      </c>
+      <c r="T45">
+        <v>2</v>
+      </c>
+      <c r="U45">
+        <v>9</v>
+      </c>
+      <c r="V45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H46">
+        <v>7.73</v>
+      </c>
+      <c r="I46">
+        <v>0.44</v>
+      </c>
+      <c r="J46">
+        <v>7.29</v>
+      </c>
+      <c r="K46">
+        <v>0.44</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>5.18</v>
+      </c>
+      <c r="Q46">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="R46">
+        <v>3.21</v>
+      </c>
+      <c r="S46">
+        <v>6</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>10</v>
+      </c>
+      <c r="V46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>81</v>
+      </c>
+      <c r="H47">
+        <v>7.57</v>
+      </c>
+      <c r="I47">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J47">
+        <v>7.28</v>
+      </c>
+      <c r="K47">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="Q47">
+        <v>20.95</v>
+      </c>
+      <c r="R47">
+        <v>6.07</v>
+      </c>
+      <c r="S47">
+        <v>12</v>
+      </c>
+      <c r="T47">
+        <v>6</v>
+      </c>
+      <c r="U47">
+        <v>15</v>
+      </c>
+      <c r="V47">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28105D79-6C02-4543-8024-D86388C34DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE3FC1C-8006-EC42-BC50-049E67CE92DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="111">
   <si>
     <t>Temps joué</t>
   </si>
@@ -281,6 +281,93 @@
   </si>
   <si>
     <t>01:27:57</t>
+  </si>
+  <si>
+    <t>Omar Benyounes</t>
+  </si>
+  <si>
+    <t>01:41:51</t>
+  </si>
+  <si>
+    <t>Yassine Toubal</t>
+  </si>
+  <si>
+    <t>01:40:44</t>
+  </si>
+  <si>
+    <t>Theo Owono</t>
+  </si>
+  <si>
+    <t>Kamal Bafounta</t>
+  </si>
+  <si>
+    <t>01:42:11</t>
+  </si>
+  <si>
+    <t>Yoan Zouma</t>
+  </si>
+  <si>
+    <t>01:40:25</t>
+  </si>
+  <si>
+    <t>Ismail Mediouna</t>
+  </si>
+  <si>
+    <t>left foward</t>
+  </si>
+  <si>
+    <t>01:42:20</t>
+  </si>
+  <si>
+    <t>Donald Onana</t>
+  </si>
+  <si>
+    <t>center foward</t>
+  </si>
+  <si>
+    <t>01:41:03</t>
+  </si>
+  <si>
+    <t>Brady Gouandjia</t>
+  </si>
+  <si>
+    <t>Romain Antunes</t>
+  </si>
+  <si>
+    <t>Fares Fahri</t>
+  </si>
+  <si>
+    <t>01:42:01</t>
+  </si>
+  <si>
+    <t>left forward</t>
+  </si>
+  <si>
+    <t>01:44:51</t>
+  </si>
+  <si>
+    <t>center forward</t>
+  </si>
+  <si>
+    <t>01:42:06</t>
+  </si>
+  <si>
+    <t>01:45:07</t>
+  </si>
+  <si>
+    <t>01:38:07</t>
+  </si>
+  <si>
+    <t>01:43:07</t>
+  </si>
+  <si>
+    <t>01:39:44</t>
+  </si>
+  <si>
+    <t>01:40:06</t>
+  </si>
+  <si>
+    <t>01:38:14</t>
   </si>
 </sst>
 </file>
@@ -652,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -3719,6 +3806,1176 @@
         <v>7</v>
       </c>
     </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48">
+        <v>10.54</v>
+      </c>
+      <c r="I48">
+        <v>2.88</v>
+      </c>
+      <c r="J48">
+        <v>7.65</v>
+      </c>
+      <c r="K48">
+        <v>2.83</v>
+      </c>
+      <c r="L48">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>6.16</v>
+      </c>
+      <c r="Q48">
+        <v>24.02</v>
+      </c>
+      <c r="R48">
+        <v>4.93</v>
+      </c>
+      <c r="S48">
+        <v>43</v>
+      </c>
+      <c r="T48">
+        <v>4</v>
+      </c>
+      <c r="U48">
+        <v>32</v>
+      </c>
+      <c r="V48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" t="s">
+        <v>85</v>
+      </c>
+      <c r="H49">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="I49">
+        <v>1.71</v>
+      </c>
+      <c r="J49">
+        <v>7.84</v>
+      </c>
+      <c r="K49">
+        <v>1.68</v>
+      </c>
+      <c r="L49">
+        <v>0.03</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>5.64</v>
+      </c>
+      <c r="Q49">
+        <v>23.48</v>
+      </c>
+      <c r="R49">
+        <v>4.2</v>
+      </c>
+      <c r="S49">
+        <v>17</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49">
+        <v>12</v>
+      </c>
+      <c r="V49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50">
+        <v>9.98</v>
+      </c>
+      <c r="I50">
+        <v>1.72</v>
+      </c>
+      <c r="J50">
+        <v>8.26</v>
+      </c>
+      <c r="K50">
+        <v>1.61</v>
+      </c>
+      <c r="L50">
+        <v>0.12</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>5.84</v>
+      </c>
+      <c r="Q50">
+        <v>24.44</v>
+      </c>
+      <c r="R50">
+        <v>4.54</v>
+      </c>
+      <c r="S50">
+        <v>39</v>
+      </c>
+      <c r="T50">
+        <v>3</v>
+      </c>
+      <c r="U50">
+        <v>34</v>
+      </c>
+      <c r="V50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51">
+        <v>10.51</v>
+      </c>
+      <c r="I51">
+        <v>2.99</v>
+      </c>
+      <c r="J51">
+        <v>7.5</v>
+      </c>
+      <c r="K51">
+        <v>2.94</v>
+      </c>
+      <c r="L51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>6.15</v>
+      </c>
+      <c r="Q51">
+        <v>22.31</v>
+      </c>
+      <c r="R51">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S51">
+        <v>19</v>
+      </c>
+      <c r="T51">
+        <v>3</v>
+      </c>
+      <c r="U51">
+        <v>27</v>
+      </c>
+      <c r="V51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="s">
+        <v>89</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>90</v>
+      </c>
+      <c r="H52">
+        <v>7.5</v>
+      </c>
+      <c r="I52">
+        <v>0.18</v>
+      </c>
+      <c r="J52">
+        <v>7.32</v>
+      </c>
+      <c r="K52">
+        <v>0.18</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>4.41</v>
+      </c>
+      <c r="Q52">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="R52">
+        <v>4.18</v>
+      </c>
+      <c r="S52">
+        <v>8</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52">
+        <v>7</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G53" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53">
+        <v>6.84</v>
+      </c>
+      <c r="I53">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J53">
+        <v>6.69</v>
+      </c>
+      <c r="K53">
+        <v>0.13</v>
+      </c>
+      <c r="L53">
+        <v>0.02</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>4.12</v>
+      </c>
+      <c r="Q53">
+        <v>23.46</v>
+      </c>
+      <c r="R53">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="S53">
+        <v>12</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="U53">
+        <v>12</v>
+      </c>
+      <c r="V53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G54" t="s">
+        <v>96</v>
+      </c>
+      <c r="H54">
+        <v>9.52</v>
+      </c>
+      <c r="I54">
+        <v>2.15</v>
+      </c>
+      <c r="J54">
+        <v>7.35</v>
+      </c>
+      <c r="K54">
+        <v>2.11</v>
+      </c>
+      <c r="L54">
+        <v>0.06</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>5.59</v>
+      </c>
+      <c r="Q54">
+        <v>23.43</v>
+      </c>
+      <c r="R54">
+        <v>4.26</v>
+      </c>
+      <c r="S54">
+        <v>25</v>
+      </c>
+      <c r="T54">
+        <v>5</v>
+      </c>
+      <c r="U54">
+        <v>23</v>
+      </c>
+      <c r="V54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55">
+        <v>9.57</v>
+      </c>
+      <c r="I55">
+        <v>2.83</v>
+      </c>
+      <c r="J55">
+        <v>6.73</v>
+      </c>
+      <c r="K55">
+        <v>2.74</v>
+      </c>
+      <c r="L55">
+        <v>0.09</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>5.57</v>
+      </c>
+      <c r="Q55">
+        <v>23.59</v>
+      </c>
+      <c r="R55">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="S55">
+        <v>47</v>
+      </c>
+      <c r="T55">
+        <v>8</v>
+      </c>
+      <c r="U55">
+        <v>34</v>
+      </c>
+      <c r="V55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="s">
+        <v>98</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" t="s">
+        <v>96</v>
+      </c>
+      <c r="H56">
+        <v>10.31</v>
+      </c>
+      <c r="I56">
+        <v>2.9</v>
+      </c>
+      <c r="J56">
+        <v>7.4</v>
+      </c>
+      <c r="K56">
+        <v>2.85</v>
+      </c>
+      <c r="L56">
+        <v>0.06</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>6.08</v>
+      </c>
+      <c r="Q56">
+        <v>21.94</v>
+      </c>
+      <c r="R56">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="S56">
+        <v>17</v>
+      </c>
+      <c r="T56">
+        <v>2</v>
+      </c>
+      <c r="U56">
+        <v>16</v>
+      </c>
+      <c r="V56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" t="s">
+        <v>99</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" t="s">
+        <v>100</v>
+      </c>
+      <c r="H57">
+        <v>9.5</v>
+      </c>
+      <c r="I57">
+        <v>2.04</v>
+      </c>
+      <c r="J57">
+        <v>7.45</v>
+      </c>
+      <c r="K57">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="L57">
+        <v>0.01</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>5.53</v>
+      </c>
+      <c r="Q57">
+        <v>21.72</v>
+      </c>
+      <c r="R57">
+        <v>3.97</v>
+      </c>
+      <c r="S57">
+        <v>16</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>4</v>
+      </c>
+      <c r="V57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" t="s">
+        <v>101</v>
+      </c>
+      <c r="G58" t="s">
+        <v>102</v>
+      </c>
+      <c r="H58">
+        <v>6.16</v>
+      </c>
+      <c r="I58">
+        <v>0.09</v>
+      </c>
+      <c r="J58">
+        <v>6.07</v>
+      </c>
+      <c r="K58">
+        <v>0.09</v>
+      </c>
+      <c r="L58">
+        <v>0.01</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>3.42</v>
+      </c>
+      <c r="Q58">
+        <v>20.92</v>
+      </c>
+      <c r="R58">
+        <v>4.3</v>
+      </c>
+      <c r="S58">
+        <v>15</v>
+      </c>
+      <c r="T58">
+        <v>4</v>
+      </c>
+      <c r="U58">
+        <v>7</v>
+      </c>
+      <c r="V58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" t="s">
+        <v>104</v>
+      </c>
+      <c r="H59">
+        <v>7.25</v>
+      </c>
+      <c r="I59">
+        <v>1.27</v>
+      </c>
+      <c r="J59">
+        <v>5.97</v>
+      </c>
+      <c r="K59">
+        <v>1.27</v>
+      </c>
+      <c r="L59">
+        <v>0.01</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>3.88</v>
+      </c>
+      <c r="Q59">
+        <v>21.68</v>
+      </c>
+      <c r="R59">
+        <v>4.78</v>
+      </c>
+      <c r="S59">
+        <v>19</v>
+      </c>
+      <c r="T59">
+        <v>2</v>
+      </c>
+      <c r="U59">
+        <v>10</v>
+      </c>
+      <c r="V59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" t="s">
+        <v>105</v>
+      </c>
+      <c r="H60">
+        <v>7.58</v>
+      </c>
+      <c r="I60">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J60">
+        <v>5.54</v>
+      </c>
+      <c r="K60">
+        <v>2</v>
+      </c>
+      <c r="L60">
+        <v>0.03</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>4.25</v>
+      </c>
+      <c r="Q60">
+        <v>21.19</v>
+      </c>
+      <c r="R60">
+        <v>4.71</v>
+      </c>
+      <c r="S60">
+        <v>11</v>
+      </c>
+      <c r="T60">
+        <v>4</v>
+      </c>
+      <c r="U60">
+        <v>11</v>
+      </c>
+      <c r="V60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H61">
+        <v>6.08</v>
+      </c>
+      <c r="I61">
+        <v>0.15</v>
+      </c>
+      <c r="J61">
+        <v>5.92</v>
+      </c>
+      <c r="K61">
+        <v>0.15</v>
+      </c>
+      <c r="L61">
+        <v>0.01</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>3.5</v>
+      </c>
+      <c r="Q61">
+        <v>20.95</v>
+      </c>
+      <c r="R61">
+        <v>4.12</v>
+      </c>
+      <c r="S61">
+        <v>8</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+      <c r="U61">
+        <v>5</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>86</v>
+      </c>
+      <c r="F62" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" t="s">
+        <v>107</v>
+      </c>
+      <c r="H62">
+        <v>6.68</v>
+      </c>
+      <c r="I62">
+        <v>1.41</v>
+      </c>
+      <c r="J62">
+        <v>5.26</v>
+      </c>
+      <c r="K62">
+        <v>1.34</v>
+      </c>
+      <c r="L62">
+        <v>0.08</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>3.79</v>
+      </c>
+      <c r="Q62">
+        <v>21.08</v>
+      </c>
+      <c r="R62">
+        <v>4.84</v>
+      </c>
+      <c r="S62">
+        <v>14</v>
+      </c>
+      <c r="T62">
+        <v>4</v>
+      </c>
+      <c r="U62">
+        <v>8</v>
+      </c>
+      <c r="V62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>99</v>
+      </c>
+      <c r="F63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" t="s">
+        <v>108</v>
+      </c>
+      <c r="H63">
+        <v>7.19</v>
+      </c>
+      <c r="I63">
+        <v>1.08</v>
+      </c>
+      <c r="J63">
+        <v>6.1</v>
+      </c>
+      <c r="K63">
+        <v>1.06</v>
+      </c>
+      <c r="L63">
+        <v>0.03</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>4.08</v>
+      </c>
+      <c r="Q63">
+        <v>21.2</v>
+      </c>
+      <c r="R63">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S63">
+        <v>13</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>9</v>
+      </c>
+      <c r="V63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>82</v>
+      </c>
+      <c r="F64" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" t="s">
+        <v>109</v>
+      </c>
+      <c r="H64">
+        <v>7.07</v>
+      </c>
+      <c r="I64">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J64">
+        <v>5.97</v>
+      </c>
+      <c r="K64">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>3.98</v>
+      </c>
+      <c r="Q64">
+        <v>20.16</v>
+      </c>
+      <c r="R64">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S64">
+        <v>12</v>
+      </c>
+      <c r="T64">
+        <v>4</v>
+      </c>
+      <c r="U64">
+        <v>13</v>
+      </c>
+      <c r="V64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>98</v>
+      </c>
+      <c r="F65" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" t="s">
+        <v>110</v>
+      </c>
+      <c r="H65">
+        <v>6.78</v>
+      </c>
+      <c r="I65">
+        <v>1.85</v>
+      </c>
+      <c r="J65">
+        <v>4.92</v>
+      </c>
+      <c r="K65">
+        <v>1.81</v>
+      </c>
+      <c r="L65">
+        <v>0.04</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>4.05</v>
+      </c>
+      <c r="Q65">
+        <v>20.73</v>
+      </c>
+      <c r="R65">
+        <v>3.85</v>
+      </c>
+      <c r="S65">
+        <v>12</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>12</v>
+      </c>
+      <c r="V65">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE3FC1C-8006-EC42-BC50-049E67CE92DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1A00C4-BBC8-F64A-BA18-6FE43671375E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="139">
   <si>
     <t>Temps joué</t>
   </si>
@@ -368,6 +368,90 @@
   </si>
   <si>
     <t>01:38:14</t>
+  </si>
+  <si>
+    <t>01:36:08</t>
+  </si>
+  <si>
+    <t>01:22:20</t>
+  </si>
+  <si>
+    <t>01:04:05</t>
+  </si>
+  <si>
+    <t>01:35:19</t>
+  </si>
+  <si>
+    <t>01:35:33</t>
+  </si>
+  <si>
+    <t>01:35:04</t>
+  </si>
+  <si>
+    <t>00:59:39</t>
+  </si>
+  <si>
+    <t>01:28:08</t>
+  </si>
+  <si>
+    <t>01:14:53</t>
+  </si>
+  <si>
+    <t>01:27:07</t>
+  </si>
+  <si>
+    <t>01:22:41</t>
+  </si>
+  <si>
+    <t>01:24:58</t>
+  </si>
+  <si>
+    <t>01:28:48</t>
+  </si>
+  <si>
+    <t>01:02:27</t>
+  </si>
+  <si>
+    <t>00:47:14</t>
+  </si>
+  <si>
+    <t>00:52:07</t>
+  </si>
+  <si>
+    <t>00:47:13</t>
+  </si>
+  <si>
+    <t>00:46:35</t>
+  </si>
+  <si>
+    <t>00:45:48</t>
+  </si>
+  <si>
+    <t>01:03:57</t>
+  </si>
+  <si>
+    <t>01:39:36</t>
+  </si>
+  <si>
+    <t>01:33:25</t>
+  </si>
+  <si>
+    <t>01:41:14</t>
+  </si>
+  <si>
+    <t>01:34:56</t>
+  </si>
+  <si>
+    <t>01:31:38</t>
+  </si>
+  <si>
+    <t>01:38:51</t>
+  </si>
+  <si>
+    <t>01:35:12</t>
+  </si>
+  <si>
+    <t>01:28:00</t>
   </si>
 </sst>
 </file>
@@ -739,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -4976,6 +5060,2086 @@
         <v>1</v>
       </c>
     </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>82</v>
+      </c>
+      <c r="F66" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" t="s">
+        <v>111</v>
+      </c>
+      <c r="H66">
+        <v>9.89</v>
+      </c>
+      <c r="I66">
+        <v>1.21</v>
+      </c>
+      <c r="J66">
+        <v>8.65</v>
+      </c>
+      <c r="K66">
+        <v>0.92</v>
+      </c>
+      <c r="L66">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M66">
+        <v>0.04</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>8</v>
+      </c>
+      <c r="P66">
+        <v>5.62</v>
+      </c>
+      <c r="Q66">
+        <v>28.04</v>
+      </c>
+      <c r="R66">
+        <v>5</v>
+      </c>
+      <c r="S66">
+        <v>59</v>
+      </c>
+      <c r="T66">
+        <v>6</v>
+      </c>
+      <c r="U66">
+        <v>51</v>
+      </c>
+      <c r="V66">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="E67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" t="s">
+        <v>103</v>
+      </c>
+      <c r="G67" t="s">
+        <v>112</v>
+      </c>
+      <c r="H67">
+        <v>6.74</v>
+      </c>
+      <c r="I67">
+        <v>0.86</v>
+      </c>
+      <c r="J67">
+        <v>5.87</v>
+      </c>
+      <c r="K67">
+        <v>0.64</v>
+      </c>
+      <c r="L67">
+        <v>0.2</v>
+      </c>
+      <c r="M67">
+        <v>0.03</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="P67">
+        <v>4.88</v>
+      </c>
+      <c r="Q67">
+        <v>26.68</v>
+      </c>
+      <c r="R67">
+        <v>4.74</v>
+      </c>
+      <c r="S67">
+        <v>23</v>
+      </c>
+      <c r="T67">
+        <v>8</v>
+      </c>
+      <c r="U67">
+        <v>15</v>
+      </c>
+      <c r="V67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="E68" t="s">
+        <v>87</v>
+      </c>
+      <c r="F68" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" t="s">
+        <v>113</v>
+      </c>
+      <c r="H68">
+        <v>5.71</v>
+      </c>
+      <c r="I68">
+        <v>0.73</v>
+      </c>
+      <c r="J68">
+        <v>4.97</v>
+      </c>
+      <c r="K68">
+        <v>0.49</v>
+      </c>
+      <c r="L68">
+        <v>0.2</v>
+      </c>
+      <c r="M68">
+        <v>0.05</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>2</v>
+      </c>
+      <c r="P68">
+        <v>5.28</v>
+      </c>
+      <c r="Q68">
+        <v>27.97</v>
+      </c>
+      <c r="R68">
+        <v>4.57</v>
+      </c>
+      <c r="S68">
+        <v>18</v>
+      </c>
+      <c r="T68">
+        <v>7</v>
+      </c>
+      <c r="U68">
+        <v>19</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="E69" t="s">
+        <v>98</v>
+      </c>
+      <c r="F69" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" t="s">
+        <v>114</v>
+      </c>
+      <c r="H69">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I69">
+        <v>1.03</v>
+      </c>
+      <c r="J69">
+        <v>8.15</v>
+      </c>
+      <c r="K69">
+        <v>0.74</v>
+      </c>
+      <c r="L69">
+        <v>0.27</v>
+      </c>
+      <c r="M69">
+        <v>0.03</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>2</v>
+      </c>
+      <c r="P69">
+        <v>5.73</v>
+      </c>
+      <c r="Q69">
+        <v>25.64</v>
+      </c>
+      <c r="R69">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="S69">
+        <v>23</v>
+      </c>
+      <c r="T69">
+        <v>2</v>
+      </c>
+      <c r="U69">
+        <v>18</v>
+      </c>
+      <c r="V69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="E70" t="s">
+        <v>91</v>
+      </c>
+      <c r="F70" t="s">
+        <v>101</v>
+      </c>
+      <c r="G70" t="s">
+        <v>113</v>
+      </c>
+      <c r="H70">
+        <v>4.28</v>
+      </c>
+      <c r="I70">
+        <v>0.42</v>
+      </c>
+      <c r="J70">
+        <v>3.85</v>
+      </c>
+      <c r="K70">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L70">
+        <v>0.13</v>
+      </c>
+      <c r="M70">
+        <v>0.02</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>2</v>
+      </c>
+      <c r="P70">
+        <v>3.95</v>
+      </c>
+      <c r="Q70">
+        <v>26.62</v>
+      </c>
+      <c r="R70">
+        <v>4.21</v>
+      </c>
+      <c r="S70">
+        <v>10</v>
+      </c>
+      <c r="T70">
+        <v>3</v>
+      </c>
+      <c r="U70">
+        <v>8</v>
+      </c>
+      <c r="V70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="E71" t="s">
+        <v>99</v>
+      </c>
+      <c r="F71" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" t="s">
+        <v>115</v>
+      </c>
+      <c r="H71">
+        <v>8.58</v>
+      </c>
+      <c r="I71">
+        <v>0.82</v>
+      </c>
+      <c r="J71">
+        <v>7.75</v>
+      </c>
+      <c r="K71">
+        <v>0.59</v>
+      </c>
+      <c r="L71">
+        <v>0.21</v>
+      </c>
+      <c r="M71">
+        <v>0.02</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>2</v>
+      </c>
+      <c r="P71">
+        <v>5.31</v>
+      </c>
+      <c r="Q71">
+        <v>28.38</v>
+      </c>
+      <c r="R71">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="S71">
+        <v>23</v>
+      </c>
+      <c r="T71">
+        <v>2</v>
+      </c>
+      <c r="U71">
+        <v>16</v>
+      </c>
+      <c r="V71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="E72" t="s">
+        <v>89</v>
+      </c>
+      <c r="F72" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" t="s">
+        <v>116</v>
+      </c>
+      <c r="H72">
+        <v>7.41</v>
+      </c>
+      <c r="I72">
+        <v>0.67</v>
+      </c>
+      <c r="J72">
+        <v>6.73</v>
+      </c>
+      <c r="K72">
+        <v>0.45</v>
+      </c>
+      <c r="L72">
+        <v>0.18</v>
+      </c>
+      <c r="M72">
+        <v>0.05</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>4</v>
+      </c>
+      <c r="P72">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="Q72">
+        <v>29.06</v>
+      </c>
+      <c r="R72">
+        <v>4.12</v>
+      </c>
+      <c r="S72">
+        <v>16</v>
+      </c>
+      <c r="T72">
+        <v>3</v>
+      </c>
+      <c r="U72">
+        <v>8</v>
+      </c>
+      <c r="V72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" t="s">
+        <v>27</v>
+      </c>
+      <c r="G73" t="s">
+        <v>117</v>
+      </c>
+      <c r="H73">
+        <v>5.35</v>
+      </c>
+      <c r="I73">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J73">
+        <v>4.76</v>
+      </c>
+      <c r="K73">
+        <v>0.45</v>
+      </c>
+      <c r="L73">
+        <v>0.1</v>
+      </c>
+      <c r="M73">
+        <v>0.03</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>5</v>
+      </c>
+      <c r="P73">
+        <v>5.34</v>
+      </c>
+      <c r="Q73">
+        <v>26.23</v>
+      </c>
+      <c r="R73">
+        <v>4.12</v>
+      </c>
+      <c r="S73">
+        <v>17</v>
+      </c>
+      <c r="T73">
+        <v>2</v>
+      </c>
+      <c r="U73">
+        <v>11</v>
+      </c>
+      <c r="V73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>99</v>
+      </c>
+      <c r="F74" t="s">
+        <v>27</v>
+      </c>
+      <c r="G74" t="s">
+        <v>77</v>
+      </c>
+      <c r="H74">
+        <v>5.23</v>
+      </c>
+      <c r="I74">
+        <v>1.73</v>
+      </c>
+      <c r="J74">
+        <v>3.5</v>
+      </c>
+      <c r="K74">
+        <v>1.48</v>
+      </c>
+      <c r="L74">
+        <v>0.25</v>
+      </c>
+      <c r="M74">
+        <v>0.01</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>1</v>
+      </c>
+      <c r="P74">
+        <v>3.33</v>
+      </c>
+      <c r="Q74">
+        <v>26.64</v>
+      </c>
+      <c r="R74">
+        <v>3.97</v>
+      </c>
+      <c r="S74">
+        <v>17</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>4</v>
+      </c>
+      <c r="V74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>98</v>
+      </c>
+      <c r="F75" t="s">
+        <v>27</v>
+      </c>
+      <c r="G75" t="s">
+        <v>118</v>
+      </c>
+      <c r="H75">
+        <v>5.67</v>
+      </c>
+      <c r="I75">
+        <v>2.08</v>
+      </c>
+      <c r="J75">
+        <v>3.58</v>
+      </c>
+      <c r="K75">
+        <v>1.84</v>
+      </c>
+      <c r="L75">
+        <v>0.25</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>3.76</v>
+      </c>
+      <c r="Q75">
+        <v>22.31</v>
+      </c>
+      <c r="R75">
+        <v>3.92</v>
+      </c>
+      <c r="S75">
+        <v>21</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>15</v>
+      </c>
+      <c r="V75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>97</v>
+      </c>
+      <c r="F76" t="s">
+        <v>101</v>
+      </c>
+      <c r="G76" t="s">
+        <v>119</v>
+      </c>
+      <c r="H76">
+        <v>4.87</v>
+      </c>
+      <c r="I76">
+        <v>1.5</v>
+      </c>
+      <c r="J76">
+        <v>3.36</v>
+      </c>
+      <c r="K76">
+        <v>1.43</v>
+      </c>
+      <c r="L76">
+        <v>0.08</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>3.79</v>
+      </c>
+      <c r="Q76">
+        <v>23.8</v>
+      </c>
+      <c r="R76">
+        <v>4.66</v>
+      </c>
+      <c r="S76">
+        <v>31</v>
+      </c>
+      <c r="T76">
+        <v>3</v>
+      </c>
+      <c r="U76">
+        <v>25</v>
+      </c>
+      <c r="V76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>87</v>
+      </c>
+      <c r="F77" t="s">
+        <v>27</v>
+      </c>
+      <c r="G77" t="s">
+        <v>120</v>
+      </c>
+      <c r="H77">
+        <v>5.95</v>
+      </c>
+      <c r="I77">
+        <v>2.11</v>
+      </c>
+      <c r="J77">
+        <v>3.83</v>
+      </c>
+      <c r="K77">
+        <v>1.56</v>
+      </c>
+      <c r="L77">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>3.95</v>
+      </c>
+      <c r="Q77">
+        <v>23.91</v>
+      </c>
+      <c r="R77">
+        <v>4.91</v>
+      </c>
+      <c r="S77">
+        <v>26</v>
+      </c>
+      <c r="T77">
+        <v>5</v>
+      </c>
+      <c r="U77">
+        <v>12</v>
+      </c>
+      <c r="V77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>89</v>
+      </c>
+      <c r="F78" t="s">
+        <v>24</v>
+      </c>
+      <c r="G78" t="s">
+        <v>121</v>
+      </c>
+      <c r="H78">
+        <v>4.32</v>
+      </c>
+      <c r="I78">
+        <v>1.01</v>
+      </c>
+      <c r="J78">
+        <v>3.3</v>
+      </c>
+      <c r="K78">
+        <v>0.92</v>
+      </c>
+      <c r="L78">
+        <v>0.1</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>2.9</v>
+      </c>
+      <c r="Q78">
+        <v>22.79</v>
+      </c>
+      <c r="R78">
+        <v>3.65</v>
+      </c>
+      <c r="S78">
+        <v>7</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>3</v>
+      </c>
+      <c r="V78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>94</v>
+      </c>
+      <c r="F79" t="s">
+        <v>103</v>
+      </c>
+      <c r="G79" t="s">
+        <v>122</v>
+      </c>
+      <c r="H79">
+        <v>5.37</v>
+      </c>
+      <c r="I79">
+        <v>1.8</v>
+      </c>
+      <c r="J79">
+        <v>3.57</v>
+      </c>
+      <c r="K79">
+        <v>1.66</v>
+      </c>
+      <c r="L79">
+        <v>0.15</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>3.67</v>
+      </c>
+      <c r="Q79">
+        <v>23.7</v>
+      </c>
+      <c r="R79">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="S79">
+        <v>14</v>
+      </c>
+      <c r="T79">
+        <v>4</v>
+      </c>
+      <c r="U79">
+        <v>6</v>
+      </c>
+      <c r="V79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>82</v>
+      </c>
+      <c r="F80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" t="s">
+        <v>123</v>
+      </c>
+      <c r="H80">
+        <v>6.1</v>
+      </c>
+      <c r="I80">
+        <v>1.57</v>
+      </c>
+      <c r="J80">
+        <v>4.51</v>
+      </c>
+      <c r="K80">
+        <v>1.38</v>
+      </c>
+      <c r="L80">
+        <v>0.19</v>
+      </c>
+      <c r="M80">
+        <v>0.01</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
+      <c r="P80">
+        <v>3.66</v>
+      </c>
+      <c r="Q80">
+        <v>28.02</v>
+      </c>
+      <c r="R80">
+        <v>5.15</v>
+      </c>
+      <c r="S80">
+        <v>35</v>
+      </c>
+      <c r="T80">
+        <v>10</v>
+      </c>
+      <c r="U80">
+        <v>26</v>
+      </c>
+      <c r="V80">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="E81" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" t="s">
+        <v>101</v>
+      </c>
+      <c r="G81" t="s">
+        <v>67</v>
+      </c>
+      <c r="H81">
+        <v>3.08</v>
+      </c>
+      <c r="I81">
+        <v>0.17</v>
+      </c>
+      <c r="J81">
+        <v>2.91</v>
+      </c>
+      <c r="K81">
+        <v>0.11</v>
+      </c>
+      <c r="L81">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>2.46</v>
+      </c>
+      <c r="Q81">
+        <v>24.9</v>
+      </c>
+      <c r="R81">
+        <v>3.75</v>
+      </c>
+      <c r="S81">
+        <v>4</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>86</v>
+      </c>
+      <c r="F82" t="s">
+        <v>27</v>
+      </c>
+      <c r="G82" t="s">
+        <v>124</v>
+      </c>
+      <c r="H82">
+        <v>3.89</v>
+      </c>
+      <c r="I82">
+        <v>0.24</v>
+      </c>
+      <c r="J82">
+        <v>3.64</v>
+      </c>
+      <c r="K82">
+        <v>0.15</v>
+      </c>
+      <c r="L82">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M82">
+        <v>0.03</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>4</v>
+      </c>
+      <c r="P82">
+        <v>3.6</v>
+      </c>
+      <c r="Q82">
+        <v>28.2</v>
+      </c>
+      <c r="R82">
+        <v>4.17</v>
+      </c>
+      <c r="S82">
+        <v>17</v>
+      </c>
+      <c r="T82">
+        <v>2</v>
+      </c>
+      <c r="U82">
+        <v>11</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="E83" t="s">
+        <v>97</v>
+      </c>
+      <c r="F83" t="s">
+        <v>101</v>
+      </c>
+      <c r="G83" t="s">
+        <v>125</v>
+      </c>
+      <c r="H83">
+        <v>3.05</v>
+      </c>
+      <c r="I83">
+        <v>0.35</v>
+      </c>
+      <c r="J83">
+        <v>2.7</v>
+      </c>
+      <c r="K83">
+        <v>0.19</v>
+      </c>
+      <c r="L83">
+        <v>0.12</v>
+      </c>
+      <c r="M83">
+        <v>0.04</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>5</v>
+      </c>
+      <c r="P83">
+        <v>3.7</v>
+      </c>
+      <c r="Q83">
+        <v>27.46</v>
+      </c>
+      <c r="R83">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="S83">
+        <v>11</v>
+      </c>
+      <c r="T83">
+        <v>4</v>
+      </c>
+      <c r="U83">
+        <v>6</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="E84" t="s">
+        <v>98</v>
+      </c>
+      <c r="F84" t="s">
+        <v>27</v>
+      </c>
+      <c r="G84" t="s">
+        <v>126</v>
+      </c>
+      <c r="H84">
+        <v>2.83</v>
+      </c>
+      <c r="I84">
+        <v>0.02</v>
+      </c>
+      <c r="J84">
+        <v>2.81</v>
+      </c>
+      <c r="K84">
+        <v>0.01</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>3.08</v>
+      </c>
+      <c r="Q84">
+        <v>20.68</v>
+      </c>
+      <c r="R84">
+        <v>3.07</v>
+      </c>
+      <c r="S84">
+        <v>1</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>1</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="E85" t="s">
+        <v>99</v>
+      </c>
+      <c r="F85" t="s">
+        <v>27</v>
+      </c>
+      <c r="G85" t="s">
+        <v>127</v>
+      </c>
+      <c r="H85">
+        <v>3.15</v>
+      </c>
+      <c r="I85">
+        <v>0.32</v>
+      </c>
+      <c r="J85">
+        <v>2.83</v>
+      </c>
+      <c r="K85">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L85">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M85">
+        <v>0.04</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>4</v>
+      </c>
+      <c r="P85">
+        <v>3.8</v>
+      </c>
+      <c r="Q85">
+        <v>27.19</v>
+      </c>
+      <c r="R85">
+        <v>3.99</v>
+      </c>
+      <c r="S85">
+        <v>7</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
+        <v>3</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="E86" t="s">
+        <v>94</v>
+      </c>
+      <c r="F86" t="s">
+        <v>103</v>
+      </c>
+      <c r="G86" t="s">
+        <v>128</v>
+      </c>
+      <c r="H86">
+        <v>2.86</v>
+      </c>
+      <c r="I86">
+        <v>0.26</v>
+      </c>
+      <c r="J86">
+        <v>2.59</v>
+      </c>
+      <c r="K86">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L86">
+        <v>0.11</v>
+      </c>
+      <c r="M86">
+        <v>0.01</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>2</v>
+      </c>
+      <c r="P86">
+        <v>3.57</v>
+      </c>
+      <c r="Q86">
+        <v>25.52</v>
+      </c>
+      <c r="R86">
+        <v>4.28</v>
+      </c>
+      <c r="S86">
+        <v>5</v>
+      </c>
+      <c r="T86">
+        <v>2</v>
+      </c>
+      <c r="U86">
+        <v>5</v>
+      </c>
+      <c r="V86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="E87" t="s">
+        <v>82</v>
+      </c>
+      <c r="F87" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" t="s">
+        <v>129</v>
+      </c>
+      <c r="H87">
+        <v>3.07</v>
+      </c>
+      <c r="I87">
+        <v>0.39</v>
+      </c>
+      <c r="J87">
+        <v>2.67</v>
+      </c>
+      <c r="K87">
+        <v>0.18</v>
+      </c>
+      <c r="L87">
+        <v>0.18</v>
+      </c>
+      <c r="M87">
+        <v>0.04</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>4</v>
+      </c>
+      <c r="P87">
+        <v>3.82</v>
+      </c>
+      <c r="Q87">
+        <v>27.72</v>
+      </c>
+      <c r="R87">
+        <v>3.68</v>
+      </c>
+      <c r="S87">
+        <v>9</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <v>8</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="E88" t="s">
+        <v>87</v>
+      </c>
+      <c r="F88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G88" t="s">
+        <v>130</v>
+      </c>
+      <c r="H88">
+        <v>5.69</v>
+      </c>
+      <c r="I88">
+        <v>0.5</v>
+      </c>
+      <c r="J88">
+        <v>5.19</v>
+      </c>
+      <c r="K88">
+        <v>0.34</v>
+      </c>
+      <c r="L88">
+        <v>0.16</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>4.62</v>
+      </c>
+      <c r="Q88">
+        <v>25.09</v>
+      </c>
+      <c r="R88">
+        <v>4.12</v>
+      </c>
+      <c r="S88">
+        <v>14</v>
+      </c>
+      <c r="T88">
+        <v>2</v>
+      </c>
+      <c r="U88">
+        <v>3</v>
+      </c>
+      <c r="V88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="E89" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" t="s">
+        <v>101</v>
+      </c>
+      <c r="G89" t="s">
+        <v>131</v>
+      </c>
+      <c r="H89">
+        <v>5.73</v>
+      </c>
+      <c r="I89">
+        <v>1.55</v>
+      </c>
+      <c r="J89">
+        <v>4.17</v>
+      </c>
+      <c r="K89">
+        <v>1.48</v>
+      </c>
+      <c r="L89">
+        <v>0.09</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>3.25</v>
+      </c>
+      <c r="Q89">
+        <v>23.21</v>
+      </c>
+      <c r="R89">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="S89">
+        <v>19</v>
+      </c>
+      <c r="T89">
+        <v>3</v>
+      </c>
+      <c r="U89">
+        <v>11</v>
+      </c>
+      <c r="V89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
+        <v>94</v>
+      </c>
+      <c r="F90" t="s">
+        <v>103</v>
+      </c>
+      <c r="G90" t="s">
+        <v>132</v>
+      </c>
+      <c r="H90">
+        <v>7.02</v>
+      </c>
+      <c r="I90">
+        <v>2.21</v>
+      </c>
+      <c r="J90">
+        <v>4.8</v>
+      </c>
+      <c r="K90">
+        <v>1.27</v>
+      </c>
+      <c r="L90">
+        <v>0.93</v>
+      </c>
+      <c r="M90">
+        <v>0.02</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>2</v>
+      </c>
+      <c r="P90">
+        <v>4.38</v>
+      </c>
+      <c r="Q90">
+        <v>27.35</v>
+      </c>
+      <c r="R90">
+        <v>4.71</v>
+      </c>
+      <c r="S90">
+        <v>46</v>
+      </c>
+      <c r="T90">
+        <v>10</v>
+      </c>
+      <c r="U90">
+        <v>33</v>
+      </c>
+      <c r="V90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
+        <v>86</v>
+      </c>
+      <c r="F91" t="s">
+        <v>27</v>
+      </c>
+      <c r="G91" t="s">
+        <v>133</v>
+      </c>
+      <c r="H91">
+        <v>6.92</v>
+      </c>
+      <c r="I91">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J91">
+        <v>4.71</v>
+      </c>
+      <c r="K91">
+        <v>1.3</v>
+      </c>
+      <c r="L91">
+        <v>0.91</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>4.01</v>
+      </c>
+      <c r="Q91">
+        <v>24.24</v>
+      </c>
+      <c r="R91">
+        <v>4.88</v>
+      </c>
+      <c r="S91">
+        <v>38</v>
+      </c>
+      <c r="T91">
+        <v>10</v>
+      </c>
+      <c r="U91">
+        <v>26</v>
+      </c>
+      <c r="V91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="E92" t="s">
+        <v>87</v>
+      </c>
+      <c r="F92" t="s">
+        <v>27</v>
+      </c>
+      <c r="G92" t="s">
+        <v>134</v>
+      </c>
+      <c r="H92">
+        <v>7.35</v>
+      </c>
+      <c r="I92">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="J92">
+        <v>4.91</v>
+      </c>
+      <c r="K92">
+        <v>1.18</v>
+      </c>
+      <c r="L92">
+        <v>1.19</v>
+      </c>
+      <c r="M92">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>2</v>
+      </c>
+      <c r="P92">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="Q92">
+        <v>27.79</v>
+      </c>
+      <c r="R92">
+        <v>4.93</v>
+      </c>
+      <c r="S92">
+        <v>36</v>
+      </c>
+      <c r="T92">
+        <v>8</v>
+      </c>
+      <c r="U92">
+        <v>21</v>
+      </c>
+      <c r="V92">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" t="s">
+        <v>27</v>
+      </c>
+      <c r="G93" t="s">
+        <v>135</v>
+      </c>
+      <c r="H93">
+        <v>7.23</v>
+      </c>
+      <c r="I93">
+        <v>2.23</v>
+      </c>
+      <c r="J93">
+        <v>4.99</v>
+      </c>
+      <c r="K93">
+        <v>1.03</v>
+      </c>
+      <c r="L93">
+        <v>1.21</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>4.67</v>
+      </c>
+      <c r="Q93">
+        <v>24.6</v>
+      </c>
+      <c r="R93">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S93">
+        <v>37</v>
+      </c>
+      <c r="T93">
+        <v>6</v>
+      </c>
+      <c r="U93">
+        <v>22</v>
+      </c>
+      <c r="V93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" t="s">
+        <v>101</v>
+      </c>
+      <c r="G94" t="s">
+        <v>136</v>
+      </c>
+      <c r="H94">
+        <v>6.9</v>
+      </c>
+      <c r="I94">
+        <v>2.38</v>
+      </c>
+      <c r="J94">
+        <v>4.5</v>
+      </c>
+      <c r="K94">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="L94">
+        <v>1.29</v>
+      </c>
+      <c r="M94">
+        <v>0.02</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>9</v>
+      </c>
+      <c r="P94">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q94">
+        <v>25.75</v>
+      </c>
+      <c r="R94">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S94">
+        <v>41</v>
+      </c>
+      <c r="T94">
+        <v>11</v>
+      </c>
+      <c r="U94">
+        <v>21</v>
+      </c>
+      <c r="V94">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>89</v>
+      </c>
+      <c r="F95" t="s">
+        <v>24</v>
+      </c>
+      <c r="G95" t="s">
+        <v>134</v>
+      </c>
+      <c r="H95">
+        <v>6.68</v>
+      </c>
+      <c r="I95">
+        <v>1.64</v>
+      </c>
+      <c r="J95">
+        <v>5.03</v>
+      </c>
+      <c r="K95">
+        <v>1.52</v>
+      </c>
+      <c r="L95">
+        <v>0.13</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="Q95">
+        <v>23.61</v>
+      </c>
+      <c r="R95">
+        <v>3.88</v>
+      </c>
+      <c r="S95">
+        <v>18</v>
+      </c>
+      <c r="T95">
+        <v>0</v>
+      </c>
+      <c r="U95">
+        <v>11</v>
+      </c>
+      <c r="V95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>99</v>
+      </c>
+      <c r="F96" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" t="s">
+        <v>137</v>
+      </c>
+      <c r="H96">
+        <v>7.18</v>
+      </c>
+      <c r="I96">
+        <v>2.04</v>
+      </c>
+      <c r="J96">
+        <v>5.13</v>
+      </c>
+      <c r="K96">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L96">
+        <v>0.86</v>
+      </c>
+      <c r="M96">
+        <v>0.03</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>4.46</v>
+      </c>
+      <c r="Q96">
+        <v>27.7</v>
+      </c>
+      <c r="R96">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="S96">
+        <v>32</v>
+      </c>
+      <c r="T96">
+        <v>13</v>
+      </c>
+      <c r="U96">
+        <v>14</v>
+      </c>
+      <c r="V96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>82</v>
+      </c>
+      <c r="F97" t="s">
+        <v>27</v>
+      </c>
+      <c r="G97" t="s">
+        <v>138</v>
+      </c>
+      <c r="H97">
+        <v>7.52</v>
+      </c>
+      <c r="I97">
+        <v>2.19</v>
+      </c>
+      <c r="J97">
+        <v>5.31</v>
+      </c>
+      <c r="K97">
+        <v>1.17</v>
+      </c>
+      <c r="L97">
+        <v>1.02</v>
+      </c>
+      <c r="M97">
+        <v>0.02</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>2</v>
+      </c>
+      <c r="P97">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q97">
+        <v>27.63</v>
+      </c>
+      <c r="R97">
+        <v>4.5</v>
+      </c>
+      <c r="S97">
+        <v>59</v>
+      </c>
+      <c r="T97">
+        <v>14</v>
+      </c>
+      <c r="U97">
+        <v>35</v>
+      </c>
+      <c r="V97">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1A00C4-BBC8-F64A-BA18-6FE43671375E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814F8C22-F718-C24D-8927-2AC1202E6B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="174">
   <si>
     <t>Temps joué</t>
   </si>
@@ -452,6 +452,111 @@
   </si>
   <si>
     <t>01:28:00</t>
+  </si>
+  <si>
+    <t>00:49:58</t>
+  </si>
+  <si>
+    <t>01:14:19</t>
+  </si>
+  <si>
+    <t>00:50:18</t>
+  </si>
+  <si>
+    <t>00:50:25</t>
+  </si>
+  <si>
+    <t>00:49:23</t>
+  </si>
+  <si>
+    <t>01:01:24</t>
+  </si>
+  <si>
+    <t>00:58:53</t>
+  </si>
+  <si>
+    <t>00:48:26</t>
+  </si>
+  <si>
+    <t>00:49:50</t>
+  </si>
+  <si>
+    <t>01:10:16</t>
+  </si>
+  <si>
+    <t>00:54:05</t>
+  </si>
+  <si>
+    <t>01:06:42</t>
+  </si>
+  <si>
+    <t>01:10:23</t>
+  </si>
+  <si>
+    <t>01:08:18</t>
+  </si>
+  <si>
+    <t>00:47:43</t>
+  </si>
+  <si>
+    <t>00:47:21</t>
+  </si>
+  <si>
+    <t>00:47:29</t>
+  </si>
+  <si>
+    <t>00:47:36</t>
+  </si>
+  <si>
+    <t>Cedrick Koffi</t>
+  </si>
+  <si>
+    <t>00:46:58</t>
+  </si>
+  <si>
+    <t>00:46:37</t>
+  </si>
+  <si>
+    <t>00:49:20</t>
+  </si>
+  <si>
+    <t>00:47:28</t>
+  </si>
+  <si>
+    <t>00:47:06</t>
+  </si>
+  <si>
+    <t>Samy Achour</t>
+  </si>
+  <si>
+    <t>00:46:51</t>
+  </si>
+  <si>
+    <t>00:46:44</t>
+  </si>
+  <si>
+    <t>Emmanuel Valey</t>
+  </si>
+  <si>
+    <t>00:47:07</t>
+  </si>
+  <si>
+    <t>00:22:53</t>
+  </si>
+  <si>
+    <t>00:46:08</t>
+  </si>
+  <si>
+    <t>Heikel Machfar</t>
+  </si>
+  <si>
+    <t>00:26:36</t>
+  </si>
+  <si>
+    <t>00:45:44</t>
+  </si>
+  <si>
+    <t>Match Amical VS Villefranche</t>
   </si>
 </sst>
 </file>
@@ -527,9 +632,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -567,7 +672,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -673,7 +778,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -815,7 +920,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -823,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V97"/>
+  <dimension ref="A1:V133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -7140,6 +7245,2346 @@
         <v>22</v>
       </c>
     </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="E98" t="s">
+        <v>98</v>
+      </c>
+      <c r="F98" t="s">
+        <v>27</v>
+      </c>
+      <c r="G98" t="s">
+        <v>139</v>
+      </c>
+      <c r="H98">
+        <v>3.79</v>
+      </c>
+      <c r="I98">
+        <v>0.3</v>
+      </c>
+      <c r="J98">
+        <v>3.49</v>
+      </c>
+      <c r="K98">
+        <v>0.25</v>
+      </c>
+      <c r="L98">
+        <v>0.05</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>4.47</v>
+      </c>
+      <c r="Q98">
+        <v>23.5</v>
+      </c>
+      <c r="R98">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="S98">
+        <v>13</v>
+      </c>
+      <c r="T98">
+        <v>3</v>
+      </c>
+      <c r="U98">
+        <v>5</v>
+      </c>
+      <c r="V98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="E99" t="s">
+        <v>91</v>
+      </c>
+      <c r="F99" t="s">
+        <v>101</v>
+      </c>
+      <c r="G99" t="s">
+        <v>140</v>
+      </c>
+      <c r="H99">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="I99">
+        <v>0.51</v>
+      </c>
+      <c r="J99">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="K99">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L99">
+        <v>0.15</v>
+      </c>
+      <c r="M99">
+        <v>0.08</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>6</v>
+      </c>
+      <c r="P99">
+        <v>3.91</v>
+      </c>
+      <c r="Q99">
+        <v>29.66</v>
+      </c>
+      <c r="R99">
+        <v>4.01</v>
+      </c>
+      <c r="S99">
+        <v>15</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+      <c r="U99">
+        <v>6</v>
+      </c>
+      <c r="V99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+      <c r="E100" t="s">
+        <v>82</v>
+      </c>
+      <c r="F100" t="s">
+        <v>27</v>
+      </c>
+      <c r="G100" t="s">
+        <v>141</v>
+      </c>
+      <c r="H100">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="I100">
+        <v>0.32</v>
+      </c>
+      <c r="J100">
+        <v>3.81</v>
+      </c>
+      <c r="K100">
+        <v>0.2</v>
+      </c>
+      <c r="L100">
+        <v>0.08</v>
+      </c>
+      <c r="M100">
+        <v>0.05</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>2</v>
+      </c>
+      <c r="P100">
+        <v>4.25</v>
+      </c>
+      <c r="Q100">
+        <v>28.72</v>
+      </c>
+      <c r="R100">
+        <v>5.04</v>
+      </c>
+      <c r="S100">
+        <v>19</v>
+      </c>
+      <c r="T100">
+        <v>5</v>
+      </c>
+      <c r="U100">
+        <v>14</v>
+      </c>
+      <c r="V100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="E101" t="s">
+        <v>89</v>
+      </c>
+      <c r="F101" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" t="s">
+        <v>140</v>
+      </c>
+      <c r="H101">
+        <v>5.52</v>
+      </c>
+      <c r="I101">
+        <v>0.51</v>
+      </c>
+      <c r="J101">
+        <v>5.01</v>
+      </c>
+      <c r="K101">
+        <v>0.32</v>
+      </c>
+      <c r="L101">
+        <v>0.13</v>
+      </c>
+      <c r="M101">
+        <v>0.06</v>
+      </c>
+      <c r="N101">
+        <v>0.01</v>
+      </c>
+      <c r="O101">
+        <v>3</v>
+      </c>
+      <c r="P101">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q101">
+        <v>31.12</v>
+      </c>
+      <c r="R101">
+        <v>3.93</v>
+      </c>
+      <c r="S101">
+        <v>7</v>
+      </c>
+      <c r="T101">
+        <v>0</v>
+      </c>
+      <c r="U101">
+        <v>6</v>
+      </c>
+      <c r="V101">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="E102" t="s">
+        <v>86</v>
+      </c>
+      <c r="F102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G102" t="s">
+        <v>119</v>
+      </c>
+      <c r="H102">
+        <v>6.53</v>
+      </c>
+      <c r="I102">
+        <v>0.89</v>
+      </c>
+      <c r="J102">
+        <v>5.63</v>
+      </c>
+      <c r="K102">
+        <v>0.69</v>
+      </c>
+      <c r="L102">
+        <v>0.18</v>
+      </c>
+      <c r="M102">
+        <v>0.03</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>3</v>
+      </c>
+      <c r="P102">
+        <v>5.17</v>
+      </c>
+      <c r="Q102">
+        <v>26.34</v>
+      </c>
+      <c r="R102">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="S102">
+        <v>25</v>
+      </c>
+      <c r="T102">
+        <v>4</v>
+      </c>
+      <c r="U102">
+        <v>23</v>
+      </c>
+      <c r="V102">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="E103" t="s">
+        <v>87</v>
+      </c>
+      <c r="F103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G103" t="s">
+        <v>142</v>
+      </c>
+      <c r="H103">
+        <v>4.37</v>
+      </c>
+      <c r="I103">
+        <v>0.53</v>
+      </c>
+      <c r="J103">
+        <v>3.84</v>
+      </c>
+      <c r="K103">
+        <v>0.3</v>
+      </c>
+      <c r="L103">
+        <v>0.19</v>
+      </c>
+      <c r="M103">
+        <v>0.05</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>4</v>
+      </c>
+      <c r="P103">
+        <v>5.12</v>
+      </c>
+      <c r="Q103">
+        <v>29.73</v>
+      </c>
+      <c r="R103">
+        <v>4.34</v>
+      </c>
+      <c r="S103">
+        <v>16</v>
+      </c>
+      <c r="T103">
+        <v>4</v>
+      </c>
+      <c r="U103">
+        <v>7</v>
+      </c>
+      <c r="V103">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="E104" t="s">
+        <v>99</v>
+      </c>
+      <c r="F104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G104" t="s">
+        <v>143</v>
+      </c>
+      <c r="H104">
+        <v>3.56</v>
+      </c>
+      <c r="I104">
+        <v>0.24</v>
+      </c>
+      <c r="J104">
+        <v>3.31</v>
+      </c>
+      <c r="K104">
+        <v>0.16</v>
+      </c>
+      <c r="L104">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M104">
+        <v>0.03</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>1</v>
+      </c>
+      <c r="P104">
+        <v>4.18</v>
+      </c>
+      <c r="Q104">
+        <v>28.03</v>
+      </c>
+      <c r="R104">
+        <v>4.75</v>
+      </c>
+      <c r="S104">
+        <v>8</v>
+      </c>
+      <c r="T104">
+        <v>2</v>
+      </c>
+      <c r="U104">
+        <v>5</v>
+      </c>
+      <c r="V104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="E105" t="s">
+        <v>97</v>
+      </c>
+      <c r="F105" t="s">
+        <v>101</v>
+      </c>
+      <c r="G105" t="s">
+        <v>144</v>
+      </c>
+      <c r="H105">
+        <v>4.62</v>
+      </c>
+      <c r="I105">
+        <v>0.5</v>
+      </c>
+      <c r="J105">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K105">
+        <v>0.32</v>
+      </c>
+      <c r="L105">
+        <v>0.12</v>
+      </c>
+      <c r="M105">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>4</v>
+      </c>
+      <c r="P105">
+        <v>4.45</v>
+      </c>
+      <c r="Q105">
+        <v>29.47</v>
+      </c>
+      <c r="R105">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S105">
+        <v>23</v>
+      </c>
+      <c r="T105">
+        <v>7</v>
+      </c>
+      <c r="U105">
+        <v>20</v>
+      </c>
+      <c r="V105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="E106" t="s">
+        <v>94</v>
+      </c>
+      <c r="F106" t="s">
+        <v>103</v>
+      </c>
+      <c r="G106" t="s">
+        <v>145</v>
+      </c>
+      <c r="H106">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="I106">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J106">
+        <v>3.89</v>
+      </c>
+      <c r="K106">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L106">
+        <v>0.13</v>
+      </c>
+      <c r="M106">
+        <v>0.13</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>7</v>
+      </c>
+      <c r="P106">
+        <v>4.47</v>
+      </c>
+      <c r="Q106">
+        <v>29.83</v>
+      </c>
+      <c r="R106">
+        <v>4.04</v>
+      </c>
+      <c r="S106">
+        <v>18</v>
+      </c>
+      <c r="T106">
+        <v>1</v>
+      </c>
+      <c r="U106">
+        <v>6</v>
+      </c>
+      <c r="V106">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C107" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" t="s">
+        <v>99</v>
+      </c>
+      <c r="F107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G107" t="s">
+        <v>146</v>
+      </c>
+      <c r="H107">
+        <v>2.57</v>
+      </c>
+      <c r="I107">
+        <v>0.24</v>
+      </c>
+      <c r="J107">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="K107">
+        <v>0.23</v>
+      </c>
+      <c r="L107">
+        <v>0.01</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>3.11</v>
+      </c>
+      <c r="Q107">
+        <v>21.03</v>
+      </c>
+      <c r="R107">
+        <v>5.32</v>
+      </c>
+      <c r="S107">
+        <v>10</v>
+      </c>
+      <c r="T107">
+        <v>10</v>
+      </c>
+      <c r="U107">
+        <v>7</v>
+      </c>
+      <c r="V107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="s">
+        <v>91</v>
+      </c>
+      <c r="F108" t="s">
+        <v>101</v>
+      </c>
+      <c r="G108" t="s">
+        <v>147</v>
+      </c>
+      <c r="H108">
+        <v>2.25</v>
+      </c>
+      <c r="I108">
+        <v>0.11</v>
+      </c>
+      <c r="J108">
+        <v>2.14</v>
+      </c>
+      <c r="K108">
+        <v>0.09</v>
+      </c>
+      <c r="L108">
+        <v>0.02</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>2.57</v>
+      </c>
+      <c r="Q108">
+        <v>23.78</v>
+      </c>
+      <c r="R108">
+        <v>5.29</v>
+      </c>
+      <c r="S108">
+        <v>7</v>
+      </c>
+      <c r="T108">
+        <v>5</v>
+      </c>
+      <c r="U108">
+        <v>3</v>
+      </c>
+      <c r="V108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C109" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" t="s">
+        <v>86</v>
+      </c>
+      <c r="F109" t="s">
+        <v>27</v>
+      </c>
+      <c r="G109" t="s">
+        <v>148</v>
+      </c>
+      <c r="H109">
+        <v>4.18</v>
+      </c>
+      <c r="I109">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J109">
+        <v>3.57</v>
+      </c>
+      <c r="K109">
+        <v>0.44</v>
+      </c>
+      <c r="L109">
+        <v>0.13</v>
+      </c>
+      <c r="M109">
+        <v>0.04</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>7</v>
+      </c>
+      <c r="P109">
+        <v>3.23</v>
+      </c>
+      <c r="Q109">
+        <v>30.11</v>
+      </c>
+      <c r="R109">
+        <v>5.82</v>
+      </c>
+      <c r="S109">
+        <v>70</v>
+      </c>
+      <c r="T109">
+        <v>28</v>
+      </c>
+      <c r="U109">
+        <v>69</v>
+      </c>
+      <c r="V109">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C110" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
+        <v>97</v>
+      </c>
+      <c r="F110" t="s">
+        <v>101</v>
+      </c>
+      <c r="G110" t="s">
+        <v>149</v>
+      </c>
+      <c r="H110">
+        <v>2.83</v>
+      </c>
+      <c r="I110">
+        <v>0.21</v>
+      </c>
+      <c r="J110">
+        <v>2.62</v>
+      </c>
+      <c r="K110">
+        <v>0.17</v>
+      </c>
+      <c r="L110">
+        <v>0.04</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>3.06</v>
+      </c>
+      <c r="Q110">
+        <v>23.37</v>
+      </c>
+      <c r="R110">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S110">
+        <v>15</v>
+      </c>
+      <c r="T110">
+        <v>2</v>
+      </c>
+      <c r="U110">
+        <v>7</v>
+      </c>
+      <c r="V110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" t="s">
+        <v>98</v>
+      </c>
+      <c r="F111" t="s">
+        <v>27</v>
+      </c>
+      <c r="G111" t="s">
+        <v>150</v>
+      </c>
+      <c r="H111">
+        <v>3.24</v>
+      </c>
+      <c r="I111">
+        <v>0.27</v>
+      </c>
+      <c r="J111">
+        <v>2.97</v>
+      </c>
+      <c r="K111">
+        <v>0.24</v>
+      </c>
+      <c r="L111">
+        <v>0.04</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>2.8</v>
+      </c>
+      <c r="Q111">
+        <v>23.59</v>
+      </c>
+      <c r="R111">
+        <v>4.51</v>
+      </c>
+      <c r="S111">
+        <v>19</v>
+      </c>
+      <c r="T111">
+        <v>3</v>
+      </c>
+      <c r="U111">
+        <v>10</v>
+      </c>
+      <c r="V111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" t="s">
+        <v>87</v>
+      </c>
+      <c r="F112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G112" t="s">
+        <v>151</v>
+      </c>
+      <c r="H112">
+        <v>3.82</v>
+      </c>
+      <c r="I112">
+        <v>0.41</v>
+      </c>
+      <c r="J112">
+        <v>3.41</v>
+      </c>
+      <c r="K112">
+        <v>0.35</v>
+      </c>
+      <c r="L112">
+        <v>0.06</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>1</v>
+      </c>
+      <c r="P112">
+        <v>3.17</v>
+      </c>
+      <c r="Q112">
+        <v>25.43</v>
+      </c>
+      <c r="R112">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S112">
+        <v>17</v>
+      </c>
+      <c r="T112">
+        <v>5</v>
+      </c>
+      <c r="U112">
+        <v>16</v>
+      </c>
+      <c r="V112">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C113" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" t="s">
+        <v>94</v>
+      </c>
+      <c r="F113" t="s">
+        <v>103</v>
+      </c>
+      <c r="G113" t="s">
+        <v>152</v>
+      </c>
+      <c r="H113">
+        <v>3.48</v>
+      </c>
+      <c r="I113">
+        <v>0.47</v>
+      </c>
+      <c r="J113">
+        <v>3</v>
+      </c>
+      <c r="K113">
+        <v>0.36</v>
+      </c>
+      <c r="L113">
+        <v>0.12</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>2.88</v>
+      </c>
+      <c r="Q113">
+        <v>24.18</v>
+      </c>
+      <c r="R113">
+        <v>5.31</v>
+      </c>
+      <c r="S113">
+        <v>17</v>
+      </c>
+      <c r="T113">
+        <v>10</v>
+      </c>
+      <c r="U113">
+        <v>12</v>
+      </c>
+      <c r="V113">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>173</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C114" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" t="s">
+        <v>31</v>
+      </c>
+      <c r="F114" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" t="s">
+        <v>153</v>
+      </c>
+      <c r="H114">
+        <v>5.36</v>
+      </c>
+      <c r="I114">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J114">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="K114">
+        <v>0.73</v>
+      </c>
+      <c r="L114">
+        <v>0.3</v>
+      </c>
+      <c r="M114">
+        <v>0.09</v>
+      </c>
+      <c r="N114">
+        <v>0.01</v>
+      </c>
+      <c r="O114">
+        <v>8</v>
+      </c>
+      <c r="P114">
+        <v>6.65</v>
+      </c>
+      <c r="Q114">
+        <v>30.6</v>
+      </c>
+      <c r="R114">
+        <v>5.41</v>
+      </c>
+      <c r="S114">
+        <v>26</v>
+      </c>
+      <c r="T114">
+        <v>6</v>
+      </c>
+      <c r="U114">
+        <v>18</v>
+      </c>
+      <c r="V114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>173</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C115" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" t="s">
+        <v>154</v>
+      </c>
+      <c r="H115">
+        <v>5.81</v>
+      </c>
+      <c r="I115">
+        <v>1.29</v>
+      </c>
+      <c r="J115">
+        <v>4.5</v>
+      </c>
+      <c r="K115">
+        <v>0.8</v>
+      </c>
+      <c r="L115">
+        <v>0.44</v>
+      </c>
+      <c r="M115">
+        <v>0.06</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>7</v>
+      </c>
+      <c r="P115">
+        <v>7.37</v>
+      </c>
+      <c r="Q115">
+        <v>27.66</v>
+      </c>
+      <c r="R115">
+        <v>5.05</v>
+      </c>
+      <c r="S115">
+        <v>33</v>
+      </c>
+      <c r="T115">
+        <v>9</v>
+      </c>
+      <c r="U115">
+        <v>22</v>
+      </c>
+      <c r="V115">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>173</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C116" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" t="s">
+        <v>25</v>
+      </c>
+      <c r="G116" t="s">
+        <v>153</v>
+      </c>
+      <c r="H116">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="I116">
+        <v>0.75</v>
+      </c>
+      <c r="J116">
+        <v>4.01</v>
+      </c>
+      <c r="K116">
+        <v>0.48</v>
+      </c>
+      <c r="L116">
+        <v>0.21</v>
+      </c>
+      <c r="M116">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>4</v>
+      </c>
+      <c r="P116">
+        <v>5.98</v>
+      </c>
+      <c r="Q116">
+        <v>29.32</v>
+      </c>
+      <c r="R116">
+        <v>4.58</v>
+      </c>
+      <c r="S116">
+        <v>21</v>
+      </c>
+      <c r="T116">
+        <v>5</v>
+      </c>
+      <c r="U116">
+        <v>21</v>
+      </c>
+      <c r="V116">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>173</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C117" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" t="s">
+        <v>94</v>
+      </c>
+      <c r="F117" t="s">
+        <v>103</v>
+      </c>
+      <c r="G117" t="s">
+        <v>155</v>
+      </c>
+      <c r="H117">
+        <v>5.36</v>
+      </c>
+      <c r="I117">
+        <v>0.92</v>
+      </c>
+      <c r="J117">
+        <v>4.43</v>
+      </c>
+      <c r="K117">
+        <v>0.61</v>
+      </c>
+      <c r="L117">
+        <v>0.25</v>
+      </c>
+      <c r="M117">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>5</v>
+      </c>
+      <c r="P117">
+        <v>6.76</v>
+      </c>
+      <c r="Q117">
+        <v>29.64</v>
+      </c>
+      <c r="R117">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="S117">
+        <v>15</v>
+      </c>
+      <c r="T117">
+        <v>5</v>
+      </c>
+      <c r="U117">
+        <v>17</v>
+      </c>
+      <c r="V117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>173</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C118" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" t="s">
+        <v>91</v>
+      </c>
+      <c r="F118" t="s">
+        <v>101</v>
+      </c>
+      <c r="G118" t="s">
+        <v>156</v>
+      </c>
+      <c r="H118">
+        <v>4.97</v>
+      </c>
+      <c r="I118">
+        <v>0.89</v>
+      </c>
+      <c r="J118">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="K118">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L118">
+        <v>0.25</v>
+      </c>
+      <c r="M118">
+        <v>0.08</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>10</v>
+      </c>
+      <c r="P118">
+        <v>6.25</v>
+      </c>
+      <c r="Q118">
+        <v>29.74</v>
+      </c>
+      <c r="R118">
+        <v>4.95</v>
+      </c>
+      <c r="S118">
+        <v>30</v>
+      </c>
+      <c r="T118">
+        <v>6</v>
+      </c>
+      <c r="U118">
+        <v>28</v>
+      </c>
+      <c r="V118">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>173</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C119" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F119" t="s">
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>158</v>
+      </c>
+      <c r="H119">
+        <v>4.51</v>
+      </c>
+      <c r="I119">
+        <v>0.53</v>
+      </c>
+      <c r="J119">
+        <v>3.97</v>
+      </c>
+      <c r="K119">
+        <v>0.35</v>
+      </c>
+      <c r="L119">
+        <v>0.16</v>
+      </c>
+      <c r="M119">
+        <v>0.04</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>4</v>
+      </c>
+      <c r="P119">
+        <v>5.73</v>
+      </c>
+      <c r="Q119">
+        <v>27.13</v>
+      </c>
+      <c r="R119">
+        <v>5.25</v>
+      </c>
+      <c r="S119">
+        <v>19</v>
+      </c>
+      <c r="T119">
+        <v>9</v>
+      </c>
+      <c r="U119">
+        <v>15</v>
+      </c>
+      <c r="V119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>173</v>
+      </c>
+      <c r="B120" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C120" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" t="s">
+        <v>99</v>
+      </c>
+      <c r="F120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G120" t="s">
+        <v>159</v>
+      </c>
+      <c r="H120">
+        <v>6.01</v>
+      </c>
+      <c r="I120">
+        <v>0.99</v>
+      </c>
+      <c r="J120">
+        <v>5.01</v>
+      </c>
+      <c r="K120">
+        <v>0.75</v>
+      </c>
+      <c r="L120">
+        <v>0.23</v>
+      </c>
+      <c r="M120">
+        <v>0.02</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>2</v>
+      </c>
+      <c r="P120">
+        <v>7.73</v>
+      </c>
+      <c r="Q120">
+        <v>27.19</v>
+      </c>
+      <c r="R120">
+        <v>5.18</v>
+      </c>
+      <c r="S120">
+        <v>13</v>
+      </c>
+      <c r="T120">
+        <v>4</v>
+      </c>
+      <c r="U120">
+        <v>13</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>173</v>
+      </c>
+      <c r="B121" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C121" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" t="s">
+        <v>98</v>
+      </c>
+      <c r="F121" t="s">
+        <v>27</v>
+      </c>
+      <c r="G121" t="s">
+        <v>160</v>
+      </c>
+      <c r="H121">
+        <v>6.08</v>
+      </c>
+      <c r="I121">
+        <v>1.04</v>
+      </c>
+      <c r="J121">
+        <v>5.03</v>
+      </c>
+      <c r="K121">
+        <v>0.77</v>
+      </c>
+      <c r="L121">
+        <v>0.21</v>
+      </c>
+      <c r="M121">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>3</v>
+      </c>
+      <c r="P121">
+        <v>7.32</v>
+      </c>
+      <c r="Q121">
+        <v>29.75</v>
+      </c>
+      <c r="R121">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S121">
+        <v>23</v>
+      </c>
+      <c r="T121">
+        <v>2</v>
+      </c>
+      <c r="U121">
+        <v>31</v>
+      </c>
+      <c r="V121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>173</v>
+      </c>
+      <c r="B122" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" t="s">
+        <v>87</v>
+      </c>
+      <c r="F122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G122" t="s">
+        <v>161</v>
+      </c>
+      <c r="H122">
+        <v>6.15</v>
+      </c>
+      <c r="I122">
+        <v>1.38</v>
+      </c>
+      <c r="J122">
+        <v>4.76</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>0.33</v>
+      </c>
+      <c r="M122">
+        <v>0.06</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>5</v>
+      </c>
+      <c r="P122">
+        <v>7.8</v>
+      </c>
+      <c r="Q122">
+        <v>27.4</v>
+      </c>
+      <c r="R122">
+        <v>4.58</v>
+      </c>
+      <c r="S122">
+        <v>18</v>
+      </c>
+      <c r="T122">
+        <v>1</v>
+      </c>
+      <c r="U122">
+        <v>16</v>
+      </c>
+      <c r="V122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>173</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C123" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" t="s">
+        <v>35</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G123" t="s">
+        <v>162</v>
+      </c>
+      <c r="H123">
+        <v>4.74</v>
+      </c>
+      <c r="I123">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J123">
+        <v>4.18</v>
+      </c>
+      <c r="K123">
+        <v>0.42</v>
+      </c>
+      <c r="L123">
+        <v>0.12</v>
+      </c>
+      <c r="M123">
+        <v>0.02</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>2</v>
+      </c>
+      <c r="P123">
+        <v>6.11</v>
+      </c>
+      <c r="Q123">
+        <v>26.3</v>
+      </c>
+      <c r="R123">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S123">
+        <v>15</v>
+      </c>
+      <c r="T123">
+        <v>2</v>
+      </c>
+      <c r="U123">
+        <v>9</v>
+      </c>
+      <c r="V123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>173</v>
+      </c>
+      <c r="B124" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C124" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G124" t="s">
+        <v>164</v>
+      </c>
+      <c r="H124">
+        <v>5.21</v>
+      </c>
+      <c r="I124">
+        <v>0.85</v>
+      </c>
+      <c r="J124">
+        <v>4.34</v>
+      </c>
+      <c r="K124">
+        <v>0.46</v>
+      </c>
+      <c r="L124">
+        <v>0.26</v>
+      </c>
+      <c r="M124">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N124">
+        <v>0.01</v>
+      </c>
+      <c r="O124">
+        <v>13</v>
+      </c>
+      <c r="P124">
+        <v>6.67</v>
+      </c>
+      <c r="Q124">
+        <v>31.71</v>
+      </c>
+      <c r="R124">
+        <v>4.91</v>
+      </c>
+      <c r="S124">
+        <v>40</v>
+      </c>
+      <c r="T124">
+        <v>5</v>
+      </c>
+      <c r="U124">
+        <v>23</v>
+      </c>
+      <c r="V124">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>173</v>
+      </c>
+      <c r="B125" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C125" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" t="s">
+        <v>82</v>
+      </c>
+      <c r="F125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G125" t="s">
+        <v>165</v>
+      </c>
+      <c r="H125">
+        <v>5.57</v>
+      </c>
+      <c r="I125">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J125">
+        <v>4.43</v>
+      </c>
+      <c r="K125">
+        <v>0.74</v>
+      </c>
+      <c r="L125">
+        <v>0.31</v>
+      </c>
+      <c r="M125">
+        <v>0.09</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>5</v>
+      </c>
+      <c r="P125">
+        <v>7.14</v>
+      </c>
+      <c r="Q125">
+        <v>30.29</v>
+      </c>
+      <c r="R125">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="S125">
+        <v>22</v>
+      </c>
+      <c r="T125">
+        <v>4</v>
+      </c>
+      <c r="U125">
+        <v>17</v>
+      </c>
+      <c r="V125">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>173</v>
+      </c>
+      <c r="B126" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" t="s">
+        <v>43</v>
+      </c>
+      <c r="F126" t="s">
+        <v>24</v>
+      </c>
+      <c r="G126" t="s">
+        <v>156</v>
+      </c>
+      <c r="H126">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I126">
+        <v>0.68</v>
+      </c>
+      <c r="J126">
+        <v>4.2</v>
+      </c>
+      <c r="K126">
+        <v>0.54</v>
+      </c>
+      <c r="L126">
+        <v>0.13</v>
+      </c>
+      <c r="M126">
+        <v>0.03</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>3</v>
+      </c>
+      <c r="P126">
+        <v>6.14</v>
+      </c>
+      <c r="Q126">
+        <v>27.93</v>
+      </c>
+      <c r="R126">
+        <v>4.49</v>
+      </c>
+      <c r="S126">
+        <v>25</v>
+      </c>
+      <c r="T126">
+        <v>2</v>
+      </c>
+      <c r="U126">
+        <v>24</v>
+      </c>
+      <c r="V126">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>173</v>
+      </c>
+      <c r="B127" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" t="s">
+        <v>166</v>
+      </c>
+      <c r="F127" t="s">
+        <v>101</v>
+      </c>
+      <c r="G127" t="s">
+        <v>167</v>
+      </c>
+      <c r="H127">
+        <v>5.17</v>
+      </c>
+      <c r="I127">
+        <v>0.96</v>
+      </c>
+      <c r="J127">
+        <v>4.2</v>
+      </c>
+      <c r="K127">
+        <v>0.53</v>
+      </c>
+      <c r="L127">
+        <v>0.31</v>
+      </c>
+      <c r="M127">
+        <v>0.09</v>
+      </c>
+      <c r="N127">
+        <v>0.03</v>
+      </c>
+      <c r="O127">
+        <v>7</v>
+      </c>
+      <c r="P127">
+        <v>6.58</v>
+      </c>
+      <c r="Q127">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="R127">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="S127">
+        <v>12</v>
+      </c>
+      <c r="T127">
+        <v>5</v>
+      </c>
+      <c r="U127">
+        <v>11</v>
+      </c>
+      <c r="V127">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>173</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C128" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" t="s">
+        <v>36</v>
+      </c>
+      <c r="F128" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" t="s">
+        <v>168</v>
+      </c>
+      <c r="H128">
+        <v>2.84</v>
+      </c>
+      <c r="I128">
+        <v>0.59</v>
+      </c>
+      <c r="J128">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="K128">
+        <v>0.42</v>
+      </c>
+      <c r="L128">
+        <v>0.17</v>
+      </c>
+      <c r="M128">
+        <v>0.01</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>1</v>
+      </c>
+      <c r="P128">
+        <v>7.44</v>
+      </c>
+      <c r="Q128">
+        <v>27.51</v>
+      </c>
+      <c r="R128">
+        <v>4.46</v>
+      </c>
+      <c r="S128">
+        <v>13</v>
+      </c>
+      <c r="T128">
+        <v>6</v>
+      </c>
+      <c r="U128">
+        <v>12</v>
+      </c>
+      <c r="V128">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>173</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" t="s">
+        <v>86</v>
+      </c>
+      <c r="F129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G129" t="s">
+        <v>158</v>
+      </c>
+      <c r="H129">
+        <v>5.08</v>
+      </c>
+      <c r="I129">
+        <v>0.84</v>
+      </c>
+      <c r="J129">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="K129">
+        <v>0.61</v>
+      </c>
+      <c r="L129">
+        <v>0.18</v>
+      </c>
+      <c r="M129">
+        <v>0.06</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>4</v>
+      </c>
+      <c r="P129">
+        <v>6.48</v>
+      </c>
+      <c r="Q129">
+        <v>28.98</v>
+      </c>
+      <c r="R129">
+        <v>4.54</v>
+      </c>
+      <c r="S129">
+        <v>23</v>
+      </c>
+      <c r="T129">
+        <v>4</v>
+      </c>
+      <c r="U129">
+        <v>18</v>
+      </c>
+      <c r="V129">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>173</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C130" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G130" t="s">
+        <v>169</v>
+      </c>
+      <c r="H130">
+        <v>5.64</v>
+      </c>
+      <c r="I130">
+        <v>0.99</v>
+      </c>
+      <c r="J130">
+        <v>4.63</v>
+      </c>
+      <c r="K130">
+        <v>0.68</v>
+      </c>
+      <c r="L130">
+        <v>0.31</v>
+      </c>
+      <c r="M130">
+        <v>0.02</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>3</v>
+      </c>
+      <c r="P130">
+        <v>7.32</v>
+      </c>
+      <c r="Q130">
+        <v>26.25</v>
+      </c>
+      <c r="R130">
+        <v>4.66</v>
+      </c>
+      <c r="S130">
+        <v>19</v>
+      </c>
+      <c r="T130">
+        <v>3</v>
+      </c>
+      <c r="U130">
+        <v>20</v>
+      </c>
+      <c r="V130">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>173</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G131" t="s">
+        <v>171</v>
+      </c>
+      <c r="H131">
+        <v>2.85</v>
+      </c>
+      <c r="I131">
+        <v>0.48</v>
+      </c>
+      <c r="J131">
+        <v>2.36</v>
+      </c>
+      <c r="K131">
+        <v>0.34</v>
+      </c>
+      <c r="L131">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M131">
+        <v>0.02</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>1</v>
+      </c>
+      <c r="P131">
+        <v>6.19</v>
+      </c>
+      <c r="Q131">
+        <v>30.27</v>
+      </c>
+      <c r="R131">
+        <v>4.49</v>
+      </c>
+      <c r="S131">
+        <v>16</v>
+      </c>
+      <c r="T131">
+        <v>7</v>
+      </c>
+      <c r="U131">
+        <v>14</v>
+      </c>
+      <c r="V131">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>173</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C132" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" t="s">
+        <v>46</v>
+      </c>
+      <c r="F132" t="s">
+        <v>24</v>
+      </c>
+      <c r="G132" t="s">
+        <v>154</v>
+      </c>
+      <c r="H132">
+        <v>4.72</v>
+      </c>
+      <c r="I132">
+        <v>0.63</v>
+      </c>
+      <c r="J132">
+        <v>4.08</v>
+      </c>
+      <c r="K132">
+        <v>0.46</v>
+      </c>
+      <c r="L132">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M132">
+        <v>0.03</v>
+      </c>
+      <c r="N132">
+        <v>0.01</v>
+      </c>
+      <c r="O132">
+        <v>2</v>
+      </c>
+      <c r="P132">
+        <v>5.95</v>
+      </c>
+      <c r="Q132">
+        <v>31.03</v>
+      </c>
+      <c r="R132">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S132">
+        <v>18</v>
+      </c>
+      <c r="T132">
+        <v>1</v>
+      </c>
+      <c r="U132">
+        <v>10</v>
+      </c>
+      <c r="V132">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>173</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C133" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" t="s">
+        <v>32</v>
+      </c>
+      <c r="F133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G133" t="s">
+        <v>172</v>
+      </c>
+      <c r="H133">
+        <v>5.66</v>
+      </c>
+      <c r="I133">
+        <v>0.83</v>
+      </c>
+      <c r="J133">
+        <v>4.82</v>
+      </c>
+      <c r="K133">
+        <v>0.68</v>
+      </c>
+      <c r="L133">
+        <v>0.15</v>
+      </c>
+      <c r="M133">
+        <v>0.01</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="P133">
+        <v>7.45</v>
+      </c>
+      <c r="Q133">
+        <v>26.11</v>
+      </c>
+      <c r="R133">
+        <v>4.21</v>
+      </c>
+      <c r="S133">
+        <v>20</v>
+      </c>
+      <c r="T133">
+        <v>1</v>
+      </c>
+      <c r="U133">
+        <v>16</v>
+      </c>
+      <c r="V133">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814F8C22-F718-C24D-8927-2AC1202E6B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01922CF-F19C-9B43-B178-F9ABD068D439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -632,9 +632,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -672,7 +672,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -778,7 +778,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -920,7 +920,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01922CF-F19C-9B43-B178-F9ABD068D439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26224A50-B424-2949-A174-CA9F28B30711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -604,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -614,6 +614,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4652,7 +4655,7 @@
       <c r="B58" s="1">
         <v>46224</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="5">
         <v>1</v>
       </c>
       <c r="E58" t="s">
@@ -4717,7 +4720,7 @@
       <c r="B59" s="1">
         <v>46224</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="5">
         <v>1</v>
       </c>
       <c r="E59" t="s">
@@ -4782,7 +4785,7 @@
       <c r="B60" s="1">
         <v>46224</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="5">
         <v>1</v>
       </c>
       <c r="E60" t="s">
@@ -4847,7 +4850,7 @@
       <c r="B61" s="1">
         <v>46224</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="5">
         <v>1</v>
       </c>
       <c r="E61" t="s">
@@ -4912,7 +4915,7 @@
       <c r="B62" s="1">
         <v>46224</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="5">
         <v>1</v>
       </c>
       <c r="E62" t="s">
@@ -4977,7 +4980,7 @@
       <c r="B63" s="1">
         <v>46224</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="5">
         <v>1</v>
       </c>
       <c r="E63" t="s">
@@ -5042,7 +5045,7 @@
       <c r="B64" s="1">
         <v>46224</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="5">
         <v>1</v>
       </c>
       <c r="E64" t="s">
@@ -5107,7 +5110,7 @@
       <c r="B65" s="1">
         <v>46224</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="5">
         <v>1</v>
       </c>
       <c r="E65" t="s">
@@ -5172,7 +5175,7 @@
       <c r="B66" s="1">
         <v>46224</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="5">
         <v>2</v>
       </c>
       <c r="E66" t="s">
@@ -5237,7 +5240,7 @@
       <c r="B67" s="1">
         <v>46224</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="5">
         <v>2</v>
       </c>
       <c r="E67" t="s">
@@ -5302,7 +5305,7 @@
       <c r="B68" s="1">
         <v>46224</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="5">
         <v>2</v>
       </c>
       <c r="E68" t="s">
@@ -5367,7 +5370,7 @@
       <c r="B69" s="1">
         <v>46224</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="5">
         <v>2</v>
       </c>
       <c r="E69" t="s">
@@ -5432,7 +5435,7 @@
       <c r="B70" s="1">
         <v>46224</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="5">
         <v>2</v>
       </c>
       <c r="E70" t="s">
@@ -5497,7 +5500,7 @@
       <c r="B71" s="1">
         <v>46224</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="5">
         <v>2</v>
       </c>
       <c r="E71" t="s">
@@ -5562,7 +5565,7 @@
       <c r="B72" s="1">
         <v>46224</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="5">
         <v>2</v>
       </c>
       <c r="E72" t="s">
@@ -5627,7 +5630,7 @@
       <c r="B73" s="1">
         <v>46224</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="5">
         <v>2</v>
       </c>
       <c r="E73" t="s">
@@ -5692,7 +5695,7 @@
       <c r="B74" s="1">
         <v>46225</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="5">
         <v>1</v>
       </c>
       <c r="E74" t="s">
@@ -5757,7 +5760,7 @@
       <c r="B75" s="1">
         <v>46225</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="5">
         <v>1</v>
       </c>
       <c r="E75" t="s">
@@ -5822,7 +5825,7 @@
       <c r="B76" s="1">
         <v>46225</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="5">
         <v>1</v>
       </c>
       <c r="E76" t="s">
@@ -5887,7 +5890,7 @@
       <c r="B77" s="1">
         <v>46225</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="5">
         <v>1</v>
       </c>
       <c r="E77" t="s">
@@ -5952,7 +5955,7 @@
       <c r="B78" s="1">
         <v>46225</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="5">
         <v>1</v>
       </c>
       <c r="E78" t="s">
@@ -6017,7 +6020,7 @@
       <c r="B79" s="1">
         <v>46225</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="5">
         <v>1</v>
       </c>
       <c r="E79" t="s">
@@ -6082,7 +6085,7 @@
       <c r="B80" s="1">
         <v>46225</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="5">
         <v>1</v>
       </c>
       <c r="E80" t="s">
@@ -6147,7 +6150,7 @@
       <c r="B81" s="1">
         <v>46225</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="5">
         <v>2</v>
       </c>
       <c r="E81" t="s">
@@ -6212,7 +6215,7 @@
       <c r="B82" s="1">
         <v>46225</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="5">
         <v>2</v>
       </c>
       <c r="E82" t="s">
@@ -6277,7 +6280,7 @@
       <c r="B83" s="1">
         <v>46225</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="5">
         <v>2</v>
       </c>
       <c r="E83" t="s">
@@ -6342,7 +6345,7 @@
       <c r="B84" s="1">
         <v>46225</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="5">
         <v>2</v>
       </c>
       <c r="E84" t="s">
@@ -6407,7 +6410,7 @@
       <c r="B85" s="1">
         <v>46225</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="5">
         <v>2</v>
       </c>
       <c r="E85" t="s">
@@ -6472,7 +6475,7 @@
       <c r="B86" s="1">
         <v>46225</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="5">
         <v>2</v>
       </c>
       <c r="E86" t="s">
@@ -6537,7 +6540,7 @@
       <c r="B87" s="1">
         <v>46225</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="5">
         <v>2</v>
       </c>
       <c r="E87" t="s">
@@ -6602,7 +6605,7 @@
       <c r="B88" s="1">
         <v>46225</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="5">
         <v>2</v>
       </c>
       <c r="E88" t="s">
@@ -6667,7 +6670,7 @@
       <c r="B89" s="1">
         <v>46226</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="5">
         <v>1</v>
       </c>
       <c r="E89" t="s">
@@ -6732,7 +6735,7 @@
       <c r="B90" s="1">
         <v>46226</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="5">
         <v>1</v>
       </c>
       <c r="E90" t="s">
@@ -6797,7 +6800,7 @@
       <c r="B91" s="1">
         <v>46226</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="5">
         <v>1</v>
       </c>
       <c r="E91" t="s">
@@ -6862,7 +6865,7 @@
       <c r="B92" s="1">
         <v>46226</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="5">
         <v>1</v>
       </c>
       <c r="E92" t="s">
@@ -6927,7 +6930,7 @@
       <c r="B93" s="1">
         <v>46226</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="5">
         <v>1</v>
       </c>
       <c r="E93" t="s">
@@ -6992,7 +6995,7 @@
       <c r="B94" s="1">
         <v>46226</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="5">
         <v>1</v>
       </c>
       <c r="E94" t="s">
@@ -7057,7 +7060,7 @@
       <c r="B95" s="1">
         <v>46226</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="5">
         <v>1</v>
       </c>
       <c r="E95" t="s">
@@ -7122,7 +7125,7 @@
       <c r="B96" s="1">
         <v>46226</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="5">
         <v>1</v>
       </c>
       <c r="E96" t="s">
@@ -7187,7 +7190,7 @@
       <c r="B97" s="1">
         <v>46226</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="5">
         <v>1</v>
       </c>
       <c r="E97" t="s">
@@ -7252,7 +7255,7 @@
       <c r="B98" s="1">
         <v>46226</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="5">
         <v>2</v>
       </c>
       <c r="E98" t="s">
@@ -7317,7 +7320,7 @@
       <c r="B99" s="1">
         <v>46226</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="5">
         <v>2</v>
       </c>
       <c r="E99" t="s">
@@ -7382,7 +7385,7 @@
       <c r="B100" s="1">
         <v>46226</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="5">
         <v>2</v>
       </c>
       <c r="E100" t="s">
@@ -7447,7 +7450,7 @@
       <c r="B101" s="1">
         <v>46226</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="5">
         <v>2</v>
       </c>
       <c r="E101" t="s">
@@ -7512,7 +7515,7 @@
       <c r="B102" s="1">
         <v>46226</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="5">
         <v>2</v>
       </c>
       <c r="E102" t="s">
@@ -7577,7 +7580,7 @@
       <c r="B103" s="1">
         <v>46226</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="5">
         <v>2</v>
       </c>
       <c r="E103" t="s">
@@ -7642,7 +7645,7 @@
       <c r="B104" s="1">
         <v>46226</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="5">
         <v>2</v>
       </c>
       <c r="E104" t="s">
@@ -7707,7 +7710,7 @@
       <c r="B105" s="1">
         <v>46226</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="5">
         <v>2</v>
       </c>
       <c r="E105" t="s">
@@ -7772,7 +7775,7 @@
       <c r="B106" s="1">
         <v>46226</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="5">
         <v>2</v>
       </c>
       <c r="E106" t="s">

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26224A50-B424-2949-A174-CA9F28B30711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6411D6FE-3E1C-3F4C-A7C7-BF2FAAD9C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="239">
   <si>
     <t>Temps joué</t>
   </si>
@@ -556,7 +556,202 @@
     <t>00:45:44</t>
   </si>
   <si>
-    <t>Match Amical VS Villefranche</t>
+    <t>01:17:49</t>
+  </si>
+  <si>
+    <t>01:19:40</t>
+  </si>
+  <si>
+    <t>01:19:48</t>
+  </si>
+  <si>
+    <t>01:18:14</t>
+  </si>
+  <si>
+    <t>01:20:03</t>
+  </si>
+  <si>
+    <t>01:33:45</t>
+  </si>
+  <si>
+    <t>01:14:13</t>
+  </si>
+  <si>
+    <t>01:28:01</t>
+  </si>
+  <si>
+    <t>01:32:50</t>
+  </si>
+  <si>
+    <t>01:29:07</t>
+  </si>
+  <si>
+    <t>01:29:48</t>
+  </si>
+  <si>
+    <t>Amine Taiar</t>
+  </si>
+  <si>
+    <t>01:31:18</t>
+  </si>
+  <si>
+    <t>right foward</t>
+  </si>
+  <si>
+    <t>01:33:13</t>
+  </si>
+  <si>
+    <t>01:27:46</t>
+  </si>
+  <si>
+    <t>01:28:51</t>
+  </si>
+  <si>
+    <t>00:47:01</t>
+  </si>
+  <si>
+    <t>00:47:02</t>
+  </si>
+  <si>
+    <t>00:46:28</t>
+  </si>
+  <si>
+    <t>Cedric Koffi</t>
+  </si>
+  <si>
+    <t>00:47:27</t>
+  </si>
+  <si>
+    <t>00:47:44</t>
+  </si>
+  <si>
+    <t>Loïc Nguende</t>
+  </si>
+  <si>
+    <t>00:47:18</t>
+  </si>
+  <si>
+    <t>Brian Chevreuil</t>
+  </si>
+  <si>
+    <t>00:47:35</t>
+  </si>
+  <si>
+    <t>00:23:23</t>
+  </si>
+  <si>
+    <t>00:47:19</t>
+  </si>
+  <si>
+    <t>00:47:52</t>
+  </si>
+  <si>
+    <t>00:47:10</t>
+  </si>
+  <si>
+    <t>00:32:06</t>
+  </si>
+  <si>
+    <t>Match Amical VS Servette 29/07/2026</t>
+  </si>
+  <si>
+    <t>Match Amical VS Villefranche 25/07/2026</t>
+  </si>
+  <si>
+    <t>01:28:32</t>
+  </si>
+  <si>
+    <t>01:30:40</t>
+  </si>
+  <si>
+    <t>01:29:36</t>
+  </si>
+  <si>
+    <t>01:30:33</t>
+  </si>
+  <si>
+    <t>01:29:12</t>
+  </si>
+  <si>
+    <t>01:31:02</t>
+  </si>
+  <si>
+    <t>01:32:13</t>
+  </si>
+  <si>
+    <t>01:39:46</t>
+  </si>
+  <si>
+    <t>01:35:44</t>
+  </si>
+  <si>
+    <t>01:38:49</t>
+  </si>
+  <si>
+    <t>01:39:38</t>
+  </si>
+  <si>
+    <t>00:48:56</t>
+  </si>
+  <si>
+    <t>01:06:07</t>
+  </si>
+  <si>
+    <t>Abou</t>
+  </si>
+  <si>
+    <t>01:06:00</t>
+  </si>
+  <si>
+    <t>01:05:37</t>
+  </si>
+  <si>
+    <t>01:06:22</t>
+  </si>
+  <si>
+    <t>01:06:30</t>
+  </si>
+  <si>
+    <t>01:06:16</t>
+  </si>
+  <si>
+    <t>01:07:08</t>
+  </si>
+  <si>
+    <t>01:07:46</t>
+  </si>
+  <si>
+    <t>Match Amical VS ESTAC 01/08/2026</t>
+  </si>
+  <si>
+    <t>01:05:03</t>
+  </si>
+  <si>
+    <t>01:12:27</t>
+  </si>
+  <si>
+    <t>01:15:03</t>
+  </si>
+  <si>
+    <t>01:12:42</t>
+  </si>
+  <si>
+    <t>01:12:51</t>
+  </si>
+  <si>
+    <t>01:14:54</t>
+  </si>
+  <si>
+    <t>01:14:21</t>
+  </si>
+  <si>
+    <t>01:06:01</t>
+  </si>
+  <si>
+    <t>01:11:38</t>
+  </si>
+  <si>
+    <t>01:13:48</t>
   </si>
 </sst>
 </file>
@@ -931,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V133"/>
+  <dimension ref="A1:V199"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -8290,7 +8485,7 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B114" s="1">
         <v>46228</v>
@@ -8355,7 +8550,7 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B115" s="1">
         <v>46228</v>
@@ -8420,7 +8615,7 @@
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B116" s="1">
         <v>46228</v>
@@ -8485,7 +8680,7 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B117" s="1">
         <v>46228</v>
@@ -8550,7 +8745,7 @@
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B118" s="1">
         <v>46228</v>
@@ -8615,7 +8810,7 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B119" s="1">
         <v>46228</v>
@@ -8680,7 +8875,7 @@
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B120" s="1">
         <v>46228</v>
@@ -8745,7 +8940,7 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B121" s="1">
         <v>46228</v>
@@ -8810,7 +9005,7 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B122" s="1">
         <v>46228</v>
@@ -8875,7 +9070,7 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B123" s="1">
         <v>46228</v>
@@ -8940,7 +9135,7 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B124" s="1">
         <v>46228</v>
@@ -9005,7 +9200,7 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B125" s="1">
         <v>46228</v>
@@ -9070,7 +9265,7 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B126" s="1">
         <v>46228</v>
@@ -9135,7 +9330,7 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B127" s="1">
         <v>46228</v>
@@ -9200,7 +9395,7 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B128" s="1">
         <v>46228</v>
@@ -9265,7 +9460,7 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B129" s="1">
         <v>46228</v>
@@ -9330,7 +9525,7 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B130" s="1">
         <v>46228</v>
@@ -9395,7 +9590,7 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B131" s="1">
         <v>46228</v>
@@ -9460,7 +9655,7 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B132" s="1">
         <v>46228</v>
@@ -9525,7 +9720,7 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B133" s="1">
         <v>46228</v>
@@ -9585,6 +9780,4296 @@
         <v>16</v>
       </c>
       <c r="V133">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C134" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F134" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" t="s">
+        <v>173</v>
+      </c>
+      <c r="H134">
+        <v>6.33</v>
+      </c>
+      <c r="I134">
+        <v>1.34</v>
+      </c>
+      <c r="J134">
+        <v>4.97</v>
+      </c>
+      <c r="K134">
+        <v>1.27</v>
+      </c>
+      <c r="L134">
+        <v>0.09</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="Q134">
+        <v>21.78</v>
+      </c>
+      <c r="R134">
+        <v>4.55</v>
+      </c>
+      <c r="S134">
+        <v>44</v>
+      </c>
+      <c r="T134">
+        <v>3</v>
+      </c>
+      <c r="U134">
+        <v>56</v>
+      </c>
+      <c r="V134">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>22</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C135" t="s">
+        <v>19</v>
+      </c>
+      <c r="E135" t="s">
+        <v>43</v>
+      </c>
+      <c r="F135" t="s">
+        <v>24</v>
+      </c>
+      <c r="G135" t="s">
+        <v>174</v>
+      </c>
+      <c r="H135">
+        <v>6.46</v>
+      </c>
+      <c r="I135">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J135">
+        <v>5.31</v>
+      </c>
+      <c r="K135">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="L135">
+        <v>0.02</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>4.8</v>
+      </c>
+      <c r="Q135">
+        <v>20.53</v>
+      </c>
+      <c r="R135">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="S135">
+        <v>47</v>
+      </c>
+      <c r="T135">
+        <v>2</v>
+      </c>
+      <c r="U135">
+        <v>41</v>
+      </c>
+      <c r="V135">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>22</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C136" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" t="s">
+        <v>35</v>
+      </c>
+      <c r="F136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G136" t="s">
+        <v>175</v>
+      </c>
+      <c r="H136">
+        <v>6.11</v>
+      </c>
+      <c r="I136">
+        <v>1.2</v>
+      </c>
+      <c r="J136">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K136">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="L136">
+        <v>0.08</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>4.49</v>
+      </c>
+      <c r="Q136">
+        <v>21.62</v>
+      </c>
+      <c r="R136">
+        <v>4.26</v>
+      </c>
+      <c r="S136">
+        <v>47</v>
+      </c>
+      <c r="T136">
+        <v>4</v>
+      </c>
+      <c r="U136">
+        <v>34</v>
+      </c>
+      <c r="V136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>22</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C137" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" t="s">
+        <v>38</v>
+      </c>
+      <c r="F137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G137" t="s">
+        <v>176</v>
+      </c>
+      <c r="H137">
+        <v>6.75</v>
+      </c>
+      <c r="I137">
+        <v>1.21</v>
+      </c>
+      <c r="J137">
+        <v>5.54</v>
+      </c>
+      <c r="K137">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="L137">
+        <v>0.06</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>5.05</v>
+      </c>
+      <c r="Q137">
+        <v>20.9</v>
+      </c>
+      <c r="R137">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="S137">
+        <v>70</v>
+      </c>
+      <c r="T137">
+        <v>5</v>
+      </c>
+      <c r="U137">
+        <v>58</v>
+      </c>
+      <c r="V137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>22</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C138" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" t="s">
+        <v>53</v>
+      </c>
+      <c r="F138" t="s">
+        <v>27</v>
+      </c>
+      <c r="G138" t="s">
+        <v>177</v>
+      </c>
+      <c r="H138">
+        <v>6.8</v>
+      </c>
+      <c r="I138">
+        <v>1.21</v>
+      </c>
+      <c r="J138">
+        <v>5.59</v>
+      </c>
+      <c r="K138">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="L138">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>5.08</v>
+      </c>
+      <c r="Q138">
+        <v>21.85</v>
+      </c>
+      <c r="R138">
+        <v>4.09</v>
+      </c>
+      <c r="S138">
+        <v>48</v>
+      </c>
+      <c r="T138">
+        <v>1</v>
+      </c>
+      <c r="U138">
+        <v>54</v>
+      </c>
+      <c r="V138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>22</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C139" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" t="s">
+        <v>32</v>
+      </c>
+      <c r="F139" t="s">
+        <v>27</v>
+      </c>
+      <c r="G139" t="s">
+        <v>178</v>
+      </c>
+      <c r="H139">
+        <v>6.56</v>
+      </c>
+      <c r="I139">
+        <v>1.94</v>
+      </c>
+      <c r="J139">
+        <v>4.62</v>
+      </c>
+      <c r="K139">
+        <v>1.02</v>
+      </c>
+      <c r="L139">
+        <v>0.92</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>3.66</v>
+      </c>
+      <c r="Q139">
+        <v>23.23</v>
+      </c>
+      <c r="R139">
+        <v>4.42</v>
+      </c>
+      <c r="S139">
+        <v>24</v>
+      </c>
+      <c r="T139">
+        <v>4</v>
+      </c>
+      <c r="U139">
+        <v>10</v>
+      </c>
+      <c r="V139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>22</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C140" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" t="s">
+        <v>163</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G140" t="s">
+        <v>179</v>
+      </c>
+      <c r="H140">
+        <v>4.84</v>
+      </c>
+      <c r="I140">
+        <v>1.74</v>
+      </c>
+      <c r="J140">
+        <v>3.09</v>
+      </c>
+      <c r="K140">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="L140">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M140">
+        <v>0.06</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>3</v>
+      </c>
+      <c r="P140">
+        <v>3.62</v>
+      </c>
+      <c r="Q140">
+        <v>30.65</v>
+      </c>
+      <c r="R140">
+        <v>4.7</v>
+      </c>
+      <c r="S140">
+        <v>24</v>
+      </c>
+      <c r="T140">
+        <v>6</v>
+      </c>
+      <c r="U140">
+        <v>9</v>
+      </c>
+      <c r="V140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C141" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" t="s">
+        <v>43</v>
+      </c>
+      <c r="F141" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141" t="s">
+        <v>180</v>
+      </c>
+      <c r="H141">
+        <v>5.8</v>
+      </c>
+      <c r="I141">
+        <v>1.47</v>
+      </c>
+      <c r="J141">
+        <v>4.33</v>
+      </c>
+      <c r="K141">
+        <v>1.22</v>
+      </c>
+      <c r="L141">
+        <v>0.26</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>3.26</v>
+      </c>
+      <c r="Q141">
+        <v>22.44</v>
+      </c>
+      <c r="R141">
+        <v>4.13</v>
+      </c>
+      <c r="S141">
+        <v>23</v>
+      </c>
+      <c r="T141">
+        <v>1</v>
+      </c>
+      <c r="U141">
+        <v>7</v>
+      </c>
+      <c r="V141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>22</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" t="s">
+        <v>166</v>
+      </c>
+      <c r="F142" t="s">
+        <v>101</v>
+      </c>
+      <c r="G142" t="s">
+        <v>181</v>
+      </c>
+      <c r="H142">
+        <v>6.67</v>
+      </c>
+      <c r="I142">
+        <v>2.04</v>
+      </c>
+      <c r="J142">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="K142">
+        <v>0.71</v>
+      </c>
+      <c r="L142">
+        <v>1.25</v>
+      </c>
+      <c r="M142">
+        <v>0.09</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>26</v>
+      </c>
+      <c r="P142">
+        <v>3.77</v>
+      </c>
+      <c r="Q142">
+        <v>28.29</v>
+      </c>
+      <c r="R142">
+        <v>5.17</v>
+      </c>
+      <c r="S142">
+        <v>47</v>
+      </c>
+      <c r="T142">
+        <v>18</v>
+      </c>
+      <c r="U142">
+        <v>40</v>
+      </c>
+      <c r="V142">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>22</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C143" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" t="s">
+        <v>38</v>
+      </c>
+      <c r="F143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G143" t="s">
+        <v>182</v>
+      </c>
+      <c r="H143">
+        <v>5.73</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
+        <v>3.72</v>
+      </c>
+      <c r="K143">
+        <v>0.97</v>
+      </c>
+      <c r="L143">
+        <v>1.03</v>
+      </c>
+      <c r="M143">
+        <v>0.01</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>2</v>
+      </c>
+      <c r="P143">
+        <v>3.68</v>
+      </c>
+      <c r="Q143">
+        <v>26.19</v>
+      </c>
+      <c r="R143">
+        <v>4.33</v>
+      </c>
+      <c r="S143">
+        <v>26</v>
+      </c>
+      <c r="T143">
+        <v>8</v>
+      </c>
+      <c r="U143">
+        <v>12</v>
+      </c>
+      <c r="V143">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>22</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C144" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" t="s">
+        <v>35</v>
+      </c>
+      <c r="F144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G144" t="s">
+        <v>183</v>
+      </c>
+      <c r="H144">
+        <v>6.4</v>
+      </c>
+      <c r="I144">
+        <v>2.16</v>
+      </c>
+      <c r="J144">
+        <v>4.16</v>
+      </c>
+      <c r="K144">
+        <v>0.88</v>
+      </c>
+      <c r="L144">
+        <v>0.94</v>
+      </c>
+      <c r="M144">
+        <v>0.39</v>
+      </c>
+      <c r="N144">
+        <v>0.03</v>
+      </c>
+      <c r="O144">
+        <v>2</v>
+      </c>
+      <c r="P144">
+        <v>3.41</v>
+      </c>
+      <c r="Q144">
+        <v>39.94</v>
+      </c>
+      <c r="R144">
+        <v>19.54</v>
+      </c>
+      <c r="S144">
+        <v>25</v>
+      </c>
+      <c r="T144">
+        <v>6</v>
+      </c>
+      <c r="U144">
+        <v>6</v>
+      </c>
+      <c r="V144">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>22</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" t="s">
+        <v>184</v>
+      </c>
+      <c r="F145" t="s">
+        <v>24</v>
+      </c>
+      <c r="G145" t="s">
+        <v>185</v>
+      </c>
+      <c r="H145">
+        <v>5.49</v>
+      </c>
+      <c r="I145">
+        <v>1.6</v>
+      </c>
+      <c r="J145">
+        <v>3.89</v>
+      </c>
+      <c r="K145">
+        <v>1.3</v>
+      </c>
+      <c r="L145">
+        <v>0.3</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>3.46</v>
+      </c>
+      <c r="Q145">
+        <v>22.8</v>
+      </c>
+      <c r="R145">
+        <v>4.5</v>
+      </c>
+      <c r="S145">
+        <v>19</v>
+      </c>
+      <c r="T145">
+        <v>5</v>
+      </c>
+      <c r="U145">
+        <v>3</v>
+      </c>
+      <c r="V145">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>22</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C146" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" t="s">
+        <v>170</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G146" t="s">
+        <v>187</v>
+      </c>
+      <c r="H146">
+        <v>6.27</v>
+      </c>
+      <c r="I146">
+        <v>2.11</v>
+      </c>
+      <c r="J146">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="K146">
+        <v>0.75</v>
+      </c>
+      <c r="L146">
+        <v>1.32</v>
+      </c>
+      <c r="M146">
+        <v>0.05</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>5</v>
+      </c>
+      <c r="P146">
+        <v>3.73</v>
+      </c>
+      <c r="Q146">
+        <v>27.46</v>
+      </c>
+      <c r="R146">
+        <v>5.22</v>
+      </c>
+      <c r="S146">
+        <v>30</v>
+      </c>
+      <c r="T146">
+        <v>7</v>
+      </c>
+      <c r="U146">
+        <v>16</v>
+      </c>
+      <c r="V146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>22</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C147" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" t="s">
+        <v>31</v>
+      </c>
+      <c r="F147" t="s">
+        <v>28</v>
+      </c>
+      <c r="G147" t="s">
+        <v>188</v>
+      </c>
+      <c r="H147">
+        <v>5.68</v>
+      </c>
+      <c r="I147">
+        <v>1.69</v>
+      </c>
+      <c r="J147">
+        <v>3.99</v>
+      </c>
+      <c r="K147">
+        <v>0.92</v>
+      </c>
+      <c r="L147">
+        <v>0.72</v>
+      </c>
+      <c r="M147">
+        <v>0.05</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>8</v>
+      </c>
+      <c r="P147">
+        <v>3.76</v>
+      </c>
+      <c r="Q147">
+        <v>27.88</v>
+      </c>
+      <c r="R147">
+        <v>5.04</v>
+      </c>
+      <c r="S147">
+        <v>29</v>
+      </c>
+      <c r="T147">
+        <v>3</v>
+      </c>
+      <c r="U147">
+        <v>5</v>
+      </c>
+      <c r="V147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>22</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C148" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" t="s">
+        <v>53</v>
+      </c>
+      <c r="F148" t="s">
+        <v>27</v>
+      </c>
+      <c r="G148" t="s">
+        <v>189</v>
+      </c>
+      <c r="H148">
+        <v>6.06</v>
+      </c>
+      <c r="I148">
+        <v>1.74</v>
+      </c>
+      <c r="J148">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="K148">
+        <v>1.03</v>
+      </c>
+      <c r="L148">
+        <v>0.7</v>
+      </c>
+      <c r="M148">
+        <v>0.01</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>1</v>
+      </c>
+      <c r="P148">
+        <v>3.51</v>
+      </c>
+      <c r="Q148">
+        <v>27.84</v>
+      </c>
+      <c r="R148">
+        <v>4.04</v>
+      </c>
+      <c r="S148">
+        <v>13</v>
+      </c>
+      <c r="T148">
+        <v>1</v>
+      </c>
+      <c r="U148">
+        <v>9</v>
+      </c>
+      <c r="V148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>205</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C149" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" t="s">
+        <v>184</v>
+      </c>
+      <c r="F149" t="s">
+        <v>24</v>
+      </c>
+      <c r="G149" t="s">
+        <v>190</v>
+      </c>
+      <c r="H149">
+        <v>4.8</v>
+      </c>
+      <c r="I149">
+        <v>0.72</v>
+      </c>
+      <c r="J149">
+        <v>4.08</v>
+      </c>
+      <c r="K149">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L149">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M149">
+        <v>0.03</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>3</v>
+      </c>
+      <c r="P149">
+        <v>6.09</v>
+      </c>
+      <c r="Q149">
+        <v>30.02</v>
+      </c>
+      <c r="R149">
+        <v>4.2</v>
+      </c>
+      <c r="S149">
+        <v>16</v>
+      </c>
+      <c r="T149">
+        <v>1</v>
+      </c>
+      <c r="U149">
+        <v>15</v>
+      </c>
+      <c r="V149">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>205</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C150" t="s">
+        <v>19</v>
+      </c>
+      <c r="E150" t="s">
+        <v>32</v>
+      </c>
+      <c r="F150" t="s">
+        <v>27</v>
+      </c>
+      <c r="G150" t="s">
+        <v>190</v>
+      </c>
+      <c r="H150">
+        <v>5.71</v>
+      </c>
+      <c r="I150">
+        <v>0.96</v>
+      </c>
+      <c r="J150">
+        <v>4.74</v>
+      </c>
+      <c r="K150">
+        <v>0.81</v>
+      </c>
+      <c r="L150">
+        <v>0.17</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>7.29</v>
+      </c>
+      <c r="Q150">
+        <v>24.65</v>
+      </c>
+      <c r="R150">
+        <v>4.49</v>
+      </c>
+      <c r="S150">
+        <v>16</v>
+      </c>
+      <c r="T150">
+        <v>1</v>
+      </c>
+      <c r="U150">
+        <v>13</v>
+      </c>
+      <c r="V150">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>205</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="s">
+        <v>38</v>
+      </c>
+      <c r="F151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G151" t="s">
+        <v>191</v>
+      </c>
+      <c r="H151">
+        <v>5.4</v>
+      </c>
+      <c r="I151">
+        <v>1.24</v>
+      </c>
+      <c r="J151">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="K151">
+        <v>0.79</v>
+      </c>
+      <c r="L151">
+        <v>0.38</v>
+      </c>
+      <c r="M151">
+        <v>0.08</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>7</v>
+      </c>
+      <c r="P151">
+        <v>6.84</v>
+      </c>
+      <c r="Q151">
+        <v>30.12</v>
+      </c>
+      <c r="R151">
+        <v>4.63</v>
+      </c>
+      <c r="S151">
+        <v>21</v>
+      </c>
+      <c r="T151">
+        <v>5</v>
+      </c>
+      <c r="U151">
+        <v>14</v>
+      </c>
+      <c r="V151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>205</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C152" t="s">
+        <v>19</v>
+      </c>
+      <c r="E152" t="s">
+        <v>82</v>
+      </c>
+      <c r="F152" t="s">
+        <v>27</v>
+      </c>
+      <c r="G152" t="s">
+        <v>192</v>
+      </c>
+      <c r="H152">
+        <v>5.01</v>
+      </c>
+      <c r="I152">
+        <v>1.05</v>
+      </c>
+      <c r="J152">
+        <v>3.96</v>
+      </c>
+      <c r="K152">
+        <v>0.66</v>
+      </c>
+      <c r="L152">
+        <v>0.32</v>
+      </c>
+      <c r="M152">
+        <v>0.08</v>
+      </c>
+      <c r="N152">
+        <v>0.01</v>
+      </c>
+      <c r="O152">
+        <v>6</v>
+      </c>
+      <c r="P152">
+        <v>6.5</v>
+      </c>
+      <c r="Q152">
+        <v>30.41</v>
+      </c>
+      <c r="R152">
+        <v>4.17</v>
+      </c>
+      <c r="S152">
+        <v>16</v>
+      </c>
+      <c r="T152">
+        <v>1</v>
+      </c>
+      <c r="U152">
+        <v>16</v>
+      </c>
+      <c r="V152">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>205</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C153" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F153" t="s">
+        <v>28</v>
+      </c>
+      <c r="G153" t="s">
+        <v>190</v>
+      </c>
+      <c r="H153">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I153">
+        <v>0.87</v>
+      </c>
+      <c r="J153">
+        <v>3.72</v>
+      </c>
+      <c r="K153">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L153">
+        <v>0.25</v>
+      </c>
+      <c r="M153">
+        <v>0.06</v>
+      </c>
+      <c r="N153">
+        <v>0.01</v>
+      </c>
+      <c r="O153">
+        <v>4</v>
+      </c>
+      <c r="P153">
+        <v>5.82</v>
+      </c>
+      <c r="Q153">
+        <v>30.46</v>
+      </c>
+      <c r="R153">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="S153">
+        <v>15</v>
+      </c>
+      <c r="T153">
+        <v>2</v>
+      </c>
+      <c r="U153">
+        <v>15</v>
+      </c>
+      <c r="V153">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>205</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C154" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154" t="s">
+        <v>46</v>
+      </c>
+      <c r="F154" t="s">
+        <v>24</v>
+      </c>
+      <c r="G154" t="s">
+        <v>194</v>
+      </c>
+      <c r="H154">
+        <v>4.74</v>
+      </c>
+      <c r="I154">
+        <v>0.62</v>
+      </c>
+      <c r="J154">
+        <v>4.12</v>
+      </c>
+      <c r="K154">
+        <v>0.44</v>
+      </c>
+      <c r="L154">
+        <v>0.16</v>
+      </c>
+      <c r="M154">
+        <v>0.03</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>2</v>
+      </c>
+      <c r="P154">
+        <v>5.96</v>
+      </c>
+      <c r="Q154">
+        <v>27.33</v>
+      </c>
+      <c r="R154">
+        <v>4.08</v>
+      </c>
+      <c r="S154">
+        <v>15</v>
+      </c>
+      <c r="T154">
+        <v>1</v>
+      </c>
+      <c r="U154">
+        <v>16</v>
+      </c>
+      <c r="V154">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>205</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155" t="s">
+        <v>166</v>
+      </c>
+      <c r="F155" t="s">
+        <v>101</v>
+      </c>
+      <c r="G155" t="s">
+        <v>195</v>
+      </c>
+      <c r="H155">
+        <v>5.19</v>
+      </c>
+      <c r="I155">
+        <v>1.03</v>
+      </c>
+      <c r="J155">
+        <v>4.16</v>
+      </c>
+      <c r="K155">
+        <v>0.71</v>
+      </c>
+      <c r="L155">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M155">
+        <v>0.04</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>3</v>
+      </c>
+      <c r="P155">
+        <v>6.52</v>
+      </c>
+      <c r="Q155">
+        <v>30.12</v>
+      </c>
+      <c r="R155">
+        <v>4.57</v>
+      </c>
+      <c r="S155">
+        <v>16</v>
+      </c>
+      <c r="T155">
+        <v>2</v>
+      </c>
+      <c r="U155">
+        <v>12</v>
+      </c>
+      <c r="V155">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>205</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F156" t="s">
+        <v>27</v>
+      </c>
+      <c r="G156" t="s">
+        <v>194</v>
+      </c>
+      <c r="H156">
+        <v>5.71</v>
+      </c>
+      <c r="I156">
+        <v>1.05</v>
+      </c>
+      <c r="J156">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K156">
+        <v>0.95</v>
+      </c>
+      <c r="L156">
+        <v>0.12</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>7.21</v>
+      </c>
+      <c r="Q156">
+        <v>24.28</v>
+      </c>
+      <c r="R156">
+        <v>3.7</v>
+      </c>
+      <c r="S156">
+        <v>8</v>
+      </c>
+      <c r="T156">
+        <v>0</v>
+      </c>
+      <c r="U156">
+        <v>10</v>
+      </c>
+      <c r="V156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>205</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C157" t="s">
+        <v>19</v>
+      </c>
+      <c r="E157" t="s">
+        <v>163</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G157" t="s">
+        <v>197</v>
+      </c>
+      <c r="H157">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="I157">
+        <v>0.76</v>
+      </c>
+      <c r="J157">
+        <v>3.92</v>
+      </c>
+      <c r="K157">
+        <v>0.44</v>
+      </c>
+      <c r="L157">
+        <v>0.22</v>
+      </c>
+      <c r="M157">
+        <v>0.08</v>
+      </c>
+      <c r="N157">
+        <v>0.03</v>
+      </c>
+      <c r="O157">
+        <v>8</v>
+      </c>
+      <c r="P157">
+        <v>5.93</v>
+      </c>
+      <c r="Q157">
+        <v>32.950000000000003</v>
+      </c>
+      <c r="R157">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="S157">
+        <v>34</v>
+      </c>
+      <c r="T157">
+        <v>3</v>
+      </c>
+      <c r="U157">
+        <v>19</v>
+      </c>
+      <c r="V157">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>205</v>
+      </c>
+      <c r="B158" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C158" t="s">
+        <v>19</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G158" t="s">
+        <v>199</v>
+      </c>
+      <c r="H158">
+        <v>4.24</v>
+      </c>
+      <c r="I158">
+        <v>0.51</v>
+      </c>
+      <c r="J158">
+        <v>3.72</v>
+      </c>
+      <c r="K158">
+        <v>0.38</v>
+      </c>
+      <c r="L158">
+        <v>0.13</v>
+      </c>
+      <c r="M158">
+        <v>0.01</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>2</v>
+      </c>
+      <c r="P158">
+        <v>5.43</v>
+      </c>
+      <c r="Q158">
+        <v>25.71</v>
+      </c>
+      <c r="R158">
+        <v>3.95</v>
+      </c>
+      <c r="S158">
+        <v>15</v>
+      </c>
+      <c r="T158">
+        <v>0</v>
+      </c>
+      <c r="U158">
+        <v>9</v>
+      </c>
+      <c r="V158">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>205</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C159" t="s">
+        <v>19</v>
+      </c>
+      <c r="E159" t="s">
+        <v>87</v>
+      </c>
+      <c r="F159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G159" t="s">
+        <v>195</v>
+      </c>
+      <c r="H159">
+        <v>5.64</v>
+      </c>
+      <c r="I159">
+        <v>1.08</v>
+      </c>
+      <c r="J159">
+        <v>4.55</v>
+      </c>
+      <c r="K159">
+        <v>0.9</v>
+      </c>
+      <c r="L159">
+        <v>0.17</v>
+      </c>
+      <c r="M159">
+        <v>0.03</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <v>3</v>
+      </c>
+      <c r="P159">
+        <v>6.99</v>
+      </c>
+      <c r="Q159">
+        <v>27.13</v>
+      </c>
+      <c r="R159">
+        <v>4.28</v>
+      </c>
+      <c r="S159">
+        <v>14</v>
+      </c>
+      <c r="T159">
+        <v>1</v>
+      </c>
+      <c r="U159">
+        <v>12</v>
+      </c>
+      <c r="V159">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>205</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C160" t="s">
+        <v>19</v>
+      </c>
+      <c r="E160" t="s">
+        <v>31</v>
+      </c>
+      <c r="F160" t="s">
+        <v>28</v>
+      </c>
+      <c r="G160" t="s">
+        <v>199</v>
+      </c>
+      <c r="H160">
+        <v>4.95</v>
+      </c>
+      <c r="I160">
+        <v>0.96</v>
+      </c>
+      <c r="J160">
+        <v>3.98</v>
+      </c>
+      <c r="K160">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L160">
+        <v>0.27</v>
+      </c>
+      <c r="M160">
+        <v>0.13</v>
+      </c>
+      <c r="N160">
+        <v>0.01</v>
+      </c>
+      <c r="O160">
+        <v>7</v>
+      </c>
+      <c r="P160">
+        <v>6.21</v>
+      </c>
+      <c r="Q160">
+        <v>30.86</v>
+      </c>
+      <c r="R160">
+        <v>4.68</v>
+      </c>
+      <c r="S160">
+        <v>9</v>
+      </c>
+      <c r="T160">
+        <v>8</v>
+      </c>
+      <c r="U160">
+        <v>14</v>
+      </c>
+      <c r="V160">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>205</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" t="s">
+        <v>53</v>
+      </c>
+      <c r="F161" t="s">
+        <v>27</v>
+      </c>
+      <c r="G161" t="s">
+        <v>200</v>
+      </c>
+      <c r="H161">
+        <v>2.59</v>
+      </c>
+      <c r="I161">
+        <v>0.45</v>
+      </c>
+      <c r="J161">
+        <v>2.14</v>
+      </c>
+      <c r="K161">
+        <v>0.31</v>
+      </c>
+      <c r="L161">
+        <v>0.09</v>
+      </c>
+      <c r="M161">
+        <v>0.05</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>3</v>
+      </c>
+      <c r="P161">
+        <v>6.6</v>
+      </c>
+      <c r="Q161">
+        <v>27.62</v>
+      </c>
+      <c r="R161">
+        <v>4.29</v>
+      </c>
+      <c r="S161">
+        <v>12</v>
+      </c>
+      <c r="T161">
+        <v>1</v>
+      </c>
+      <c r="U161">
+        <v>10</v>
+      </c>
+      <c r="V161">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>205</v>
+      </c>
+      <c r="B162" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C162" t="s">
+        <v>19</v>
+      </c>
+      <c r="E162" t="s">
+        <v>43</v>
+      </c>
+      <c r="F162" t="s">
+        <v>24</v>
+      </c>
+      <c r="G162" t="s">
+        <v>201</v>
+      </c>
+      <c r="H162">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="I162">
+        <v>0.76</v>
+      </c>
+      <c r="J162">
+        <v>4.17</v>
+      </c>
+      <c r="K162">
+        <v>0.51</v>
+      </c>
+      <c r="L162">
+        <v>0.21</v>
+      </c>
+      <c r="M162">
+        <v>0.05</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>7</v>
+      </c>
+      <c r="P162">
+        <v>6.24</v>
+      </c>
+      <c r="Q162">
+        <v>27.81</v>
+      </c>
+      <c r="R162">
+        <v>4.41</v>
+      </c>
+      <c r="S162">
+        <v>14</v>
+      </c>
+      <c r="T162">
+        <v>2</v>
+      </c>
+      <c r="U162">
+        <v>13</v>
+      </c>
+      <c r="V162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>205</v>
+      </c>
+      <c r="B163" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C163" t="s">
+        <v>19</v>
+      </c>
+      <c r="E163" t="s">
+        <v>98</v>
+      </c>
+      <c r="F163" t="s">
+        <v>27</v>
+      </c>
+      <c r="G163" t="s">
+        <v>195</v>
+      </c>
+      <c r="H163">
+        <v>5.71</v>
+      </c>
+      <c r="I163">
+        <v>0.9</v>
+      </c>
+      <c r="J163">
+        <v>4.8</v>
+      </c>
+      <c r="K163">
+        <v>0.74</v>
+      </c>
+      <c r="L163">
+        <v>0.16</v>
+      </c>
+      <c r="M163">
+        <v>0.02</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>3</v>
+      </c>
+      <c r="P163">
+        <v>7.17</v>
+      </c>
+      <c r="Q163">
+        <v>25.93</v>
+      </c>
+      <c r="R163">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="S163">
+        <v>20</v>
+      </c>
+      <c r="T163">
+        <v>3</v>
+      </c>
+      <c r="U163">
+        <v>19</v>
+      </c>
+      <c r="V163">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>205</v>
+      </c>
+      <c r="B164" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C164" t="s">
+        <v>19</v>
+      </c>
+      <c r="E164" t="s">
+        <v>99</v>
+      </c>
+      <c r="F164" t="s">
+        <v>27</v>
+      </c>
+      <c r="G164" t="s">
+        <v>202</v>
+      </c>
+      <c r="H164">
+        <v>5.39</v>
+      </c>
+      <c r="I164">
+        <v>0.93</v>
+      </c>
+      <c r="J164">
+        <v>4.45</v>
+      </c>
+      <c r="K164">
+        <v>0.7</v>
+      </c>
+      <c r="L164">
+        <v>0.22</v>
+      </c>
+      <c r="M164">
+        <v>0.03</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>3</v>
+      </c>
+      <c r="P164">
+        <v>6.74</v>
+      </c>
+      <c r="Q164">
+        <v>27.26</v>
+      </c>
+      <c r="R164">
+        <v>4.24</v>
+      </c>
+      <c r="S164">
+        <v>20</v>
+      </c>
+      <c r="T164">
+        <v>3</v>
+      </c>
+      <c r="U164">
+        <v>14</v>
+      </c>
+      <c r="V164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>205</v>
+      </c>
+      <c r="B165" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C165" t="s">
+        <v>19</v>
+      </c>
+      <c r="E165" t="s">
+        <v>94</v>
+      </c>
+      <c r="F165" t="s">
+        <v>103</v>
+      </c>
+      <c r="G165" t="s">
+        <v>199</v>
+      </c>
+      <c r="H165">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I165">
+        <v>0.98</v>
+      </c>
+      <c r="J165">
+        <v>4.07</v>
+      </c>
+      <c r="K165">
+        <v>0.68</v>
+      </c>
+      <c r="L165">
+        <v>0.22</v>
+      </c>
+      <c r="M165">
+        <v>0.1</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>5</v>
+      </c>
+      <c r="P165">
+        <v>6.36</v>
+      </c>
+      <c r="Q165">
+        <v>29.39</v>
+      </c>
+      <c r="R165">
+        <v>4.51</v>
+      </c>
+      <c r="S165">
+        <v>14</v>
+      </c>
+      <c r="T165">
+        <v>3</v>
+      </c>
+      <c r="U165">
+        <v>18</v>
+      </c>
+      <c r="V165">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>205</v>
+      </c>
+      <c r="B166" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="s">
+        <v>35</v>
+      </c>
+      <c r="F166" t="s">
+        <v>27</v>
+      </c>
+      <c r="G166" t="s">
+        <v>203</v>
+      </c>
+      <c r="H166">
+        <v>4.78</v>
+      </c>
+      <c r="I166">
+        <v>0.53</v>
+      </c>
+      <c r="J166">
+        <v>4.24</v>
+      </c>
+      <c r="K166">
+        <v>0.33</v>
+      </c>
+      <c r="L166">
+        <v>0.16</v>
+      </c>
+      <c r="M166">
+        <v>0.05</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>3</v>
+      </c>
+      <c r="P166">
+        <v>6.04</v>
+      </c>
+      <c r="Q166">
+        <v>29.66</v>
+      </c>
+      <c r="R166">
+        <v>4.51</v>
+      </c>
+      <c r="S166">
+        <v>18</v>
+      </c>
+      <c r="T166">
+        <v>5</v>
+      </c>
+      <c r="U166">
+        <v>9</v>
+      </c>
+      <c r="V166">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>205</v>
+      </c>
+      <c r="B167" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C167" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" t="s">
+        <v>86</v>
+      </c>
+      <c r="F167" t="s">
+        <v>27</v>
+      </c>
+      <c r="G167" t="s">
+        <v>191</v>
+      </c>
+      <c r="H167">
+        <v>5.25</v>
+      </c>
+      <c r="I167">
+        <v>0.87</v>
+      </c>
+      <c r="J167">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="K167">
+        <v>0.67</v>
+      </c>
+      <c r="L167">
+        <v>0.19</v>
+      </c>
+      <c r="M167">
+        <v>0.03</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>2</v>
+      </c>
+      <c r="P167">
+        <v>6.67</v>
+      </c>
+      <c r="Q167">
+        <v>27.71</v>
+      </c>
+      <c r="R167">
+        <v>4.59</v>
+      </c>
+      <c r="S167">
+        <v>28</v>
+      </c>
+      <c r="T167">
+        <v>5</v>
+      </c>
+      <c r="U167">
+        <v>26</v>
+      </c>
+      <c r="V167">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>205</v>
+      </c>
+      <c r="B168" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C168" t="s">
+        <v>19</v>
+      </c>
+      <c r="E168" t="s">
+        <v>170</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G168" t="s">
+        <v>204</v>
+      </c>
+      <c r="H168">
+        <v>3.31</v>
+      </c>
+      <c r="I168">
+        <v>0.71</v>
+      </c>
+      <c r="J168">
+        <v>2.59</v>
+      </c>
+      <c r="K168">
+        <v>0.46</v>
+      </c>
+      <c r="L168">
+        <v>0.18</v>
+      </c>
+      <c r="M168">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N168">
+        <v>0.02</v>
+      </c>
+      <c r="O168">
+        <v>7</v>
+      </c>
+      <c r="P168">
+        <v>6.16</v>
+      </c>
+      <c r="Q168">
+        <v>32.56</v>
+      </c>
+      <c r="R168">
+        <v>4.3</v>
+      </c>
+      <c r="S168">
+        <v>21</v>
+      </c>
+      <c r="T168">
+        <v>3</v>
+      </c>
+      <c r="U168">
+        <v>11</v>
+      </c>
+      <c r="V168">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>22</v>
+      </c>
+      <c r="B169" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C169" t="s">
+        <v>19</v>
+      </c>
+      <c r="E169" t="s">
+        <v>166</v>
+      </c>
+      <c r="F169" t="s">
+        <v>101</v>
+      </c>
+      <c r="G169" t="s">
+        <v>207</v>
+      </c>
+      <c r="H169">
+        <v>6.44</v>
+      </c>
+      <c r="I169">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J169">
+        <v>6.36</v>
+      </c>
+      <c r="K169">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>3.85</v>
+      </c>
+      <c r="Q169">
+        <v>20.45</v>
+      </c>
+      <c r="R169">
+        <v>5.01</v>
+      </c>
+      <c r="S169">
+        <v>34</v>
+      </c>
+      <c r="T169">
+        <v>5</v>
+      </c>
+      <c r="U169">
+        <v>26</v>
+      </c>
+      <c r="V169">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>22</v>
+      </c>
+      <c r="B170" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C170" t="s">
+        <v>19</v>
+      </c>
+      <c r="E170" t="s">
+        <v>38</v>
+      </c>
+      <c r="F170" t="s">
+        <v>27</v>
+      </c>
+      <c r="G170" t="s">
+        <v>208</v>
+      </c>
+      <c r="H170">
+        <v>6.65</v>
+      </c>
+      <c r="I170">
+        <v>0.12</v>
+      </c>
+      <c r="J170">
+        <v>6.52</v>
+      </c>
+      <c r="K170">
+        <v>0.12</v>
+      </c>
+      <c r="L170">
+        <v>0.01</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>3.89</v>
+      </c>
+      <c r="Q170">
+        <v>22.2</v>
+      </c>
+      <c r="R170">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="S170">
+        <v>54</v>
+      </c>
+      <c r="T170">
+        <v>10</v>
+      </c>
+      <c r="U170">
+        <v>52</v>
+      </c>
+      <c r="V170">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>22</v>
+      </c>
+      <c r="B171" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C171" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" t="s">
+        <v>35</v>
+      </c>
+      <c r="F171" t="s">
+        <v>27</v>
+      </c>
+      <c r="G171" t="s">
+        <v>209</v>
+      </c>
+      <c r="H171">
+        <v>5.67</v>
+      </c>
+      <c r="I171">
+        <v>0.12</v>
+      </c>
+      <c r="J171">
+        <v>5.55</v>
+      </c>
+      <c r="K171">
+        <v>0.12</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>3.7</v>
+      </c>
+      <c r="Q171">
+        <v>18.32</v>
+      </c>
+      <c r="R171">
+        <v>4.21</v>
+      </c>
+      <c r="S171">
+        <v>23</v>
+      </c>
+      <c r="T171">
+        <v>1</v>
+      </c>
+      <c r="U171">
+        <v>5</v>
+      </c>
+      <c r="V171">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>22</v>
+      </c>
+      <c r="B172" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C172" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" t="s">
+        <v>170</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G172" t="s">
+        <v>210</v>
+      </c>
+      <c r="H172">
+        <v>5.78</v>
+      </c>
+      <c r="I172">
+        <v>0.18</v>
+      </c>
+      <c r="J172">
+        <v>5.6</v>
+      </c>
+      <c r="K172">
+        <v>0.17</v>
+      </c>
+      <c r="L172">
+        <v>0.01</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>3.7</v>
+      </c>
+      <c r="Q172">
+        <v>21.53</v>
+      </c>
+      <c r="R172">
+        <v>4.55</v>
+      </c>
+      <c r="S172">
+        <v>29</v>
+      </c>
+      <c r="T172">
+        <v>4</v>
+      </c>
+      <c r="U172">
+        <v>22</v>
+      </c>
+      <c r="V172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C173" t="s">
+        <v>19</v>
+      </c>
+      <c r="E173" t="s">
+        <v>184</v>
+      </c>
+      <c r="F173" t="s">
+        <v>24</v>
+      </c>
+      <c r="G173" t="s">
+        <v>211</v>
+      </c>
+      <c r="H173">
+        <v>5.57</v>
+      </c>
+      <c r="I173">
+        <v>0.09</v>
+      </c>
+      <c r="J173">
+        <v>5.48</v>
+      </c>
+      <c r="K173">
+        <v>0.09</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>3.63</v>
+      </c>
+      <c r="Q173">
+        <v>20.82</v>
+      </c>
+      <c r="R173">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="S173">
+        <v>13</v>
+      </c>
+      <c r="T173">
+        <v>3</v>
+      </c>
+      <c r="U173">
+        <v>14</v>
+      </c>
+      <c r="V173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>22</v>
+      </c>
+      <c r="B174" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C174" t="s">
+        <v>19</v>
+      </c>
+      <c r="E174" t="s">
+        <v>170</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G174" t="s">
+        <v>212</v>
+      </c>
+      <c r="H174">
+        <v>4.95</v>
+      </c>
+      <c r="I174">
+        <v>1.23</v>
+      </c>
+      <c r="J174">
+        <v>3.72</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>0.23</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>3.07</v>
+      </c>
+      <c r="Q174">
+        <v>23.82</v>
+      </c>
+      <c r="R174">
+        <v>4.49</v>
+      </c>
+      <c r="S174">
+        <v>28</v>
+      </c>
+      <c r="T174">
+        <v>1</v>
+      </c>
+      <c r="U174">
+        <v>10</v>
+      </c>
+      <c r="V174">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>22</v>
+      </c>
+      <c r="B175" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C175" t="s">
+        <v>19</v>
+      </c>
+      <c r="E175" t="s">
+        <v>184</v>
+      </c>
+      <c r="F175" t="s">
+        <v>24</v>
+      </c>
+      <c r="G175" t="s">
+        <v>213</v>
+      </c>
+      <c r="H175">
+        <v>5.64</v>
+      </c>
+      <c r="I175">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J175">
+        <v>4.51</v>
+      </c>
+      <c r="K175">
+        <v>1.05</v>
+      </c>
+      <c r="L175">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M175">
+        <v>0.01</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175">
+        <v>1</v>
+      </c>
+      <c r="P175">
+        <v>3.56</v>
+      </c>
+      <c r="Q175">
+        <v>25.81</v>
+      </c>
+      <c r="R175">
+        <v>3.95</v>
+      </c>
+      <c r="S175">
+        <v>13</v>
+      </c>
+      <c r="T175">
+        <v>0</v>
+      </c>
+      <c r="U175">
+        <v>8</v>
+      </c>
+      <c r="V175">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>22</v>
+      </c>
+      <c r="B176" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C176" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176" t="s">
+        <v>38</v>
+      </c>
+      <c r="F176" t="s">
+        <v>27</v>
+      </c>
+      <c r="G176" t="s">
+        <v>214</v>
+      </c>
+      <c r="H176">
+        <v>6.52</v>
+      </c>
+      <c r="I176">
+        <v>1.52</v>
+      </c>
+      <c r="J176">
+        <v>4.99</v>
+      </c>
+      <c r="K176">
+        <v>0.66</v>
+      </c>
+      <c r="L176">
+        <v>0.87</v>
+      </c>
+      <c r="M176">
+        <v>0.01</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176">
+        <v>2</v>
+      </c>
+      <c r="P176">
+        <v>3.76</v>
+      </c>
+      <c r="Q176">
+        <v>25.42</v>
+      </c>
+      <c r="R176">
+        <v>4.53</v>
+      </c>
+      <c r="S176">
+        <v>17</v>
+      </c>
+      <c r="T176">
+        <v>10</v>
+      </c>
+      <c r="U176">
+        <v>21</v>
+      </c>
+      <c r="V176">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>22</v>
+      </c>
+      <c r="B177" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C177" t="s">
+        <v>19</v>
+      </c>
+      <c r="E177" t="s">
+        <v>32</v>
+      </c>
+      <c r="F177" t="s">
+        <v>27</v>
+      </c>
+      <c r="G177" t="s">
+        <v>215</v>
+      </c>
+      <c r="H177">
+        <v>6.35</v>
+      </c>
+      <c r="I177">
+        <v>1.5</v>
+      </c>
+      <c r="J177">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="K177">
+        <v>0.69</v>
+      </c>
+      <c r="L177">
+        <v>0.81</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <v>3.77</v>
+      </c>
+      <c r="Q177">
+        <v>23.32</v>
+      </c>
+      <c r="R177">
+        <v>4.76</v>
+      </c>
+      <c r="S177">
+        <v>20</v>
+      </c>
+      <c r="T177">
+        <v>2</v>
+      </c>
+      <c r="U177">
+        <v>7</v>
+      </c>
+      <c r="V177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>22</v>
+      </c>
+      <c r="B178" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C178" t="s">
+        <v>19</v>
+      </c>
+      <c r="E178" t="s">
+        <v>43</v>
+      </c>
+      <c r="F178" t="s">
+        <v>24</v>
+      </c>
+      <c r="G178" t="s">
+        <v>216</v>
+      </c>
+      <c r="H178">
+        <v>6.06</v>
+      </c>
+      <c r="I178">
+        <v>1.4</v>
+      </c>
+      <c r="J178">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K178">
+        <v>0.61</v>
+      </c>
+      <c r="L178">
+        <v>0.79</v>
+      </c>
+      <c r="M178">
+        <v>0.01</v>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
+      <c r="P178">
+        <v>3.38</v>
+      </c>
+      <c r="Q178">
+        <v>26.45</v>
+      </c>
+      <c r="R178">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S178">
+        <v>19</v>
+      </c>
+      <c r="T178">
+        <v>2</v>
+      </c>
+      <c r="U178">
+        <v>13</v>
+      </c>
+      <c r="V178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="s">
+        <v>31</v>
+      </c>
+      <c r="F179" t="s">
+        <v>28</v>
+      </c>
+      <c r="G179" t="s">
+        <v>217</v>
+      </c>
+      <c r="H179">
+        <v>6.28</v>
+      </c>
+      <c r="I179">
+        <v>1.07</v>
+      </c>
+      <c r="J179">
+        <v>5.2</v>
+      </c>
+      <c r="K179">
+        <v>0.63</v>
+      </c>
+      <c r="L179">
+        <v>0.45</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>1</v>
+      </c>
+      <c r="P179">
+        <v>3.61</v>
+      </c>
+      <c r="Q179">
+        <v>25.02</v>
+      </c>
+      <c r="R179">
+        <v>3.92</v>
+      </c>
+      <c r="S179">
+        <v>22</v>
+      </c>
+      <c r="T179">
+        <v>0</v>
+      </c>
+      <c r="U179">
+        <v>10</v>
+      </c>
+      <c r="V179">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>22</v>
+      </c>
+      <c r="B180" s="1">
+        <v>46234</v>
+      </c>
+      <c r="C180" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" t="s">
+        <v>35</v>
+      </c>
+      <c r="F180" t="s">
+        <v>27</v>
+      </c>
+      <c r="G180" t="s">
+        <v>218</v>
+      </c>
+      <c r="H180">
+        <v>2.89</v>
+      </c>
+      <c r="I180">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J180">
+        <v>1.74</v>
+      </c>
+      <c r="K180">
+        <v>0.5</v>
+      </c>
+      <c r="L180">
+        <v>0.64</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180">
+        <v>0</v>
+      </c>
+      <c r="P180">
+        <v>3.31</v>
+      </c>
+      <c r="Q180">
+        <v>23.96</v>
+      </c>
+      <c r="R180">
+        <v>3.89</v>
+      </c>
+      <c r="S180">
+        <v>12</v>
+      </c>
+      <c r="T180">
+        <v>0</v>
+      </c>
+      <c r="U180">
+        <v>5</v>
+      </c>
+      <c r="V180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>228</v>
+      </c>
+      <c r="B181" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C181" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" t="s">
+        <v>82</v>
+      </c>
+      <c r="F181" t="s">
+        <v>27</v>
+      </c>
+      <c r="G181" t="s">
+        <v>219</v>
+      </c>
+      <c r="H181">
+        <v>7.61</v>
+      </c>
+      <c r="I181">
+        <v>1.57</v>
+      </c>
+      <c r="J181">
+        <v>6.03</v>
+      </c>
+      <c r="K181">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="L181">
+        <v>0.39</v>
+      </c>
+      <c r="M181">
+        <v>0.08</v>
+      </c>
+      <c r="N181">
+        <v>0</v>
+      </c>
+      <c r="O181">
+        <v>9</v>
+      </c>
+      <c r="P181">
+        <v>6.7</v>
+      </c>
+      <c r="Q181">
+        <v>27.66</v>
+      </c>
+      <c r="R181">
+        <v>4.49</v>
+      </c>
+      <c r="S181">
+        <v>37</v>
+      </c>
+      <c r="T181">
+        <v>6</v>
+      </c>
+      <c r="U181">
+        <v>33</v>
+      </c>
+      <c r="V181">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>228</v>
+      </c>
+      <c r="B182" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C182" t="s">
+        <v>19</v>
+      </c>
+      <c r="E182" t="s">
+        <v>166</v>
+      </c>
+      <c r="F182" t="s">
+        <v>101</v>
+      </c>
+      <c r="G182" t="s">
+        <v>219</v>
+      </c>
+      <c r="H182">
+        <v>7.74</v>
+      </c>
+      <c r="I182">
+        <v>1.45</v>
+      </c>
+      <c r="J182">
+        <v>6.27</v>
+      </c>
+      <c r="K182">
+        <v>0.96</v>
+      </c>
+      <c r="L182">
+        <v>0.42</v>
+      </c>
+      <c r="M182">
+        <v>0.09</v>
+      </c>
+      <c r="N182">
+        <v>0.01</v>
+      </c>
+      <c r="O182">
+        <v>7</v>
+      </c>
+      <c r="P182">
+        <v>6.8</v>
+      </c>
+      <c r="Q182">
+        <v>30.96</v>
+      </c>
+      <c r="R182">
+        <v>4.62</v>
+      </c>
+      <c r="S182">
+        <v>30</v>
+      </c>
+      <c r="T182">
+        <v>4</v>
+      </c>
+      <c r="U182">
+        <v>22</v>
+      </c>
+      <c r="V182">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>228</v>
+      </c>
+      <c r="B183" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C183" t="s">
+        <v>19</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G183" t="s">
+        <v>221</v>
+      </c>
+      <c r="H183">
+        <v>6.78</v>
+      </c>
+      <c r="I183">
+        <v>0.94</v>
+      </c>
+      <c r="J183">
+        <v>5.83</v>
+      </c>
+      <c r="K183">
+        <v>0.64</v>
+      </c>
+      <c r="L183">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M183">
+        <v>0.03</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183">
+        <v>4</v>
+      </c>
+      <c r="P183">
+        <v>5.98</v>
+      </c>
+      <c r="Q183">
+        <v>25.93</v>
+      </c>
+      <c r="R183">
+        <v>4.03</v>
+      </c>
+      <c r="S183">
+        <v>21</v>
+      </c>
+      <c r="T183">
+        <v>3</v>
+      </c>
+      <c r="U183">
+        <v>22</v>
+      </c>
+      <c r="V183">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>228</v>
+      </c>
+      <c r="B184" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C184" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F184" t="s">
+        <v>27</v>
+      </c>
+      <c r="G184" t="s">
+        <v>222</v>
+      </c>
+      <c r="H184">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="I184">
+        <v>1.47</v>
+      </c>
+      <c r="J184">
+        <v>6.89</v>
+      </c>
+      <c r="K184">
+        <v>1.29</v>
+      </c>
+      <c r="L184">
+        <v>0.2</v>
+      </c>
+      <c r="M184">
+        <v>0.01</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>1</v>
+      </c>
+      <c r="P184">
+        <v>7.22</v>
+      </c>
+      <c r="Q184">
+        <v>25.19</v>
+      </c>
+      <c r="R184">
+        <v>5.32</v>
+      </c>
+      <c r="S184">
+        <v>15</v>
+      </c>
+      <c r="T184">
+        <v>1</v>
+      </c>
+      <c r="U184">
+        <v>27</v>
+      </c>
+      <c r="V184">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>228</v>
+      </c>
+      <c r="B185" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C185" t="s">
+        <v>19</v>
+      </c>
+      <c r="E185" t="s">
+        <v>163</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G185" t="s">
+        <v>223</v>
+      </c>
+      <c r="H185">
+        <v>7.26</v>
+      </c>
+      <c r="I185">
+        <v>1.17</v>
+      </c>
+      <c r="J185">
+        <v>6.07</v>
+      </c>
+      <c r="K185">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L185">
+        <v>0.39</v>
+      </c>
+      <c r="M185">
+        <v>0.18</v>
+      </c>
+      <c r="N185">
+        <v>0.04</v>
+      </c>
+      <c r="O185">
+        <v>16</v>
+      </c>
+      <c r="P185">
+        <v>6.05</v>
+      </c>
+      <c r="Q185">
+        <v>31.96</v>
+      </c>
+      <c r="R185">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S185">
+        <v>39</v>
+      </c>
+      <c r="T185">
+        <v>9</v>
+      </c>
+      <c r="U185">
+        <v>31</v>
+      </c>
+      <c r="V185">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>228</v>
+      </c>
+      <c r="B186" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C186" t="s">
+        <v>19</v>
+      </c>
+      <c r="E186" t="s">
+        <v>32</v>
+      </c>
+      <c r="F186" t="s">
+        <v>27</v>
+      </c>
+      <c r="G186" t="s">
+        <v>224</v>
+      </c>
+      <c r="H186">
+        <v>8.41</v>
+      </c>
+      <c r="I186">
+        <v>1.44</v>
+      </c>
+      <c r="J186">
+        <v>6.95</v>
+      </c>
+      <c r="K186">
+        <v>1.18</v>
+      </c>
+      <c r="L186">
+        <v>0.21</v>
+      </c>
+      <c r="M186">
+        <v>0.06</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>4</v>
+      </c>
+      <c r="P186">
+        <v>7.38</v>
+      </c>
+      <c r="Q186">
+        <v>28.01</v>
+      </c>
+      <c r="R186">
+        <v>4.33</v>
+      </c>
+      <c r="S186">
+        <v>31</v>
+      </c>
+      <c r="T186">
+        <v>2</v>
+      </c>
+      <c r="U186">
+        <v>27</v>
+      </c>
+      <c r="V186">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>228</v>
+      </c>
+      <c r="B187" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C187" t="s">
+        <v>19</v>
+      </c>
+      <c r="E187" t="s">
+        <v>31</v>
+      </c>
+      <c r="F187" t="s">
+        <v>28</v>
+      </c>
+      <c r="G187" t="s">
+        <v>225</v>
+      </c>
+      <c r="H187">
+        <v>7.13</v>
+      </c>
+      <c r="I187">
+        <v>1.02</v>
+      </c>
+      <c r="J187">
+        <v>6.09</v>
+      </c>
+      <c r="K187">
+        <v>0.64</v>
+      </c>
+      <c r="L187">
+        <v>0.33</v>
+      </c>
+      <c r="M187">
+        <v>0.06</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187">
+        <v>6</v>
+      </c>
+      <c r="P187">
+        <v>6.11</v>
+      </c>
+      <c r="Q187">
+        <v>28.96</v>
+      </c>
+      <c r="R187">
+        <v>4.22</v>
+      </c>
+      <c r="S187">
+        <v>17</v>
+      </c>
+      <c r="T187">
+        <v>2</v>
+      </c>
+      <c r="U187">
+        <v>21</v>
+      </c>
+      <c r="V187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>228</v>
+      </c>
+      <c r="B188" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C188" t="s">
+        <v>19</v>
+      </c>
+      <c r="E188" t="s">
+        <v>184</v>
+      </c>
+      <c r="F188" t="s">
+        <v>24</v>
+      </c>
+      <c r="G188" t="s">
+        <v>226</v>
+      </c>
+      <c r="H188">
+        <v>7</v>
+      </c>
+      <c r="I188">
+        <v>0.98</v>
+      </c>
+      <c r="J188">
+        <v>6</v>
+      </c>
+      <c r="K188">
+        <v>0.71</v>
+      </c>
+      <c r="L188">
+        <v>0.24</v>
+      </c>
+      <c r="M188">
+        <v>0.05</v>
+      </c>
+      <c r="N188">
+        <v>0.01</v>
+      </c>
+      <c r="O188">
+        <v>3</v>
+      </c>
+      <c r="P188">
+        <v>6.01</v>
+      </c>
+      <c r="Q188">
+        <v>30.59</v>
+      </c>
+      <c r="R188">
+        <v>4.59</v>
+      </c>
+      <c r="S188">
+        <v>25</v>
+      </c>
+      <c r="T188">
+        <v>5</v>
+      </c>
+      <c r="U188">
+        <v>20</v>
+      </c>
+      <c r="V188">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>228</v>
+      </c>
+      <c r="B189" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C189" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189" t="s">
+        <v>43</v>
+      </c>
+      <c r="F189" t="s">
+        <v>24</v>
+      </c>
+      <c r="G189" t="s">
+        <v>227</v>
+      </c>
+      <c r="H189">
+        <v>7.53</v>
+      </c>
+      <c r="I189">
+        <v>0.98</v>
+      </c>
+      <c r="J189">
+        <v>6.54</v>
+      </c>
+      <c r="K189">
+        <v>0.6</v>
+      </c>
+      <c r="L189">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M189">
+        <v>0.11</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189">
+        <v>9</v>
+      </c>
+      <c r="P189">
+        <v>6.04</v>
+      </c>
+      <c r="Q189">
+        <v>29.31</v>
+      </c>
+      <c r="R189">
+        <v>4.66</v>
+      </c>
+      <c r="S189">
+        <v>17</v>
+      </c>
+      <c r="T189">
+        <v>4</v>
+      </c>
+      <c r="U189">
+        <v>24</v>
+      </c>
+      <c r="V189">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>22</v>
+      </c>
+      <c r="B190" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C190" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" t="s">
+        <v>84</v>
+      </c>
+      <c r="F190" t="s">
+        <v>24</v>
+      </c>
+      <c r="G190" t="s">
+        <v>229</v>
+      </c>
+      <c r="H190">
+        <v>5.12</v>
+      </c>
+      <c r="I190">
+        <v>0.91</v>
+      </c>
+      <c r="J190">
+        <v>4.2</v>
+      </c>
+      <c r="K190">
+        <v>0.6</v>
+      </c>
+      <c r="L190">
+        <v>0.32</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>0</v>
+      </c>
+      <c r="O190">
+        <v>0</v>
+      </c>
+      <c r="P190">
+        <v>4.67</v>
+      </c>
+      <c r="Q190">
+        <v>24.29</v>
+      </c>
+      <c r="R190">
+        <v>4.29</v>
+      </c>
+      <c r="S190">
+        <v>20</v>
+      </c>
+      <c r="T190">
+        <v>2</v>
+      </c>
+      <c r="U190">
+        <v>10</v>
+      </c>
+      <c r="V190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>22</v>
+      </c>
+      <c r="B191" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C191" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" t="s">
+        <v>98</v>
+      </c>
+      <c r="F191" t="s">
+        <v>27</v>
+      </c>
+      <c r="G191" t="s">
+        <v>230</v>
+      </c>
+      <c r="H191">
+        <v>6.06</v>
+      </c>
+      <c r="I191">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J191">
+        <v>4.95</v>
+      </c>
+      <c r="K191">
+        <v>0.43</v>
+      </c>
+      <c r="L191">
+        <v>0.67</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>0</v>
+      </c>
+      <c r="O191">
+        <v>0</v>
+      </c>
+      <c r="P191">
+        <v>4.99</v>
+      </c>
+      <c r="Q191">
+        <v>23.66</v>
+      </c>
+      <c r="R191">
+        <v>4.28</v>
+      </c>
+      <c r="S191">
+        <v>25</v>
+      </c>
+      <c r="T191">
+        <v>6</v>
+      </c>
+      <c r="U191">
+        <v>17</v>
+      </c>
+      <c r="V191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>22</v>
+      </c>
+      <c r="B192" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" t="s">
+        <v>82</v>
+      </c>
+      <c r="F192" t="s">
+        <v>27</v>
+      </c>
+      <c r="G192" t="s">
+        <v>231</v>
+      </c>
+      <c r="H192">
+        <v>6</v>
+      </c>
+      <c r="I192">
+        <v>0.68</v>
+      </c>
+      <c r="J192">
+        <v>5.32</v>
+      </c>
+      <c r="K192">
+        <v>0.45</v>
+      </c>
+      <c r="L192">
+        <v>0.23</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>0</v>
+      </c>
+      <c r="O192">
+        <v>0</v>
+      </c>
+      <c r="P192">
+        <v>4.75</v>
+      </c>
+      <c r="Q192">
+        <v>23.87</v>
+      </c>
+      <c r="R192">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="S192">
+        <v>23</v>
+      </c>
+      <c r="T192">
+        <v>1</v>
+      </c>
+      <c r="U192">
+        <v>17</v>
+      </c>
+      <c r="V192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>22</v>
+      </c>
+      <c r="B193" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C193" t="s">
+        <v>19</v>
+      </c>
+      <c r="E193" t="s">
+        <v>99</v>
+      </c>
+      <c r="F193" t="s">
+        <v>27</v>
+      </c>
+      <c r="G193" t="s">
+        <v>232</v>
+      </c>
+      <c r="H193">
+        <v>6</v>
+      </c>
+      <c r="I193">
+        <v>1.03</v>
+      </c>
+      <c r="J193">
+        <v>4.97</v>
+      </c>
+      <c r="K193">
+        <v>0.46</v>
+      </c>
+      <c r="L193">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193">
+        <v>0</v>
+      </c>
+      <c r="P193">
+        <v>4.91</v>
+      </c>
+      <c r="Q193">
+        <v>24.41</v>
+      </c>
+      <c r="R193">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="S193">
+        <v>30</v>
+      </c>
+      <c r="T193">
+        <v>4</v>
+      </c>
+      <c r="U193">
+        <v>11</v>
+      </c>
+      <c r="V193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>22</v>
+      </c>
+      <c r="B194" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C194" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" t="s">
+        <v>97</v>
+      </c>
+      <c r="F194" t="s">
+        <v>101</v>
+      </c>
+      <c r="G194" t="s">
+        <v>233</v>
+      </c>
+      <c r="H194">
+        <v>5.23</v>
+      </c>
+      <c r="I194">
+        <v>0.53</v>
+      </c>
+      <c r="J194">
+        <v>4.7</v>
+      </c>
+      <c r="K194">
+        <v>0.52</v>
+      </c>
+      <c r="L194">
+        <v>0.02</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+      <c r="P194">
+        <v>4.26</v>
+      </c>
+      <c r="Q194">
+        <v>22.82</v>
+      </c>
+      <c r="R194">
+        <v>5.03</v>
+      </c>
+      <c r="S194">
+        <v>27</v>
+      </c>
+      <c r="T194">
+        <v>7</v>
+      </c>
+      <c r="U194">
+        <v>21</v>
+      </c>
+      <c r="V194">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>22</v>
+      </c>
+      <c r="B195" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C195" t="s">
+        <v>19</v>
+      </c>
+      <c r="E195" t="s">
+        <v>36</v>
+      </c>
+      <c r="F195" t="s">
+        <v>26</v>
+      </c>
+      <c r="G195" t="s">
+        <v>234</v>
+      </c>
+      <c r="H195">
+        <v>5.68</v>
+      </c>
+      <c r="I195">
+        <v>0.97</v>
+      </c>
+      <c r="J195">
+        <v>4.7</v>
+      </c>
+      <c r="K195">
+        <v>0.42</v>
+      </c>
+      <c r="L195">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195">
+        <v>0</v>
+      </c>
+      <c r="P195">
+        <v>4.49</v>
+      </c>
+      <c r="Q195">
+        <v>23.59</v>
+      </c>
+      <c r="R195">
+        <v>4.24</v>
+      </c>
+      <c r="S195">
+        <v>18</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+      <c r="U195">
+        <v>12</v>
+      </c>
+      <c r="V195">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>22</v>
+      </c>
+      <c r="B196" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="s">
+        <v>87</v>
+      </c>
+      <c r="F196" t="s">
+        <v>27</v>
+      </c>
+      <c r="G196" t="s">
+        <v>235</v>
+      </c>
+      <c r="H196">
+        <v>6.13</v>
+      </c>
+      <c r="I196">
+        <v>1.05</v>
+      </c>
+      <c r="J196">
+        <v>5.08</v>
+      </c>
+      <c r="K196">
+        <v>0.75</v>
+      </c>
+      <c r="L196">
+        <v>0.3</v>
+      </c>
+      <c r="M196">
+        <v>0.01</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196">
+        <v>3</v>
+      </c>
+      <c r="P196">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="Q196">
+        <v>25.34</v>
+      </c>
+      <c r="R196">
+        <v>4.95</v>
+      </c>
+      <c r="S196">
+        <v>32</v>
+      </c>
+      <c r="T196">
+        <v>7</v>
+      </c>
+      <c r="U196">
+        <v>16</v>
+      </c>
+      <c r="V196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>22</v>
+      </c>
+      <c r="B197" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C197" t="s">
+        <v>19</v>
+      </c>
+      <c r="E197" t="s">
+        <v>86</v>
+      </c>
+      <c r="F197" t="s">
+        <v>27</v>
+      </c>
+      <c r="G197" t="s">
+        <v>236</v>
+      </c>
+      <c r="H197">
+        <v>5.09</v>
+      </c>
+      <c r="I197">
+        <v>0.4</v>
+      </c>
+      <c r="J197">
+        <v>4.68</v>
+      </c>
+      <c r="K197">
+        <v>0.34</v>
+      </c>
+      <c r="L197">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197">
+        <v>0</v>
+      </c>
+      <c r="P197">
+        <v>4</v>
+      </c>
+      <c r="Q197">
+        <v>23.86</v>
+      </c>
+      <c r="R197">
+        <v>5.31</v>
+      </c>
+      <c r="S197">
+        <v>51</v>
+      </c>
+      <c r="T197">
+        <v>11</v>
+      </c>
+      <c r="U197">
+        <v>45</v>
+      </c>
+      <c r="V197">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>22</v>
+      </c>
+      <c r="B198" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="s">
+        <v>94</v>
+      </c>
+      <c r="F198" t="s">
+        <v>103</v>
+      </c>
+      <c r="G198" t="s">
+        <v>237</v>
+      </c>
+      <c r="H198">
+        <v>5.23</v>
+      </c>
+      <c r="I198">
+        <v>0.9</v>
+      </c>
+      <c r="J198">
+        <v>4.32</v>
+      </c>
+      <c r="K198">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L198">
+        <v>0.33</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <v>0</v>
+      </c>
+      <c r="P198">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="Q198">
+        <v>23.24</v>
+      </c>
+      <c r="R198">
+        <v>4.47</v>
+      </c>
+      <c r="S198">
+        <v>22</v>
+      </c>
+      <c r="T198">
+        <v>6</v>
+      </c>
+      <c r="U198">
+        <v>20</v>
+      </c>
+      <c r="V198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>22</v>
+      </c>
+      <c r="B199" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="s">
+        <v>46</v>
+      </c>
+      <c r="F199" t="s">
+        <v>24</v>
+      </c>
+      <c r="G199" t="s">
+        <v>238</v>
+      </c>
+      <c r="H199">
+        <v>5.59</v>
+      </c>
+      <c r="I199">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="J199">
+        <v>4.47</v>
+      </c>
+      <c r="K199">
+        <v>0.49</v>
+      </c>
+      <c r="L199">
+        <v>0.62</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199">
+        <v>0</v>
+      </c>
+      <c r="P199">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="Q199">
+        <v>23.33</v>
+      </c>
+      <c r="R199">
+        <v>4.34</v>
+      </c>
+      <c r="S199">
+        <v>26</v>
+      </c>
+      <c r="T199">
+        <v>7</v>
+      </c>
+      <c r="U199">
+        <v>22</v>
+      </c>
+      <c r="V199">
         <v>3</v>
       </c>
     </row>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6411D6FE-3E1C-3F4C-A7C7-BF2FAAD9C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4056AF7C-DC6C-684E-AB41-144654C3DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="248">
   <si>
     <t>Temps joué</t>
   </si>
@@ -752,6 +752,33 @@
   </si>
   <si>
     <t>01:13:48</t>
+  </si>
+  <si>
+    <t>01:13:41</t>
+  </si>
+  <si>
+    <t>01:16:47</t>
+  </si>
+  <si>
+    <t>01:19:55</t>
+  </si>
+  <si>
+    <t>01:06:46</t>
+  </si>
+  <si>
+    <t>01:08:13</t>
+  </si>
+  <si>
+    <t>01:18:42</t>
+  </si>
+  <si>
+    <t>01:13:28</t>
+  </si>
+  <si>
+    <t>01:02:31</t>
+  </si>
+  <si>
+    <t>01:10:59</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V199"/>
+  <dimension ref="A1:V209"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -14073,6 +14100,656 @@
         <v>3</v>
       </c>
     </row>
+    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>22</v>
+      </c>
+      <c r="B200" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C200" t="s">
+        <v>19</v>
+      </c>
+      <c r="E200" t="s">
+        <v>97</v>
+      </c>
+      <c r="F200" t="s">
+        <v>101</v>
+      </c>
+      <c r="G200" t="s">
+        <v>239</v>
+      </c>
+      <c r="H200">
+        <v>3.67</v>
+      </c>
+      <c r="I200">
+        <v>0.41</v>
+      </c>
+      <c r="J200">
+        <v>3.25</v>
+      </c>
+      <c r="K200">
+        <v>0.3</v>
+      </c>
+      <c r="L200">
+        <v>0.11</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+      <c r="P200">
+        <v>2.87</v>
+      </c>
+      <c r="Q200">
+        <v>24.01</v>
+      </c>
+      <c r="R200">
+        <v>4.68</v>
+      </c>
+      <c r="S200">
+        <v>21</v>
+      </c>
+      <c r="T200">
+        <v>8</v>
+      </c>
+      <c r="U200">
+        <v>12</v>
+      </c>
+      <c r="V200">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>22</v>
+      </c>
+      <c r="B201" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C201" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" t="s">
+        <v>36</v>
+      </c>
+      <c r="F201" t="s">
+        <v>26</v>
+      </c>
+      <c r="G201" t="s">
+        <v>240</v>
+      </c>
+      <c r="H201">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="I201">
+        <v>0.27</v>
+      </c>
+      <c r="J201">
+        <v>4.58</v>
+      </c>
+      <c r="K201">
+        <v>0.23</v>
+      </c>
+      <c r="L201">
+        <v>0.05</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201">
+        <v>0</v>
+      </c>
+      <c r="P201">
+        <v>3.6</v>
+      </c>
+      <c r="Q201">
+        <v>22.31</v>
+      </c>
+      <c r="R201">
+        <v>5.03</v>
+      </c>
+      <c r="S201">
+        <v>18</v>
+      </c>
+      <c r="T201">
+        <v>15</v>
+      </c>
+      <c r="U201">
+        <v>15</v>
+      </c>
+      <c r="V201">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>22</v>
+      </c>
+      <c r="B202" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C202" t="s">
+        <v>19</v>
+      </c>
+      <c r="E202" t="s">
+        <v>46</v>
+      </c>
+      <c r="F202" t="s">
+        <v>24</v>
+      </c>
+      <c r="G202" t="s">
+        <v>241</v>
+      </c>
+      <c r="H202">
+        <v>3.74</v>
+      </c>
+      <c r="I202">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J202">
+        <v>3.66</v>
+      </c>
+      <c r="K202">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L202">
+        <v>0.01</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>0</v>
+      </c>
+      <c r="O202">
+        <v>0</v>
+      </c>
+      <c r="P202">
+        <v>2.72</v>
+      </c>
+      <c r="Q202">
+        <v>21.22</v>
+      </c>
+      <c r="R202">
+        <v>4.09</v>
+      </c>
+      <c r="S202">
+        <v>11</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>1</v>
+      </c>
+      <c r="V202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>22</v>
+      </c>
+      <c r="B203" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C203" t="s">
+        <v>19</v>
+      </c>
+      <c r="E203" t="s">
+        <v>86</v>
+      </c>
+      <c r="F203" t="s">
+        <v>27</v>
+      </c>
+      <c r="G203" t="s">
+        <v>242</v>
+      </c>
+      <c r="H203">
+        <v>4.03</v>
+      </c>
+      <c r="I203">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J203">
+        <v>3.95</v>
+      </c>
+      <c r="K203">
+        <v>0.05</v>
+      </c>
+      <c r="L203">
+        <v>0.03</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203">
+        <v>1</v>
+      </c>
+      <c r="P203">
+        <v>2.88</v>
+      </c>
+      <c r="Q203">
+        <v>25</v>
+      </c>
+      <c r="R203">
+        <v>4.75</v>
+      </c>
+      <c r="S203">
+        <v>20</v>
+      </c>
+      <c r="T203">
+        <v>3</v>
+      </c>
+      <c r="U203">
+        <v>18</v>
+      </c>
+      <c r="V203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>22</v>
+      </c>
+      <c r="B204" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C204" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" t="s">
+        <v>84</v>
+      </c>
+      <c r="F204" t="s">
+        <v>24</v>
+      </c>
+      <c r="G204" t="s">
+        <v>243</v>
+      </c>
+      <c r="H204">
+        <v>2.97</v>
+      </c>
+      <c r="I204">
+        <v>0.08</v>
+      </c>
+      <c r="J204">
+        <v>2.89</v>
+      </c>
+      <c r="K204">
+        <v>0.05</v>
+      </c>
+      <c r="L204">
+        <v>0.03</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204">
+        <v>0</v>
+      </c>
+      <c r="P204">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="Q204">
+        <v>21.85</v>
+      </c>
+      <c r="R204">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S204">
+        <v>2</v>
+      </c>
+      <c r="T204">
+        <v>4</v>
+      </c>
+      <c r="U204">
+        <v>1</v>
+      </c>
+      <c r="V204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>22</v>
+      </c>
+      <c r="B205" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C205" t="s">
+        <v>19</v>
+      </c>
+      <c r="E205" t="s">
+        <v>99</v>
+      </c>
+      <c r="F205" t="s">
+        <v>27</v>
+      </c>
+      <c r="G205" t="s">
+        <v>244</v>
+      </c>
+      <c r="H205">
+        <v>3.43</v>
+      </c>
+      <c r="I205">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J205">
+        <v>3.29</v>
+      </c>
+      <c r="K205">
+        <v>0.11</v>
+      </c>
+      <c r="L205">
+        <v>0.03</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205">
+        <v>0</v>
+      </c>
+      <c r="P205">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="Q205">
+        <v>22.15</v>
+      </c>
+      <c r="R205">
+        <v>4.25</v>
+      </c>
+      <c r="S205">
+        <v>8</v>
+      </c>
+      <c r="T205">
+        <v>4</v>
+      </c>
+      <c r="U205">
+        <v>5</v>
+      </c>
+      <c r="V205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>22</v>
+      </c>
+      <c r="B206" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C206" t="s">
+        <v>19</v>
+      </c>
+      <c r="E206" t="s">
+        <v>98</v>
+      </c>
+      <c r="F206" t="s">
+        <v>27</v>
+      </c>
+      <c r="G206" t="s">
+        <v>245</v>
+      </c>
+      <c r="H206">
+        <v>3.26</v>
+      </c>
+      <c r="I206">
+        <v>0.11</v>
+      </c>
+      <c r="J206">
+        <v>3.14</v>
+      </c>
+      <c r="K206">
+        <v>0.09</v>
+      </c>
+      <c r="L206">
+        <v>0.02</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>0</v>
+      </c>
+      <c r="O206">
+        <v>0</v>
+      </c>
+      <c r="P206">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="Q206">
+        <v>23.24</v>
+      </c>
+      <c r="R206">
+        <v>4.7</v>
+      </c>
+      <c r="S206">
+        <v>14</v>
+      </c>
+      <c r="T206">
+        <v>2</v>
+      </c>
+      <c r="U206">
+        <v>13</v>
+      </c>
+      <c r="V206">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>22</v>
+      </c>
+      <c r="B207" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C207" t="s">
+        <v>19</v>
+      </c>
+      <c r="E207" t="s">
+        <v>82</v>
+      </c>
+      <c r="F207" t="s">
+        <v>27</v>
+      </c>
+      <c r="G207" t="s">
+        <v>246</v>
+      </c>
+      <c r="H207">
+        <v>3.11</v>
+      </c>
+      <c r="I207">
+        <v>0.15</v>
+      </c>
+      <c r="J207">
+        <v>2.95</v>
+      </c>
+      <c r="K207">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L207">
+        <v>0.01</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>0</v>
+      </c>
+      <c r="O207">
+        <v>0</v>
+      </c>
+      <c r="P207">
+        <v>2.9</v>
+      </c>
+      <c r="Q207">
+        <v>20.62</v>
+      </c>
+      <c r="R207">
+        <v>4.13</v>
+      </c>
+      <c r="S207">
+        <v>11</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <v>3</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>22</v>
+      </c>
+      <c r="B208" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C208" t="s">
+        <v>19</v>
+      </c>
+      <c r="E208" t="s">
+        <v>94</v>
+      </c>
+      <c r="F208" t="s">
+        <v>103</v>
+      </c>
+      <c r="G208" t="s">
+        <v>247</v>
+      </c>
+      <c r="H208">
+        <v>3.36</v>
+      </c>
+      <c r="I208">
+        <v>0.16</v>
+      </c>
+      <c r="J208">
+        <v>3.2</v>
+      </c>
+      <c r="K208">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L208">
+        <v>0.02</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>0</v>
+      </c>
+      <c r="O208">
+        <v>0</v>
+      </c>
+      <c r="P208">
+        <v>2.71</v>
+      </c>
+      <c r="Q208">
+        <v>23.71</v>
+      </c>
+      <c r="R208">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S208">
+        <v>14</v>
+      </c>
+      <c r="T208">
+        <v>8</v>
+      </c>
+      <c r="U208">
+        <v>12</v>
+      </c>
+      <c r="V208">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>22</v>
+      </c>
+      <c r="B209" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C209" t="s">
+        <v>19</v>
+      </c>
+      <c r="E209" t="s">
+        <v>87</v>
+      </c>
+      <c r="F209" t="s">
+        <v>27</v>
+      </c>
+      <c r="G209" t="s">
+        <v>175</v>
+      </c>
+      <c r="H209">
+        <v>4.97</v>
+      </c>
+      <c r="I209">
+        <v>0.25</v>
+      </c>
+      <c r="J209">
+        <v>4.71</v>
+      </c>
+      <c r="K209">
+        <v>0.2</v>
+      </c>
+      <c r="L209">
+        <v>0.05</v>
+      </c>
+      <c r="M209">
+        <v>0.01</v>
+      </c>
+      <c r="N209">
+        <v>0</v>
+      </c>
+      <c r="O209">
+        <v>1</v>
+      </c>
+      <c r="P209">
+        <v>3.66</v>
+      </c>
+      <c r="Q209">
+        <v>26.05</v>
+      </c>
+      <c r="R209">
+        <v>4.72</v>
+      </c>
+      <c r="S209">
+        <v>12</v>
+      </c>
+      <c r="T209">
+        <v>9</v>
+      </c>
+      <c r="U209">
+        <v>8</v>
+      </c>
+      <c r="V209">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4056AF7C-DC6C-684E-AB41-144654C3DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E0CF84-8A9B-1545-8476-F9884A7F04A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="250">
   <si>
     <t>Temps joué</t>
   </si>
@@ -779,6 +779,12 @@
   </si>
   <si>
     <t>01:10:59</t>
+  </si>
+  <si>
+    <t>Séance 1</t>
+  </si>
+  <si>
+    <t>Séance 2</t>
   </si>
 </sst>
 </file>
@@ -4877,8 +4883,8 @@
       <c r="B58" s="1">
         <v>46224</v>
       </c>
-      <c r="C58" s="5">
-        <v>1</v>
+      <c r="C58" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E58" t="s">
         <v>91</v>
@@ -4942,8 +4948,8 @@
       <c r="B59" s="1">
         <v>46224</v>
       </c>
-      <c r="C59" s="5">
-        <v>1</v>
+      <c r="C59" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E59" t="s">
         <v>94</v>
@@ -5007,8 +5013,8 @@
       <c r="B60" s="1">
         <v>46224</v>
       </c>
-      <c r="C60" s="5">
-        <v>1</v>
+      <c r="C60" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E60" t="s">
         <v>87</v>
@@ -5072,8 +5078,8 @@
       <c r="B61" s="1">
         <v>46224</v>
       </c>
-      <c r="C61" s="5">
-        <v>1</v>
+      <c r="C61" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E61" t="s">
         <v>89</v>
@@ -5137,8 +5143,8 @@
       <c r="B62" s="1">
         <v>46224</v>
       </c>
-      <c r="C62" s="5">
-        <v>1</v>
+      <c r="C62" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E62" t="s">
         <v>86</v>
@@ -5202,8 +5208,8 @@
       <c r="B63" s="1">
         <v>46224</v>
       </c>
-      <c r="C63" s="5">
-        <v>1</v>
+      <c r="C63" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E63" t="s">
         <v>99</v>
@@ -5267,8 +5273,8 @@
       <c r="B64" s="1">
         <v>46224</v>
       </c>
-      <c r="C64" s="5">
-        <v>1</v>
+      <c r="C64" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E64" t="s">
         <v>82</v>
@@ -5332,8 +5338,8 @@
       <c r="B65" s="1">
         <v>46224</v>
       </c>
-      <c r="C65" s="5">
-        <v>1</v>
+      <c r="C65" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E65" t="s">
         <v>98</v>
@@ -5397,8 +5403,8 @@
       <c r="B66" s="1">
         <v>46224</v>
       </c>
-      <c r="C66" s="5">
-        <v>2</v>
+      <c r="C66" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E66" t="s">
         <v>82</v>
@@ -5462,8 +5468,8 @@
       <c r="B67" s="1">
         <v>46224</v>
       </c>
-      <c r="C67" s="5">
-        <v>2</v>
+      <c r="C67" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E67" t="s">
         <v>94</v>
@@ -5527,8 +5533,8 @@
       <c r="B68" s="1">
         <v>46224</v>
       </c>
-      <c r="C68" s="5">
-        <v>2</v>
+      <c r="C68" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E68" t="s">
         <v>87</v>
@@ -5592,8 +5598,8 @@
       <c r="B69" s="1">
         <v>46224</v>
       </c>
-      <c r="C69" s="5">
-        <v>2</v>
+      <c r="C69" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E69" t="s">
         <v>98</v>
@@ -5657,8 +5663,8 @@
       <c r="B70" s="1">
         <v>46224</v>
       </c>
-      <c r="C70" s="5">
-        <v>2</v>
+      <c r="C70" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E70" t="s">
         <v>91</v>
@@ -5722,8 +5728,8 @@
       <c r="B71" s="1">
         <v>46224</v>
       </c>
-      <c r="C71" s="5">
-        <v>2</v>
+      <c r="C71" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E71" t="s">
         <v>99</v>
@@ -5787,8 +5793,8 @@
       <c r="B72" s="1">
         <v>46224</v>
       </c>
-      <c r="C72" s="5">
-        <v>2</v>
+      <c r="C72" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E72" t="s">
         <v>89</v>
@@ -5852,8 +5858,8 @@
       <c r="B73" s="1">
         <v>46224</v>
       </c>
-      <c r="C73" s="5">
-        <v>2</v>
+      <c r="C73" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E73" t="s">
         <v>86</v>
@@ -5917,8 +5923,8 @@
       <c r="B74" s="1">
         <v>46225</v>
       </c>
-      <c r="C74" s="5">
-        <v>1</v>
+      <c r="C74" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E74" t="s">
         <v>99</v>
@@ -5982,8 +5988,8 @@
       <c r="B75" s="1">
         <v>46225</v>
       </c>
-      <c r="C75" s="5">
-        <v>1</v>
+      <c r="C75" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E75" t="s">
         <v>98</v>
@@ -6047,8 +6053,8 @@
       <c r="B76" s="1">
         <v>46225</v>
       </c>
-      <c r="C76" s="5">
-        <v>1</v>
+      <c r="C76" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E76" t="s">
         <v>97</v>
@@ -6112,8 +6118,8 @@
       <c r="B77" s="1">
         <v>46225</v>
       </c>
-      <c r="C77" s="5">
-        <v>1</v>
+      <c r="C77" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E77" t="s">
         <v>87</v>
@@ -6177,8 +6183,8 @@
       <c r="B78" s="1">
         <v>46225</v>
       </c>
-      <c r="C78" s="5">
-        <v>1</v>
+      <c r="C78" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E78" t="s">
         <v>89</v>
@@ -6242,8 +6248,8 @@
       <c r="B79" s="1">
         <v>46225</v>
       </c>
-      <c r="C79" s="5">
-        <v>1</v>
+      <c r="C79" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E79" t="s">
         <v>94</v>
@@ -6307,8 +6313,8 @@
       <c r="B80" s="1">
         <v>46225</v>
       </c>
-      <c r="C80" s="5">
-        <v>1</v>
+      <c r="C80" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E80" t="s">
         <v>82</v>
@@ -6372,8 +6378,8 @@
       <c r="B81" s="1">
         <v>46225</v>
       </c>
-      <c r="C81" s="5">
-        <v>2</v>
+      <c r="C81" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E81" t="s">
         <v>91</v>
@@ -6437,8 +6443,8 @@
       <c r="B82" s="1">
         <v>46225</v>
       </c>
-      <c r="C82" s="5">
-        <v>2</v>
+      <c r="C82" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E82" t="s">
         <v>86</v>
@@ -6502,8 +6508,8 @@
       <c r="B83" s="1">
         <v>46225</v>
       </c>
-      <c r="C83" s="5">
-        <v>2</v>
+      <c r="C83" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E83" t="s">
         <v>97</v>
@@ -6567,8 +6573,8 @@
       <c r="B84" s="1">
         <v>46225</v>
       </c>
-      <c r="C84" s="5">
-        <v>2</v>
+      <c r="C84" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E84" t="s">
         <v>98</v>
@@ -6632,8 +6638,8 @@
       <c r="B85" s="1">
         <v>46225</v>
       </c>
-      <c r="C85" s="5">
-        <v>2</v>
+      <c r="C85" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E85" t="s">
         <v>99</v>
@@ -6697,8 +6703,8 @@
       <c r="B86" s="1">
         <v>46225</v>
       </c>
-      <c r="C86" s="5">
-        <v>2</v>
+      <c r="C86" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E86" t="s">
         <v>94</v>
@@ -6762,8 +6768,8 @@
       <c r="B87" s="1">
         <v>46225</v>
       </c>
-      <c r="C87" s="5">
-        <v>2</v>
+      <c r="C87" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E87" t="s">
         <v>82</v>
@@ -6827,8 +6833,8 @@
       <c r="B88" s="1">
         <v>46225</v>
       </c>
-      <c r="C88" s="5">
-        <v>2</v>
+      <c r="C88" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E88" t="s">
         <v>87</v>
@@ -6892,8 +6898,8 @@
       <c r="B89" s="1">
         <v>46226</v>
       </c>
-      <c r="C89" s="5">
-        <v>1</v>
+      <c r="C89" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E89" t="s">
         <v>91</v>
@@ -6957,8 +6963,8 @@
       <c r="B90" s="1">
         <v>46226</v>
       </c>
-      <c r="C90" s="5">
-        <v>1</v>
+      <c r="C90" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E90" t="s">
         <v>94</v>
@@ -7022,8 +7028,8 @@
       <c r="B91" s="1">
         <v>46226</v>
       </c>
-      <c r="C91" s="5">
-        <v>1</v>
+      <c r="C91" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E91" t="s">
         <v>86</v>
@@ -7087,8 +7093,8 @@
       <c r="B92" s="1">
         <v>46226</v>
       </c>
-      <c r="C92" s="5">
-        <v>1</v>
+      <c r="C92" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E92" t="s">
         <v>87</v>
@@ -7152,8 +7158,8 @@
       <c r="B93" s="1">
         <v>46226</v>
       </c>
-      <c r="C93" s="5">
-        <v>1</v>
+      <c r="C93" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E93" t="s">
         <v>98</v>
@@ -7217,8 +7223,8 @@
       <c r="B94" s="1">
         <v>46226</v>
       </c>
-      <c r="C94" s="5">
-        <v>1</v>
+      <c r="C94" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E94" t="s">
         <v>97</v>
@@ -7282,8 +7288,8 @@
       <c r="B95" s="1">
         <v>46226</v>
       </c>
-      <c r="C95" s="5">
-        <v>1</v>
+      <c r="C95" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E95" t="s">
         <v>89</v>
@@ -7347,8 +7353,8 @@
       <c r="B96" s="1">
         <v>46226</v>
       </c>
-      <c r="C96" s="5">
-        <v>1</v>
+      <c r="C96" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E96" t="s">
         <v>99</v>
@@ -7412,8 +7418,8 @@
       <c r="B97" s="1">
         <v>46226</v>
       </c>
-      <c r="C97" s="5">
-        <v>1</v>
+      <c r="C97" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="E97" t="s">
         <v>82</v>
@@ -7477,8 +7483,8 @@
       <c r="B98" s="1">
         <v>46226</v>
       </c>
-      <c r="C98" s="5">
-        <v>2</v>
+      <c r="C98" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E98" t="s">
         <v>98</v>
@@ -7542,8 +7548,8 @@
       <c r="B99" s="1">
         <v>46226</v>
       </c>
-      <c r="C99" s="5">
-        <v>2</v>
+      <c r="C99" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E99" t="s">
         <v>91</v>
@@ -7607,8 +7613,8 @@
       <c r="B100" s="1">
         <v>46226</v>
       </c>
-      <c r="C100" s="5">
-        <v>2</v>
+      <c r="C100" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E100" t="s">
         <v>82</v>
@@ -7672,8 +7678,8 @@
       <c r="B101" s="1">
         <v>46226</v>
       </c>
-      <c r="C101" s="5">
-        <v>2</v>
+      <c r="C101" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E101" t="s">
         <v>89</v>
@@ -7737,8 +7743,8 @@
       <c r="B102" s="1">
         <v>46226</v>
       </c>
-      <c r="C102" s="5">
-        <v>2</v>
+      <c r="C102" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E102" t="s">
         <v>86</v>
@@ -7802,8 +7808,8 @@
       <c r="B103" s="1">
         <v>46226</v>
       </c>
-      <c r="C103" s="5">
-        <v>2</v>
+      <c r="C103" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E103" t="s">
         <v>87</v>
@@ -7867,8 +7873,8 @@
       <c r="B104" s="1">
         <v>46226</v>
       </c>
-      <c r="C104" s="5">
-        <v>2</v>
+      <c r="C104" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E104" t="s">
         <v>99</v>
@@ -7932,8 +7938,8 @@
       <c r="B105" s="1">
         <v>46226</v>
       </c>
-      <c r="C105" s="5">
-        <v>2</v>
+      <c r="C105" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E105" t="s">
         <v>97</v>
@@ -7997,8 +8003,8 @@
       <c r="B106" s="1">
         <v>46226</v>
       </c>
-      <c r="C106" s="5">
-        <v>2</v>
+      <c r="C106" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="E106" t="s">
         <v>94</v>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E0CF84-8A9B-1545-8476-F9884A7F04A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D1DF7F-7F74-A14A-B16C-7F42EBBE6755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="267">
   <si>
     <t>Temps joué</t>
   </si>
@@ -785,6 +785,57 @@
   </si>
   <si>
     <t>Séance 2</t>
+  </si>
+  <si>
+    <t>01:23:49</t>
+  </si>
+  <si>
+    <t>01:06:10</t>
+  </si>
+  <si>
+    <t>01:22:31</t>
+  </si>
+  <si>
+    <t>01:04:52</t>
+  </si>
+  <si>
+    <t>01:06:04</t>
+  </si>
+  <si>
+    <t>Marc Thomas</t>
+  </si>
+  <si>
+    <t>00:52:40</t>
+  </si>
+  <si>
+    <t>01:05:19</t>
+  </si>
+  <si>
+    <t>Match Amical VS Toulon 05/08/2026</t>
+  </si>
+  <si>
+    <t>00:51:37</t>
+  </si>
+  <si>
+    <t>00:50:27</t>
+  </si>
+  <si>
+    <t>00:50:57</t>
+  </si>
+  <si>
+    <t>00:51:06</t>
+  </si>
+  <si>
+    <t>00:50:47</t>
+  </si>
+  <si>
+    <t>00:51:07</t>
+  </si>
+  <si>
+    <t>00:50:37</t>
+  </si>
+  <si>
+    <t>00:50:36</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V209"/>
+  <dimension ref="A1:V225"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -14756,6 +14807,1046 @@
         <v>0</v>
       </c>
     </row>
+    <row r="210" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>258</v>
+      </c>
+      <c r="B210" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C210" t="s">
+        <v>19</v>
+      </c>
+      <c r="E210" t="s">
+        <v>184</v>
+      </c>
+      <c r="F210" t="s">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>250</v>
+      </c>
+      <c r="H210">
+        <v>8.43</v>
+      </c>
+      <c r="I210">
+        <v>1.3</v>
+      </c>
+      <c r="J210">
+        <v>7.12</v>
+      </c>
+      <c r="K210">
+        <v>0.86</v>
+      </c>
+      <c r="L210">
+        <v>0.36</v>
+      </c>
+      <c r="M210">
+        <v>0.09</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210">
+        <v>9</v>
+      </c>
+      <c r="P210">
+        <v>5.99</v>
+      </c>
+      <c r="Q210">
+        <v>28.92</v>
+      </c>
+      <c r="R210">
+        <v>4.32</v>
+      </c>
+      <c r="S210">
+        <v>35</v>
+      </c>
+      <c r="T210">
+        <v>4</v>
+      </c>
+      <c r="U210">
+        <v>16</v>
+      </c>
+      <c r="V210">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>258</v>
+      </c>
+      <c r="B211" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C211" t="s">
+        <v>19</v>
+      </c>
+      <c r="E211" t="s">
+        <v>98</v>
+      </c>
+      <c r="F211" t="s">
+        <v>27</v>
+      </c>
+      <c r="G211" t="s">
+        <v>251</v>
+      </c>
+      <c r="H211">
+        <v>7.23</v>
+      </c>
+      <c r="I211">
+        <v>1.38</v>
+      </c>
+      <c r="J211">
+        <v>5.84</v>
+      </c>
+      <c r="K211">
+        <v>1.05</v>
+      </c>
+      <c r="L211">
+        <v>0.26</v>
+      </c>
+      <c r="M211">
+        <v>0.09</v>
+      </c>
+      <c r="N211">
+        <v>0</v>
+      </c>
+      <c r="O211">
+        <v>4</v>
+      </c>
+      <c r="P211">
+        <v>6.53</v>
+      </c>
+      <c r="Q211">
+        <v>28.64</v>
+      </c>
+      <c r="R211">
+        <v>4.37</v>
+      </c>
+      <c r="S211">
+        <v>25</v>
+      </c>
+      <c r="T211">
+        <v>3</v>
+      </c>
+      <c r="U211">
+        <v>34</v>
+      </c>
+      <c r="V211">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>258</v>
+      </c>
+      <c r="B212" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C212" t="s">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>89</v>
+      </c>
+      <c r="F212" t="s">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>252</v>
+      </c>
+      <c r="H212">
+        <v>7.26</v>
+      </c>
+      <c r="I212">
+        <v>0.86</v>
+      </c>
+      <c r="J212">
+        <v>6.39</v>
+      </c>
+      <c r="K212">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L212">
+        <v>0.22</v>
+      </c>
+      <c r="M212">
+        <v>0.08</v>
+      </c>
+      <c r="N212">
+        <v>0</v>
+      </c>
+      <c r="O212">
+        <v>6</v>
+      </c>
+      <c r="P212">
+        <v>5.21</v>
+      </c>
+      <c r="Q212">
+        <v>29.49</v>
+      </c>
+      <c r="R212">
+        <v>4.21</v>
+      </c>
+      <c r="S212">
+        <v>21</v>
+      </c>
+      <c r="T212">
+        <v>5</v>
+      </c>
+      <c r="U212">
+        <v>12</v>
+      </c>
+      <c r="V212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>258</v>
+      </c>
+      <c r="B213" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C213" t="s">
+        <v>19</v>
+      </c>
+      <c r="E213" t="s">
+        <v>43</v>
+      </c>
+      <c r="F213" t="s">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>251</v>
+      </c>
+      <c r="H213">
+        <v>6.86</v>
+      </c>
+      <c r="I213">
+        <v>0.93</v>
+      </c>
+      <c r="J213">
+        <v>5.91</v>
+      </c>
+      <c r="K213">
+        <v>0.7</v>
+      </c>
+      <c r="L213">
+        <v>0.22</v>
+      </c>
+      <c r="M213">
+        <v>0.03</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213">
+        <v>4</v>
+      </c>
+      <c r="P213">
+        <v>6.16</v>
+      </c>
+      <c r="Q213">
+        <v>27.08</v>
+      </c>
+      <c r="R213">
+        <v>4.54</v>
+      </c>
+      <c r="S213">
+        <v>26</v>
+      </c>
+      <c r="T213">
+        <v>2</v>
+      </c>
+      <c r="U213">
+        <v>16</v>
+      </c>
+      <c r="V213">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>258</v>
+      </c>
+      <c r="B214" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C214" t="s">
+        <v>19</v>
+      </c>
+      <c r="E214" t="s">
+        <v>94</v>
+      </c>
+      <c r="F214" t="s">
+        <v>103</v>
+      </c>
+      <c r="G214" t="s">
+        <v>253</v>
+      </c>
+      <c r="H214">
+        <v>6.66</v>
+      </c>
+      <c r="I214">
+        <v>1.26</v>
+      </c>
+      <c r="J214">
+        <v>5.39</v>
+      </c>
+      <c r="K214">
+        <v>0.98</v>
+      </c>
+      <c r="L214">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>0</v>
+      </c>
+      <c r="O214">
+        <v>1</v>
+      </c>
+      <c r="P214">
+        <v>6.1</v>
+      </c>
+      <c r="Q214">
+        <v>25.47</v>
+      </c>
+      <c r="R214">
+        <v>4.07</v>
+      </c>
+      <c r="S214">
+        <v>26</v>
+      </c>
+      <c r="T214">
+        <v>2</v>
+      </c>
+      <c r="U214">
+        <v>20</v>
+      </c>
+      <c r="V214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>258</v>
+      </c>
+      <c r="B215" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C215" t="s">
+        <v>19</v>
+      </c>
+      <c r="E215" t="s">
+        <v>87</v>
+      </c>
+      <c r="F215" t="s">
+        <v>27</v>
+      </c>
+      <c r="G215" t="s">
+        <v>254</v>
+      </c>
+      <c r="H215">
+        <v>7.84</v>
+      </c>
+      <c r="I215">
+        <v>1.76</v>
+      </c>
+      <c r="J215">
+        <v>6.06</v>
+      </c>
+      <c r="K215">
+        <v>1.31</v>
+      </c>
+      <c r="L215">
+        <v>0.34</v>
+      </c>
+      <c r="M215">
+        <v>0.11</v>
+      </c>
+      <c r="N215">
+        <v>0.02</v>
+      </c>
+      <c r="O215">
+        <v>7</v>
+      </c>
+      <c r="P215">
+        <v>6.98</v>
+      </c>
+      <c r="Q215">
+        <v>30.92</v>
+      </c>
+      <c r="R215">
+        <v>4.2</v>
+      </c>
+      <c r="S215">
+        <v>29</v>
+      </c>
+      <c r="T215">
+        <v>2</v>
+      </c>
+      <c r="U215">
+        <v>23</v>
+      </c>
+      <c r="V215">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>258</v>
+      </c>
+      <c r="B216" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C216" t="s">
+        <v>19</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F216" t="s">
+        <v>101</v>
+      </c>
+      <c r="G216" t="s">
+        <v>256</v>
+      </c>
+      <c r="H216">
+        <v>6.54</v>
+      </c>
+      <c r="I216">
+        <v>0.36</v>
+      </c>
+      <c r="J216">
+        <v>6.18</v>
+      </c>
+      <c r="K216">
+        <v>0.32</v>
+      </c>
+      <c r="L216">
+        <v>0.05</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>0</v>
+      </c>
+      <c r="O216">
+        <v>0</v>
+      </c>
+      <c r="P216">
+        <v>4.82</v>
+      </c>
+      <c r="Q216">
+        <v>23.21</v>
+      </c>
+      <c r="R216">
+        <v>3.11</v>
+      </c>
+      <c r="S216">
+        <v>2</v>
+      </c>
+      <c r="T216">
+        <v>0</v>
+      </c>
+      <c r="U216">
+        <v>3</v>
+      </c>
+      <c r="V216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>258</v>
+      </c>
+      <c r="B217" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C217" t="s">
+        <v>19</v>
+      </c>
+      <c r="E217" t="s">
+        <v>31</v>
+      </c>
+      <c r="F217" t="s">
+        <v>28</v>
+      </c>
+      <c r="G217" t="s">
+        <v>257</v>
+      </c>
+      <c r="H217">
+        <v>6.76</v>
+      </c>
+      <c r="I217">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J217">
+        <v>5.59</v>
+      </c>
+      <c r="K217">
+        <v>0.64</v>
+      </c>
+      <c r="L217">
+        <v>0.34</v>
+      </c>
+      <c r="M217">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N217">
+        <v>0.04</v>
+      </c>
+      <c r="O217">
+        <v>14</v>
+      </c>
+      <c r="P217">
+        <v>6.16</v>
+      </c>
+      <c r="Q217">
+        <v>34.229999999999997</v>
+      </c>
+      <c r="R217">
+        <v>4.71</v>
+      </c>
+      <c r="S217">
+        <v>23</v>
+      </c>
+      <c r="T217">
+        <v>5</v>
+      </c>
+      <c r="U217">
+        <v>25</v>
+      </c>
+      <c r="V217">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>22</v>
+      </c>
+      <c r="B218" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C218" t="s">
+        <v>19</v>
+      </c>
+      <c r="E218" t="s">
+        <v>86</v>
+      </c>
+      <c r="F218" t="s">
+        <v>27</v>
+      </c>
+      <c r="G218" t="s">
+        <v>259</v>
+      </c>
+      <c r="H218">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>0</v>
+      </c>
+      <c r="O218">
+        <v>0</v>
+      </c>
+      <c r="P218">
+        <v>4.05</v>
+      </c>
+      <c r="Q218">
+        <v>15.47</v>
+      </c>
+      <c r="R218">
+        <v>4.67</v>
+      </c>
+      <c r="S218">
+        <v>4</v>
+      </c>
+      <c r="T218">
+        <v>1</v>
+      </c>
+      <c r="U218">
+        <v>3</v>
+      </c>
+      <c r="V218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>22</v>
+      </c>
+      <c r="B219" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C219" t="s">
+        <v>19</v>
+      </c>
+      <c r="E219" t="s">
+        <v>46</v>
+      </c>
+      <c r="F219" t="s">
+        <v>24</v>
+      </c>
+      <c r="G219" t="s">
+        <v>260</v>
+      </c>
+      <c r="H219">
+        <v>4.66</v>
+      </c>
+      <c r="I219">
+        <v>0.06</v>
+      </c>
+      <c r="J219">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="K219">
+        <v>0.04</v>
+      </c>
+      <c r="L219">
+        <v>0.02</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>0</v>
+      </c>
+      <c r="O219">
+        <v>0</v>
+      </c>
+      <c r="P219">
+        <v>5.4</v>
+      </c>
+      <c r="Q219">
+        <v>22.89</v>
+      </c>
+      <c r="R219">
+        <v>0</v>
+      </c>
+      <c r="S219">
+        <v>0</v>
+      </c>
+      <c r="T219">
+        <v>0</v>
+      </c>
+      <c r="U219">
+        <v>1</v>
+      </c>
+      <c r="V219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>22</v>
+      </c>
+      <c r="B220" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C220" t="s">
+        <v>19</v>
+      </c>
+      <c r="E220" t="s">
+        <v>99</v>
+      </c>
+      <c r="F220" t="s">
+        <v>27</v>
+      </c>
+      <c r="G220" t="s">
+        <v>261</v>
+      </c>
+      <c r="H220">
+        <v>4.75</v>
+      </c>
+      <c r="I220">
+        <v>0.06</v>
+      </c>
+      <c r="J220">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="K220">
+        <v>0.05</v>
+      </c>
+      <c r="L220">
+        <v>0.01</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>0</v>
+      </c>
+      <c r="O220">
+        <v>0</v>
+      </c>
+      <c r="P220">
+        <v>5.5</v>
+      </c>
+      <c r="Q220">
+        <v>22.98</v>
+      </c>
+      <c r="R220">
+        <v>3.4</v>
+      </c>
+      <c r="S220">
+        <v>1</v>
+      </c>
+      <c r="T220">
+        <v>0</v>
+      </c>
+      <c r="U220">
+        <v>0</v>
+      </c>
+      <c r="V220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>22</v>
+      </c>
+      <c r="B221" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C221" t="s">
+        <v>19</v>
+      </c>
+      <c r="E221" t="s">
+        <v>97</v>
+      </c>
+      <c r="F221" t="s">
+        <v>101</v>
+      </c>
+      <c r="G221" t="s">
+        <v>262</v>
+      </c>
+      <c r="H221">
+        <v>3.61</v>
+      </c>
+      <c r="I221">
+        <v>0.01</v>
+      </c>
+      <c r="J221">
+        <v>3.6</v>
+      </c>
+      <c r="K221">
+        <v>0.01</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>0</v>
+      </c>
+      <c r="O221">
+        <v>0</v>
+      </c>
+      <c r="P221">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Q221">
+        <v>16.3</v>
+      </c>
+      <c r="R221">
+        <v>3.21</v>
+      </c>
+      <c r="S221">
+        <v>1</v>
+      </c>
+      <c r="T221">
+        <v>0</v>
+      </c>
+      <c r="U221">
+        <v>0</v>
+      </c>
+      <c r="V221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>22</v>
+      </c>
+      <c r="B222" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C222" t="s">
+        <v>19</v>
+      </c>
+      <c r="E222" t="s">
+        <v>98</v>
+      </c>
+      <c r="F222" t="s">
+        <v>27</v>
+      </c>
+      <c r="G222" t="s">
+        <v>263</v>
+      </c>
+      <c r="H222">
+        <v>5.15</v>
+      </c>
+      <c r="I222">
+        <v>0.1</v>
+      </c>
+      <c r="J222">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="K222">
+        <v>0.1</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>0</v>
+      </c>
+      <c r="O222">
+        <v>0</v>
+      </c>
+      <c r="P222">
+        <v>6.03</v>
+      </c>
+      <c r="Q222">
+        <v>17.54</v>
+      </c>
+      <c r="R222">
+        <v>3.19</v>
+      </c>
+      <c r="S222">
+        <v>2</v>
+      </c>
+      <c r="T222">
+        <v>0</v>
+      </c>
+      <c r="U222">
+        <v>4</v>
+      </c>
+      <c r="V222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>22</v>
+      </c>
+      <c r="B223" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C223" t="s">
+        <v>19</v>
+      </c>
+      <c r="E223" t="s">
+        <v>36</v>
+      </c>
+      <c r="F223" t="s">
+        <v>26</v>
+      </c>
+      <c r="G223" t="s">
+        <v>264</v>
+      </c>
+      <c r="H223">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="I223">
+        <v>0.04</v>
+      </c>
+      <c r="J223">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="K223">
+        <v>0.04</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>0</v>
+      </c>
+      <c r="O223">
+        <v>0</v>
+      </c>
+      <c r="P223">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="Q223">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="R223">
+        <v>4.45</v>
+      </c>
+      <c r="S223">
+        <v>0</v>
+      </c>
+      <c r="T223">
+        <v>1</v>
+      </c>
+      <c r="U223">
+        <v>0</v>
+      </c>
+      <c r="V223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>22</v>
+      </c>
+      <c r="B224" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C224" t="s">
+        <v>19</v>
+      </c>
+      <c r="E224" t="s">
+        <v>84</v>
+      </c>
+      <c r="F224" t="s">
+        <v>24</v>
+      </c>
+      <c r="G224" t="s">
+        <v>265</v>
+      </c>
+      <c r="H224">
+        <v>4.37</v>
+      </c>
+      <c r="I224">
+        <v>0.02</v>
+      </c>
+      <c r="J224">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="K224">
+        <v>0.02</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>0</v>
+      </c>
+      <c r="O224">
+        <v>0</v>
+      </c>
+      <c r="P224">
+        <v>5.09</v>
+      </c>
+      <c r="Q224">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="R224">
+        <v>0</v>
+      </c>
+      <c r="S224">
+        <v>0</v>
+      </c>
+      <c r="T224">
+        <v>0</v>
+      </c>
+      <c r="U224">
+        <v>0</v>
+      </c>
+      <c r="V224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>22</v>
+      </c>
+      <c r="B225" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C225" t="s">
+        <v>19</v>
+      </c>
+      <c r="E225" t="s">
+        <v>94</v>
+      </c>
+      <c r="F225" t="s">
+        <v>103</v>
+      </c>
+      <c r="G225" t="s">
+        <v>266</v>
+      </c>
+      <c r="H225">
+        <v>4.71</v>
+      </c>
+      <c r="I225">
+        <v>0.02</v>
+      </c>
+      <c r="J225">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="K225">
+        <v>0.01</v>
+      </c>
+      <c r="L225">
+        <v>0.01</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>0</v>
+      </c>
+      <c r="O225">
+        <v>0</v>
+      </c>
+      <c r="P225">
+        <v>5.5</v>
+      </c>
+      <c r="Q225">
+        <v>22.45</v>
+      </c>
+      <c r="R225">
+        <v>0</v>
+      </c>
+      <c r="S225">
+        <v>0</v>
+      </c>
+      <c r="T225">
+        <v>0</v>
+      </c>
+      <c r="U225">
+        <v>1</v>
+      </c>
+      <c r="V225">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D1DF7F-7F74-A14A-B16C-7F42EBBE6755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6169299-ACA7-E141-8CAA-639C0FFD93F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="275">
   <si>
     <t>Temps joué</t>
   </si>
@@ -836,6 +836,30 @@
   </si>
   <si>
     <t>00:50:36</t>
+  </si>
+  <si>
+    <t>01:28:18</t>
+  </si>
+  <si>
+    <t>01:38:50</t>
+  </si>
+  <si>
+    <t>01:10:26</t>
+  </si>
+  <si>
+    <t>01:30:48</t>
+  </si>
+  <si>
+    <t>01:13:06</t>
+  </si>
+  <si>
+    <t>01:23:28</t>
+  </si>
+  <si>
+    <t>01:26:20</t>
+  </si>
+  <si>
+    <t>Match Amical VS Bourgoin 07/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V225"/>
+  <dimension ref="A1:V233"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -15847,6 +15871,526 @@
         <v>0</v>
       </c>
     </row>
+    <row r="226" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>274</v>
+      </c>
+      <c r="B226" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C226" t="s">
+        <v>19</v>
+      </c>
+      <c r="E226" t="s">
+        <v>31</v>
+      </c>
+      <c r="F226" t="s">
+        <v>28</v>
+      </c>
+      <c r="G226" t="s">
+        <v>267</v>
+      </c>
+      <c r="H226">
+        <v>9.27</v>
+      </c>
+      <c r="I226">
+        <v>1.67</v>
+      </c>
+      <c r="J226">
+        <v>7.57</v>
+      </c>
+      <c r="K226">
+        <v>1.07</v>
+      </c>
+      <c r="L226">
+        <v>0.39</v>
+      </c>
+      <c r="M226">
+        <v>0.2</v>
+      </c>
+      <c r="N226">
+        <v>0.04</v>
+      </c>
+      <c r="O226">
+        <v>12</v>
+      </c>
+      <c r="P226">
+        <v>6.26</v>
+      </c>
+      <c r="Q226">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="R226">
+        <v>4.93</v>
+      </c>
+      <c r="S226">
+        <v>51</v>
+      </c>
+      <c r="T226">
+        <v>8</v>
+      </c>
+      <c r="U226">
+        <v>43</v>
+      </c>
+      <c r="V226">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="227" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>274</v>
+      </c>
+      <c r="B227" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C227" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227" t="s">
+        <v>89</v>
+      </c>
+      <c r="F227" t="s">
+        <v>24</v>
+      </c>
+      <c r="G227" t="s">
+        <v>268</v>
+      </c>
+      <c r="H227">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="I227">
+        <v>1.03</v>
+      </c>
+      <c r="J227">
+        <v>8.24</v>
+      </c>
+      <c r="K227">
+        <v>0.65</v>
+      </c>
+      <c r="L227">
+        <v>0.26</v>
+      </c>
+      <c r="M227">
+        <v>0.12</v>
+      </c>
+      <c r="N227">
+        <v>0.01</v>
+      </c>
+      <c r="O227">
+        <v>9</v>
+      </c>
+      <c r="P227">
+        <v>5.6</v>
+      </c>
+      <c r="Q227">
+        <v>30.85</v>
+      </c>
+      <c r="R227">
+        <v>4.63</v>
+      </c>
+      <c r="S227">
+        <v>31</v>
+      </c>
+      <c r="T227">
+        <v>7</v>
+      </c>
+      <c r="U227">
+        <v>23</v>
+      </c>
+      <c r="V227">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>274</v>
+      </c>
+      <c r="B228" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C228" t="s">
+        <v>19</v>
+      </c>
+      <c r="E228" t="s">
+        <v>46</v>
+      </c>
+      <c r="F228" t="s">
+        <v>24</v>
+      </c>
+      <c r="G228" t="s">
+        <v>269</v>
+      </c>
+      <c r="H228">
+        <v>6.42</v>
+      </c>
+      <c r="I228">
+        <v>0.67</v>
+      </c>
+      <c r="J228">
+        <v>5.74</v>
+      </c>
+      <c r="K228">
+        <v>0.48</v>
+      </c>
+      <c r="L228">
+        <v>0.16</v>
+      </c>
+      <c r="M228">
+        <v>0.03</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228">
+        <v>3</v>
+      </c>
+      <c r="P228">
+        <v>5.37</v>
+      </c>
+      <c r="Q228">
+        <v>26.25</v>
+      </c>
+      <c r="R228">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S228">
+        <v>24</v>
+      </c>
+      <c r="T228">
+        <v>2</v>
+      </c>
+      <c r="U228">
+        <v>21</v>
+      </c>
+      <c r="V228">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>274</v>
+      </c>
+      <c r="B229" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C229" t="s">
+        <v>19</v>
+      </c>
+      <c r="E229" t="s">
+        <v>98</v>
+      </c>
+      <c r="F229" t="s">
+        <v>27</v>
+      </c>
+      <c r="G229" t="s">
+        <v>270</v>
+      </c>
+      <c r="H229">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I229">
+        <v>1.51</v>
+      </c>
+      <c r="J229">
+        <v>8.66</v>
+      </c>
+      <c r="K229">
+        <v>1.21</v>
+      </c>
+      <c r="L229">
+        <v>0.32</v>
+      </c>
+      <c r="M229">
+        <v>0.01</v>
+      </c>
+      <c r="N229">
+        <v>0</v>
+      </c>
+      <c r="O229">
+        <v>3</v>
+      </c>
+      <c r="P229">
+        <v>6.72</v>
+      </c>
+      <c r="Q229">
+        <v>25.69</v>
+      </c>
+      <c r="R229">
+        <v>4.13</v>
+      </c>
+      <c r="S229">
+        <v>43</v>
+      </c>
+      <c r="T229">
+        <v>2</v>
+      </c>
+      <c r="U229">
+        <v>53</v>
+      </c>
+      <c r="V229">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>274</v>
+      </c>
+      <c r="B230" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C230" t="s">
+        <v>19</v>
+      </c>
+      <c r="E230" t="s">
+        <v>184</v>
+      </c>
+      <c r="F230" t="s">
+        <v>24</v>
+      </c>
+      <c r="G230" t="s">
+        <v>268</v>
+      </c>
+      <c r="H230">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="I230">
+        <v>1.19</v>
+      </c>
+      <c r="J230">
+        <v>8.83</v>
+      </c>
+      <c r="K230">
+        <v>0.79</v>
+      </c>
+      <c r="L230">
+        <v>0.34</v>
+      </c>
+      <c r="M230">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N230">
+        <v>0.01</v>
+      </c>
+      <c r="O230">
+        <v>6</v>
+      </c>
+      <c r="P230">
+        <v>6.08</v>
+      </c>
+      <c r="Q230">
+        <v>30.59</v>
+      </c>
+      <c r="R230">
+        <v>4.68</v>
+      </c>
+      <c r="S230">
+        <v>47</v>
+      </c>
+      <c r="T230">
+        <v>9</v>
+      </c>
+      <c r="U230">
+        <v>30</v>
+      </c>
+      <c r="V230">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>274</v>
+      </c>
+      <c r="B231" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C231" t="s">
+        <v>19</v>
+      </c>
+      <c r="E231" t="s">
+        <v>32</v>
+      </c>
+      <c r="F231" t="s">
+        <v>27</v>
+      </c>
+      <c r="G231" t="s">
+        <v>271</v>
+      </c>
+      <c r="H231">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="I231">
+        <v>1.46</v>
+      </c>
+      <c r="J231">
+        <v>7.5</v>
+      </c>
+      <c r="K231">
+        <v>1.27</v>
+      </c>
+      <c r="L231">
+        <v>0.17</v>
+      </c>
+      <c r="M231">
+        <v>0.04</v>
+      </c>
+      <c r="N231">
+        <v>0</v>
+      </c>
+      <c r="O231">
+        <v>2</v>
+      </c>
+      <c r="P231">
+        <v>7.34</v>
+      </c>
+      <c r="Q231">
+        <v>28.89</v>
+      </c>
+      <c r="R231">
+        <v>5.29</v>
+      </c>
+      <c r="S231">
+        <v>37</v>
+      </c>
+      <c r="T231">
+        <v>4</v>
+      </c>
+      <c r="U231">
+        <v>36</v>
+      </c>
+      <c r="V231">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>274</v>
+      </c>
+      <c r="B232" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C232" t="s">
+        <v>19</v>
+      </c>
+      <c r="E232" t="s">
+        <v>94</v>
+      </c>
+      <c r="F232" t="s">
+        <v>103</v>
+      </c>
+      <c r="G232" t="s">
+        <v>272</v>
+      </c>
+      <c r="H232">
+        <v>8.82</v>
+      </c>
+      <c r="I232">
+        <v>1.69</v>
+      </c>
+      <c r="J232">
+        <v>7.1</v>
+      </c>
+      <c r="K232">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="L232">
+        <v>0.44</v>
+      </c>
+      <c r="M232">
+        <v>0.16</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232">
+        <v>10</v>
+      </c>
+      <c r="P232">
+        <v>6.28</v>
+      </c>
+      <c r="Q232">
+        <v>30.11</v>
+      </c>
+      <c r="R232">
+        <v>4.83</v>
+      </c>
+      <c r="S232">
+        <v>45</v>
+      </c>
+      <c r="T232">
+        <v>12</v>
+      </c>
+      <c r="U232">
+        <v>41</v>
+      </c>
+      <c r="V232">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>274</v>
+      </c>
+      <c r="B233" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C233" t="s">
+        <v>19</v>
+      </c>
+      <c r="E233" t="s">
+        <v>163</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G233" t="s">
+        <v>273</v>
+      </c>
+      <c r="H233">
+        <v>8.4</v>
+      </c>
+      <c r="I233">
+        <v>1.41</v>
+      </c>
+      <c r="J233">
+        <v>6.97</v>
+      </c>
+      <c r="K233">
+        <v>0.85</v>
+      </c>
+      <c r="L233">
+        <v>0.41</v>
+      </c>
+      <c r="M233">
+        <v>0.15</v>
+      </c>
+      <c r="N233">
+        <v>0.02</v>
+      </c>
+      <c r="O233">
+        <v>15</v>
+      </c>
+      <c r="P233">
+        <v>5.8</v>
+      </c>
+      <c r="Q233">
+        <v>31.5</v>
+      </c>
+      <c r="R233">
+        <v>5.26</v>
+      </c>
+      <c r="S233">
+        <v>54</v>
+      </c>
+      <c r="T233">
+        <v>11</v>
+      </c>
+      <c r="U233">
+        <v>27</v>
+      </c>
+      <c r="V233">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6169299-ACA7-E141-8CAA-639C0FFD93F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59D3DA9-C2F4-B542-A9D5-23B162D16912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="296">
   <si>
     <t>Temps joué</t>
   </si>
@@ -860,6 +860,69 @@
   </si>
   <si>
     <t>Match Amical VS Bourgoin 07/08/2026</t>
+  </si>
+  <si>
+    <t>01:53:24</t>
+  </si>
+  <si>
+    <t>01:54:41</t>
+  </si>
+  <si>
+    <t>01:54:08</t>
+  </si>
+  <si>
+    <t>01:49:54</t>
+  </si>
+  <si>
+    <t>01:55:25</t>
+  </si>
+  <si>
+    <t>01:30:05</t>
+  </si>
+  <si>
+    <t>01:51:23</t>
+  </si>
+  <si>
+    <t>01:09:14</t>
+  </si>
+  <si>
+    <t>01:06:53</t>
+  </si>
+  <si>
+    <t>01:07:40</t>
+  </si>
+  <si>
+    <t>00:58:24</t>
+  </si>
+  <si>
+    <t>01:13:55</t>
+  </si>
+  <si>
+    <t>00:59:59</t>
+  </si>
+  <si>
+    <t>Match Amical VS Chassieu 11/08/2026</t>
+  </si>
+  <si>
+    <t>01:18:50</t>
+  </si>
+  <si>
+    <t>00:52:36</t>
+  </si>
+  <si>
+    <t>01:16:58</t>
+  </si>
+  <si>
+    <t>01:19:22</t>
+  </si>
+  <si>
+    <t>01:02:47</t>
+  </si>
+  <si>
+    <t>01:18:10</t>
+  </si>
+  <si>
+    <t>01:17:06</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V233"/>
+  <dimension ref="A1:V256"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -16391,6 +16454,1501 @@
         <v>21</v>
       </c>
     </row>
+    <row r="234" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>22</v>
+      </c>
+      <c r="B234" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C234" t="s">
+        <v>19</v>
+      </c>
+      <c r="E234" t="s">
+        <v>184</v>
+      </c>
+      <c r="F234" t="s">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>275</v>
+      </c>
+      <c r="H234">
+        <v>6.9</v>
+      </c>
+      <c r="I234">
+        <v>0.38</v>
+      </c>
+      <c r="J234">
+        <v>6.51</v>
+      </c>
+      <c r="K234">
+        <v>0.3</v>
+      </c>
+      <c r="L234">
+        <v>0.08</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234">
+        <v>1</v>
+      </c>
+      <c r="P234">
+        <v>3.46</v>
+      </c>
+      <c r="Q234">
+        <v>25.14</v>
+      </c>
+      <c r="R234">
+        <v>4.57</v>
+      </c>
+      <c r="S234">
+        <v>21</v>
+      </c>
+      <c r="T234">
+        <v>3</v>
+      </c>
+      <c r="U234">
+        <v>17</v>
+      </c>
+      <c r="V234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>22</v>
+      </c>
+      <c r="B235" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C235" t="s">
+        <v>19</v>
+      </c>
+      <c r="E235" t="s">
+        <v>31</v>
+      </c>
+      <c r="F235" t="s">
+        <v>28</v>
+      </c>
+      <c r="G235" t="s">
+        <v>276</v>
+      </c>
+      <c r="H235">
+        <v>7.57</v>
+      </c>
+      <c r="I235">
+        <v>0.85</v>
+      </c>
+      <c r="J235">
+        <v>6.71</v>
+      </c>
+      <c r="K235">
+        <v>0.53</v>
+      </c>
+      <c r="L235">
+        <v>0.24</v>
+      </c>
+      <c r="M235">
+        <v>0.08</v>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235">
+        <v>4</v>
+      </c>
+      <c r="P235">
+        <v>3.84</v>
+      </c>
+      <c r="Q235">
+        <v>29.38</v>
+      </c>
+      <c r="R235">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S235">
+        <v>31</v>
+      </c>
+      <c r="T235">
+        <v>7</v>
+      </c>
+      <c r="U235">
+        <v>18</v>
+      </c>
+      <c r="V235">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>22</v>
+      </c>
+      <c r="B236" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C236" t="s">
+        <v>19</v>
+      </c>
+      <c r="E236" t="s">
+        <v>91</v>
+      </c>
+      <c r="F236" t="s">
+        <v>101</v>
+      </c>
+      <c r="G236" t="s">
+        <v>277</v>
+      </c>
+      <c r="H236">
+        <v>6.22</v>
+      </c>
+      <c r="I236">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J236">
+        <v>5.62</v>
+      </c>
+      <c r="K236">
+        <v>0.43</v>
+      </c>
+      <c r="L236">
+        <v>0.15</v>
+      </c>
+      <c r="M236">
+        <v>0.01</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236">
+        <v>1</v>
+      </c>
+      <c r="P236">
+        <v>3.03</v>
+      </c>
+      <c r="Q236">
+        <v>26.25</v>
+      </c>
+      <c r="R236">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="S236">
+        <v>22</v>
+      </c>
+      <c r="T236">
+        <v>5</v>
+      </c>
+      <c r="U236">
+        <v>26</v>
+      </c>
+      <c r="V236">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>22</v>
+      </c>
+      <c r="B237" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C237" t="s">
+        <v>19</v>
+      </c>
+      <c r="E237" t="s">
+        <v>170</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G237" t="s">
+        <v>275</v>
+      </c>
+      <c r="H237">
+        <v>6.2</v>
+      </c>
+      <c r="I237">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J237">
+        <v>5.63</v>
+      </c>
+      <c r="K237">
+        <v>0.44</v>
+      </c>
+      <c r="L237">
+        <v>0.12</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237">
+        <v>1</v>
+      </c>
+      <c r="P237">
+        <v>3.13</v>
+      </c>
+      <c r="Q237">
+        <v>25.84</v>
+      </c>
+      <c r="R237">
+        <v>5.13</v>
+      </c>
+      <c r="S237">
+        <v>47</v>
+      </c>
+      <c r="T237">
+        <v>5</v>
+      </c>
+      <c r="U237">
+        <v>30</v>
+      </c>
+      <c r="V237">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>22</v>
+      </c>
+      <c r="B238" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C238" t="s">
+        <v>19</v>
+      </c>
+      <c r="E238" t="s">
+        <v>35</v>
+      </c>
+      <c r="F238" t="s">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>278</v>
+      </c>
+      <c r="H238">
+        <v>7.23</v>
+      </c>
+      <c r="I238">
+        <v>0.59</v>
+      </c>
+      <c r="J238">
+        <v>6.64</v>
+      </c>
+      <c r="K238">
+        <v>0.42</v>
+      </c>
+      <c r="L238">
+        <v>0.13</v>
+      </c>
+      <c r="M238">
+        <v>0.04</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <v>6</v>
+      </c>
+      <c r="P238">
+        <v>3.81</v>
+      </c>
+      <c r="Q238">
+        <v>27.55</v>
+      </c>
+      <c r="R238">
+        <v>4.99</v>
+      </c>
+      <c r="S238">
+        <v>26</v>
+      </c>
+      <c r="T238">
+        <v>6</v>
+      </c>
+      <c r="U238">
+        <v>18</v>
+      </c>
+      <c r="V238">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>22</v>
+      </c>
+      <c r="B239" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C239" t="s">
+        <v>19</v>
+      </c>
+      <c r="E239" t="s">
+        <v>38</v>
+      </c>
+      <c r="F239" t="s">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>279</v>
+      </c>
+      <c r="H239">
+        <v>7.64</v>
+      </c>
+      <c r="I239">
+        <v>0.84</v>
+      </c>
+      <c r="J239">
+        <v>6.79</v>
+      </c>
+      <c r="K239">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L239">
+        <v>0.2</v>
+      </c>
+      <c r="M239">
+        <v>0.1</v>
+      </c>
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>6</v>
+      </c>
+      <c r="P239">
+        <v>3.81</v>
+      </c>
+      <c r="Q239">
+        <v>29.65</v>
+      </c>
+      <c r="R239">
+        <v>4.66</v>
+      </c>
+      <c r="S239">
+        <v>38</v>
+      </c>
+      <c r="T239">
+        <v>4</v>
+      </c>
+      <c r="U239">
+        <v>23</v>
+      </c>
+      <c r="V239">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>22</v>
+      </c>
+      <c r="B240" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C240" t="s">
+        <v>19</v>
+      </c>
+      <c r="E240" t="s">
+        <v>166</v>
+      </c>
+      <c r="F240" t="s">
+        <v>101</v>
+      </c>
+      <c r="G240" t="s">
+        <v>280</v>
+      </c>
+      <c r="H240">
+        <v>6.4</v>
+      </c>
+      <c r="I240">
+        <v>0.48</v>
+      </c>
+      <c r="J240">
+        <v>5.92</v>
+      </c>
+      <c r="K240">
+        <v>0.31</v>
+      </c>
+      <c r="L240">
+        <v>0.15</v>
+      </c>
+      <c r="M240">
+        <v>0.03</v>
+      </c>
+      <c r="N240">
+        <v>0</v>
+      </c>
+      <c r="O240">
+        <v>6</v>
+      </c>
+      <c r="P240">
+        <v>3.15</v>
+      </c>
+      <c r="Q240">
+        <v>30.19</v>
+      </c>
+      <c r="R240">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S240">
+        <v>27</v>
+      </c>
+      <c r="T240">
+        <v>6</v>
+      </c>
+      <c r="U240">
+        <v>20</v>
+      </c>
+      <c r="V240">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>22</v>
+      </c>
+      <c r="B241" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C241" t="s">
+        <v>19</v>
+      </c>
+      <c r="E241" t="s">
+        <v>89</v>
+      </c>
+      <c r="F241" t="s">
+        <v>24</v>
+      </c>
+      <c r="G241" t="s">
+        <v>281</v>
+      </c>
+      <c r="H241">
+        <v>5.47</v>
+      </c>
+      <c r="I241">
+        <v>0.23</v>
+      </c>
+      <c r="J241">
+        <v>5.24</v>
+      </c>
+      <c r="K241">
+        <v>0.15</v>
+      </c>
+      <c r="L241">
+        <v>0.08</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>0</v>
+      </c>
+      <c r="O241">
+        <v>0</v>
+      </c>
+      <c r="P241">
+        <v>2.74</v>
+      </c>
+      <c r="Q241">
+        <v>24.58</v>
+      </c>
+      <c r="R241">
+        <v>3.77</v>
+      </c>
+      <c r="S241">
+        <v>8</v>
+      </c>
+      <c r="T241">
+        <v>0</v>
+      </c>
+      <c r="U241">
+        <v>8</v>
+      </c>
+      <c r="V241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>22</v>
+      </c>
+      <c r="B242" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C242" t="s">
+        <v>19</v>
+      </c>
+      <c r="E242" t="s">
+        <v>30</v>
+      </c>
+      <c r="F242" t="s">
+        <v>26</v>
+      </c>
+      <c r="G242" t="s">
+        <v>123</v>
+      </c>
+      <c r="H242">
+        <v>5.44</v>
+      </c>
+      <c r="I242">
+        <v>0.71</v>
+      </c>
+      <c r="J242">
+        <v>4.72</v>
+      </c>
+      <c r="K242">
+        <v>0.46</v>
+      </c>
+      <c r="L242">
+        <v>0.23</v>
+      </c>
+      <c r="M242">
+        <v>0.03</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>7</v>
+      </c>
+      <c r="P242">
+        <v>3.28</v>
+      </c>
+      <c r="Q242">
+        <v>27.99</v>
+      </c>
+      <c r="R242">
+        <v>5.98</v>
+      </c>
+      <c r="S242">
+        <v>50</v>
+      </c>
+      <c r="T242">
+        <v>14</v>
+      </c>
+      <c r="U242">
+        <v>21</v>
+      </c>
+      <c r="V242">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>288</v>
+      </c>
+      <c r="B243" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C243" t="s">
+        <v>19</v>
+      </c>
+      <c r="E243" t="s">
+        <v>86</v>
+      </c>
+      <c r="F243" t="s">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>282</v>
+      </c>
+      <c r="H243">
+        <v>7.28</v>
+      </c>
+      <c r="I243">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J243">
+        <v>6.16</v>
+      </c>
+      <c r="K243">
+        <v>0.82</v>
+      </c>
+      <c r="L243">
+        <v>0.27</v>
+      </c>
+      <c r="M243">
+        <v>0.03</v>
+      </c>
+      <c r="N243">
+        <v>0</v>
+      </c>
+      <c r="O243">
+        <v>5</v>
+      </c>
+      <c r="P243">
+        <v>6.29</v>
+      </c>
+      <c r="Q243">
+        <v>28.1</v>
+      </c>
+      <c r="R243">
+        <v>4.33</v>
+      </c>
+      <c r="S243">
+        <v>25</v>
+      </c>
+      <c r="T243">
+        <v>4</v>
+      </c>
+      <c r="U243">
+        <v>18</v>
+      </c>
+      <c r="V243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>288</v>
+      </c>
+      <c r="B244" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C244" t="s">
+        <v>19</v>
+      </c>
+      <c r="E244" t="s">
+        <v>170</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G244" t="s">
+        <v>283</v>
+      </c>
+      <c r="H244">
+        <v>6.16</v>
+      </c>
+      <c r="I244">
+        <v>0.96</v>
+      </c>
+      <c r="J244">
+        <v>5.18</v>
+      </c>
+      <c r="K244">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L244">
+        <v>0.26</v>
+      </c>
+      <c r="M244">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N244">
+        <v>0.01</v>
+      </c>
+      <c r="O244">
+        <v>10</v>
+      </c>
+      <c r="P244">
+        <v>5.49</v>
+      </c>
+      <c r="Q244">
+        <v>30.97</v>
+      </c>
+      <c r="R244">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S244">
+        <v>22</v>
+      </c>
+      <c r="T244">
+        <v>7</v>
+      </c>
+      <c r="U244">
+        <v>23</v>
+      </c>
+      <c r="V244">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>288</v>
+      </c>
+      <c r="B245" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C245" t="s">
+        <v>19</v>
+      </c>
+      <c r="E245" t="s">
+        <v>36</v>
+      </c>
+      <c r="F245" t="s">
+        <v>26</v>
+      </c>
+      <c r="G245" t="s">
+        <v>284</v>
+      </c>
+      <c r="H245">
+        <v>7.18</v>
+      </c>
+      <c r="I245">
+        <v>1.26</v>
+      </c>
+      <c r="J245">
+        <v>5.9</v>
+      </c>
+      <c r="K245">
+        <v>0.93</v>
+      </c>
+      <c r="L245">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M245">
+        <v>0.06</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245">
+        <v>5</v>
+      </c>
+      <c r="P245">
+        <v>6.36</v>
+      </c>
+      <c r="Q245">
+        <v>28.8</v>
+      </c>
+      <c r="R245">
+        <v>4.91</v>
+      </c>
+      <c r="S245">
+        <v>27</v>
+      </c>
+      <c r="T245">
+        <v>10</v>
+      </c>
+      <c r="U245">
+        <v>32</v>
+      </c>
+      <c r="V245">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>288</v>
+      </c>
+      <c r="B246" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C246" t="s">
+        <v>19</v>
+      </c>
+      <c r="E246" t="s">
+        <v>99</v>
+      </c>
+      <c r="F246" t="s">
+        <v>27</v>
+      </c>
+      <c r="G246" t="s">
+        <v>285</v>
+      </c>
+      <c r="H246">
+        <v>6.23</v>
+      </c>
+      <c r="I246">
+        <v>0.85</v>
+      </c>
+      <c r="J246">
+        <v>5.38</v>
+      </c>
+      <c r="K246">
+        <v>0.52</v>
+      </c>
+      <c r="L246">
+        <v>0.25</v>
+      </c>
+      <c r="M246">
+        <v>0.09</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246">
+        <v>7</v>
+      </c>
+      <c r="P246">
+        <v>6.12</v>
+      </c>
+      <c r="Q246">
+        <v>29.44</v>
+      </c>
+      <c r="R246">
+        <v>4.46</v>
+      </c>
+      <c r="S246">
+        <v>15</v>
+      </c>
+      <c r="T246">
+        <v>5</v>
+      </c>
+      <c r="U246">
+        <v>21</v>
+      </c>
+      <c r="V246">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>288</v>
+      </c>
+      <c r="B247" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C247" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" t="s">
+        <v>38</v>
+      </c>
+      <c r="F247" t="s">
+        <v>27</v>
+      </c>
+      <c r="G247" t="s">
+        <v>286</v>
+      </c>
+      <c r="H247">
+        <v>8.31</v>
+      </c>
+      <c r="I247">
+        <v>1.51</v>
+      </c>
+      <c r="J247">
+        <v>6.78</v>
+      </c>
+      <c r="K247">
+        <v>1.17</v>
+      </c>
+      <c r="L247">
+        <v>0.3</v>
+      </c>
+      <c r="M247">
+        <v>0.06</v>
+      </c>
+      <c r="N247">
+        <v>0</v>
+      </c>
+      <c r="O247">
+        <v>5</v>
+      </c>
+      <c r="P247">
+        <v>6.76</v>
+      </c>
+      <c r="Q247">
+        <v>29.28</v>
+      </c>
+      <c r="R247">
+        <v>4.34</v>
+      </c>
+      <c r="S247">
+        <v>25</v>
+      </c>
+      <c r="T247">
+        <v>2</v>
+      </c>
+      <c r="U247">
+        <v>20</v>
+      </c>
+      <c r="V247">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>288</v>
+      </c>
+      <c r="B248" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C248" t="s">
+        <v>19</v>
+      </c>
+      <c r="E248" t="s">
+        <v>84</v>
+      </c>
+      <c r="F248" t="s">
+        <v>24</v>
+      </c>
+      <c r="G248" t="s">
+        <v>287</v>
+      </c>
+      <c r="H248">
+        <v>5.72</v>
+      </c>
+      <c r="I248">
+        <v>0.69</v>
+      </c>
+      <c r="J248">
+        <v>5.01</v>
+      </c>
+      <c r="K248">
+        <v>0.48</v>
+      </c>
+      <c r="L248">
+        <v>0.19</v>
+      </c>
+      <c r="M248">
+        <v>0.03</v>
+      </c>
+      <c r="N248">
+        <v>0</v>
+      </c>
+      <c r="O248">
+        <v>3</v>
+      </c>
+      <c r="P248">
+        <v>5.62</v>
+      </c>
+      <c r="Q248">
+        <v>28.85</v>
+      </c>
+      <c r="R248">
+        <v>3.85</v>
+      </c>
+      <c r="S248">
+        <v>14</v>
+      </c>
+      <c r="T248">
+        <v>0</v>
+      </c>
+      <c r="U248">
+        <v>12</v>
+      </c>
+      <c r="V248">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>22</v>
+      </c>
+      <c r="B249" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C249" t="s">
+        <v>19</v>
+      </c>
+      <c r="E249" t="s">
+        <v>38</v>
+      </c>
+      <c r="F249" t="s">
+        <v>27</v>
+      </c>
+      <c r="G249" t="s">
+        <v>289</v>
+      </c>
+      <c r="H249">
+        <v>6.32</v>
+      </c>
+      <c r="I249">
+        <v>0.41</v>
+      </c>
+      <c r="J249">
+        <v>5.9</v>
+      </c>
+      <c r="K249">
+        <v>0.32</v>
+      </c>
+      <c r="L249">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M249">
+        <v>0.02</v>
+      </c>
+      <c r="N249">
+        <v>0</v>
+      </c>
+      <c r="O249">
+        <v>2</v>
+      </c>
+      <c r="P249">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Q249">
+        <v>28.42</v>
+      </c>
+      <c r="R249">
+        <v>4.57</v>
+      </c>
+      <c r="S249">
+        <v>35</v>
+      </c>
+      <c r="T249">
+        <v>4</v>
+      </c>
+      <c r="U249">
+        <v>31</v>
+      </c>
+      <c r="V249">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>22</v>
+      </c>
+      <c r="B250" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C250" t="s">
+        <v>19</v>
+      </c>
+      <c r="E250" t="s">
+        <v>166</v>
+      </c>
+      <c r="F250" t="s">
+        <v>101</v>
+      </c>
+      <c r="G250" t="s">
+        <v>290</v>
+      </c>
+      <c r="H250">
+        <v>7.97</v>
+      </c>
+      <c r="I250">
+        <v>0.36</v>
+      </c>
+      <c r="J250">
+        <v>7.6</v>
+      </c>
+      <c r="K250">
+        <v>0.27</v>
+      </c>
+      <c r="L250">
+        <v>0.08</v>
+      </c>
+      <c r="M250">
+        <v>0.01</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250">
+        <v>1</v>
+      </c>
+      <c r="P250">
+        <v>4.25</v>
+      </c>
+      <c r="Q250">
+        <v>28.64</v>
+      </c>
+      <c r="R250">
+        <v>5.32</v>
+      </c>
+      <c r="S250">
+        <v>33</v>
+      </c>
+      <c r="T250">
+        <v>8</v>
+      </c>
+      <c r="U250">
+        <v>24</v>
+      </c>
+      <c r="V250">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="251" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>22</v>
+      </c>
+      <c r="B251" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C251" t="s">
+        <v>19</v>
+      </c>
+      <c r="E251" t="s">
+        <v>35</v>
+      </c>
+      <c r="F251" t="s">
+        <v>27</v>
+      </c>
+      <c r="G251" t="s">
+        <v>291</v>
+      </c>
+      <c r="H251">
+        <v>6.01</v>
+      </c>
+      <c r="I251">
+        <v>0.49</v>
+      </c>
+      <c r="J251">
+        <v>5.51</v>
+      </c>
+      <c r="K251">
+        <v>0.47</v>
+      </c>
+      <c r="L251">
+        <v>0.03</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0</v>
+      </c>
+      <c r="O251">
+        <v>0</v>
+      </c>
+      <c r="P251">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q251">
+        <v>22.66</v>
+      </c>
+      <c r="R251">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S251">
+        <v>26</v>
+      </c>
+      <c r="T251">
+        <v>4</v>
+      </c>
+      <c r="U251">
+        <v>25</v>
+      </c>
+      <c r="V251">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>22</v>
+      </c>
+      <c r="B252" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C252" t="s">
+        <v>19</v>
+      </c>
+      <c r="E252" t="s">
+        <v>31</v>
+      </c>
+      <c r="F252" t="s">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>292</v>
+      </c>
+      <c r="H252">
+        <v>6.16</v>
+      </c>
+      <c r="I252">
+        <v>0.5</v>
+      </c>
+      <c r="J252">
+        <v>5.65</v>
+      </c>
+      <c r="K252">
+        <v>0.3</v>
+      </c>
+      <c r="L252">
+        <v>0.18</v>
+      </c>
+      <c r="M252">
+        <v>0.03</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>3</v>
+      </c>
+      <c r="P252">
+        <v>4.59</v>
+      </c>
+      <c r="Q252">
+        <v>28.65</v>
+      </c>
+      <c r="R252">
+        <v>5.27</v>
+      </c>
+      <c r="S252">
+        <v>24</v>
+      </c>
+      <c r="T252">
+        <v>5</v>
+      </c>
+      <c r="U252">
+        <v>25</v>
+      </c>
+      <c r="V252">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>22</v>
+      </c>
+      <c r="B253" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C253" t="s">
+        <v>19</v>
+      </c>
+      <c r="E253" t="s">
+        <v>89</v>
+      </c>
+      <c r="F253" t="s">
+        <v>24</v>
+      </c>
+      <c r="G253" t="s">
+        <v>293</v>
+      </c>
+      <c r="H253">
+        <v>4.33</v>
+      </c>
+      <c r="I253">
+        <v>0.25</v>
+      </c>
+      <c r="J253">
+        <v>4.07</v>
+      </c>
+      <c r="K253">
+        <v>0.2</v>
+      </c>
+      <c r="L253">
+        <v>0.05</v>
+      </c>
+      <c r="M253">
+        <v>0.01</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>1</v>
+      </c>
+      <c r="P253">
+        <v>4</v>
+      </c>
+      <c r="Q253">
+        <v>29.38</v>
+      </c>
+      <c r="R253">
+        <v>3.73</v>
+      </c>
+      <c r="S253">
+        <v>9</v>
+      </c>
+      <c r="T253">
+        <v>0</v>
+      </c>
+      <c r="U253">
+        <v>8</v>
+      </c>
+      <c r="V253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>22</v>
+      </c>
+      <c r="B254" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C254" t="s">
+        <v>19</v>
+      </c>
+      <c r="E254" t="s">
+        <v>170</v>
+      </c>
+      <c r="F254" t="s">
+        <v>26</v>
+      </c>
+      <c r="G254" t="s">
+        <v>294</v>
+      </c>
+      <c r="H254">
+        <v>5.42</v>
+      </c>
+      <c r="I254">
+        <v>0.41</v>
+      </c>
+      <c r="J254">
+        <v>5.01</v>
+      </c>
+      <c r="K254">
+        <v>0.25</v>
+      </c>
+      <c r="L254">
+        <v>0.12</v>
+      </c>
+      <c r="M254">
+        <v>0.04</v>
+      </c>
+      <c r="N254">
+        <v>0</v>
+      </c>
+      <c r="O254">
+        <v>3</v>
+      </c>
+      <c r="P254">
+        <v>4.08</v>
+      </c>
+      <c r="Q254">
+        <v>29.88</v>
+      </c>
+      <c r="R254">
+        <v>4.53</v>
+      </c>
+      <c r="S254">
+        <v>39</v>
+      </c>
+      <c r="T254">
+        <v>3</v>
+      </c>
+      <c r="U254">
+        <v>39</v>
+      </c>
+      <c r="V254">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>22</v>
+      </c>
+      <c r="B255" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C255" t="s">
+        <v>19</v>
+      </c>
+      <c r="E255" t="s">
+        <v>91</v>
+      </c>
+      <c r="F255" t="s">
+        <v>101</v>
+      </c>
+      <c r="G255" t="s">
+        <v>295</v>
+      </c>
+      <c r="H255">
+        <v>5.3</v>
+      </c>
+      <c r="I255">
+        <v>0.38</v>
+      </c>
+      <c r="J255">
+        <v>4.91</v>
+      </c>
+      <c r="K255">
+        <v>0.27</v>
+      </c>
+      <c r="L255">
+        <v>0.1</v>
+      </c>
+      <c r="M255">
+        <v>0.02</v>
+      </c>
+      <c r="N255">
+        <v>0</v>
+      </c>
+      <c r="O255">
+        <v>1</v>
+      </c>
+      <c r="P255">
+        <v>4.03</v>
+      </c>
+      <c r="Q255">
+        <v>28.85</v>
+      </c>
+      <c r="R255">
+        <v>4.79</v>
+      </c>
+      <c r="S255">
+        <v>24</v>
+      </c>
+      <c r="T255">
+        <v>4</v>
+      </c>
+      <c r="U255">
+        <v>23</v>
+      </c>
+      <c r="V255">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>22</v>
+      </c>
+      <c r="B256" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C256" t="s">
+        <v>19</v>
+      </c>
+      <c r="E256" t="s">
+        <v>184</v>
+      </c>
+      <c r="F256" t="s">
+        <v>24</v>
+      </c>
+      <c r="G256" t="s">
+        <v>295</v>
+      </c>
+      <c r="H256">
+        <v>5.48</v>
+      </c>
+      <c r="I256">
+        <v>0.26</v>
+      </c>
+      <c r="J256">
+        <v>5.22</v>
+      </c>
+      <c r="K256">
+        <v>0.21</v>
+      </c>
+      <c r="L256">
+        <v>0.04</v>
+      </c>
+      <c r="M256">
+        <v>0.02</v>
+      </c>
+      <c r="N256">
+        <v>0</v>
+      </c>
+      <c r="O256">
+        <v>1</v>
+      </c>
+      <c r="P256">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="Q256">
+        <v>29.26</v>
+      </c>
+      <c r="R256">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="S256">
+        <v>21</v>
+      </c>
+      <c r="T256">
+        <v>1</v>
+      </c>
+      <c r="U256">
+        <v>17</v>
+      </c>
+      <c r="V256">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59D3DA9-C2F4-B542-A9D5-23B162D16912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DDAA31-8B9C-7643-8C0E-6E1CDA6D4EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="313">
   <si>
     <t>Temps joué</t>
   </si>
@@ -923,6 +923,57 @@
   </si>
   <si>
     <t>01:17:06</t>
+  </si>
+  <si>
+    <t>01:22:42</t>
+  </si>
+  <si>
+    <t>01:29:42</t>
+  </si>
+  <si>
+    <t>01:09:31</t>
+  </si>
+  <si>
+    <t>01:26:22</t>
+  </si>
+  <si>
+    <t>01:39:22</t>
+  </si>
+  <si>
+    <t>01:22:52</t>
+  </si>
+  <si>
+    <t>01:11:31</t>
+  </si>
+  <si>
+    <t>01:09:51</t>
+  </si>
+  <si>
+    <t>Match Amical VS OL (U19) 14/08/2026</t>
+  </si>
+  <si>
+    <t>01:12:05</t>
+  </si>
+  <si>
+    <t>01:05:21</t>
+  </si>
+  <si>
+    <t>01:35:56</t>
+  </si>
+  <si>
+    <t>01:38:00</t>
+  </si>
+  <si>
+    <t>01:34:34</t>
+  </si>
+  <si>
+    <t>01:35:40</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>Match Amical VS Réserve 15/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V256"/>
+  <dimension ref="A1:V272"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -17949,6 +18000,1046 @@
         <v>1</v>
       </c>
     </row>
+    <row r="257" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>304</v>
+      </c>
+      <c r="B257" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C257" t="s">
+        <v>19</v>
+      </c>
+      <c r="E257" t="s">
+        <v>35</v>
+      </c>
+      <c r="F257" t="s">
+        <v>27</v>
+      </c>
+      <c r="G257" t="s">
+        <v>296</v>
+      </c>
+      <c r="H257">
+        <v>8.93</v>
+      </c>
+      <c r="I257">
+        <v>1.19</v>
+      </c>
+      <c r="J257">
+        <v>7.73</v>
+      </c>
+      <c r="K257">
+        <v>1.05</v>
+      </c>
+      <c r="L257">
+        <v>0.15</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257">
+        <v>1</v>
+      </c>
+      <c r="P257">
+        <v>6.38</v>
+      </c>
+      <c r="Q257">
+        <v>25.34</v>
+      </c>
+      <c r="R257">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S257">
+        <v>28</v>
+      </c>
+      <c r="T257">
+        <v>2</v>
+      </c>
+      <c r="U257">
+        <v>28</v>
+      </c>
+      <c r="V257">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>304</v>
+      </c>
+      <c r="B258" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C258" t="s">
+        <v>19</v>
+      </c>
+      <c r="E258" t="s">
+        <v>38</v>
+      </c>
+      <c r="F258" t="s">
+        <v>27</v>
+      </c>
+      <c r="G258" t="s">
+        <v>297</v>
+      </c>
+      <c r="H258">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="I258">
+        <v>1.61</v>
+      </c>
+      <c r="J258">
+        <v>7.92</v>
+      </c>
+      <c r="K258">
+        <v>1.06</v>
+      </c>
+      <c r="L258">
+        <v>0.46</v>
+      </c>
+      <c r="M258">
+        <v>0.12</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>15</v>
+      </c>
+      <c r="P258">
+        <v>6.26</v>
+      </c>
+      <c r="Q258">
+        <v>27.39</v>
+      </c>
+      <c r="R258">
+        <v>4.26</v>
+      </c>
+      <c r="S258">
+        <v>47</v>
+      </c>
+      <c r="T258">
+        <v>4</v>
+      </c>
+      <c r="U258">
+        <v>36</v>
+      </c>
+      <c r="V258">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>304</v>
+      </c>
+      <c r="B259" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C259" t="s">
+        <v>19</v>
+      </c>
+      <c r="E259" t="s">
+        <v>30</v>
+      </c>
+      <c r="F259" t="s">
+        <v>26</v>
+      </c>
+      <c r="G259" t="s">
+        <v>298</v>
+      </c>
+      <c r="H259">
+        <v>7.15</v>
+      </c>
+      <c r="I259">
+        <v>1.32</v>
+      </c>
+      <c r="J259">
+        <v>5.81</v>
+      </c>
+      <c r="K259">
+        <v>0.8</v>
+      </c>
+      <c r="L259">
+        <v>0.38</v>
+      </c>
+      <c r="M259">
+        <v>0.13</v>
+      </c>
+      <c r="N259">
+        <v>0.03</v>
+      </c>
+      <c r="O259">
+        <v>10</v>
+      </c>
+      <c r="P259">
+        <v>6.13</v>
+      </c>
+      <c r="Q259">
+        <v>32.43</v>
+      </c>
+      <c r="R259">
+        <v>4.63</v>
+      </c>
+      <c r="S259">
+        <v>31</v>
+      </c>
+      <c r="T259">
+        <v>8</v>
+      </c>
+      <c r="U259">
+        <v>27</v>
+      </c>
+      <c r="V259">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>304</v>
+      </c>
+      <c r="B260" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C260" t="s">
+        <v>19</v>
+      </c>
+      <c r="E260" t="s">
+        <v>84</v>
+      </c>
+      <c r="F260" t="s">
+        <v>24</v>
+      </c>
+      <c r="G260" t="s">
+        <v>299</v>
+      </c>
+      <c r="H260">
+        <v>8.17</v>
+      </c>
+      <c r="I260">
+        <v>0.87</v>
+      </c>
+      <c r="J260">
+        <v>7.28</v>
+      </c>
+      <c r="K260">
+        <v>0.68</v>
+      </c>
+      <c r="L260">
+        <v>0.19</v>
+      </c>
+      <c r="M260">
+        <v>0.01</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>1</v>
+      </c>
+      <c r="P260">
+        <v>5.58</v>
+      </c>
+      <c r="Q260">
+        <v>26.91</v>
+      </c>
+      <c r="R260">
+        <v>3.44</v>
+      </c>
+      <c r="S260">
+        <v>9</v>
+      </c>
+      <c r="T260">
+        <v>0</v>
+      </c>
+      <c r="U260">
+        <v>17</v>
+      </c>
+      <c r="V260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>304</v>
+      </c>
+      <c r="B261" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C261" t="s">
+        <v>19</v>
+      </c>
+      <c r="E261" t="s">
+        <v>46</v>
+      </c>
+      <c r="F261" t="s">
+        <v>24</v>
+      </c>
+      <c r="G261" t="s">
+        <v>300</v>
+      </c>
+      <c r="H261">
+        <v>9.02</v>
+      </c>
+      <c r="I261">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J261">
+        <v>7.85</v>
+      </c>
+      <c r="K261">
+        <v>0.76</v>
+      </c>
+      <c r="L261">
+        <v>0.32</v>
+      </c>
+      <c r="M261">
+        <v>0.08</v>
+      </c>
+      <c r="N261">
+        <v>0</v>
+      </c>
+      <c r="O261">
+        <v>8</v>
+      </c>
+      <c r="P261">
+        <v>5.39</v>
+      </c>
+      <c r="Q261">
+        <v>29.24</v>
+      </c>
+      <c r="R261">
+        <v>4.76</v>
+      </c>
+      <c r="S261">
+        <v>25</v>
+      </c>
+      <c r="T261">
+        <v>3</v>
+      </c>
+      <c r="U261">
+        <v>26</v>
+      </c>
+      <c r="V261">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>304</v>
+      </c>
+      <c r="B262" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C262" t="s">
+        <v>19</v>
+      </c>
+      <c r="E262" t="s">
+        <v>86</v>
+      </c>
+      <c r="F262" t="s">
+        <v>27</v>
+      </c>
+      <c r="G262" t="s">
+        <v>301</v>
+      </c>
+      <c r="H262">
+        <v>8.32</v>
+      </c>
+      <c r="I262">
+        <v>1.25</v>
+      </c>
+      <c r="J262">
+        <v>7.05</v>
+      </c>
+      <c r="K262">
+        <v>0.93</v>
+      </c>
+      <c r="L262">
+        <v>0.33</v>
+      </c>
+      <c r="M262">
+        <v>0.01</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262">
+        <v>3</v>
+      </c>
+      <c r="P262">
+        <v>6.02</v>
+      </c>
+      <c r="Q262">
+        <v>25.97</v>
+      </c>
+      <c r="R262">
+        <v>4.71</v>
+      </c>
+      <c r="S262">
+        <v>28</v>
+      </c>
+      <c r="T262">
+        <v>6</v>
+      </c>
+      <c r="U262">
+        <v>28</v>
+      </c>
+      <c r="V262">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>304</v>
+      </c>
+      <c r="B263" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C263" t="s">
+        <v>19</v>
+      </c>
+      <c r="E263" t="s">
+        <v>170</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G263" t="s">
+        <v>302</v>
+      </c>
+      <c r="H263">
+        <v>7.04</v>
+      </c>
+      <c r="I263">
+        <v>1.47</v>
+      </c>
+      <c r="J263">
+        <v>5.54</v>
+      </c>
+      <c r="K263">
+        <v>0.85</v>
+      </c>
+      <c r="L263">
+        <v>0.47</v>
+      </c>
+      <c r="M263">
+        <v>0.15</v>
+      </c>
+      <c r="N263">
+        <v>0.01</v>
+      </c>
+      <c r="O263">
+        <v>10</v>
+      </c>
+      <c r="P263">
+        <v>5.85</v>
+      </c>
+      <c r="Q263">
+        <v>30.9</v>
+      </c>
+      <c r="R263">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S263">
+        <v>39</v>
+      </c>
+      <c r="T263">
+        <v>9</v>
+      </c>
+      <c r="U263">
+        <v>23</v>
+      </c>
+      <c r="V263">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="264" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>304</v>
+      </c>
+      <c r="B264" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C264" t="s">
+        <v>19</v>
+      </c>
+      <c r="E264" t="s">
+        <v>16</v>
+      </c>
+      <c r="F264" t="s">
+        <v>25</v>
+      </c>
+      <c r="G264" t="s">
+        <v>303</v>
+      </c>
+      <c r="H264">
+        <v>6.25</v>
+      </c>
+      <c r="I264">
+        <v>1.03</v>
+      </c>
+      <c r="J264">
+        <v>5.2</v>
+      </c>
+      <c r="K264">
+        <v>0.7</v>
+      </c>
+      <c r="L264">
+        <v>0.32</v>
+      </c>
+      <c r="M264">
+        <v>0.04</v>
+      </c>
+      <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>5</v>
+      </c>
+      <c r="P264">
+        <v>5.33</v>
+      </c>
+      <c r="Q264">
+        <v>27.44</v>
+      </c>
+      <c r="R264">
+        <v>4.78</v>
+      </c>
+      <c r="S264">
+        <v>27</v>
+      </c>
+      <c r="T264">
+        <v>7</v>
+      </c>
+      <c r="U264">
+        <v>33</v>
+      </c>
+      <c r="V264">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="265" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>304</v>
+      </c>
+      <c r="B265" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C265" t="s">
+        <v>19</v>
+      </c>
+      <c r="E265" t="s">
+        <v>94</v>
+      </c>
+      <c r="F265" t="s">
+        <v>103</v>
+      </c>
+      <c r="G265" t="s">
+        <v>300</v>
+      </c>
+      <c r="H265">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="I265">
+        <v>1.6</v>
+      </c>
+      <c r="J265">
+        <v>8.09</v>
+      </c>
+      <c r="K265">
+        <v>1.19</v>
+      </c>
+      <c r="L265">
+        <v>0.37</v>
+      </c>
+      <c r="M265">
+        <v>0.06</v>
+      </c>
+      <c r="N265">
+        <v>0</v>
+      </c>
+      <c r="O265">
+        <v>7</v>
+      </c>
+      <c r="P265">
+        <v>5.73</v>
+      </c>
+      <c r="Q265">
+        <v>27.97</v>
+      </c>
+      <c r="R265">
+        <v>4.26</v>
+      </c>
+      <c r="S265">
+        <v>41</v>
+      </c>
+      <c r="T265">
+        <v>6</v>
+      </c>
+      <c r="U265">
+        <v>34</v>
+      </c>
+      <c r="V265">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>312</v>
+      </c>
+      <c r="B266" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C266" t="s">
+        <v>19</v>
+      </c>
+      <c r="E266" t="s">
+        <v>89</v>
+      </c>
+      <c r="F266" t="s">
+        <v>24</v>
+      </c>
+      <c r="G266" t="s">
+        <v>305</v>
+      </c>
+      <c r="H266">
+        <v>7.04</v>
+      </c>
+      <c r="I266">
+        <v>0.88</v>
+      </c>
+      <c r="J266">
+        <v>6.15</v>
+      </c>
+      <c r="K266">
+        <v>0.59</v>
+      </c>
+      <c r="L266">
+        <v>0.21</v>
+      </c>
+      <c r="M266">
+        <v>0.08</v>
+      </c>
+      <c r="N266">
+        <v>0.01</v>
+      </c>
+      <c r="O266">
+        <v>6</v>
+      </c>
+      <c r="P266">
+        <v>5.88</v>
+      </c>
+      <c r="Q266">
+        <v>31.65</v>
+      </c>
+      <c r="R266">
+        <v>4.12</v>
+      </c>
+      <c r="S266">
+        <v>18</v>
+      </c>
+      <c r="T266">
+        <v>3</v>
+      </c>
+      <c r="U266">
+        <v>8</v>
+      </c>
+      <c r="V266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>312</v>
+      </c>
+      <c r="B267" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C267" t="s">
+        <v>19</v>
+      </c>
+      <c r="E267" t="s">
+        <v>97</v>
+      </c>
+      <c r="F267" t="s">
+        <v>101</v>
+      </c>
+      <c r="G267" t="s">
+        <v>306</v>
+      </c>
+      <c r="H267">
+        <v>7.4</v>
+      </c>
+      <c r="I267">
+        <v>1.66</v>
+      </c>
+      <c r="J267">
+        <v>5.71</v>
+      </c>
+      <c r="K267">
+        <v>1.03</v>
+      </c>
+      <c r="L267">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M267">
+        <v>0.11</v>
+      </c>
+      <c r="N267">
+        <v>0</v>
+      </c>
+      <c r="O267">
+        <v>14</v>
+      </c>
+      <c r="P267">
+        <v>6.78</v>
+      </c>
+      <c r="Q267">
+        <v>27.33</v>
+      </c>
+      <c r="R267">
+        <v>4.97</v>
+      </c>
+      <c r="S267">
+        <v>43</v>
+      </c>
+      <c r="T267">
+        <v>13</v>
+      </c>
+      <c r="U267">
+        <v>32</v>
+      </c>
+      <c r="V267">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>312</v>
+      </c>
+      <c r="B268" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C268" t="s">
+        <v>19</v>
+      </c>
+      <c r="E268" t="s">
+        <v>87</v>
+      </c>
+      <c r="F268" t="s">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>307</v>
+      </c>
+      <c r="H268">
+        <v>10.88</v>
+      </c>
+      <c r="I268">
+        <v>1.91</v>
+      </c>
+      <c r="J268">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="K268">
+        <v>1.59</v>
+      </c>
+      <c r="L268">
+        <v>0.31</v>
+      </c>
+      <c r="M268">
+        <v>0.03</v>
+      </c>
+      <c r="N268">
+        <v>0</v>
+      </c>
+      <c r="O268">
+        <v>2</v>
+      </c>
+      <c r="P268">
+        <v>6.79</v>
+      </c>
+      <c r="Q268">
+        <v>28.95</v>
+      </c>
+      <c r="R268">
+        <v>4.3</v>
+      </c>
+      <c r="S268">
+        <v>32</v>
+      </c>
+      <c r="T268">
+        <v>7</v>
+      </c>
+      <c r="U268">
+        <v>16</v>
+      </c>
+      <c r="V268">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>312</v>
+      </c>
+      <c r="B269" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C269" t="s">
+        <v>19</v>
+      </c>
+      <c r="E269" t="s">
+        <v>99</v>
+      </c>
+      <c r="F269" t="s">
+        <v>27</v>
+      </c>
+      <c r="G269" t="s">
+        <v>308</v>
+      </c>
+      <c r="H269">
+        <v>11.13</v>
+      </c>
+      <c r="I269">
+        <v>1.78</v>
+      </c>
+      <c r="J269">
+        <v>9.33</v>
+      </c>
+      <c r="K269">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="L269">
+        <v>0.44</v>
+      </c>
+      <c r="M269">
+        <v>0.19</v>
+      </c>
+      <c r="N269">
+        <v>0.01</v>
+      </c>
+      <c r="O269">
+        <v>12</v>
+      </c>
+      <c r="P269">
+        <v>6.81</v>
+      </c>
+      <c r="Q269">
+        <v>30.65</v>
+      </c>
+      <c r="R269">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="S269">
+        <v>30</v>
+      </c>
+      <c r="T269">
+        <v>5</v>
+      </c>
+      <c r="U269">
+        <v>27</v>
+      </c>
+      <c r="V269">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>312</v>
+      </c>
+      <c r="B270" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C270" t="s">
+        <v>19</v>
+      </c>
+      <c r="E270" t="s">
+        <v>163</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G270" t="s">
+        <v>309</v>
+      </c>
+      <c r="H270">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I270">
+        <v>1.75</v>
+      </c>
+      <c r="J270">
+        <v>8.11</v>
+      </c>
+      <c r="K270">
+        <v>0.98</v>
+      </c>
+      <c r="L270">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M270">
+        <v>0.22</v>
+      </c>
+      <c r="N270">
+        <v>0.01</v>
+      </c>
+      <c r="O270">
+        <v>16</v>
+      </c>
+      <c r="P270">
+        <v>6.22</v>
+      </c>
+      <c r="Q270">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="R270">
+        <v>5.08</v>
+      </c>
+      <c r="S270">
+        <v>45</v>
+      </c>
+      <c r="T270">
+        <v>16</v>
+      </c>
+      <c r="U270">
+        <v>36</v>
+      </c>
+      <c r="V270">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="271" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>312</v>
+      </c>
+      <c r="B271" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C271" t="s">
+        <v>19</v>
+      </c>
+      <c r="E271" t="s">
+        <v>98</v>
+      </c>
+      <c r="F271" t="s">
+        <v>27</v>
+      </c>
+      <c r="G271" t="s">
+        <v>310</v>
+      </c>
+      <c r="H271">
+        <v>10.06</v>
+      </c>
+      <c r="I271">
+        <v>1.35</v>
+      </c>
+      <c r="J271">
+        <v>8.69</v>
+      </c>
+      <c r="K271">
+        <v>0.97</v>
+      </c>
+      <c r="L271">
+        <v>0.34</v>
+      </c>
+      <c r="M271">
+        <v>0.06</v>
+      </c>
+      <c r="N271">
+        <v>0</v>
+      </c>
+      <c r="O271">
+        <v>8</v>
+      </c>
+      <c r="P271">
+        <v>6.29</v>
+      </c>
+      <c r="Q271">
+        <v>26.47</v>
+      </c>
+      <c r="R271">
+        <v>4.05</v>
+      </c>
+      <c r="S271">
+        <v>34</v>
+      </c>
+      <c r="T271">
+        <v>2</v>
+      </c>
+      <c r="U271">
+        <v>25</v>
+      </c>
+      <c r="V271">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>312</v>
+      </c>
+      <c r="B272" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C272" t="s">
+        <v>19</v>
+      </c>
+      <c r="E272" t="s">
+        <v>166</v>
+      </c>
+      <c r="F272" t="s">
+        <v>101</v>
+      </c>
+      <c r="G272" t="s">
+        <v>311</v>
+      </c>
+      <c r="H272">
+        <v>9.66</v>
+      </c>
+      <c r="I272">
+        <v>1.64</v>
+      </c>
+      <c r="J272">
+        <v>8</v>
+      </c>
+      <c r="K272">
+        <v>0.97</v>
+      </c>
+      <c r="L272">
+        <v>0.52</v>
+      </c>
+      <c r="M272">
+        <v>0.16</v>
+      </c>
+      <c r="N272">
+        <v>0.01</v>
+      </c>
+      <c r="O272">
+        <v>13</v>
+      </c>
+      <c r="P272">
+        <v>6.42</v>
+      </c>
+      <c r="Q272">
+        <v>30.71</v>
+      </c>
+      <c r="R272">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="S272">
+        <v>50</v>
+      </c>
+      <c r="T272">
+        <v>6</v>
+      </c>
+      <c r="U272">
+        <v>29</v>
+      </c>
+      <c r="V272">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DDAA31-8B9C-7643-8C0E-6E1CDA6D4EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0ABCED-EB7F-E342-8873-C70E6492A682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="321">
   <si>
     <t>Temps joué</t>
   </si>
@@ -974,6 +974,30 @@
   </si>
   <si>
     <t>Match Amical VS Réserve 15/08/2026</t>
+  </si>
+  <si>
+    <t>01:18:06</t>
+  </si>
+  <si>
+    <t>Sofiane Belkheir</t>
+  </si>
+  <si>
+    <t>01:17:51</t>
+  </si>
+  <si>
+    <t>01:18:48</t>
+  </si>
+  <si>
+    <t>01:17:45</t>
+  </si>
+  <si>
+    <t>01:19:10</t>
+  </si>
+  <si>
+    <t>01:19:03</t>
+  </si>
+  <si>
+    <t>01:16:53</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V272"/>
+  <dimension ref="A1:V279"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -19040,6 +19064,461 @@
         <v>6</v>
       </c>
     </row>
+    <row r="273" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>22</v>
+      </c>
+      <c r="B273" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C273" t="s">
+        <v>19</v>
+      </c>
+      <c r="E273" t="s">
+        <v>16</v>
+      </c>
+      <c r="F273" t="s">
+        <v>25</v>
+      </c>
+      <c r="G273" t="s">
+        <v>313</v>
+      </c>
+      <c r="H273">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I273">
+        <v>0.42</v>
+      </c>
+      <c r="J273">
+        <v>4.63</v>
+      </c>
+      <c r="K273">
+        <v>0.3</v>
+      </c>
+      <c r="L273">
+        <v>0.1</v>
+      </c>
+      <c r="M273">
+        <v>0.03</v>
+      </c>
+      <c r="N273">
+        <v>0</v>
+      </c>
+      <c r="O273">
+        <v>1</v>
+      </c>
+      <c r="P273">
+        <v>3.78</v>
+      </c>
+      <c r="Q273">
+        <v>28.16</v>
+      </c>
+      <c r="R273">
+        <v>4.93</v>
+      </c>
+      <c r="S273">
+        <v>33</v>
+      </c>
+      <c r="T273">
+        <v>5</v>
+      </c>
+      <c r="U273">
+        <v>31</v>
+      </c>
+      <c r="V273">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>22</v>
+      </c>
+      <c r="B274" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C274" t="s">
+        <v>19</v>
+      </c>
+      <c r="E274" t="s">
+        <v>314</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G274" t="s">
+        <v>315</v>
+      </c>
+      <c r="H274">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="I274">
+        <v>0.33</v>
+      </c>
+      <c r="J274">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="K274">
+        <v>0.22</v>
+      </c>
+      <c r="L274">
+        <v>0.09</v>
+      </c>
+      <c r="M274">
+        <v>0.02</v>
+      </c>
+      <c r="N274">
+        <v>0</v>
+      </c>
+      <c r="O274">
+        <v>2</v>
+      </c>
+      <c r="P274">
+        <v>3.75</v>
+      </c>
+      <c r="Q274">
+        <v>27.64</v>
+      </c>
+      <c r="R274">
+        <v>4.72</v>
+      </c>
+      <c r="S274">
+        <v>19</v>
+      </c>
+      <c r="T274">
+        <v>3</v>
+      </c>
+      <c r="U274">
+        <v>12</v>
+      </c>
+      <c r="V274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>22</v>
+      </c>
+      <c r="B275" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C275" t="s">
+        <v>19</v>
+      </c>
+      <c r="E275" t="s">
+        <v>86</v>
+      </c>
+      <c r="F275" t="s">
+        <v>27</v>
+      </c>
+      <c r="G275" t="s">
+        <v>316</v>
+      </c>
+      <c r="H275">
+        <v>5.22</v>
+      </c>
+      <c r="I275">
+        <v>0.34</v>
+      </c>
+      <c r="J275">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="K275">
+        <v>0.32</v>
+      </c>
+      <c r="L275">
+        <v>0.03</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
+      </c>
+      <c r="N275">
+        <v>0</v>
+      </c>
+      <c r="O275">
+        <v>2</v>
+      </c>
+      <c r="P275">
+        <v>3.38</v>
+      </c>
+      <c r="Q275">
+        <v>25.88</v>
+      </c>
+      <c r="R275">
+        <v>5.94</v>
+      </c>
+      <c r="S275">
+        <v>62</v>
+      </c>
+      <c r="T275">
+        <v>13</v>
+      </c>
+      <c r="U275">
+        <v>51</v>
+      </c>
+      <c r="V275">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="276" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>22</v>
+      </c>
+      <c r="B276" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C276" t="s">
+        <v>19</v>
+      </c>
+      <c r="E276" t="s">
+        <v>46</v>
+      </c>
+      <c r="F276" t="s">
+        <v>24</v>
+      </c>
+      <c r="G276" t="s">
+        <v>317</v>
+      </c>
+      <c r="H276">
+        <v>5.17</v>
+      </c>
+      <c r="I276">
+        <v>0.24</v>
+      </c>
+      <c r="J276">
+        <v>4.92</v>
+      </c>
+      <c r="K276">
+        <v>0.21</v>
+      </c>
+      <c r="L276">
+        <v>0.04</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
+      </c>
+      <c r="N276">
+        <v>0</v>
+      </c>
+      <c r="O276">
+        <v>0</v>
+      </c>
+      <c r="P276">
+        <v>3.5</v>
+      </c>
+      <c r="Q276">
+        <v>23.23</v>
+      </c>
+      <c r="R276">
+        <v>4.51</v>
+      </c>
+      <c r="S276">
+        <v>38</v>
+      </c>
+      <c r="T276">
+        <v>7</v>
+      </c>
+      <c r="U276">
+        <v>23</v>
+      </c>
+      <c r="V276">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="277" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>22</v>
+      </c>
+      <c r="B277" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C277" t="s">
+        <v>19</v>
+      </c>
+      <c r="E277" t="s">
+        <v>87</v>
+      </c>
+      <c r="F277" t="s">
+        <v>27</v>
+      </c>
+      <c r="G277" t="s">
+        <v>318</v>
+      </c>
+      <c r="H277">
+        <v>5.38</v>
+      </c>
+      <c r="I277">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J277">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="K277">
+        <v>0.5</v>
+      </c>
+      <c r="L277">
+        <v>0.08</v>
+      </c>
+      <c r="M277">
+        <v>0</v>
+      </c>
+      <c r="N277">
+        <v>0</v>
+      </c>
+      <c r="O277">
+        <v>0</v>
+      </c>
+      <c r="P277">
+        <v>4</v>
+      </c>
+      <c r="Q277">
+        <v>24.39</v>
+      </c>
+      <c r="R277">
+        <v>4.32</v>
+      </c>
+      <c r="S277">
+        <v>28</v>
+      </c>
+      <c r="T277">
+        <v>2</v>
+      </c>
+      <c r="U277">
+        <v>23</v>
+      </c>
+      <c r="V277">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>22</v>
+      </c>
+      <c r="B278" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C278" t="s">
+        <v>19</v>
+      </c>
+      <c r="E278" t="s">
+        <v>98</v>
+      </c>
+      <c r="F278" t="s">
+        <v>27</v>
+      </c>
+      <c r="G278" t="s">
+        <v>319</v>
+      </c>
+      <c r="H278">
+        <v>5.34</v>
+      </c>
+      <c r="I278">
+        <v>0.48</v>
+      </c>
+      <c r="J278">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="K278">
+        <v>0.44</v>
+      </c>
+      <c r="L278">
+        <v>0.05</v>
+      </c>
+      <c r="M278">
+        <v>0</v>
+      </c>
+      <c r="N278">
+        <v>0</v>
+      </c>
+      <c r="O278">
+        <v>0</v>
+      </c>
+      <c r="P278">
+        <v>3.95</v>
+      </c>
+      <c r="Q278">
+        <v>22.1</v>
+      </c>
+      <c r="R278">
+        <v>4.12</v>
+      </c>
+      <c r="S278">
+        <v>27</v>
+      </c>
+      <c r="T278">
+        <v>2</v>
+      </c>
+      <c r="U278">
+        <v>25</v>
+      </c>
+      <c r="V278">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>22</v>
+      </c>
+      <c r="B279" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C279" t="s">
+        <v>19</v>
+      </c>
+      <c r="E279" t="s">
+        <v>53</v>
+      </c>
+      <c r="F279" t="s">
+        <v>27</v>
+      </c>
+      <c r="G279" t="s">
+        <v>320</v>
+      </c>
+      <c r="H279">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="I279">
+        <v>0.34</v>
+      </c>
+      <c r="J279">
+        <v>4.46</v>
+      </c>
+      <c r="K279">
+        <v>0.32</v>
+      </c>
+      <c r="L279">
+        <v>0.03</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>0</v>
+      </c>
+      <c r="O279">
+        <v>0</v>
+      </c>
+      <c r="P279">
+        <v>3.7</v>
+      </c>
+      <c r="Q279">
+        <v>24.15</v>
+      </c>
+      <c r="R279">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="S279">
+        <v>8</v>
+      </c>
+      <c r="T279">
+        <v>1</v>
+      </c>
+      <c r="U279">
+        <v>15</v>
+      </c>
+      <c r="V279">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0ABCED-EB7F-E342-8873-C70E6492A682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA48C6E-F29B-D545-B340-300D4A7EE3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="341">
   <si>
     <t>Temps joué</t>
   </si>
@@ -998,6 +998,66 @@
   </si>
   <si>
     <t>01:16:53</t>
+  </si>
+  <si>
+    <t>01:14:46</t>
+  </si>
+  <si>
+    <t>01:15:18</t>
+  </si>
+  <si>
+    <t>01:11:15</t>
+  </si>
+  <si>
+    <t>01:12:38</t>
+  </si>
+  <si>
+    <t>01:15:25</t>
+  </si>
+  <si>
+    <t>00:51:03</t>
+  </si>
+  <si>
+    <t>01:16:15</t>
+  </si>
+  <si>
+    <t>00:52:44</t>
+  </si>
+  <si>
+    <t>01:26:57</t>
+  </si>
+  <si>
+    <t>01:37:38</t>
+  </si>
+  <si>
+    <t>01:14:34</t>
+  </si>
+  <si>
+    <t>00:49:55</t>
+  </si>
+  <si>
+    <t>01:36:07</t>
+  </si>
+  <si>
+    <t>01:25:38</t>
+  </si>
+  <si>
+    <t>01:07:41</t>
+  </si>
+  <si>
+    <t>01:37:35</t>
+  </si>
+  <si>
+    <t>01:37:08</t>
+  </si>
+  <si>
+    <t>01:37:48</t>
+  </si>
+  <si>
+    <t>01:33:55</t>
+  </si>
+  <si>
+    <t>Match Amical VS Charvieux 21/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V279"/>
+  <dimension ref="A1:V301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -19519,6 +19579,1436 @@
         <v>4</v>
       </c>
     </row>
+    <row r="280" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>22</v>
+      </c>
+      <c r="B280" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C280" t="s">
+        <v>19</v>
+      </c>
+      <c r="E280" t="s">
+        <v>16</v>
+      </c>
+      <c r="F280" t="s">
+        <v>25</v>
+      </c>
+      <c r="G280" t="s">
+        <v>321</v>
+      </c>
+      <c r="H280">
+        <v>4.72</v>
+      </c>
+      <c r="I280">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J280">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="K280">
+        <v>0.3</v>
+      </c>
+      <c r="L280">
+        <v>0.2</v>
+      </c>
+      <c r="M280">
+        <v>0.08</v>
+      </c>
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280">
+        <v>11</v>
+      </c>
+      <c r="P280">
+        <v>3.7</v>
+      </c>
+      <c r="Q280">
+        <v>27.25</v>
+      </c>
+      <c r="R280">
+        <v>5.08</v>
+      </c>
+      <c r="S280">
+        <v>26</v>
+      </c>
+      <c r="T280">
+        <v>11</v>
+      </c>
+      <c r="U280">
+        <v>32</v>
+      </c>
+      <c r="V280">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>22</v>
+      </c>
+      <c r="B281" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C281" t="s">
+        <v>19</v>
+      </c>
+      <c r="E281" t="s">
+        <v>86</v>
+      </c>
+      <c r="F281" t="s">
+        <v>27</v>
+      </c>
+      <c r="G281" t="s">
+        <v>322</v>
+      </c>
+      <c r="H281">
+        <v>5.29</v>
+      </c>
+      <c r="I281">
+        <v>0.33</v>
+      </c>
+      <c r="J281">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="K281">
+        <v>0.31</v>
+      </c>
+      <c r="L281">
+        <v>0.05</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
+        <v>0</v>
+      </c>
+      <c r="O281">
+        <v>0</v>
+      </c>
+      <c r="P281">
+        <v>3.67</v>
+      </c>
+      <c r="Q281">
+        <v>24.09</v>
+      </c>
+      <c r="R281">
+        <v>5.71</v>
+      </c>
+      <c r="S281">
+        <v>85</v>
+      </c>
+      <c r="T281">
+        <v>18</v>
+      </c>
+      <c r="U281">
+        <v>54</v>
+      </c>
+      <c r="V281">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="282" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>22</v>
+      </c>
+      <c r="B282" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C282" t="s">
+        <v>19</v>
+      </c>
+      <c r="E282" t="s">
+        <v>314</v>
+      </c>
+      <c r="F282" t="s">
+        <v>103</v>
+      </c>
+      <c r="G282" t="s">
+        <v>323</v>
+      </c>
+      <c r="H282">
+        <v>4.05</v>
+      </c>
+      <c r="I282">
+        <v>0.25</v>
+      </c>
+      <c r="J282">
+        <v>3.79</v>
+      </c>
+      <c r="K282">
+        <v>0.15</v>
+      </c>
+      <c r="L282">
+        <v>0.09</v>
+      </c>
+      <c r="M282">
+        <v>0.02</v>
+      </c>
+      <c r="N282">
+        <v>0</v>
+      </c>
+      <c r="O282">
+        <v>2</v>
+      </c>
+      <c r="P282">
+        <v>3.15</v>
+      </c>
+      <c r="Q282">
+        <v>27.45</v>
+      </c>
+      <c r="R282">
+        <v>5.03</v>
+      </c>
+      <c r="S282">
+        <v>17</v>
+      </c>
+      <c r="T282">
+        <v>3</v>
+      </c>
+      <c r="U282">
+        <v>8</v>
+      </c>
+      <c r="V282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>22</v>
+      </c>
+      <c r="B283" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C283" t="s">
+        <v>19</v>
+      </c>
+      <c r="E283" t="s">
+        <v>87</v>
+      </c>
+      <c r="F283" t="s">
+        <v>27</v>
+      </c>
+      <c r="G283" t="s">
+        <v>324</v>
+      </c>
+      <c r="H283">
+        <v>5.26</v>
+      </c>
+      <c r="I283">
+        <v>0.39</v>
+      </c>
+      <c r="J283">
+        <v>4.87</v>
+      </c>
+      <c r="K283">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L283">
+        <v>0.1</v>
+      </c>
+      <c r="M283">
+        <v>0.02</v>
+      </c>
+      <c r="N283">
+        <v>0</v>
+      </c>
+      <c r="O283">
+        <v>1</v>
+      </c>
+      <c r="P283">
+        <v>4.3</v>
+      </c>
+      <c r="Q283">
+        <v>28.46</v>
+      </c>
+      <c r="R283">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S283">
+        <v>28</v>
+      </c>
+      <c r="T283">
+        <v>3</v>
+      </c>
+      <c r="U283">
+        <v>20</v>
+      </c>
+      <c r="V283">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>22</v>
+      </c>
+      <c r="B284" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C284" t="s">
+        <v>19</v>
+      </c>
+      <c r="E284" t="s">
+        <v>98</v>
+      </c>
+      <c r="F284" t="s">
+        <v>27</v>
+      </c>
+      <c r="G284" t="s">
+        <v>325</v>
+      </c>
+      <c r="H284">
+        <v>5.03</v>
+      </c>
+      <c r="I284">
+        <v>0.24</v>
+      </c>
+      <c r="J284">
+        <v>4.79</v>
+      </c>
+      <c r="K284">
+        <v>0.18</v>
+      </c>
+      <c r="L284">
+        <v>0.05</v>
+      </c>
+      <c r="M284">
+        <v>0.01</v>
+      </c>
+      <c r="N284">
+        <v>0</v>
+      </c>
+      <c r="O284">
+        <v>2</v>
+      </c>
+      <c r="P284">
+        <v>3.76</v>
+      </c>
+      <c r="Q284">
+        <v>25.89</v>
+      </c>
+      <c r="R284">
+        <v>3.71</v>
+      </c>
+      <c r="S284">
+        <v>23</v>
+      </c>
+      <c r="T284">
+        <v>0</v>
+      </c>
+      <c r="U284">
+        <v>15</v>
+      </c>
+      <c r="V284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>22</v>
+      </c>
+      <c r="B285" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C285" t="s">
+        <v>19</v>
+      </c>
+      <c r="E285" t="s">
+        <v>46</v>
+      </c>
+      <c r="F285" t="s">
+        <v>24</v>
+      </c>
+      <c r="G285" t="s">
+        <v>326</v>
+      </c>
+      <c r="H285">
+        <v>3.58</v>
+      </c>
+      <c r="I285">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J285">
+        <v>3.44</v>
+      </c>
+      <c r="K285">
+        <v>0.09</v>
+      </c>
+      <c r="L285">
+        <v>0.03</v>
+      </c>
+      <c r="M285">
+        <v>0.02</v>
+      </c>
+      <c r="N285">
+        <v>0</v>
+      </c>
+      <c r="O285">
+        <v>2</v>
+      </c>
+      <c r="P285">
+        <v>3.47</v>
+      </c>
+      <c r="Q285">
+        <v>28.62</v>
+      </c>
+      <c r="R285">
+        <v>5.42</v>
+      </c>
+      <c r="S285">
+        <v>30</v>
+      </c>
+      <c r="T285">
+        <v>6</v>
+      </c>
+      <c r="U285">
+        <v>17</v>
+      </c>
+      <c r="V285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>22</v>
+      </c>
+      <c r="B286" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C286" t="s">
+        <v>19</v>
+      </c>
+      <c r="E286" t="s">
+        <v>53</v>
+      </c>
+      <c r="F286" t="s">
+        <v>27</v>
+      </c>
+      <c r="G286" t="s">
+        <v>327</v>
+      </c>
+      <c r="H286">
+        <v>5.03</v>
+      </c>
+      <c r="I286">
+        <v>0.49</v>
+      </c>
+      <c r="J286">
+        <v>4.53</v>
+      </c>
+      <c r="K286">
+        <v>0.33</v>
+      </c>
+      <c r="L286">
+        <v>0.16</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
+      </c>
+      <c r="N286">
+        <v>0</v>
+      </c>
+      <c r="O286">
+        <v>0</v>
+      </c>
+      <c r="P286">
+        <v>3.9</v>
+      </c>
+      <c r="Q286">
+        <v>24.86</v>
+      </c>
+      <c r="R286">
+        <v>4.5</v>
+      </c>
+      <c r="S286">
+        <v>9</v>
+      </c>
+      <c r="T286">
+        <v>3</v>
+      </c>
+      <c r="U286">
+        <v>7</v>
+      </c>
+      <c r="V286">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>22</v>
+      </c>
+      <c r="B287" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C287" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" t="s">
+        <v>53</v>
+      </c>
+      <c r="F287" t="s">
+        <v>27</v>
+      </c>
+      <c r="G287" t="s">
+        <v>328</v>
+      </c>
+      <c r="H287">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="I287">
+        <v>0.24</v>
+      </c>
+      <c r="J287">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="K287">
+        <v>0.1</v>
+      </c>
+      <c r="L287">
+        <v>0.04</v>
+      </c>
+      <c r="M287">
+        <v>0.1</v>
+      </c>
+      <c r="N287">
+        <v>0</v>
+      </c>
+      <c r="O287">
+        <v>4</v>
+      </c>
+      <c r="P287">
+        <v>2.72</v>
+      </c>
+      <c r="Q287">
+        <v>29.87</v>
+      </c>
+      <c r="R287">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="S287">
+        <v>6</v>
+      </c>
+      <c r="T287">
+        <v>1</v>
+      </c>
+      <c r="U287">
+        <v>5</v>
+      </c>
+      <c r="V287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>22</v>
+      </c>
+      <c r="B288" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C288" t="s">
+        <v>19</v>
+      </c>
+      <c r="E288" t="s">
+        <v>16</v>
+      </c>
+      <c r="F288" t="s">
+        <v>25</v>
+      </c>
+      <c r="G288" t="s">
+        <v>329</v>
+      </c>
+      <c r="H288">
+        <v>3.52</v>
+      </c>
+      <c r="I288">
+        <v>0.27</v>
+      </c>
+      <c r="J288">
+        <v>3.25</v>
+      </c>
+      <c r="K288">
+        <v>0.17</v>
+      </c>
+      <c r="L288">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M288">
+        <v>0.04</v>
+      </c>
+      <c r="N288">
+        <v>0</v>
+      </c>
+      <c r="O288">
+        <v>2</v>
+      </c>
+      <c r="P288">
+        <v>2.33</v>
+      </c>
+      <c r="Q288">
+        <v>28.48</v>
+      </c>
+      <c r="R288">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="S288">
+        <v>22</v>
+      </c>
+      <c r="T288">
+        <v>5</v>
+      </c>
+      <c r="U288">
+        <v>16</v>
+      </c>
+      <c r="V288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>22</v>
+      </c>
+      <c r="B289" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C289" t="s">
+        <v>19</v>
+      </c>
+      <c r="E289" t="s">
+        <v>86</v>
+      </c>
+      <c r="F289" t="s">
+        <v>27</v>
+      </c>
+      <c r="G289" t="s">
+        <v>245</v>
+      </c>
+      <c r="H289">
+        <v>3.6</v>
+      </c>
+      <c r="I289">
+        <v>0.35</v>
+      </c>
+      <c r="J289">
+        <v>3.24</v>
+      </c>
+      <c r="K289">
+        <v>0.16</v>
+      </c>
+      <c r="L289">
+        <v>0.08</v>
+      </c>
+      <c r="M289">
+        <v>0.08</v>
+      </c>
+      <c r="N289">
+        <v>0.03</v>
+      </c>
+      <c r="O289">
+        <v>6</v>
+      </c>
+      <c r="P289">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Q289">
+        <v>34.39</v>
+      </c>
+      <c r="R289">
+        <v>5.56</v>
+      </c>
+      <c r="S289">
+        <v>32</v>
+      </c>
+      <c r="T289">
+        <v>10</v>
+      </c>
+      <c r="U289">
+        <v>31</v>
+      </c>
+      <c r="V289">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="290" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>22</v>
+      </c>
+      <c r="B290" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C290" t="s">
+        <v>19</v>
+      </c>
+      <c r="E290" t="s">
+        <v>43</v>
+      </c>
+      <c r="F290" t="s">
+        <v>24</v>
+      </c>
+      <c r="G290" t="s">
+        <v>330</v>
+      </c>
+      <c r="H290">
+        <v>4.46</v>
+      </c>
+      <c r="I290">
+        <v>0.19</v>
+      </c>
+      <c r="J290">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="K290">
+        <v>0.16</v>
+      </c>
+      <c r="L290">
+        <v>0.04</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>0</v>
+      </c>
+      <c r="O290">
+        <v>0</v>
+      </c>
+      <c r="P290">
+        <v>2.66</v>
+      </c>
+      <c r="Q290">
+        <v>23.76</v>
+      </c>
+      <c r="R290">
+        <v>3.88</v>
+      </c>
+      <c r="S290">
+        <v>12</v>
+      </c>
+      <c r="T290">
+        <v>0</v>
+      </c>
+      <c r="U290">
+        <v>4</v>
+      </c>
+      <c r="V290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>22</v>
+      </c>
+      <c r="B291" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C291" t="s">
+        <v>19</v>
+      </c>
+      <c r="E291" t="s">
+        <v>87</v>
+      </c>
+      <c r="F291" t="s">
+        <v>27</v>
+      </c>
+      <c r="G291" t="s">
+        <v>187</v>
+      </c>
+      <c r="H291">
+        <v>4.78</v>
+      </c>
+      <c r="I291">
+        <v>0.59</v>
+      </c>
+      <c r="J291">
+        <v>4.18</v>
+      </c>
+      <c r="K291">
+        <v>0.43</v>
+      </c>
+      <c r="L291">
+        <v>0.1</v>
+      </c>
+      <c r="M291">
+        <v>0.06</v>
+      </c>
+      <c r="N291">
+        <v>0.01</v>
+      </c>
+      <c r="O291">
+        <v>4</v>
+      </c>
+      <c r="P291">
+        <v>2.97</v>
+      </c>
+      <c r="Q291">
+        <v>31.03</v>
+      </c>
+      <c r="R291">
+        <v>4.63</v>
+      </c>
+      <c r="S291">
+        <v>23</v>
+      </c>
+      <c r="T291">
+        <v>7</v>
+      </c>
+      <c r="U291">
+        <v>23</v>
+      </c>
+      <c r="V291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>22</v>
+      </c>
+      <c r="B292" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C292" t="s">
+        <v>19</v>
+      </c>
+      <c r="E292" t="s">
+        <v>98</v>
+      </c>
+      <c r="F292" t="s">
+        <v>27</v>
+      </c>
+      <c r="G292" t="s">
+        <v>55</v>
+      </c>
+      <c r="H292">
+        <v>3.27</v>
+      </c>
+      <c r="I292">
+        <v>0.42</v>
+      </c>
+      <c r="J292">
+        <v>2.85</v>
+      </c>
+      <c r="K292">
+        <v>0.23</v>
+      </c>
+      <c r="L292">
+        <v>0.11</v>
+      </c>
+      <c r="M292">
+        <v>0.06</v>
+      </c>
+      <c r="N292">
+        <v>0.03</v>
+      </c>
+      <c r="O292">
+        <v>4</v>
+      </c>
+      <c r="P292">
+        <v>2.59</v>
+      </c>
+      <c r="Q292">
+        <v>31.57</v>
+      </c>
+      <c r="R292">
+        <v>3.98</v>
+      </c>
+      <c r="S292">
+        <v>20</v>
+      </c>
+      <c r="T292">
+        <v>0</v>
+      </c>
+      <c r="U292">
+        <v>5</v>
+      </c>
+      <c r="V292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>22</v>
+      </c>
+      <c r="B293" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C293" t="s">
+        <v>19</v>
+      </c>
+      <c r="E293" t="s">
+        <v>46</v>
+      </c>
+      <c r="F293" t="s">
+        <v>24</v>
+      </c>
+      <c r="G293" t="s">
+        <v>331</v>
+      </c>
+      <c r="H293">
+        <v>3.78</v>
+      </c>
+      <c r="I293">
+        <v>0.25</v>
+      </c>
+      <c r="J293">
+        <v>3.53</v>
+      </c>
+      <c r="K293">
+        <v>0.11</v>
+      </c>
+      <c r="L293">
+        <v>0.06</v>
+      </c>
+      <c r="M293">
+        <v>0.06</v>
+      </c>
+      <c r="N293">
+        <v>0.03</v>
+      </c>
+      <c r="O293">
+        <v>4</v>
+      </c>
+      <c r="P293">
+        <v>2.39</v>
+      </c>
+      <c r="Q293">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="R293">
+        <v>5.12</v>
+      </c>
+      <c r="S293">
+        <v>23</v>
+      </c>
+      <c r="T293">
+        <v>5</v>
+      </c>
+      <c r="U293">
+        <v>14</v>
+      </c>
+      <c r="V293">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>22</v>
+      </c>
+      <c r="B294" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C294" t="s">
+        <v>19</v>
+      </c>
+      <c r="E294" t="s">
+        <v>314</v>
+      </c>
+      <c r="F294" t="s">
+        <v>103</v>
+      </c>
+      <c r="G294" t="s">
+        <v>332</v>
+      </c>
+      <c r="H294">
+        <v>2.36</v>
+      </c>
+      <c r="I294">
+        <v>0.32</v>
+      </c>
+      <c r="J294">
+        <v>2.04</v>
+      </c>
+      <c r="K294">
+        <v>0.17</v>
+      </c>
+      <c r="L294">
+        <v>0.1</v>
+      </c>
+      <c r="M294">
+        <v>0.05</v>
+      </c>
+      <c r="N294">
+        <v>0</v>
+      </c>
+      <c r="O294">
+        <v>6</v>
+      </c>
+      <c r="P294">
+        <v>2.68</v>
+      </c>
+      <c r="Q294">
+        <v>29.78</v>
+      </c>
+      <c r="R294">
+        <v>4.41</v>
+      </c>
+      <c r="S294">
+        <v>7</v>
+      </c>
+      <c r="T294">
+        <v>3</v>
+      </c>
+      <c r="U294">
+        <v>5</v>
+      </c>
+      <c r="V294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>340</v>
+      </c>
+      <c r="B295" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C295" t="s">
+        <v>19</v>
+      </c>
+      <c r="E295" t="s">
+        <v>84</v>
+      </c>
+      <c r="F295" t="s">
+        <v>24</v>
+      </c>
+      <c r="G295" t="s">
+        <v>333</v>
+      </c>
+      <c r="H295">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="I295">
+        <v>0.6</v>
+      </c>
+      <c r="J295">
+        <v>8.85</v>
+      </c>
+      <c r="K295">
+        <v>0.52</v>
+      </c>
+      <c r="L295">
+        <v>0.09</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
+      </c>
+      <c r="N295">
+        <v>0</v>
+      </c>
+      <c r="O295">
+        <v>0</v>
+      </c>
+      <c r="P295">
+        <v>5.8</v>
+      </c>
+      <c r="Q295">
+        <v>24.87</v>
+      </c>
+      <c r="R295">
+        <v>4.72</v>
+      </c>
+      <c r="S295">
+        <v>17</v>
+      </c>
+      <c r="T295">
+        <v>2</v>
+      </c>
+      <c r="U295">
+        <v>19</v>
+      </c>
+      <c r="V295">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>340</v>
+      </c>
+      <c r="B296" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C296" t="s">
+        <v>19</v>
+      </c>
+      <c r="E296" t="s">
+        <v>36</v>
+      </c>
+      <c r="F296" t="s">
+        <v>26</v>
+      </c>
+      <c r="G296" t="s">
+        <v>334</v>
+      </c>
+      <c r="H296">
+        <v>10.4</v>
+      </c>
+      <c r="I296">
+        <v>1.99</v>
+      </c>
+      <c r="J296">
+        <v>8.39</v>
+      </c>
+      <c r="K296">
+        <v>1.32</v>
+      </c>
+      <c r="L296">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M296">
+        <v>0.11</v>
+      </c>
+      <c r="N296">
+        <v>0</v>
+      </c>
+      <c r="O296">
+        <v>11</v>
+      </c>
+      <c r="P296">
+        <v>7.13</v>
+      </c>
+      <c r="Q296">
+        <v>29.92</v>
+      </c>
+      <c r="R296">
+        <v>4.87</v>
+      </c>
+      <c r="S296">
+        <v>34</v>
+      </c>
+      <c r="T296">
+        <v>12</v>
+      </c>
+      <c r="U296">
+        <v>30</v>
+      </c>
+      <c r="V296">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="297" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>340</v>
+      </c>
+      <c r="B297" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C297" t="s">
+        <v>19</v>
+      </c>
+      <c r="E297" t="s">
+        <v>97</v>
+      </c>
+      <c r="F297" t="s">
+        <v>101</v>
+      </c>
+      <c r="G297" t="s">
+        <v>335</v>
+      </c>
+      <c r="H297">
+        <v>7.61</v>
+      </c>
+      <c r="I297">
+        <v>1.4</v>
+      </c>
+      <c r="J297">
+        <v>6.19</v>
+      </c>
+      <c r="K297">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L297">
+        <v>0.25</v>
+      </c>
+      <c r="M297">
+        <v>0.06</v>
+      </c>
+      <c r="N297">
+        <v>0</v>
+      </c>
+      <c r="O297">
+        <v>3</v>
+      </c>
+      <c r="P297">
+        <v>6.61</v>
+      </c>
+      <c r="Q297">
+        <v>30.06</v>
+      </c>
+      <c r="R297">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S297">
+        <v>41</v>
+      </c>
+      <c r="T297">
+        <v>9</v>
+      </c>
+      <c r="U297">
+        <v>21</v>
+      </c>
+      <c r="V297">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>340</v>
+      </c>
+      <c r="B298" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C298" t="s">
+        <v>19</v>
+      </c>
+      <c r="E298" t="s">
+        <v>91</v>
+      </c>
+      <c r="F298" t="s">
+        <v>101</v>
+      </c>
+      <c r="G298" t="s">
+        <v>336</v>
+      </c>
+      <c r="H298">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="I298">
+        <v>1.62</v>
+      </c>
+      <c r="J298">
+        <v>7.57</v>
+      </c>
+      <c r="K298">
+        <v>0.92</v>
+      </c>
+      <c r="L298">
+        <v>0.48</v>
+      </c>
+      <c r="M298">
+        <v>0.23</v>
+      </c>
+      <c r="N298">
+        <v>0.02</v>
+      </c>
+      <c r="O298">
+        <v>13</v>
+      </c>
+      <c r="P298">
+        <v>5.58</v>
+      </c>
+      <c r="Q298">
+        <v>31.85</v>
+      </c>
+      <c r="R298">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="S298">
+        <v>45</v>
+      </c>
+      <c r="T298">
+        <v>5</v>
+      </c>
+      <c r="U298">
+        <v>29</v>
+      </c>
+      <c r="V298">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>340</v>
+      </c>
+      <c r="B299" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C299" t="s">
+        <v>19</v>
+      </c>
+      <c r="E299" t="s">
+        <v>35</v>
+      </c>
+      <c r="F299" t="s">
+        <v>27</v>
+      </c>
+      <c r="G299" t="s">
+        <v>337</v>
+      </c>
+      <c r="H299">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="I299">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J299">
+        <v>8.59</v>
+      </c>
+      <c r="K299">
+        <v>0.88</v>
+      </c>
+      <c r="L299">
+        <v>0.18</v>
+      </c>
+      <c r="M299">
+        <v>0.05</v>
+      </c>
+      <c r="N299">
+        <v>0</v>
+      </c>
+      <c r="O299">
+        <v>6</v>
+      </c>
+      <c r="P299">
+        <v>5.96</v>
+      </c>
+      <c r="Q299">
+        <v>30.23</v>
+      </c>
+      <c r="R299">
+        <v>4.55</v>
+      </c>
+      <c r="S299">
+        <v>25</v>
+      </c>
+      <c r="T299">
+        <v>4</v>
+      </c>
+      <c r="U299">
+        <v>37</v>
+      </c>
+      <c r="V299">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>340</v>
+      </c>
+      <c r="B300" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C300" t="s">
+        <v>19</v>
+      </c>
+      <c r="E300" t="s">
+        <v>314</v>
+      </c>
+      <c r="F300" t="s">
+        <v>103</v>
+      </c>
+      <c r="G300" t="s">
+        <v>338</v>
+      </c>
+      <c r="H300">
+        <v>9.42</v>
+      </c>
+      <c r="I300">
+        <v>1.41</v>
+      </c>
+      <c r="J300">
+        <v>7.99</v>
+      </c>
+      <c r="K300">
+        <v>0.96</v>
+      </c>
+      <c r="L300">
+        <v>0.39</v>
+      </c>
+      <c r="M300">
+        <v>0.08</v>
+      </c>
+      <c r="N300">
+        <v>0</v>
+      </c>
+      <c r="O300">
+        <v>9</v>
+      </c>
+      <c r="P300">
+        <v>5.67</v>
+      </c>
+      <c r="Q300">
+        <v>28.99</v>
+      </c>
+      <c r="R300">
+        <v>4.46</v>
+      </c>
+      <c r="S300">
+        <v>41</v>
+      </c>
+      <c r="T300">
+        <v>3</v>
+      </c>
+      <c r="U300">
+        <v>25</v>
+      </c>
+      <c r="V300">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>340</v>
+      </c>
+      <c r="B301" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C301" t="s">
+        <v>19</v>
+      </c>
+      <c r="E301" t="s">
+        <v>31</v>
+      </c>
+      <c r="F301" t="s">
+        <v>28</v>
+      </c>
+      <c r="G301" t="s">
+        <v>339</v>
+      </c>
+      <c r="H301">
+        <v>10.26</v>
+      </c>
+      <c r="I301">
+        <v>1.96</v>
+      </c>
+      <c r="J301">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="K301">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="L301">
+        <v>0.53</v>
+      </c>
+      <c r="M301">
+        <v>0.27</v>
+      </c>
+      <c r="N301">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O301">
+        <v>15</v>
+      </c>
+      <c r="P301">
+        <v>6.3</v>
+      </c>
+      <c r="Q301">
+        <v>31.55</v>
+      </c>
+      <c r="R301">
+        <v>5.15</v>
+      </c>
+      <c r="S301">
+        <v>48</v>
+      </c>
+      <c r="T301">
+        <v>14</v>
+      </c>
+      <c r="U301">
+        <v>41</v>
+      </c>
+      <c r="V301">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA48C6E-F29B-D545-B340-300D4A7EE3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE4E3E-1353-0747-AE77-D4D1D7A362D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="346">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1058,6 +1058,21 @@
   </si>
   <si>
     <t>Match Amical VS Charvieux 21/08/2026</t>
+  </si>
+  <si>
+    <t>01:13:22</t>
+  </si>
+  <si>
+    <t>01:40:14</t>
+  </si>
+  <si>
+    <t>01:41:01</t>
+  </si>
+  <si>
+    <t>01:46:27</t>
+  </si>
+  <si>
+    <t>N1 J1 VS Rumilly Valières 22/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1432,7 +1447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V301"/>
+  <dimension ref="A1:V307"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -20559,7 +20574,7 @@
         <v>340</v>
       </c>
       <c r="B295" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C295" t="s">
         <v>19</v>
@@ -20624,7 +20639,7 @@
         <v>340</v>
       </c>
       <c r="B296" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C296" t="s">
         <v>19</v>
@@ -20689,7 +20704,7 @@
         <v>340</v>
       </c>
       <c r="B297" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C297" t="s">
         <v>19</v>
@@ -20754,7 +20769,7 @@
         <v>340</v>
       </c>
       <c r="B298" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C298" t="s">
         <v>19</v>
@@ -20819,7 +20834,7 @@
         <v>340</v>
       </c>
       <c r="B299" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C299" t="s">
         <v>19</v>
@@ -20884,7 +20899,7 @@
         <v>340</v>
       </c>
       <c r="B300" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C300" t="s">
         <v>19</v>
@@ -20949,7 +20964,7 @@
         <v>340</v>
       </c>
       <c r="B301" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C301" t="s">
         <v>19</v>
@@ -21007,6 +21022,396 @@
       </c>
       <c r="V301">
         <v>11</v>
+      </c>
+    </row>
+    <row r="302" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>345</v>
+      </c>
+      <c r="B302" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C302" t="s">
+        <v>19</v>
+      </c>
+      <c r="E302" t="s">
+        <v>43</v>
+      </c>
+      <c r="F302" t="s">
+        <v>24</v>
+      </c>
+      <c r="G302" t="s">
+        <v>50</v>
+      </c>
+      <c r="H302">
+        <v>7.75</v>
+      </c>
+      <c r="I302">
+        <v>0.95</v>
+      </c>
+      <c r="J302">
+        <v>6.79</v>
+      </c>
+      <c r="K302">
+        <v>0.66</v>
+      </c>
+      <c r="L302">
+        <v>0.19</v>
+      </c>
+      <c r="M302">
+        <v>0.11</v>
+      </c>
+      <c r="N302">
+        <v>0</v>
+      </c>
+      <c r="O302">
+        <v>6</v>
+      </c>
+      <c r="P302">
+        <v>6.49</v>
+      </c>
+      <c r="Q302">
+        <v>29.97</v>
+      </c>
+      <c r="R302">
+        <v>4.62</v>
+      </c>
+      <c r="S302">
+        <v>27</v>
+      </c>
+      <c r="T302">
+        <v>1</v>
+      </c>
+      <c r="U302">
+        <v>27</v>
+      </c>
+      <c r="V302">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>345</v>
+      </c>
+      <c r="B303" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C303" t="s">
+        <v>19</v>
+      </c>
+      <c r="E303" t="s">
+        <v>99</v>
+      </c>
+      <c r="F303" t="s">
+        <v>27</v>
+      </c>
+      <c r="G303" t="s">
+        <v>335</v>
+      </c>
+      <c r="H303">
+        <v>7.95</v>
+      </c>
+      <c r="I303">
+        <v>1.42</v>
+      </c>
+      <c r="J303">
+        <v>6.5</v>
+      </c>
+      <c r="K303">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L303">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M303">
+        <v>0.03</v>
+      </c>
+      <c r="N303">
+        <v>0</v>
+      </c>
+      <c r="O303">
+        <v>4</v>
+      </c>
+      <c r="P303">
+        <v>7.03</v>
+      </c>
+      <c r="Q303">
+        <v>30.27</v>
+      </c>
+      <c r="R303">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="S303">
+        <v>24</v>
+      </c>
+      <c r="T303">
+        <v>2</v>
+      </c>
+      <c r="U303">
+        <v>21</v>
+      </c>
+      <c r="V303">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>345</v>
+      </c>
+      <c r="B304" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C304" t="s">
+        <v>19</v>
+      </c>
+      <c r="E304" t="s">
+        <v>87</v>
+      </c>
+      <c r="F304" t="s">
+        <v>27</v>
+      </c>
+      <c r="G304" t="s">
+        <v>341</v>
+      </c>
+      <c r="H304">
+        <v>8.93</v>
+      </c>
+      <c r="I304">
+        <v>1.87</v>
+      </c>
+      <c r="J304">
+        <v>7.04</v>
+      </c>
+      <c r="K304">
+        <v>1.48</v>
+      </c>
+      <c r="L304">
+        <v>0.33</v>
+      </c>
+      <c r="M304">
+        <v>0.08</v>
+      </c>
+      <c r="N304">
+        <v>0</v>
+      </c>
+      <c r="O304">
+        <v>6</v>
+      </c>
+      <c r="P304">
+        <v>7.25</v>
+      </c>
+      <c r="Q304">
+        <v>27.9</v>
+      </c>
+      <c r="R304">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="S304">
+        <v>50</v>
+      </c>
+      <c r="T304">
+        <v>6</v>
+      </c>
+      <c r="U304">
+        <v>37</v>
+      </c>
+      <c r="V304">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="305" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>345</v>
+      </c>
+      <c r="B305" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C305" t="s">
+        <v>19</v>
+      </c>
+      <c r="E305" t="s">
+        <v>38</v>
+      </c>
+      <c r="F305" t="s">
+        <v>27</v>
+      </c>
+      <c r="G305" t="s">
+        <v>342</v>
+      </c>
+      <c r="H305">
+        <v>11.12</v>
+      </c>
+      <c r="I305">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="J305">
+        <v>8.81</v>
+      </c>
+      <c r="K305">
+        <v>1.38</v>
+      </c>
+      <c r="L305">
+        <v>0.69</v>
+      </c>
+      <c r="M305">
+        <v>0.21</v>
+      </c>
+      <c r="N305">
+        <v>0.03</v>
+      </c>
+      <c r="O305">
+        <v>17</v>
+      </c>
+      <c r="P305">
+        <v>6.52</v>
+      </c>
+      <c r="Q305">
+        <v>31.1</v>
+      </c>
+      <c r="R305">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="S305">
+        <v>61</v>
+      </c>
+      <c r="T305">
+        <v>11</v>
+      </c>
+      <c r="U305">
+        <v>38</v>
+      </c>
+      <c r="V305">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>345</v>
+      </c>
+      <c r="B306" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C306" t="s">
+        <v>19</v>
+      </c>
+      <c r="E306" t="s">
+        <v>163</v>
+      </c>
+      <c r="F306" t="s">
+        <v>28</v>
+      </c>
+      <c r="G306" t="s">
+        <v>343</v>
+      </c>
+      <c r="H306">
+        <v>10.28</v>
+      </c>
+      <c r="I306">
+        <v>1.65</v>
+      </c>
+      <c r="J306">
+        <v>8.6</v>
+      </c>
+      <c r="K306">
+        <v>1</v>
+      </c>
+      <c r="L306">
+        <v>0.43</v>
+      </c>
+      <c r="M306">
+        <v>0.22</v>
+      </c>
+      <c r="N306">
+        <v>0.03</v>
+      </c>
+      <c r="O306">
+        <v>19</v>
+      </c>
+      <c r="P306">
+        <v>5.88</v>
+      </c>
+      <c r="Q306">
+        <v>31.99</v>
+      </c>
+      <c r="R306">
+        <v>5.82</v>
+      </c>
+      <c r="S306">
+        <v>51</v>
+      </c>
+      <c r="T306">
+        <v>21</v>
+      </c>
+      <c r="U306">
+        <v>42</v>
+      </c>
+      <c r="V306">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>345</v>
+      </c>
+      <c r="B307" s="1">
+        <v>46256</v>
+      </c>
+      <c r="C307" t="s">
+        <v>19</v>
+      </c>
+      <c r="E307" t="s">
+        <v>98</v>
+      </c>
+      <c r="F307" t="s">
+        <v>27</v>
+      </c>
+      <c r="G307" t="s">
+        <v>344</v>
+      </c>
+      <c r="H307">
+        <v>11.72</v>
+      </c>
+      <c r="I307">
+        <v>1.74</v>
+      </c>
+      <c r="J307">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="K307">
+        <v>1.42</v>
+      </c>
+      <c r="L307">
+        <v>0.31</v>
+      </c>
+      <c r="M307">
+        <v>0.03</v>
+      </c>
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>4</v>
+      </c>
+      <c r="P307">
+        <v>6.33</v>
+      </c>
+      <c r="Q307">
+        <v>29.32</v>
+      </c>
+      <c r="R307">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="S307">
+        <v>29</v>
+      </c>
+      <c r="T307">
+        <v>1</v>
+      </c>
+      <c r="U307">
+        <v>47</v>
+      </c>
+      <c r="V307">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE4E3E-1353-0747-AE77-D4D1D7A362D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DC63AB-CE28-9349-B287-A77892BE470B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="348">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1073,6 +1073,12 @@
   </si>
   <si>
     <t>N1 J1 VS Rumilly Valières 22/08/2026</t>
+  </si>
+  <si>
+    <t>01:21:55</t>
+  </si>
+  <si>
+    <t>00:57:59</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V307"/>
+  <dimension ref="A1:V309"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -21414,6 +21420,136 @@
         <v>6</v>
       </c>
     </row>
+    <row r="308" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>22</v>
+      </c>
+      <c r="B308" s="1">
+        <v>46259</v>
+      </c>
+      <c r="C308" t="s">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>166</v>
+      </c>
+      <c r="F308" t="s">
+        <v>101</v>
+      </c>
+      <c r="G308" t="s">
+        <v>346</v>
+      </c>
+      <c r="H308">
+        <v>5.81</v>
+      </c>
+      <c r="I308">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J308">
+        <v>5.25</v>
+      </c>
+      <c r="K308">
+        <v>0.35</v>
+      </c>
+      <c r="L308">
+        <v>0.17</v>
+      </c>
+      <c r="M308">
+        <v>0.05</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308">
+        <v>6</v>
+      </c>
+      <c r="P308">
+        <v>3.78</v>
+      </c>
+      <c r="Q308">
+        <v>28.24</v>
+      </c>
+      <c r="R308">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="S308">
+        <v>41</v>
+      </c>
+      <c r="T308">
+        <v>15</v>
+      </c>
+      <c r="U308">
+        <v>27</v>
+      </c>
+      <c r="V308">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="309" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>22</v>
+      </c>
+      <c r="B309" s="1">
+        <v>46259</v>
+      </c>
+      <c r="C309" t="s">
+        <v>19</v>
+      </c>
+      <c r="E309" t="s">
+        <v>35</v>
+      </c>
+      <c r="F309" t="s">
+        <v>27</v>
+      </c>
+      <c r="G309" t="s">
+        <v>347</v>
+      </c>
+      <c r="H309">
+        <v>3.77</v>
+      </c>
+      <c r="I309">
+        <v>0.23</v>
+      </c>
+      <c r="J309">
+        <v>3.54</v>
+      </c>
+      <c r="K309">
+        <v>0.19</v>
+      </c>
+      <c r="L309">
+        <v>0.04</v>
+      </c>
+      <c r="M309">
+        <v>0.01</v>
+      </c>
+      <c r="N309">
+        <v>0</v>
+      </c>
+      <c r="O309">
+        <v>1</v>
+      </c>
+      <c r="P309">
+        <v>3.79</v>
+      </c>
+      <c r="Q309">
+        <v>26.17</v>
+      </c>
+      <c r="R309">
+        <v>3.9</v>
+      </c>
+      <c r="S309">
+        <v>9</v>
+      </c>
+      <c r="T309">
+        <v>0</v>
+      </c>
+      <c r="U309">
+        <v>9</v>
+      </c>
+      <c r="V309">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DC63AB-CE28-9349-B287-A77892BE470B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B764D673-8F6D-2C42-9F2F-9FEB2B97F734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="353">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1079,6 +1079,21 @@
   </si>
   <si>
     <t>00:57:59</t>
+  </si>
+  <si>
+    <t>01:26:18</t>
+  </si>
+  <si>
+    <t>01:25:25</t>
+  </si>
+  <si>
+    <t>01:36:35</t>
+  </si>
+  <si>
+    <t>01:03:21</t>
+  </si>
+  <si>
+    <t>01:27:30</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V309"/>
+  <dimension ref="A1:V316"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -21550,6 +21565,461 @@
         <v>2</v>
       </c>
     </row>
+    <row r="310" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>22</v>
+      </c>
+      <c r="B310" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C310" t="s">
+        <v>19</v>
+      </c>
+      <c r="E310" t="s">
+        <v>91</v>
+      </c>
+      <c r="F310" t="s">
+        <v>101</v>
+      </c>
+      <c r="G310" t="s">
+        <v>348</v>
+      </c>
+      <c r="H310">
+        <v>5.73</v>
+      </c>
+      <c r="I310">
+        <v>0.92</v>
+      </c>
+      <c r="J310">
+        <v>4.79</v>
+      </c>
+      <c r="K310">
+        <v>0.6</v>
+      </c>
+      <c r="L310">
+        <v>0.2</v>
+      </c>
+      <c r="M310">
+        <v>0.12</v>
+      </c>
+      <c r="N310">
+        <v>0.02</v>
+      </c>
+      <c r="O310">
+        <v>8</v>
+      </c>
+      <c r="P310">
+        <v>3.45</v>
+      </c>
+      <c r="Q310">
+        <v>31.45</v>
+      </c>
+      <c r="R310">
+        <v>5.3</v>
+      </c>
+      <c r="S310">
+        <v>46</v>
+      </c>
+      <c r="T310">
+        <v>22</v>
+      </c>
+      <c r="U310">
+        <v>35</v>
+      </c>
+      <c r="V310">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="311" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>22</v>
+      </c>
+      <c r="B311" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C311" t="s">
+        <v>19</v>
+      </c>
+      <c r="E311" t="s">
+        <v>35</v>
+      </c>
+      <c r="F311" t="s">
+        <v>27</v>
+      </c>
+      <c r="G311" t="s">
+        <v>349</v>
+      </c>
+      <c r="H311">
+        <v>5.46</v>
+      </c>
+      <c r="I311">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="J311">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="K311">
+        <v>0.9</v>
+      </c>
+      <c r="L311">
+        <v>0.15</v>
+      </c>
+      <c r="M311">
+        <v>0.05</v>
+      </c>
+      <c r="N311">
+        <v>0</v>
+      </c>
+      <c r="O311">
+        <v>4</v>
+      </c>
+      <c r="P311">
+        <v>3.7</v>
+      </c>
+      <c r="Q311">
+        <v>27.83</v>
+      </c>
+      <c r="R311">
+        <v>4.26</v>
+      </c>
+      <c r="S311">
+        <v>25</v>
+      </c>
+      <c r="T311">
+        <v>1</v>
+      </c>
+      <c r="U311">
+        <v>15</v>
+      </c>
+      <c r="V311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>22</v>
+      </c>
+      <c r="B312" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C312" t="s">
+        <v>19</v>
+      </c>
+      <c r="E312" t="s">
+        <v>38</v>
+      </c>
+      <c r="F312" t="s">
+        <v>27</v>
+      </c>
+      <c r="G312" t="s">
+        <v>350</v>
+      </c>
+      <c r="H312">
+        <v>6.53</v>
+      </c>
+      <c r="I312">
+        <v>0.74</v>
+      </c>
+      <c r="J312">
+        <v>5.78</v>
+      </c>
+      <c r="K312">
+        <v>0.46</v>
+      </c>
+      <c r="L312">
+        <v>0.23</v>
+      </c>
+      <c r="M312">
+        <v>0.06</v>
+      </c>
+      <c r="N312">
+        <v>0</v>
+      </c>
+      <c r="O312">
+        <v>5</v>
+      </c>
+      <c r="P312">
+        <v>3.99</v>
+      </c>
+      <c r="Q312">
+        <v>27.77</v>
+      </c>
+      <c r="R312">
+        <v>4.41</v>
+      </c>
+      <c r="S312">
+        <v>33</v>
+      </c>
+      <c r="T312">
+        <v>4</v>
+      </c>
+      <c r="U312">
+        <v>23</v>
+      </c>
+      <c r="V312">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="313" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>22</v>
+      </c>
+      <c r="B313" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C313" t="s">
+        <v>19</v>
+      </c>
+      <c r="E313" t="s">
+        <v>166</v>
+      </c>
+      <c r="F313" t="s">
+        <v>101</v>
+      </c>
+      <c r="G313" t="s">
+        <v>351</v>
+      </c>
+      <c r="H313">
+        <v>4.46</v>
+      </c>
+      <c r="I313">
+        <v>0.63</v>
+      </c>
+      <c r="J313">
+        <v>3.82</v>
+      </c>
+      <c r="K313">
+        <v>0.36</v>
+      </c>
+      <c r="L313">
+        <v>0.18</v>
+      </c>
+      <c r="M313">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N313">
+        <v>0.02</v>
+      </c>
+      <c r="O313">
+        <v>6</v>
+      </c>
+      <c r="P313">
+        <v>3.89</v>
+      </c>
+      <c r="Q313">
+        <v>32.159999999999997</v>
+      </c>
+      <c r="R313">
+        <v>4.74</v>
+      </c>
+      <c r="S313">
+        <v>18</v>
+      </c>
+      <c r="T313">
+        <v>4</v>
+      </c>
+      <c r="U313">
+        <v>12</v>
+      </c>
+      <c r="V313">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>22</v>
+      </c>
+      <c r="B314" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C314" t="s">
+        <v>19</v>
+      </c>
+      <c r="E314" t="s">
+        <v>89</v>
+      </c>
+      <c r="F314" t="s">
+        <v>24</v>
+      </c>
+      <c r="G314" t="s">
+        <v>272</v>
+      </c>
+      <c r="H314">
+        <v>5.72</v>
+      </c>
+      <c r="I314">
+        <v>0.43</v>
+      </c>
+      <c r="J314">
+        <v>5.29</v>
+      </c>
+      <c r="K314">
+        <v>0.34</v>
+      </c>
+      <c r="L314">
+        <v>0.09</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
+      </c>
+      <c r="N314">
+        <v>0</v>
+      </c>
+      <c r="O314">
+        <v>0</v>
+      </c>
+      <c r="P314">
+        <v>3.99</v>
+      </c>
+      <c r="Q314">
+        <v>23.47</v>
+      </c>
+      <c r="R314">
+        <v>3.94</v>
+      </c>
+      <c r="S314">
+        <v>13</v>
+      </c>
+      <c r="T314">
+        <v>0</v>
+      </c>
+      <c r="U314">
+        <v>7</v>
+      </c>
+      <c r="V314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>22</v>
+      </c>
+      <c r="B315" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C315" t="s">
+        <v>19</v>
+      </c>
+      <c r="E315" t="s">
+        <v>30</v>
+      </c>
+      <c r="F315" t="s">
+        <v>26</v>
+      </c>
+      <c r="G315" t="s">
+        <v>352</v>
+      </c>
+      <c r="H315">
+        <v>5.87</v>
+      </c>
+      <c r="I315">
+        <v>0.95</v>
+      </c>
+      <c r="J315">
+        <v>4.91</v>
+      </c>
+      <c r="K315">
+        <v>0.71</v>
+      </c>
+      <c r="L315">
+        <v>0.21</v>
+      </c>
+      <c r="M315">
+        <v>0.04</v>
+      </c>
+      <c r="N315">
+        <v>0</v>
+      </c>
+      <c r="O315">
+        <v>5</v>
+      </c>
+      <c r="P315">
+        <v>3.82</v>
+      </c>
+      <c r="Q315">
+        <v>27.53</v>
+      </c>
+      <c r="R315">
+        <v>5.04</v>
+      </c>
+      <c r="S315">
+        <v>23</v>
+      </c>
+      <c r="T315">
+        <v>10</v>
+      </c>
+      <c r="U315">
+        <v>17</v>
+      </c>
+      <c r="V315">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="316" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>22</v>
+      </c>
+      <c r="B316" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C316" t="s">
+        <v>19</v>
+      </c>
+      <c r="E316" t="s">
+        <v>31</v>
+      </c>
+      <c r="F316" t="s">
+        <v>28</v>
+      </c>
+      <c r="G316" t="s">
+        <v>207</v>
+      </c>
+      <c r="H316">
+        <v>7.23</v>
+      </c>
+      <c r="I316">
+        <v>0.91</v>
+      </c>
+      <c r="J316">
+        <v>6.3</v>
+      </c>
+      <c r="K316">
+        <v>0.44</v>
+      </c>
+      <c r="L316">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M316">
+        <v>0.18</v>
+      </c>
+      <c r="N316">
+        <v>0.02</v>
+      </c>
+      <c r="O316">
+        <v>12</v>
+      </c>
+      <c r="P316">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q316">
+        <v>31.22</v>
+      </c>
+      <c r="R316">
+        <v>3.81</v>
+      </c>
+      <c r="S316">
+        <v>26</v>
+      </c>
+      <c r="T316">
+        <v>0</v>
+      </c>
+      <c r="U316">
+        <v>20</v>
+      </c>
+      <c r="V316">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B764D673-8F6D-2C42-9F2F-9FEB2B97F734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6B3A48-435A-D64C-A074-44DDDE715B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="359">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1094,6 +1094,24 @@
   </si>
   <si>
     <t>01:27:30</t>
+  </si>
+  <si>
+    <t>01:24:25</t>
+  </si>
+  <si>
+    <t>01:20:13</t>
+  </si>
+  <si>
+    <t>01:21:04</t>
+  </si>
+  <si>
+    <t>01:30:30</t>
+  </si>
+  <si>
+    <t>01:26:40</t>
+  </si>
+  <si>
+    <t>01:20:49</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V316"/>
+  <dimension ref="A1:V323"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -22020,6 +22038,461 @@
         <v>4</v>
       </c>
     </row>
+    <row r="317" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>22</v>
+      </c>
+      <c r="B317" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C317" t="s">
+        <v>19</v>
+      </c>
+      <c r="E317" t="s">
+        <v>170</v>
+      </c>
+      <c r="F317" t="s">
+        <v>26</v>
+      </c>
+      <c r="G317" t="s">
+        <v>353</v>
+      </c>
+      <c r="H317">
+        <v>3.13</v>
+      </c>
+      <c r="I317">
+        <v>0.15</v>
+      </c>
+      <c r="J317">
+        <v>2.97</v>
+      </c>
+      <c r="K317">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L317">
+        <v>0.04</v>
+      </c>
+      <c r="M317">
+        <v>0.04</v>
+      </c>
+      <c r="N317">
+        <v>0</v>
+      </c>
+      <c r="O317">
+        <v>4</v>
+      </c>
+      <c r="P317">
+        <v>1.91</v>
+      </c>
+      <c r="Q317">
+        <v>29.15</v>
+      </c>
+      <c r="R317">
+        <v>4.22</v>
+      </c>
+      <c r="S317">
+        <v>9</v>
+      </c>
+      <c r="T317">
+        <v>2</v>
+      </c>
+      <c r="U317">
+        <v>12</v>
+      </c>
+      <c r="V317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>22</v>
+      </c>
+      <c r="B318" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C318" t="s">
+        <v>19</v>
+      </c>
+      <c r="E318" t="s">
+        <v>166</v>
+      </c>
+      <c r="F318" t="s">
+        <v>101</v>
+      </c>
+      <c r="G318" t="s">
+        <v>354</v>
+      </c>
+      <c r="H318">
+        <v>5.33</v>
+      </c>
+      <c r="I318">
+        <v>0.24</v>
+      </c>
+      <c r="J318">
+        <v>5.09</v>
+      </c>
+      <c r="K318">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L318">
+        <v>0.05</v>
+      </c>
+      <c r="M318">
+        <v>0.04</v>
+      </c>
+      <c r="N318">
+        <v>0.01</v>
+      </c>
+      <c r="O318">
+        <v>3</v>
+      </c>
+      <c r="P318">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="Q318">
+        <v>31.73</v>
+      </c>
+      <c r="R318">
+        <v>6.73</v>
+      </c>
+      <c r="S318">
+        <v>24</v>
+      </c>
+      <c r="T318">
+        <v>20</v>
+      </c>
+      <c r="U318">
+        <v>21</v>
+      </c>
+      <c r="V318">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="319" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>22</v>
+      </c>
+      <c r="B319" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C319" t="s">
+        <v>19</v>
+      </c>
+      <c r="E319" t="s">
+        <v>91</v>
+      </c>
+      <c r="F319" t="s">
+        <v>101</v>
+      </c>
+      <c r="G319" t="s">
+        <v>355</v>
+      </c>
+      <c r="H319">
+        <v>3.72</v>
+      </c>
+      <c r="I319">
+        <v>0.21</v>
+      </c>
+      <c r="J319">
+        <v>3.5</v>
+      </c>
+      <c r="K319">
+        <v>0.09</v>
+      </c>
+      <c r="L319">
+        <v>0.04</v>
+      </c>
+      <c r="M319">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N319">
+        <v>0.02</v>
+      </c>
+      <c r="O319">
+        <v>4</v>
+      </c>
+      <c r="P319">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Q319">
+        <v>31.49</v>
+      </c>
+      <c r="R319">
+        <v>5.16</v>
+      </c>
+      <c r="S319">
+        <v>20</v>
+      </c>
+      <c r="T319">
+        <v>11</v>
+      </c>
+      <c r="U319">
+        <v>20</v>
+      </c>
+      <c r="V319">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="320" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>22</v>
+      </c>
+      <c r="B320" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C320" t="s">
+        <v>19</v>
+      </c>
+      <c r="E320" t="s">
+        <v>38</v>
+      </c>
+      <c r="F320" t="s">
+        <v>27</v>
+      </c>
+      <c r="G320" t="s">
+        <v>356</v>
+      </c>
+      <c r="H320">
+        <v>4.09</v>
+      </c>
+      <c r="I320">
+        <v>0.36</v>
+      </c>
+      <c r="J320">
+        <v>3.72</v>
+      </c>
+      <c r="K320">
+        <v>0.26</v>
+      </c>
+      <c r="L320">
+        <v>0.11</v>
+      </c>
+      <c r="M320">
+        <v>0</v>
+      </c>
+      <c r="N320">
+        <v>0</v>
+      </c>
+      <c r="O320">
+        <v>1</v>
+      </c>
+      <c r="P320">
+        <v>2.56</v>
+      </c>
+      <c r="Q320">
+        <v>25.2</v>
+      </c>
+      <c r="R320">
+        <v>4.18</v>
+      </c>
+      <c r="S320">
+        <v>27</v>
+      </c>
+      <c r="T320">
+        <v>2</v>
+      </c>
+      <c r="U320">
+        <v>17</v>
+      </c>
+      <c r="V320">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A321" t="s">
+        <v>22</v>
+      </c>
+      <c r="B321" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C321" t="s">
+        <v>19</v>
+      </c>
+      <c r="E321" t="s">
+        <v>31</v>
+      </c>
+      <c r="F321" t="s">
+        <v>28</v>
+      </c>
+      <c r="G321" t="s">
+        <v>357</v>
+      </c>
+      <c r="H321">
+        <v>3.43</v>
+      </c>
+      <c r="I321">
+        <v>0.26</v>
+      </c>
+      <c r="J321">
+        <v>3.17</v>
+      </c>
+      <c r="K321">
+        <v>0.09</v>
+      </c>
+      <c r="L321">
+        <v>0.06</v>
+      </c>
+      <c r="M321">
+        <v>0.09</v>
+      </c>
+      <c r="N321">
+        <v>0.02</v>
+      </c>
+      <c r="O321">
+        <v>5</v>
+      </c>
+      <c r="P321">
+        <v>2.23</v>
+      </c>
+      <c r="Q321">
+        <v>30.92</v>
+      </c>
+      <c r="R321">
+        <v>4.42</v>
+      </c>
+      <c r="S321">
+        <v>11</v>
+      </c>
+      <c r="T321">
+        <v>5</v>
+      </c>
+      <c r="U321">
+        <v>6</v>
+      </c>
+      <c r="V321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A322" t="s">
+        <v>22</v>
+      </c>
+      <c r="B322" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C322" t="s">
+        <v>19</v>
+      </c>
+      <c r="E322" t="s">
+        <v>35</v>
+      </c>
+      <c r="F322" t="s">
+        <v>27</v>
+      </c>
+      <c r="G322" t="s">
+        <v>349</v>
+      </c>
+      <c r="H322">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="I322">
+        <v>0.38</v>
+      </c>
+      <c r="J322">
+        <v>3.72</v>
+      </c>
+      <c r="K322">
+        <v>0.24</v>
+      </c>
+      <c r="L322">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M322">
+        <v>0.01</v>
+      </c>
+      <c r="N322">
+        <v>0</v>
+      </c>
+      <c r="O322">
+        <v>1</v>
+      </c>
+      <c r="P322">
+        <v>2.76</v>
+      </c>
+      <c r="Q322">
+        <v>26.26</v>
+      </c>
+      <c r="R322">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="S322">
+        <v>21</v>
+      </c>
+      <c r="T322">
+        <v>3</v>
+      </c>
+      <c r="U322">
+        <v>6</v>
+      </c>
+      <c r="V322">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A323" t="s">
+        <v>22</v>
+      </c>
+      <c r="B323" s="1">
+        <v>46261</v>
+      </c>
+      <c r="C323" t="s">
+        <v>19</v>
+      </c>
+      <c r="E323" t="s">
+        <v>30</v>
+      </c>
+      <c r="F323" t="s">
+        <v>26</v>
+      </c>
+      <c r="G323" t="s">
+        <v>358</v>
+      </c>
+      <c r="H323">
+        <v>3.9</v>
+      </c>
+      <c r="I323">
+        <v>0.34</v>
+      </c>
+      <c r="J323">
+        <v>3.56</v>
+      </c>
+      <c r="K323">
+        <v>0.21</v>
+      </c>
+      <c r="L323">
+        <v>0.08</v>
+      </c>
+      <c r="M323">
+        <v>0.05</v>
+      </c>
+      <c r="N323">
+        <v>0</v>
+      </c>
+      <c r="O323">
+        <v>3</v>
+      </c>
+      <c r="P323">
+        <v>2.77</v>
+      </c>
+      <c r="Q323">
+        <v>28.68</v>
+      </c>
+      <c r="R323">
+        <v>4.75</v>
+      </c>
+      <c r="S323">
+        <v>20</v>
+      </c>
+      <c r="T323">
+        <v>4</v>
+      </c>
+      <c r="U323">
+        <v>11</v>
+      </c>
+      <c r="V323">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6B3A48-435A-D64C-A074-44DDDE715B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFDFD03-5353-D74A-A472-7C0895CF6FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="363">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1112,6 +1112,18 @@
   </si>
   <si>
     <t>01:20:49</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>J+3</t>
+  </si>
+  <si>
+    <t>J-3</t>
+  </si>
+  <si>
+    <t>J-2</t>
   </si>
 </sst>
 </file>
@@ -21073,6 +21085,9 @@
       <c r="C302" t="s">
         <v>19</v>
       </c>
+      <c r="D302" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="E302" t="s">
         <v>43</v>
       </c>
@@ -21138,6 +21153,9 @@
       <c r="C303" t="s">
         <v>19</v>
       </c>
+      <c r="D303" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="E303" t="s">
         <v>99</v>
       </c>
@@ -21203,6 +21221,9 @@
       <c r="C304" t="s">
         <v>19</v>
       </c>
+      <c r="D304" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="E304" t="s">
         <v>87</v>
       </c>
@@ -21268,6 +21289,9 @@
       <c r="C305" t="s">
         <v>19</v>
       </c>
+      <c r="D305" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="E305" t="s">
         <v>38</v>
       </c>
@@ -21333,6 +21357,9 @@
       <c r="C306" t="s">
         <v>19</v>
       </c>
+      <c r="D306" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="E306" t="s">
         <v>163</v>
       </c>
@@ -21398,6 +21425,9 @@
       <c r="C307" t="s">
         <v>19</v>
       </c>
+      <c r="D307" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="E307" t="s">
         <v>98</v>
       </c>
@@ -21463,6 +21493,9 @@
       <c r="C308" t="s">
         <v>19</v>
       </c>
+      <c r="D308" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="E308" t="s">
         <v>166</v>
       </c>
@@ -21528,6 +21561,9 @@
       <c r="C309" t="s">
         <v>19</v>
       </c>
+      <c r="D309" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="E309" t="s">
         <v>35</v>
       </c>
@@ -21593,6 +21629,9 @@
       <c r="C310" t="s">
         <v>19</v>
       </c>
+      <c r="D310" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E310" t="s">
         <v>91</v>
       </c>
@@ -21658,6 +21697,9 @@
       <c r="C311" t="s">
         <v>19</v>
       </c>
+      <c r="D311" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E311" t="s">
         <v>35</v>
       </c>
@@ -21723,6 +21765,9 @@
       <c r="C312" t="s">
         <v>19</v>
       </c>
+      <c r="D312" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E312" t="s">
         <v>38</v>
       </c>
@@ -21788,6 +21833,9 @@
       <c r="C313" t="s">
         <v>19</v>
       </c>
+      <c r="D313" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E313" t="s">
         <v>166</v>
       </c>
@@ -21853,6 +21901,9 @@
       <c r="C314" t="s">
         <v>19</v>
       </c>
+      <c r="D314" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E314" t="s">
         <v>89</v>
       </c>
@@ -21918,6 +21969,9 @@
       <c r="C315" t="s">
         <v>19</v>
       </c>
+      <c r="D315" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E315" t="s">
         <v>30</v>
       </c>
@@ -21983,6 +22037,9 @@
       <c r="C316" t="s">
         <v>19</v>
       </c>
+      <c r="D316" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E316" t="s">
         <v>31</v>
       </c>
@@ -22048,6 +22105,9 @@
       <c r="C317" t="s">
         <v>19</v>
       </c>
+      <c r="D317" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="E317" t="s">
         <v>170</v>
       </c>
@@ -22113,6 +22173,9 @@
       <c r="C318" t="s">
         <v>19</v>
       </c>
+      <c r="D318" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="E318" t="s">
         <v>166</v>
       </c>
@@ -22178,6 +22241,9 @@
       <c r="C319" t="s">
         <v>19</v>
       </c>
+      <c r="D319" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="E319" t="s">
         <v>91</v>
       </c>
@@ -22243,6 +22309,9 @@
       <c r="C320" t="s">
         <v>19</v>
       </c>
+      <c r="D320" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="E320" t="s">
         <v>38</v>
       </c>
@@ -22308,6 +22377,9 @@
       <c r="C321" t="s">
         <v>19</v>
       </c>
+      <c r="D321" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="E321" t="s">
         <v>31</v>
       </c>
@@ -22373,6 +22445,9 @@
       <c r="C322" t="s">
         <v>19</v>
       </c>
+      <c r="D322" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="E322" t="s">
         <v>35</v>
       </c>
@@ -22437,6 +22512,9 @@
       </c>
       <c r="C323" t="s">
         <v>19</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="E323" t="s">
         <v>30</v>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFDFD03-5353-D74A-A472-7C0895CF6FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EABADD-8741-CD4E-9B7C-545877866B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="378">
   <si>
     <t>Temps joué</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Global</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Nom du joueur</t>
   </si>
   <si>
@@ -1124,6 +1121,54 @@
   </si>
   <si>
     <t>J-2</t>
+  </si>
+  <si>
+    <t>01:14:07</t>
+  </si>
+  <si>
+    <t>00:56:58</t>
+  </si>
+  <si>
+    <t>J-1</t>
+  </si>
+  <si>
+    <t>01:39:32</t>
+  </si>
+  <si>
+    <t>01:16:57</t>
+  </si>
+  <si>
+    <t>01:38:48</t>
+  </si>
+  <si>
+    <t>01:01:20</t>
+  </si>
+  <si>
+    <t>01:14:41</t>
+  </si>
+  <si>
+    <t>N1 J2 VS AS Saint-Priest 29/08/2026</t>
+  </si>
+  <si>
+    <t>01:21:59</t>
+  </si>
+  <si>
+    <t>01:21:42</t>
+  </si>
+  <si>
+    <t>01:21:33</t>
+  </si>
+  <si>
+    <t>01:20:58</t>
+  </si>
+  <si>
+    <t>01:09:38</t>
+  </si>
+  <si>
+    <t>01:01:19</t>
+  </si>
+  <si>
+    <t>J+2</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V323"/>
+  <dimension ref="A1:V337"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -1508,9 +1553,6 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
       <c r="B1" t="s">
         <v>17</v>
       </c>
@@ -1518,13 +1560,13 @@
         <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1577,7 +1619,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1">
         <v>46216</v>
@@ -1586,13 +1628,13 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
         <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -1642,7 +1684,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1">
         <v>46216</v>
@@ -1651,13 +1693,13 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>7.41</v>
@@ -1707,7 +1749,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1">
         <v>46216</v>
@@ -1716,13 +1758,13 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4">
         <v>6.91</v>
@@ -1772,7 +1814,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1">
         <v>46216</v>
@@ -1781,13 +1823,13 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5">
         <v>6.88</v>
@@ -1837,7 +1879,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1">
         <v>46216</v>
@@ -1846,13 +1888,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6">
         <v>7.31</v>
@@ -1902,7 +1944,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>46216</v>
@@ -1911,13 +1953,13 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
       </c>
       <c r="H7">
         <v>7.38</v>
@@ -1967,7 +2009,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
         <v>46216</v>
@@ -1976,13 +2018,13 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H8">
         <v>7.01</v>
@@ -2032,7 +2074,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1">
         <v>46216</v>
@@ -2041,13 +2083,13 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9">
         <v>6.84</v>
@@ -2097,7 +2139,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1">
         <v>46216</v>
@@ -2109,10 +2151,10 @@
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H10">
         <v>6.45</v>
@@ -2162,7 +2204,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1">
         <v>46217</v>
@@ -2171,13 +2213,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
         <v>46</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
       </c>
       <c r="H11">
         <v>6.27</v>
@@ -2227,7 +2269,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
         <v>46217</v>
@@ -2236,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12">
         <v>7.06</v>
@@ -2292,7 +2334,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1">
         <v>46217</v>
@@ -2301,13 +2343,13 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H13">
         <v>7.07</v>
@@ -2357,7 +2399,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1">
         <v>46217</v>
@@ -2369,10 +2411,10 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>6.53</v>
@@ -2422,7 +2464,7 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1">
         <v>46217</v>
@@ -2431,13 +2473,13 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15">
         <v>6.69</v>
@@ -2487,7 +2529,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1">
         <v>46217</v>
@@ -2496,13 +2538,13 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H16">
         <v>7.56</v>
@@ -2552,7 +2594,7 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1">
         <v>46217</v>
@@ -2561,13 +2603,13 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H17">
         <v>6.58</v>
@@ -2617,7 +2659,7 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>46217</v>
@@ -2626,13 +2668,13 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
       </c>
       <c r="H18">
         <v>5.26</v>
@@ -2682,7 +2724,7 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
         <v>46217</v>
@@ -2691,13 +2733,13 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H19">
         <v>6.96</v>
@@ -2747,7 +2789,7 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1">
         <v>46218</v>
@@ -2756,13 +2798,13 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20">
         <v>9.36</v>
@@ -2812,7 +2854,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1">
         <v>46218</v>
@@ -2821,13 +2863,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21">
         <v>9.7899999999999991</v>
@@ -2877,7 +2919,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
         <v>46218</v>
@@ -2886,13 +2928,13 @@
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H22">
         <v>8.6999999999999993</v>
@@ -2942,7 +2984,7 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1">
         <v>46218</v>
@@ -2951,13 +2993,13 @@
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H23">
         <v>9.2100000000000009</v>
@@ -3007,7 +3049,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1">
         <v>46218</v>
@@ -3016,13 +3058,13 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H24">
         <v>9.49</v>
@@ -3072,7 +3114,7 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1">
         <v>46218</v>
@@ -3081,13 +3123,13 @@
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H25">
         <v>9.69</v>
@@ -3137,7 +3179,7 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1">
         <v>46218</v>
@@ -3146,13 +3188,13 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H26">
         <v>7.11</v>
@@ -3202,7 +3244,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="1">
         <v>46218</v>
@@ -3211,13 +3253,13 @@
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H27">
         <v>9.3800000000000008</v>
@@ -3267,7 +3309,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="1">
         <v>46218</v>
@@ -3279,10 +3321,10 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H28">
         <v>9.16</v>
@@ -3332,7 +3374,7 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1">
         <v>46219</v>
@@ -3341,13 +3383,13 @@
         <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H29">
         <v>10</v>
@@ -3397,7 +3439,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1">
         <v>46219</v>
@@ -3406,13 +3448,13 @@
         <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H30">
         <v>8.77</v>
@@ -3462,7 +3504,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="1">
         <v>46219</v>
@@ -3471,13 +3513,13 @@
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H31">
         <v>9.2200000000000006</v>
@@ -3527,7 +3569,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1">
         <v>46219</v>
@@ -3539,10 +3581,10 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H32">
         <v>6.96</v>
@@ -3592,7 +3634,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" s="1">
         <v>46219</v>
@@ -3601,13 +3643,13 @@
         <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H33">
         <v>9.77</v>
@@ -3657,7 +3699,7 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="1">
         <v>46219</v>
@@ -3666,13 +3708,13 @@
         <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H34">
         <v>9.4</v>
@@ -3722,7 +3764,7 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" s="1">
         <v>46219</v>
@@ -3731,13 +3773,13 @@
         <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H35">
         <v>9.75</v>
@@ -3787,7 +3829,7 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="1">
         <v>46219</v>
@@ -3796,13 +3838,13 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H36">
         <v>9.33</v>
@@ -3852,7 +3894,7 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="1">
         <v>46219</v>
@@ -3861,13 +3903,13 @@
         <v>19</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H37">
         <v>8.81</v>
@@ -3917,7 +3959,7 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1">
         <v>46220</v>
@@ -3926,13 +3968,13 @@
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H38">
         <v>7.03</v>
@@ -3982,7 +4024,7 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1">
         <v>46220</v>
@@ -3991,13 +4033,13 @@
         <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H39">
         <v>8.01</v>
@@ -4047,7 +4089,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" s="1">
         <v>46220</v>
@@ -4056,13 +4098,13 @@
         <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H40">
         <v>7.67</v>
@@ -4112,7 +4154,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="1">
         <v>46220</v>
@@ -4121,13 +4163,13 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H41">
         <v>7.23</v>
@@ -4177,7 +4219,7 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="1">
         <v>46220</v>
@@ -4186,13 +4228,13 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H42">
         <v>8.08</v>
@@ -4242,7 +4284,7 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B43" s="1">
         <v>46220</v>
@@ -4251,13 +4293,13 @@
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H43">
         <v>8.09</v>
@@ -4307,7 +4349,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" s="1">
         <v>46220</v>
@@ -4316,13 +4358,13 @@
         <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H44">
         <v>7.51</v>
@@ -4372,7 +4414,7 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B45" s="1">
         <v>46220</v>
@@ -4381,13 +4423,13 @@
         <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H45">
         <v>8.2899999999999991</v>
@@ -4437,7 +4479,7 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B46" s="1">
         <v>46220</v>
@@ -4446,13 +4488,13 @@
         <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H46">
         <v>7.73</v>
@@ -4502,7 +4544,7 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B47" s="1">
         <v>46220</v>
@@ -4514,10 +4556,10 @@
         <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H47">
         <v>7.57</v>
@@ -4567,7 +4609,7 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B48" s="1">
         <v>46223</v>
@@ -4576,13 +4618,13 @@
         <v>19</v>
       </c>
       <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" t="s">
         <v>82</v>
-      </c>
-      <c r="F48" t="s">
-        <v>27</v>
-      </c>
-      <c r="G48" t="s">
-        <v>83</v>
       </c>
       <c r="H48">
         <v>10.54</v>
@@ -4632,7 +4674,7 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" s="1">
         <v>46223</v>
@@ -4641,13 +4683,13 @@
         <v>19</v>
       </c>
       <c r="E49" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" t="s">
         <v>84</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" t="s">
-        <v>85</v>
       </c>
       <c r="H49">
         <v>9.5500000000000007</v>
@@ -4697,7 +4739,7 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="1">
         <v>46223</v>
@@ -4706,13 +4748,13 @@
         <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H50">
         <v>9.98</v>
@@ -4762,7 +4804,7 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="1">
         <v>46223</v>
@@ -4771,13 +4813,13 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" t="s">
         <v>87</v>
-      </c>
-      <c r="F51" t="s">
-        <v>27</v>
-      </c>
-      <c r="G51" t="s">
-        <v>88</v>
       </c>
       <c r="H51">
         <v>10.51</v>
@@ -4827,7 +4869,7 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B52" s="1">
         <v>46223</v>
@@ -4836,13 +4878,13 @@
         <v>19</v>
       </c>
       <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" t="s">
         <v>89</v>
-      </c>
-      <c r="F52" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" t="s">
-        <v>90</v>
       </c>
       <c r="H52">
         <v>7.5</v>
@@ -4892,7 +4934,7 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" s="1">
         <v>46223</v>
@@ -4901,13 +4943,13 @@
         <v>19</v>
       </c>
       <c r="E53" t="s">
+        <v>90</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="G53" t="s">
         <v>92</v>
-      </c>
-      <c r="G53" t="s">
-        <v>93</v>
       </c>
       <c r="H53">
         <v>6.84</v>
@@ -4957,7 +4999,7 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="1">
         <v>46223</v>
@@ -4966,13 +5008,13 @@
         <v>19</v>
       </c>
       <c r="E54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" t="s">
         <v>95</v>
-      </c>
-      <c r="G54" t="s">
-        <v>96</v>
       </c>
       <c r="H54">
         <v>9.52</v>
@@ -5022,7 +5064,7 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B55" s="1">
         <v>46223</v>
@@ -5031,13 +5073,13 @@
         <v>19</v>
       </c>
       <c r="E55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H55">
         <v>9.57</v>
@@ -5087,7 +5129,7 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B56" s="1">
         <v>46223</v>
@@ -5096,13 +5138,13 @@
         <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H56">
         <v>10.31</v>
@@ -5152,7 +5194,7 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B57" s="1">
         <v>46223</v>
@@ -5161,13 +5203,13 @@
         <v>19</v>
       </c>
       <c r="E57" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" t="s">
         <v>99</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G57" t="s">
-        <v>100</v>
       </c>
       <c r="H57">
         <v>9.5</v>
@@ -5217,22 +5259,22 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B58" s="1">
         <v>46224</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F58" t="s">
+        <v>100</v>
+      </c>
+      <c r="G58" t="s">
         <v>101</v>
-      </c>
-      <c r="G58" t="s">
-        <v>102</v>
       </c>
       <c r="H58">
         <v>6.16</v>
@@ -5282,22 +5324,22 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B59" s="1">
         <v>46224</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F59" t="s">
+        <v>102</v>
+      </c>
+      <c r="G59" t="s">
         <v>103</v>
-      </c>
-      <c r="G59" t="s">
-        <v>104</v>
       </c>
       <c r="H59">
         <v>7.25</v>
@@ -5347,22 +5389,22 @@
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B60" s="1">
         <v>46224</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H60">
         <v>7.58</v>
@@ -5412,22 +5454,22 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B61" s="1">
         <v>46224</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H61">
         <v>6.08</v>
@@ -5477,22 +5519,22 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B62" s="1">
         <v>46224</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H62">
         <v>6.68</v>
@@ -5542,22 +5584,22 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B63" s="1">
         <v>46224</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H63">
         <v>7.19</v>
@@ -5607,22 +5649,22 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B64" s="1">
         <v>46224</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H64">
         <v>7.07</v>
@@ -5672,22 +5714,22 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B65" s="1">
         <v>46224</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H65">
         <v>6.78</v>
@@ -5737,22 +5779,22 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B66" s="1">
         <v>46224</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H66">
         <v>9.89</v>
@@ -5802,22 +5844,22 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B67" s="1">
         <v>46224</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H67">
         <v>6.74</v>
@@ -5867,22 +5909,22 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B68" s="1">
         <v>46224</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H68">
         <v>5.71</v>
@@ -5932,22 +5974,22 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B69" s="1">
         <v>46224</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H69">
         <v>9.1999999999999993</v>
@@ -5997,22 +6039,22 @@
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B70" s="1">
         <v>46224</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H70">
         <v>4.28</v>
@@ -6062,22 +6104,22 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B71" s="1">
         <v>46224</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H71">
         <v>8.58</v>
@@ -6127,22 +6169,22 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B72" s="1">
         <v>46224</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H72">
         <v>7.41</v>
@@ -6192,22 +6234,22 @@
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B73" s="1">
         <v>46224</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H73">
         <v>5.35</v>
@@ -6257,22 +6299,22 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B74" s="1">
         <v>46225</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H74">
         <v>5.23</v>
@@ -6322,22 +6364,22 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B75" s="1">
         <v>46225</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H75">
         <v>5.67</v>
@@ -6387,22 +6429,22 @@
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B76" s="1">
         <v>46225</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H76">
         <v>4.87</v>
@@ -6452,22 +6494,22 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B77" s="1">
         <v>46225</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H77">
         <v>5.95</v>
@@ -6517,22 +6559,22 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B78" s="1">
         <v>46225</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H78">
         <v>4.32</v>
@@ -6582,22 +6624,22 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B79" s="1">
         <v>46225</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H79">
         <v>5.37</v>
@@ -6647,22 +6689,22 @@
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B80" s="1">
         <v>46225</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F80" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H80">
         <v>6.1</v>
@@ -6712,22 +6754,22 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B81" s="1">
         <v>46225</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H81">
         <v>3.08</v>
@@ -6777,22 +6819,22 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B82" s="1">
         <v>46225</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H82">
         <v>3.89</v>
@@ -6842,22 +6884,22 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B83" s="1">
         <v>46225</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H83">
         <v>3.05</v>
@@ -6907,22 +6949,22 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B84" s="1">
         <v>46225</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F84" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G84" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H84">
         <v>2.83</v>
@@ -6972,22 +7014,22 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B85" s="1">
         <v>46225</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H85">
         <v>3.15</v>
@@ -7037,22 +7079,22 @@
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B86" s="1">
         <v>46225</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H86">
         <v>2.86</v>
@@ -7102,22 +7144,22 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B87" s="1">
         <v>46225</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H87">
         <v>3.07</v>
@@ -7167,22 +7209,22 @@
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B88" s="1">
         <v>46225</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F88" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H88">
         <v>5.69</v>
@@ -7232,22 +7274,22 @@
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B89" s="1">
         <v>46226</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E89" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H89">
         <v>5.73</v>
@@ -7297,22 +7339,22 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B90" s="1">
         <v>46226</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H90">
         <v>7.02</v>
@@ -7362,22 +7404,22 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B91" s="1">
         <v>46226</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E91" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H91">
         <v>6.92</v>
@@ -7427,22 +7469,22 @@
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B92" s="1">
         <v>46226</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F92" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H92">
         <v>7.35</v>
@@ -7492,22 +7534,22 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B93" s="1">
         <v>46226</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F93" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H93">
         <v>7.23</v>
@@ -7557,22 +7599,22 @@
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B94" s="1">
         <v>46226</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H94">
         <v>6.9</v>
@@ -7622,22 +7664,22 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B95" s="1">
         <v>46226</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E95" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F95" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G95" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H95">
         <v>6.68</v>
@@ -7687,22 +7729,22 @@
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B96" s="1">
         <v>46226</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F96" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H96">
         <v>7.18</v>
@@ -7752,22 +7794,22 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B97" s="1">
         <v>46226</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E97" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F97" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G97" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H97">
         <v>7.52</v>
@@ -7817,22 +7859,22 @@
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B98" s="1">
         <v>46226</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F98" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G98" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H98">
         <v>3.79</v>
@@ -7882,22 +7924,22 @@
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B99" s="1">
         <v>46226</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E99" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G99" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H99">
         <v>4.8600000000000003</v>
@@ -7947,22 +7989,22 @@
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B100" s="1">
         <v>46226</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G100" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H100">
         <v>4.1399999999999997</v>
@@ -8012,22 +8054,22 @@
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B101" s="1">
         <v>46226</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E101" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G101" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H101">
         <v>5.52</v>
@@ -8077,22 +8119,22 @@
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B102" s="1">
         <v>46226</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E102" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F102" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G102" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H102">
         <v>6.53</v>
@@ -8142,22 +8184,22 @@
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103" s="1">
         <v>46226</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E103" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G103" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H103">
         <v>4.37</v>
@@ -8207,22 +8249,22 @@
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B104" s="1">
         <v>46226</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F104" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G104" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H104">
         <v>3.56</v>
@@ -8272,22 +8314,22 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B105" s="1">
         <v>46226</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E105" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F105" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G105" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H105">
         <v>4.62</v>
@@ -8337,22 +8379,22 @@
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B106" s="1">
         <v>46226</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F106" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H106">
         <v>4.4400000000000004</v>
@@ -8402,7 +8444,7 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B107" s="1">
         <v>46227</v>
@@ -8411,13 +8453,13 @@
         <v>19</v>
       </c>
       <c r="E107" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F107" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H107">
         <v>2.57</v>
@@ -8467,7 +8509,7 @@
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B108" s="1">
         <v>46227</v>
@@ -8476,13 +8518,13 @@
         <v>19</v>
       </c>
       <c r="E108" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F108" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H108">
         <v>2.25</v>
@@ -8532,7 +8574,7 @@
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B109" s="1">
         <v>46227</v>
@@ -8541,13 +8583,13 @@
         <v>19</v>
       </c>
       <c r="E109" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G109" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H109">
         <v>4.18</v>
@@ -8597,7 +8639,7 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B110" s="1">
         <v>46227</v>
@@ -8606,13 +8648,13 @@
         <v>19</v>
       </c>
       <c r="E110" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F110" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G110" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H110">
         <v>2.83</v>
@@ -8662,7 +8704,7 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B111" s="1">
         <v>46227</v>
@@ -8671,13 +8713,13 @@
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F111" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H111">
         <v>3.24</v>
@@ -8727,7 +8769,7 @@
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B112" s="1">
         <v>46227</v>
@@ -8736,13 +8778,13 @@
         <v>19</v>
       </c>
       <c r="E112" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F112" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G112" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H112">
         <v>3.82</v>
@@ -8792,7 +8834,7 @@
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B113" s="1">
         <v>46227</v>
@@ -8801,13 +8843,13 @@
         <v>19</v>
       </c>
       <c r="E113" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F113" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G113" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H113">
         <v>3.48</v>
@@ -8857,7 +8899,7 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B114" s="1">
         <v>46228</v>
@@ -8866,13 +8908,13 @@
         <v>19</v>
       </c>
       <c r="E114" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H114">
         <v>5.36</v>
@@ -8922,7 +8964,7 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B115" s="1">
         <v>46228</v>
@@ -8931,13 +8973,13 @@
         <v>19</v>
       </c>
       <c r="E115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G115" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H115">
         <v>5.81</v>
@@ -8987,7 +9029,7 @@
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B116" s="1">
         <v>46228</v>
@@ -8999,10 +9041,10 @@
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H116">
         <v>4.7699999999999996</v>
@@ -9052,7 +9094,7 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B117" s="1">
         <v>46228</v>
@@ -9061,13 +9103,13 @@
         <v>19</v>
       </c>
       <c r="E117" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F117" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G117" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H117">
         <v>5.36</v>
@@ -9117,7 +9159,7 @@
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B118" s="1">
         <v>46228</v>
@@ -9126,13 +9168,13 @@
         <v>19</v>
       </c>
       <c r="E118" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G118" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H118">
         <v>4.97</v>
@@ -9182,7 +9224,7 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B119" s="1">
         <v>46228</v>
@@ -9191,13 +9233,13 @@
         <v>19</v>
       </c>
       <c r="E119" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F119" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" t="s">
         <v>157</v>
-      </c>
-      <c r="F119" t="s">
-        <v>24</v>
-      </c>
-      <c r="G119" t="s">
-        <v>158</v>
       </c>
       <c r="H119">
         <v>4.51</v>
@@ -9247,7 +9289,7 @@
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B120" s="1">
         <v>46228</v>
@@ -9256,13 +9298,13 @@
         <v>19</v>
       </c>
       <c r="E120" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F120" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G120" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H120">
         <v>6.01</v>
@@ -9312,7 +9354,7 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B121" s="1">
         <v>46228</v>
@@ -9321,13 +9363,13 @@
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F121" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G121" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H121">
         <v>6.08</v>
@@ -9377,7 +9419,7 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B122" s="1">
         <v>46228</v>
@@ -9386,13 +9428,13 @@
         <v>19</v>
       </c>
       <c r="E122" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F122" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G122" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H122">
         <v>6.15</v>
@@ -9442,7 +9484,7 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B123" s="1">
         <v>46228</v>
@@ -9451,13 +9493,13 @@
         <v>19</v>
       </c>
       <c r="E123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G123" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H123">
         <v>4.74</v>
@@ -9507,7 +9549,7 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B124" s="1">
         <v>46228</v>
@@ -9516,13 +9558,13 @@
         <v>19</v>
       </c>
       <c r="E124" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G124" t="s">
         <v>163</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G124" t="s">
-        <v>164</v>
       </c>
       <c r="H124">
         <v>5.21</v>
@@ -9572,7 +9614,7 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B125" s="1">
         <v>46228</v>
@@ -9581,13 +9623,13 @@
         <v>19</v>
       </c>
       <c r="E125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F125" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H125">
         <v>5.57</v>
@@ -9637,7 +9679,7 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B126" s="1">
         <v>46228</v>
@@ -9646,13 +9688,13 @@
         <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F126" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G126" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H126">
         <v>4.9000000000000004</v>
@@ -9702,7 +9744,7 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B127" s="1">
         <v>46228</v>
@@ -9711,13 +9753,13 @@
         <v>19</v>
       </c>
       <c r="E127" t="s">
+        <v>165</v>
+      </c>
+      <c r="F127" t="s">
+        <v>100</v>
+      </c>
+      <c r="G127" t="s">
         <v>166</v>
-      </c>
-      <c r="F127" t="s">
-        <v>101</v>
-      </c>
-      <c r="G127" t="s">
-        <v>167</v>
       </c>
       <c r="H127">
         <v>5.17</v>
@@ -9767,7 +9809,7 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B128" s="1">
         <v>46228</v>
@@ -9776,13 +9818,13 @@
         <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F128" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G128" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H128">
         <v>2.84</v>
@@ -9832,7 +9874,7 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B129" s="1">
         <v>46228</v>
@@ -9841,13 +9883,13 @@
         <v>19</v>
       </c>
       <c r="E129" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F129" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G129" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H129">
         <v>5.08</v>
@@ -9897,7 +9939,7 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B130" s="1">
         <v>46228</v>
@@ -9906,13 +9948,13 @@
         <v>19</v>
       </c>
       <c r="E130" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F130" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G130" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H130">
         <v>5.64</v>
@@ -9962,7 +10004,7 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B131" s="1">
         <v>46228</v>
@@ -9971,13 +10013,13 @@
         <v>19</v>
       </c>
       <c r="E131" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G131" t="s">
         <v>170</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G131" t="s">
-        <v>171</v>
       </c>
       <c r="H131">
         <v>2.85</v>
@@ -10027,7 +10069,7 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B132" s="1">
         <v>46228</v>
@@ -10036,13 +10078,13 @@
         <v>19</v>
       </c>
       <c r="E132" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G132" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H132">
         <v>4.72</v>
@@ -10092,7 +10134,7 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B133" s="1">
         <v>46228</v>
@@ -10101,13 +10143,13 @@
         <v>19</v>
       </c>
       <c r="E133" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F133" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G133" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H133">
         <v>5.66</v>
@@ -10157,7 +10199,7 @@
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B134" s="1">
         <v>46230</v>
@@ -10166,13 +10208,13 @@
         <v>19</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F134" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G134" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H134">
         <v>6.33</v>
@@ -10222,7 +10264,7 @@
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B135" s="1">
         <v>46230</v>
@@ -10231,13 +10273,13 @@
         <v>19</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F135" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G135" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H135">
         <v>6.46</v>
@@ -10287,7 +10329,7 @@
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B136" s="1">
         <v>46230</v>
@@ -10296,13 +10338,13 @@
         <v>19</v>
       </c>
       <c r="E136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F136" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G136" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H136">
         <v>6.11</v>
@@ -10352,7 +10394,7 @@
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B137" s="1">
         <v>46230</v>
@@ -10361,13 +10403,13 @@
         <v>19</v>
       </c>
       <c r="E137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F137" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G137" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H137">
         <v>6.75</v>
@@ -10417,7 +10459,7 @@
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B138" s="1">
         <v>46230</v>
@@ -10426,13 +10468,13 @@
         <v>19</v>
       </c>
       <c r="E138" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F138" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G138" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H138">
         <v>6.8</v>
@@ -10482,7 +10524,7 @@
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B139" s="1">
         <v>46231</v>
@@ -10491,13 +10533,13 @@
         <v>19</v>
       </c>
       <c r="E139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F139" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H139">
         <v>6.56</v>
@@ -10547,7 +10589,7 @@
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B140" s="1">
         <v>46231</v>
@@ -10556,13 +10598,13 @@
         <v>19</v>
       </c>
       <c r="E140" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G140" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H140">
         <v>4.84</v>
@@ -10612,7 +10654,7 @@
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B141" s="1">
         <v>46231</v>
@@ -10621,13 +10663,13 @@
         <v>19</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F141" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G141" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H141">
         <v>5.8</v>
@@ -10677,7 +10719,7 @@
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B142" s="1">
         <v>46231</v>
@@ -10686,13 +10728,13 @@
         <v>19</v>
       </c>
       <c r="E142" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F142" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G142" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H142">
         <v>6.67</v>
@@ -10742,7 +10784,7 @@
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B143" s="1">
         <v>46231</v>
@@ -10751,13 +10793,13 @@
         <v>19</v>
       </c>
       <c r="E143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F143" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G143" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H143">
         <v>5.73</v>
@@ -10807,7 +10849,7 @@
     </row>
     <row r="144" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B144" s="1">
         <v>46231</v>
@@ -10816,13 +10858,13 @@
         <v>19</v>
       </c>
       <c r="E144" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F144" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G144" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H144">
         <v>6.4</v>
@@ -10872,7 +10914,7 @@
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B145" s="1">
         <v>46231</v>
@@ -10881,13 +10923,13 @@
         <v>19</v>
       </c>
       <c r="E145" t="s">
+        <v>183</v>
+      </c>
+      <c r="F145" t="s">
+        <v>23</v>
+      </c>
+      <c r="G145" t="s">
         <v>184</v>
-      </c>
-      <c r="F145" t="s">
-        <v>24</v>
-      </c>
-      <c r="G145" t="s">
-        <v>185</v>
       </c>
       <c r="H145">
         <v>5.49</v>
@@ -10937,7 +10979,7 @@
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B146" s="1">
         <v>46231</v>
@@ -10946,13 +10988,13 @@
         <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F146" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G146" t="s">
         <v>186</v>
-      </c>
-      <c r="G146" t="s">
-        <v>187</v>
       </c>
       <c r="H146">
         <v>6.27</v>
@@ -11002,7 +11044,7 @@
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B147" s="1">
         <v>46231</v>
@@ -11011,13 +11053,13 @@
         <v>19</v>
       </c>
       <c r="E147" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F147" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G147" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H147">
         <v>5.68</v>
@@ -11067,7 +11109,7 @@
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B148" s="1">
         <v>46231</v>
@@ -11076,13 +11118,13 @@
         <v>19</v>
       </c>
       <c r="E148" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G148" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H148">
         <v>6.06</v>
@@ -11132,7 +11174,7 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B149" s="1">
         <v>46232</v>
@@ -11141,13 +11183,13 @@
         <v>19</v>
       </c>
       <c r="E149" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G149" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H149">
         <v>4.8</v>
@@ -11197,7 +11239,7 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B150" s="1">
         <v>46232</v>
@@ -11206,13 +11248,13 @@
         <v>19</v>
       </c>
       <c r="E150" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F150" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G150" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H150">
         <v>5.71</v>
@@ -11262,7 +11304,7 @@
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B151" s="1">
         <v>46232</v>
@@ -11271,13 +11313,13 @@
         <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F151" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G151" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H151">
         <v>5.4</v>
@@ -11327,7 +11369,7 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B152" s="1">
         <v>46232</v>
@@ -11336,13 +11378,13 @@
         <v>19</v>
       </c>
       <c r="E152" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F152" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G152" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H152">
         <v>5.01</v>
@@ -11392,7 +11434,7 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B153" s="1">
         <v>46232</v>
@@ -11401,13 +11443,13 @@
         <v>19</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F153" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G153" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H153">
         <v>4.5999999999999996</v>
@@ -11457,7 +11499,7 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B154" s="1">
         <v>46232</v>
@@ -11466,13 +11508,13 @@
         <v>19</v>
       </c>
       <c r="E154" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F154" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G154" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H154">
         <v>4.74</v>
@@ -11522,7 +11564,7 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B155" s="1">
         <v>46232</v>
@@ -11531,13 +11573,13 @@
         <v>19</v>
       </c>
       <c r="E155" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F155" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G155" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H155">
         <v>5.19</v>
@@ -11587,7 +11629,7 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B156" s="1">
         <v>46232</v>
@@ -11596,13 +11638,13 @@
         <v>19</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F156" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G156" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H156">
         <v>5.71</v>
@@ -11652,7 +11694,7 @@
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B157" s="1">
         <v>46232</v>
@@ -11661,13 +11703,13 @@
         <v>19</v>
       </c>
       <c r="E157" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G157" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H157">
         <v>4.6900000000000004</v>
@@ -11717,7 +11759,7 @@
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B158" s="1">
         <v>46232</v>
@@ -11726,13 +11768,13 @@
         <v>19</v>
       </c>
       <c r="E158" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F158" t="s">
+        <v>26</v>
+      </c>
+      <c r="G158" t="s">
         <v>198</v>
-      </c>
-      <c r="F158" t="s">
-        <v>27</v>
-      </c>
-      <c r="G158" t="s">
-        <v>199</v>
       </c>
       <c r="H158">
         <v>4.24</v>
@@ -11782,7 +11824,7 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B159" s="1">
         <v>46232</v>
@@ -11791,13 +11833,13 @@
         <v>19</v>
       </c>
       <c r="E159" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F159" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H159">
         <v>5.64</v>
@@ -11847,7 +11889,7 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B160" s="1">
         <v>46232</v>
@@ -11856,13 +11898,13 @@
         <v>19</v>
       </c>
       <c r="E160" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G160" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H160">
         <v>4.95</v>
@@ -11912,7 +11954,7 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B161" s="1">
         <v>46232</v>
@@ -11921,13 +11963,13 @@
         <v>19</v>
       </c>
       <c r="E161" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F161" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G161" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H161">
         <v>2.59</v>
@@ -11977,7 +12019,7 @@
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B162" s="1">
         <v>46232</v>
@@ -11986,13 +12028,13 @@
         <v>19</v>
       </c>
       <c r="E162" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F162" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G162" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H162">
         <v>4.9400000000000004</v>
@@ -12042,7 +12084,7 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B163" s="1">
         <v>46232</v>
@@ -12051,13 +12093,13 @@
         <v>19</v>
       </c>
       <c r="E163" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F163" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G163" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H163">
         <v>5.71</v>
@@ -12107,7 +12149,7 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B164" s="1">
         <v>46232</v>
@@ -12116,13 +12158,13 @@
         <v>19</v>
       </c>
       <c r="E164" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F164" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G164" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H164">
         <v>5.39</v>
@@ -12172,7 +12214,7 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B165" s="1">
         <v>46232</v>
@@ -12181,13 +12223,13 @@
         <v>19</v>
       </c>
       <c r="E165" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F165" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G165" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H165">
         <v>5.0599999999999996</v>
@@ -12237,7 +12279,7 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B166" s="1">
         <v>46232</v>
@@ -12246,13 +12288,13 @@
         <v>19</v>
       </c>
       <c r="E166" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F166" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G166" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H166">
         <v>4.78</v>
@@ -12302,7 +12344,7 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B167" s="1">
         <v>46232</v>
@@ -12311,13 +12353,13 @@
         <v>19</v>
       </c>
       <c r="E167" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F167" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G167" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H167">
         <v>5.25</v>
@@ -12367,7 +12409,7 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B168" s="1">
         <v>46232</v>
@@ -12376,13 +12418,13 @@
         <v>19</v>
       </c>
       <c r="E168" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G168" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H168">
         <v>3.31</v>
@@ -12432,7 +12474,7 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B169" s="1">
         <v>46233</v>
@@ -12441,13 +12483,13 @@
         <v>19</v>
       </c>
       <c r="E169" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F169" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G169" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H169">
         <v>6.44</v>
@@ -12497,7 +12539,7 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B170" s="1">
         <v>46233</v>
@@ -12506,13 +12548,13 @@
         <v>19</v>
       </c>
       <c r="E170" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F170" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G170" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H170">
         <v>6.65</v>
@@ -12562,7 +12604,7 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B171" s="1">
         <v>46233</v>
@@ -12571,13 +12613,13 @@
         <v>19</v>
       </c>
       <c r="E171" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F171" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H171">
         <v>5.67</v>
@@ -12627,7 +12669,7 @@
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B172" s="1">
         <v>46233</v>
@@ -12636,13 +12678,13 @@
         <v>19</v>
       </c>
       <c r="E172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G172" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H172">
         <v>5.78</v>
@@ -12692,7 +12734,7 @@
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B173" s="1">
         <v>46233</v>
@@ -12701,13 +12743,13 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F173" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G173" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H173">
         <v>5.57</v>
@@ -12757,7 +12799,7 @@
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B174" s="1">
         <v>46234</v>
@@ -12766,13 +12808,13 @@
         <v>19</v>
       </c>
       <c r="E174" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G174" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H174">
         <v>4.95</v>
@@ -12822,7 +12864,7 @@
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B175" s="1">
         <v>46234</v>
@@ -12831,13 +12873,13 @@
         <v>19</v>
       </c>
       <c r="E175" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F175" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G175" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H175">
         <v>5.64</v>
@@ -12887,7 +12929,7 @@
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B176" s="1">
         <v>46234</v>
@@ -12896,13 +12938,13 @@
         <v>19</v>
       </c>
       <c r="E176" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F176" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G176" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H176">
         <v>6.52</v>
@@ -12952,7 +12994,7 @@
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B177" s="1">
         <v>46234</v>
@@ -12961,13 +13003,13 @@
         <v>19</v>
       </c>
       <c r="E177" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F177" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G177" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H177">
         <v>6.35</v>
@@ -13017,7 +13059,7 @@
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B178" s="1">
         <v>46234</v>
@@ -13026,13 +13068,13 @@
         <v>19</v>
       </c>
       <c r="E178" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F178" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G178" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H178">
         <v>6.06</v>
@@ -13082,7 +13124,7 @@
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B179" s="1">
         <v>46234</v>
@@ -13091,13 +13133,13 @@
         <v>19</v>
       </c>
       <c r="E179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F179" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G179" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H179">
         <v>6.28</v>
@@ -13147,7 +13189,7 @@
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B180" s="1">
         <v>46234</v>
@@ -13156,13 +13198,13 @@
         <v>19</v>
       </c>
       <c r="E180" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F180" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G180" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H180">
         <v>2.89</v>
@@ -13212,7 +13254,7 @@
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B181" s="1">
         <v>46235</v>
@@ -13221,13 +13263,13 @@
         <v>19</v>
       </c>
       <c r="E181" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F181" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G181" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H181">
         <v>7.61</v>
@@ -13277,7 +13319,7 @@
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B182" s="1">
         <v>46235</v>
@@ -13286,13 +13328,13 @@
         <v>19</v>
       </c>
       <c r="E182" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F182" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G182" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H182">
         <v>7.74</v>
@@ -13342,7 +13384,7 @@
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B183" s="1">
         <v>46235</v>
@@ -13351,13 +13393,13 @@
         <v>19</v>
       </c>
       <c r="E183" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G183" t="s">
         <v>220</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G183" t="s">
-        <v>221</v>
       </c>
       <c r="H183">
         <v>6.78</v>
@@ -13407,7 +13449,7 @@
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B184" s="1">
         <v>46235</v>
@@ -13416,13 +13458,13 @@
         <v>19</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F184" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G184" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H184">
         <v>8.3800000000000008</v>
@@ -13472,7 +13514,7 @@
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B185" s="1">
         <v>46235</v>
@@ -13481,13 +13523,13 @@
         <v>19</v>
       </c>
       <c r="E185" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G185" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H185">
         <v>7.26</v>
@@ -13537,7 +13579,7 @@
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B186" s="1">
         <v>46235</v>
@@ -13546,13 +13588,13 @@
         <v>19</v>
       </c>
       <c r="E186" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F186" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G186" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H186">
         <v>8.41</v>
@@ -13602,7 +13644,7 @@
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B187" s="1">
         <v>46235</v>
@@ -13611,13 +13653,13 @@
         <v>19</v>
       </c>
       <c r="E187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G187" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H187">
         <v>7.13</v>
@@ -13667,7 +13709,7 @@
     </row>
     <row r="188" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B188" s="1">
         <v>46235</v>
@@ -13676,13 +13718,13 @@
         <v>19</v>
       </c>
       <c r="E188" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F188" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G188" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H188">
         <v>7</v>
@@ -13732,7 +13774,7 @@
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B189" s="1">
         <v>46235</v>
@@ -13741,13 +13783,13 @@
         <v>19</v>
       </c>
       <c r="E189" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F189" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H189">
         <v>7.53</v>
@@ -13797,7 +13839,7 @@
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B190" s="1">
         <v>46237</v>
@@ -13806,13 +13848,13 @@
         <v>19</v>
       </c>
       <c r="E190" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F190" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G190" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H190">
         <v>5.12</v>
@@ -13862,7 +13904,7 @@
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B191" s="1">
         <v>46237</v>
@@ -13871,13 +13913,13 @@
         <v>19</v>
       </c>
       <c r="E191" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F191" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G191" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H191">
         <v>6.06</v>
@@ -13927,7 +13969,7 @@
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B192" s="1">
         <v>46237</v>
@@ -13936,13 +13978,13 @@
         <v>19</v>
       </c>
       <c r="E192" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F192" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G192" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H192">
         <v>6</v>
@@ -13992,7 +14034,7 @@
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B193" s="1">
         <v>46237</v>
@@ -14001,13 +14043,13 @@
         <v>19</v>
       </c>
       <c r="E193" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G193" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H193">
         <v>6</v>
@@ -14057,7 +14099,7 @@
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B194" s="1">
         <v>46237</v>
@@ -14066,13 +14108,13 @@
         <v>19</v>
       </c>
       <c r="E194" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F194" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G194" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H194">
         <v>5.23</v>
@@ -14122,7 +14164,7 @@
     </row>
     <row r="195" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B195" s="1">
         <v>46237</v>
@@ -14131,13 +14173,13 @@
         <v>19</v>
       </c>
       <c r="E195" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F195" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G195" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H195">
         <v>5.68</v>
@@ -14187,7 +14229,7 @@
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B196" s="1">
         <v>46237</v>
@@ -14196,13 +14238,13 @@
         <v>19</v>
       </c>
       <c r="E196" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F196" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G196" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H196">
         <v>6.13</v>
@@ -14252,7 +14294,7 @@
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B197" s="1">
         <v>46237</v>
@@ -14261,13 +14303,13 @@
         <v>19</v>
       </c>
       <c r="E197" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F197" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G197" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H197">
         <v>5.09</v>
@@ -14317,7 +14359,7 @@
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B198" s="1">
         <v>46237</v>
@@ -14326,13 +14368,13 @@
         <v>19</v>
       </c>
       <c r="E198" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F198" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G198" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H198">
         <v>5.23</v>
@@ -14382,7 +14424,7 @@
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B199" s="1">
         <v>46237</v>
@@ -14391,13 +14433,13 @@
         <v>19</v>
       </c>
       <c r="E199" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F199" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G199" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H199">
         <v>5.59</v>
@@ -14447,7 +14489,7 @@
     </row>
     <row r="200" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B200" s="1">
         <v>46238</v>
@@ -14456,13 +14498,13 @@
         <v>19</v>
       </c>
       <c r="E200" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F200" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G200" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H200">
         <v>3.67</v>
@@ -14512,7 +14554,7 @@
     </row>
     <row r="201" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B201" s="1">
         <v>46238</v>
@@ -14521,13 +14563,13 @@
         <v>19</v>
       </c>
       <c r="E201" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F201" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G201" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H201">
         <v>4.8499999999999996</v>
@@ -14577,7 +14619,7 @@
     </row>
     <row r="202" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B202" s="1">
         <v>46238</v>
@@ -14586,13 +14628,13 @@
         <v>19</v>
       </c>
       <c r="E202" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F202" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G202" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H202">
         <v>3.74</v>
@@ -14642,7 +14684,7 @@
     </row>
     <row r="203" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B203" s="1">
         <v>46238</v>
@@ -14651,13 +14693,13 @@
         <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F203" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G203" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H203">
         <v>4.03</v>
@@ -14707,7 +14749,7 @@
     </row>
     <row r="204" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B204" s="1">
         <v>46238</v>
@@ -14716,13 +14758,13 @@
         <v>19</v>
       </c>
       <c r="E204" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G204" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H204">
         <v>2.97</v>
@@ -14772,7 +14814,7 @@
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B205" s="1">
         <v>46238</v>
@@ -14781,13 +14823,13 @@
         <v>19</v>
       </c>
       <c r="E205" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F205" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G205" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H205">
         <v>3.43</v>
@@ -14837,7 +14879,7 @@
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B206" s="1">
         <v>46238</v>
@@ -14846,13 +14888,13 @@
         <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F206" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G206" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H206">
         <v>3.26</v>
@@ -14902,7 +14944,7 @@
     </row>
     <row r="207" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B207" s="1">
         <v>46238</v>
@@ -14911,13 +14953,13 @@
         <v>19</v>
       </c>
       <c r="E207" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F207" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G207" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H207">
         <v>3.11</v>
@@ -14967,7 +15009,7 @@
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B208" s="1">
         <v>46238</v>
@@ -14976,13 +15018,13 @@
         <v>19</v>
       </c>
       <c r="E208" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F208" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G208" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H208">
         <v>3.36</v>
@@ -15032,7 +15074,7 @@
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B209" s="1">
         <v>46238</v>
@@ -15041,13 +15083,13 @@
         <v>19</v>
       </c>
       <c r="E209" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F209" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G209" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H209">
         <v>4.97</v>
@@ -15097,7 +15139,7 @@
     </row>
     <row r="210" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B210" s="1">
         <v>46239</v>
@@ -15106,13 +15148,13 @@
         <v>19</v>
       </c>
       <c r="E210" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F210" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G210" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H210">
         <v>8.43</v>
@@ -15162,7 +15204,7 @@
     </row>
     <row r="211" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B211" s="1">
         <v>46239</v>
@@ -15171,13 +15213,13 @@
         <v>19</v>
       </c>
       <c r="E211" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F211" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G211" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H211">
         <v>7.23</v>
@@ -15227,7 +15269,7 @@
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B212" s="1">
         <v>46239</v>
@@ -15236,13 +15278,13 @@
         <v>19</v>
       </c>
       <c r="E212" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F212" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G212" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H212">
         <v>7.26</v>
@@ -15292,7 +15334,7 @@
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B213" s="1">
         <v>46239</v>
@@ -15301,13 +15343,13 @@
         <v>19</v>
       </c>
       <c r="E213" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F213" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G213" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H213">
         <v>6.86</v>
@@ -15357,7 +15399,7 @@
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B214" s="1">
         <v>46239</v>
@@ -15366,13 +15408,13 @@
         <v>19</v>
       </c>
       <c r="E214" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F214" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G214" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H214">
         <v>6.66</v>
@@ -15422,7 +15464,7 @@
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B215" s="1">
         <v>46239</v>
@@ -15431,13 +15473,13 @@
         <v>19</v>
       </c>
       <c r="E215" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F215" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G215" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H215">
         <v>7.84</v>
@@ -15487,7 +15529,7 @@
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B216" s="1">
         <v>46239</v>
@@ -15496,13 +15538,13 @@
         <v>19</v>
       </c>
       <c r="E216" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F216" t="s">
+        <v>100</v>
+      </c>
+      <c r="G216" t="s">
         <v>255</v>
-      </c>
-      <c r="F216" t="s">
-        <v>101</v>
-      </c>
-      <c r="G216" t="s">
-        <v>256</v>
       </c>
       <c r="H216">
         <v>6.54</v>
@@ -15552,7 +15594,7 @@
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B217" s="1">
         <v>46239</v>
@@ -15561,13 +15603,13 @@
         <v>19</v>
       </c>
       <c r="E217" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F217" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G217" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H217">
         <v>6.76</v>
@@ -15617,7 +15659,7 @@
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B218" s="1">
         <v>46240</v>
@@ -15626,13 +15668,13 @@
         <v>19</v>
       </c>
       <c r="E218" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F218" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G218" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H218">
         <v>4.0999999999999996</v>
@@ -15682,7 +15724,7 @@
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B219" s="1">
         <v>46240</v>
@@ -15691,13 +15733,13 @@
         <v>19</v>
       </c>
       <c r="E219" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F219" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G219" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H219">
         <v>4.66</v>
@@ -15747,7 +15789,7 @@
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B220" s="1">
         <v>46240</v>
@@ -15756,13 +15798,13 @@
         <v>19</v>
       </c>
       <c r="E220" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F220" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G220" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H220">
         <v>4.75</v>
@@ -15812,7 +15854,7 @@
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B221" s="1">
         <v>46240</v>
@@ -15821,13 +15863,13 @@
         <v>19</v>
       </c>
       <c r="E221" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F221" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G221" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H221">
         <v>3.61</v>
@@ -15877,7 +15919,7 @@
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B222" s="1">
         <v>46240</v>
@@ -15886,13 +15928,13 @@
         <v>19</v>
       </c>
       <c r="E222" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F222" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G222" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H222">
         <v>5.15</v>
@@ -15942,7 +15984,7 @@
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B223" s="1">
         <v>46240</v>
@@ -15951,13 +15993,13 @@
         <v>19</v>
       </c>
       <c r="E223" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F223" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G223" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H223">
         <v>4.2300000000000004</v>
@@ -16007,7 +16049,7 @@
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B224" s="1">
         <v>46240</v>
@@ -16016,13 +16058,13 @@
         <v>19</v>
       </c>
       <c r="E224" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F224" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G224" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H224">
         <v>4.37</v>
@@ -16072,7 +16114,7 @@
     </row>
     <row r="225" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B225" s="1">
         <v>46240</v>
@@ -16081,13 +16123,13 @@
         <v>19</v>
       </c>
       <c r="E225" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F225" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G225" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H225">
         <v>4.71</v>
@@ -16137,7 +16179,7 @@
     </row>
     <row r="226" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B226" s="1">
         <v>46241</v>
@@ -16146,13 +16188,13 @@
         <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F226" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G226" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H226">
         <v>9.27</v>
@@ -16202,7 +16244,7 @@
     </row>
     <row r="227" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B227" s="1">
         <v>46241</v>
@@ -16211,13 +16253,13 @@
         <v>19</v>
       </c>
       <c r="E227" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F227" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G227" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H227">
         <v>9.2799999999999994</v>
@@ -16267,7 +16309,7 @@
     </row>
     <row r="228" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B228" s="1">
         <v>46241</v>
@@ -16276,13 +16318,13 @@
         <v>19</v>
       </c>
       <c r="E228" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F228" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G228" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H228">
         <v>6.42</v>
@@ -16332,7 +16374,7 @@
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B229" s="1">
         <v>46241</v>
@@ -16341,13 +16383,13 @@
         <v>19</v>
       </c>
       <c r="E229" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F229" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G229" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H229">
         <v>10.199999999999999</v>
@@ -16397,7 +16439,7 @@
     </row>
     <row r="230" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B230" s="1">
         <v>46241</v>
@@ -16406,13 +16448,13 @@
         <v>19</v>
       </c>
       <c r="E230" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F230" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G230" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H230">
         <v>10.039999999999999</v>
@@ -16462,7 +16504,7 @@
     </row>
     <row r="231" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B231" s="1">
         <v>46241</v>
@@ -16471,13 +16513,13 @@
         <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F231" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G231" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H231">
         <v>8.9700000000000006</v>
@@ -16527,7 +16569,7 @@
     </row>
     <row r="232" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B232" s="1">
         <v>46241</v>
@@ -16536,13 +16578,13 @@
         <v>19</v>
       </c>
       <c r="E232" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F232" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G232" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H232">
         <v>8.82</v>
@@ -16592,7 +16634,7 @@
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B233" s="1">
         <v>46241</v>
@@ -16601,13 +16643,13 @@
         <v>19</v>
       </c>
       <c r="E233" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G233" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H233">
         <v>8.4</v>
@@ -16657,7 +16699,7 @@
     </row>
     <row r="234" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B234" s="1">
         <v>46244</v>
@@ -16666,13 +16708,13 @@
         <v>19</v>
       </c>
       <c r="E234" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F234" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G234" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H234">
         <v>6.9</v>
@@ -16722,7 +16764,7 @@
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B235" s="1">
         <v>46244</v>
@@ -16731,13 +16773,13 @@
         <v>19</v>
       </c>
       <c r="E235" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F235" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G235" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H235">
         <v>7.57</v>
@@ -16787,7 +16829,7 @@
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B236" s="1">
         <v>46244</v>
@@ -16796,13 +16838,13 @@
         <v>19</v>
       </c>
       <c r="E236" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F236" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G236" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H236">
         <v>6.22</v>
@@ -16852,7 +16894,7 @@
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B237" s="1">
         <v>46244</v>
@@ -16861,13 +16903,13 @@
         <v>19</v>
       </c>
       <c r="E237" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G237" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H237">
         <v>6.2</v>
@@ -16917,7 +16959,7 @@
     </row>
     <row r="238" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B238" s="1">
         <v>46244</v>
@@ -16926,13 +16968,13 @@
         <v>19</v>
       </c>
       <c r="E238" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F238" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G238" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H238">
         <v>7.23</v>
@@ -16982,7 +17024,7 @@
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B239" s="1">
         <v>46244</v>
@@ -16991,13 +17033,13 @@
         <v>19</v>
       </c>
       <c r="E239" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F239" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G239" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H239">
         <v>7.64</v>
@@ -17047,7 +17089,7 @@
     </row>
     <row r="240" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B240" s="1">
         <v>46244</v>
@@ -17056,13 +17098,13 @@
         <v>19</v>
       </c>
       <c r="E240" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F240" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G240" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H240">
         <v>6.4</v>
@@ -17112,7 +17154,7 @@
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B241" s="1">
         <v>46244</v>
@@ -17121,13 +17163,13 @@
         <v>19</v>
       </c>
       <c r="E241" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F241" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G241" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H241">
         <v>5.47</v>
@@ -17177,7 +17219,7 @@
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B242" s="1">
         <v>46244</v>
@@ -17186,13 +17228,13 @@
         <v>19</v>
       </c>
       <c r="E242" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F242" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G242" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H242">
         <v>5.44</v>
@@ -17242,7 +17284,7 @@
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B243" s="1">
         <v>46245</v>
@@ -17251,13 +17293,13 @@
         <v>19</v>
       </c>
       <c r="E243" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F243" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G243" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H243">
         <v>7.28</v>
@@ -17307,7 +17349,7 @@
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B244" s="1">
         <v>46245</v>
@@ -17316,13 +17358,13 @@
         <v>19</v>
       </c>
       <c r="E244" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G244" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H244">
         <v>6.16</v>
@@ -17372,7 +17414,7 @@
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B245" s="1">
         <v>46245</v>
@@ -17381,13 +17423,13 @@
         <v>19</v>
       </c>
       <c r="E245" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F245" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G245" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H245">
         <v>7.18</v>
@@ -17437,7 +17479,7 @@
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B246" s="1">
         <v>46245</v>
@@ -17446,13 +17488,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F246" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G246" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H246">
         <v>6.23</v>
@@ -17502,7 +17544,7 @@
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B247" s="1">
         <v>46245</v>
@@ -17511,13 +17553,13 @@
         <v>19</v>
       </c>
       <c r="E247" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F247" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G247" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H247">
         <v>8.31</v>
@@ -17567,7 +17609,7 @@
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B248" s="1">
         <v>46245</v>
@@ -17576,13 +17618,13 @@
         <v>19</v>
       </c>
       <c r="E248" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F248" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G248" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H248">
         <v>5.72</v>
@@ -17632,7 +17674,7 @@
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B249" s="1">
         <v>46247</v>
@@ -17641,13 +17683,13 @@
         <v>19</v>
       </c>
       <c r="E249" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F249" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G249" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H249">
         <v>6.32</v>
@@ -17697,7 +17739,7 @@
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B250" s="1">
         <v>46247</v>
@@ -17706,13 +17748,13 @@
         <v>19</v>
       </c>
       <c r="E250" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F250" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G250" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H250">
         <v>7.97</v>
@@ -17762,7 +17804,7 @@
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B251" s="1">
         <v>46247</v>
@@ -17771,13 +17813,13 @@
         <v>19</v>
       </c>
       <c r="E251" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F251" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G251" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H251">
         <v>6.01</v>
@@ -17827,7 +17869,7 @@
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B252" s="1">
         <v>46247</v>
@@ -17836,13 +17878,13 @@
         <v>19</v>
       </c>
       <c r="E252" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F252" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G252" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H252">
         <v>6.16</v>
@@ -17892,7 +17934,7 @@
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B253" s="1">
         <v>46247</v>
@@ -17901,13 +17943,13 @@
         <v>19</v>
       </c>
       <c r="E253" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F253" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G253" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H253">
         <v>4.33</v>
@@ -17957,7 +17999,7 @@
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B254" s="1">
         <v>46247</v>
@@ -17966,13 +18008,13 @@
         <v>19</v>
       </c>
       <c r="E254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F254" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G254" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H254">
         <v>5.42</v>
@@ -18022,7 +18064,7 @@
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B255" s="1">
         <v>46247</v>
@@ -18031,13 +18073,13 @@
         <v>19</v>
       </c>
       <c r="E255" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F255" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H255">
         <v>5.3</v>
@@ -18087,7 +18129,7 @@
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B256" s="1">
         <v>46247</v>
@@ -18096,13 +18138,13 @@
         <v>19</v>
       </c>
       <c r="E256" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F256" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G256" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H256">
         <v>5.48</v>
@@ -18152,7 +18194,7 @@
     </row>
     <row r="257" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B257" s="1">
         <v>46248</v>
@@ -18161,13 +18203,13 @@
         <v>19</v>
       </c>
       <c r="E257" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F257" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G257" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H257">
         <v>8.93</v>
@@ -18217,7 +18259,7 @@
     </row>
     <row r="258" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B258" s="1">
         <v>46248</v>
@@ -18226,13 +18268,13 @@
         <v>19</v>
       </c>
       <c r="E258" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F258" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G258" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H258">
         <v>9.5500000000000007</v>
@@ -18282,7 +18324,7 @@
     </row>
     <row r="259" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B259" s="1">
         <v>46248</v>
@@ -18291,13 +18333,13 @@
         <v>19</v>
       </c>
       <c r="E259" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F259" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G259" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H259">
         <v>7.15</v>
@@ -18347,7 +18389,7 @@
     </row>
     <row r="260" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B260" s="1">
         <v>46248</v>
@@ -18356,13 +18398,13 @@
         <v>19</v>
       </c>
       <c r="E260" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F260" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G260" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H260">
         <v>8.17</v>
@@ -18412,7 +18454,7 @@
     </row>
     <row r="261" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B261" s="1">
         <v>46248</v>
@@ -18421,13 +18463,13 @@
         <v>19</v>
       </c>
       <c r="E261" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F261" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G261" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H261">
         <v>9.02</v>
@@ -18477,7 +18519,7 @@
     </row>
     <row r="262" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B262" s="1">
         <v>46248</v>
@@ -18486,13 +18528,13 @@
         <v>19</v>
       </c>
       <c r="E262" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F262" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G262" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H262">
         <v>8.32</v>
@@ -18542,7 +18584,7 @@
     </row>
     <row r="263" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B263" s="1">
         <v>46248</v>
@@ -18551,13 +18593,13 @@
         <v>19</v>
       </c>
       <c r="E263" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G263" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H263">
         <v>7.04</v>
@@ -18607,7 +18649,7 @@
     </row>
     <row r="264" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B264" s="1">
         <v>46248</v>
@@ -18619,10 +18661,10 @@
         <v>16</v>
       </c>
       <c r="F264" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G264" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H264">
         <v>6.25</v>
@@ -18672,7 +18714,7 @@
     </row>
     <row r="265" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B265" s="1">
         <v>46248</v>
@@ -18681,13 +18723,13 @@
         <v>19</v>
       </c>
       <c r="E265" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F265" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G265" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H265">
         <v>9.7200000000000006</v>
@@ -18737,7 +18779,7 @@
     </row>
     <row r="266" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B266" s="1">
         <v>46249</v>
@@ -18746,13 +18788,13 @@
         <v>19</v>
       </c>
       <c r="E266" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F266" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G266" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H266">
         <v>7.04</v>
@@ -18802,7 +18844,7 @@
     </row>
     <row r="267" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B267" s="1">
         <v>46249</v>
@@ -18811,13 +18853,13 @@
         <v>19</v>
       </c>
       <c r="E267" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G267" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H267">
         <v>7.4</v>
@@ -18867,7 +18909,7 @@
     </row>
     <row r="268" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B268" s="1">
         <v>46249</v>
@@ -18876,13 +18918,13 @@
         <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F268" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G268" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H268">
         <v>10.88</v>
@@ -18932,7 +18974,7 @@
     </row>
     <row r="269" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B269" s="1">
         <v>46249</v>
@@ -18941,13 +18983,13 @@
         <v>19</v>
       </c>
       <c r="E269" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F269" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G269" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H269">
         <v>11.13</v>
@@ -18997,7 +19039,7 @@
     </row>
     <row r="270" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B270" s="1">
         <v>46249</v>
@@ -19006,13 +19048,13 @@
         <v>19</v>
       </c>
       <c r="E270" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G270" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H270">
         <v>9.8800000000000008</v>
@@ -19062,7 +19104,7 @@
     </row>
     <row r="271" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B271" s="1">
         <v>46249</v>
@@ -19071,13 +19113,13 @@
         <v>19</v>
       </c>
       <c r="E271" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F271" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G271" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H271">
         <v>10.06</v>
@@ -19127,7 +19169,7 @@
     </row>
     <row r="272" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B272" s="1">
         <v>46249</v>
@@ -19136,13 +19178,13 @@
         <v>19</v>
       </c>
       <c r="E272" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F272" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G272" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H272">
         <v>9.66</v>
@@ -19192,7 +19234,7 @@
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B273" s="1">
         <v>46252</v>
@@ -19204,10 +19246,10 @@
         <v>16</v>
       </c>
       <c r="F273" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G273" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H273">
         <v>5.0599999999999996</v>
@@ -19257,7 +19299,7 @@
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B274" s="1">
         <v>46252</v>
@@ -19266,13 +19308,13 @@
         <v>19</v>
       </c>
       <c r="E274" t="s">
+        <v>313</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G274" t="s">
         <v>314</v>
-      </c>
-      <c r="F274" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G274" t="s">
-        <v>315</v>
       </c>
       <c r="H274">
         <v>4.9800000000000004</v>
@@ -19322,7 +19364,7 @@
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B275" s="1">
         <v>46252</v>
@@ -19331,13 +19373,13 @@
         <v>19</v>
       </c>
       <c r="E275" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F275" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G275" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H275">
         <v>5.22</v>
@@ -19387,7 +19429,7 @@
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B276" s="1">
         <v>46252</v>
@@ -19396,13 +19438,13 @@
         <v>19</v>
       </c>
       <c r="E276" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F276" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G276" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H276">
         <v>5.17</v>
@@ -19452,7 +19494,7 @@
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B277" s="1">
         <v>46252</v>
@@ -19461,13 +19503,13 @@
         <v>19</v>
       </c>
       <c r="E277" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F277" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G277" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H277">
         <v>5.38</v>
@@ -19517,7 +19559,7 @@
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B278" s="1">
         <v>46252</v>
@@ -19526,13 +19568,13 @@
         <v>19</v>
       </c>
       <c r="E278" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F278" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G278" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H278">
         <v>5.34</v>
@@ -19582,7 +19624,7 @@
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B279" s="1">
         <v>46252</v>
@@ -19591,13 +19633,13 @@
         <v>19</v>
       </c>
       <c r="E279" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F279" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G279" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H279">
         <v>4.8099999999999996</v>
@@ -19647,7 +19689,7 @@
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B280" s="1">
         <v>46253</v>
@@ -19659,10 +19701,10 @@
         <v>16</v>
       </c>
       <c r="F280" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G280" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H280">
         <v>4.72</v>
@@ -19712,7 +19754,7 @@
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B281" s="1">
         <v>46253</v>
@@ -19721,13 +19763,13 @@
         <v>19</v>
       </c>
       <c r="E281" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F281" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H281">
         <v>5.29</v>
@@ -19777,7 +19819,7 @@
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B282" s="1">
         <v>46253</v>
@@ -19786,13 +19828,13 @@
         <v>19</v>
       </c>
       <c r="E282" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F282" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H282">
         <v>4.05</v>
@@ -19842,7 +19884,7 @@
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B283" s="1">
         <v>46253</v>
@@ -19851,13 +19893,13 @@
         <v>19</v>
       </c>
       <c r="E283" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F283" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G283" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H283">
         <v>5.26</v>
@@ -19907,7 +19949,7 @@
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B284" s="1">
         <v>46253</v>
@@ -19916,13 +19958,13 @@
         <v>19</v>
       </c>
       <c r="E284" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F284" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G284" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H284">
         <v>5.03</v>
@@ -19972,7 +20014,7 @@
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B285" s="1">
         <v>46253</v>
@@ -19981,13 +20023,13 @@
         <v>19</v>
       </c>
       <c r="E285" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F285" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G285" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H285">
         <v>3.58</v>
@@ -20037,7 +20079,7 @@
     </row>
     <row r="286" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B286" s="1">
         <v>46253</v>
@@ -20046,13 +20088,13 @@
         <v>19</v>
       </c>
       <c r="E286" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F286" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G286" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H286">
         <v>5.03</v>
@@ -20102,7 +20144,7 @@
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B287" s="1">
         <v>46254</v>
@@ -20111,13 +20153,13 @@
         <v>19</v>
       </c>
       <c r="E287" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F287" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G287" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H287">
         <v>2.4900000000000002</v>
@@ -20167,7 +20209,7 @@
     </row>
     <row r="288" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B288" s="1">
         <v>46254</v>
@@ -20179,10 +20221,10 @@
         <v>16</v>
       </c>
       <c r="F288" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G288" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H288">
         <v>3.52</v>
@@ -20232,7 +20274,7 @@
     </row>
     <row r="289" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B289" s="1">
         <v>46254</v>
@@ -20241,13 +20283,13 @@
         <v>19</v>
       </c>
       <c r="E289" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G289" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H289">
         <v>3.6</v>
@@ -20297,7 +20339,7 @@
     </row>
     <row r="290" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B290" s="1">
         <v>46254</v>
@@ -20306,13 +20348,13 @@
         <v>19</v>
       </c>
       <c r="E290" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F290" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G290" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H290">
         <v>4.46</v>
@@ -20362,7 +20404,7 @@
     </row>
     <row r="291" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B291" s="1">
         <v>46254</v>
@@ -20371,13 +20413,13 @@
         <v>19</v>
       </c>
       <c r="E291" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F291" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G291" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H291">
         <v>4.78</v>
@@ -20427,7 +20469,7 @@
     </row>
     <row r="292" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B292" s="1">
         <v>46254</v>
@@ -20436,13 +20478,13 @@
         <v>19</v>
       </c>
       <c r="E292" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F292" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G292" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H292">
         <v>3.27</v>
@@ -20492,7 +20534,7 @@
     </row>
     <row r="293" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B293" s="1">
         <v>46254</v>
@@ -20501,13 +20543,13 @@
         <v>19</v>
       </c>
       <c r="E293" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F293" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G293" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H293">
         <v>3.78</v>
@@ -20557,7 +20599,7 @@
     </row>
     <row r="294" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B294" s="1">
         <v>46254</v>
@@ -20566,13 +20608,13 @@
         <v>19</v>
       </c>
       <c r="E294" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G294" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H294">
         <v>2.36</v>
@@ -20622,7 +20664,7 @@
     </row>
     <row r="295" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B295" s="1">
         <v>46255</v>
@@ -20631,13 +20673,13 @@
         <v>19</v>
       </c>
       <c r="E295" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F295" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G295" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H295">
         <v>9.4499999999999993</v>
@@ -20687,7 +20729,7 @@
     </row>
     <row r="296" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B296" s="1">
         <v>46255</v>
@@ -20696,13 +20738,13 @@
         <v>19</v>
       </c>
       <c r="E296" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F296" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G296" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H296">
         <v>10.4</v>
@@ -20752,7 +20794,7 @@
     </row>
     <row r="297" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B297" s="1">
         <v>46255</v>
@@ -20761,13 +20803,13 @@
         <v>19</v>
       </c>
       <c r="E297" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F297" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G297" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H297">
         <v>7.61</v>
@@ -20817,7 +20859,7 @@
     </row>
     <row r="298" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B298" s="1">
         <v>46255</v>
@@ -20826,13 +20868,13 @@
         <v>19</v>
       </c>
       <c r="E298" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F298" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G298" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H298">
         <v>9.2100000000000009</v>
@@ -20882,7 +20924,7 @@
     </row>
     <row r="299" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B299" s="1">
         <v>46255</v>
@@ -20891,13 +20933,13 @@
         <v>19</v>
       </c>
       <c r="E299" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F299" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G299" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H299">
         <v>9.7100000000000009</v>
@@ -20947,7 +20989,7 @@
     </row>
     <row r="300" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B300" s="1">
         <v>46255</v>
@@ -20956,13 +20998,13 @@
         <v>19</v>
       </c>
       <c r="E300" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F300" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G300" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H300">
         <v>9.42</v>
@@ -21012,7 +21054,7 @@
     </row>
     <row r="301" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B301" s="1">
         <v>46255</v>
@@ -21021,13 +21063,13 @@
         <v>19</v>
       </c>
       <c r="E301" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F301" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G301" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H301">
         <v>10.26</v>
@@ -21077,7 +21119,7 @@
     </row>
     <row r="302" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B302" s="1">
         <v>46256</v>
@@ -21086,16 +21128,16 @@
         <v>19</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E302" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F302" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G302" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H302">
         <v>7.75</v>
@@ -21145,7 +21187,7 @@
     </row>
     <row r="303" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B303" s="1">
         <v>46256</v>
@@ -21154,16 +21196,16 @@
         <v>19</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E303" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F303" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G303" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H303">
         <v>7.95</v>
@@ -21213,7 +21255,7 @@
     </row>
     <row r="304" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B304" s="1">
         <v>46256</v>
@@ -21222,16 +21264,16 @@
         <v>19</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E304" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F304" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G304" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H304">
         <v>8.93</v>
@@ -21281,7 +21323,7 @@
     </row>
     <row r="305" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B305" s="1">
         <v>46256</v>
@@ -21290,16 +21332,16 @@
         <v>19</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E305" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F305" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G305" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H305">
         <v>11.12</v>
@@ -21349,7 +21391,7 @@
     </row>
     <row r="306" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B306" s="1">
         <v>46256</v>
@@ -21358,16 +21400,16 @@
         <v>19</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E306" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F306" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G306" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H306">
         <v>10.28</v>
@@ -21417,7 +21459,7 @@
     </row>
     <row r="307" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B307" s="1">
         <v>46256</v>
@@ -21426,16 +21468,16 @@
         <v>19</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E307" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F307" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G307" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H307">
         <v>11.72</v>
@@ -21485,7 +21527,7 @@
     </row>
     <row r="308" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B308" s="1">
         <v>46259</v>
@@ -21494,16 +21536,16 @@
         <v>19</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E308" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F308" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G308" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H308">
         <v>5.81</v>
@@ -21553,7 +21595,7 @@
     </row>
     <row r="309" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B309" s="1">
         <v>46259</v>
@@ -21562,16 +21604,16 @@
         <v>19</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E309" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F309" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G309" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H309">
         <v>3.77</v>
@@ -21621,7 +21663,7 @@
     </row>
     <row r="310" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B310" s="1">
         <v>46260</v>
@@ -21630,16 +21672,16 @@
         <v>19</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E310" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F310" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G310" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H310">
         <v>5.73</v>
@@ -21689,7 +21731,7 @@
     </row>
     <row r="311" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B311" s="1">
         <v>46260</v>
@@ -21698,16 +21740,16 @@
         <v>19</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E311" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F311" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G311" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H311">
         <v>5.46</v>
@@ -21757,7 +21799,7 @@
     </row>
     <row r="312" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B312" s="1">
         <v>46260</v>
@@ -21766,16 +21808,16 @@
         <v>19</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E312" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F312" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G312" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H312">
         <v>6.53</v>
@@ -21825,7 +21867,7 @@
     </row>
     <row r="313" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B313" s="1">
         <v>46260</v>
@@ -21834,16 +21876,16 @@
         <v>19</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E313" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F313" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G313" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H313">
         <v>4.46</v>
@@ -21893,7 +21935,7 @@
     </row>
     <row r="314" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B314" s="1">
         <v>46260</v>
@@ -21902,16 +21944,16 @@
         <v>19</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E314" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G314" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H314">
         <v>5.72</v>
@@ -21961,7 +22003,7 @@
     </row>
     <row r="315" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B315" s="1">
         <v>46260</v>
@@ -21970,16 +22012,16 @@
         <v>19</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E315" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F315" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G315" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H315">
         <v>5.87</v>
@@ -22029,7 +22071,7 @@
     </row>
     <row r="316" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B316" s="1">
         <v>46260</v>
@@ -22038,16 +22080,16 @@
         <v>19</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E316" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F316" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G316" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H316">
         <v>7.23</v>
@@ -22097,7 +22139,7 @@
     </row>
     <row r="317" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B317" s="1">
         <v>46261</v>
@@ -22106,16 +22148,16 @@
         <v>19</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E317" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F317" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G317" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H317">
         <v>3.13</v>
@@ -22165,7 +22207,7 @@
     </row>
     <row r="318" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B318" s="1">
         <v>46261</v>
@@ -22174,16 +22216,16 @@
         <v>19</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E318" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F318" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G318" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H318">
         <v>5.33</v>
@@ -22233,7 +22275,7 @@
     </row>
     <row r="319" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B319" s="1">
         <v>46261</v>
@@ -22242,16 +22284,16 @@
         <v>19</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E319" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F319" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G319" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H319">
         <v>3.72</v>
@@ -22301,7 +22343,7 @@
     </row>
     <row r="320" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B320" s="1">
         <v>46261</v>
@@ -22310,16 +22352,16 @@
         <v>19</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E320" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F320" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G320" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H320">
         <v>4.09</v>
@@ -22369,7 +22411,7 @@
     </row>
     <row r="321" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B321" s="1">
         <v>46261</v>
@@ -22378,16 +22420,16 @@
         <v>19</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E321" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F321" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G321" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H321">
         <v>3.43</v>
@@ -22437,7 +22479,7 @@
     </row>
     <row r="322" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B322" s="1">
         <v>46261</v>
@@ -22446,16 +22488,16 @@
         <v>19</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E322" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F322" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G322" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H322">
         <v>4.1100000000000003</v>
@@ -22505,7 +22547,7 @@
     </row>
     <row r="323" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B323" s="1">
         <v>46261</v>
@@ -22514,16 +22556,16 @@
         <v>19</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E323" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F323" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G323" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H323">
         <v>3.9</v>
@@ -22568,6 +22610,958 @@
         <v>11</v>
       </c>
       <c r="V323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A324" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" s="1">
+        <v>46262</v>
+      </c>
+      <c r="C324" t="s">
+        <v>19</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E324" t="s">
+        <v>37</v>
+      </c>
+      <c r="F324" t="s">
+        <v>26</v>
+      </c>
+      <c r="G324" t="s">
+        <v>362</v>
+      </c>
+      <c r="H324">
+        <v>4.67</v>
+      </c>
+      <c r="I324">
+        <v>0.4</v>
+      </c>
+      <c r="J324">
+        <v>4.26</v>
+      </c>
+      <c r="K324">
+        <v>0.33</v>
+      </c>
+      <c r="L324">
+        <v>0.08</v>
+      </c>
+      <c r="M324">
+        <v>0</v>
+      </c>
+      <c r="N324">
+        <v>0</v>
+      </c>
+      <c r="O324">
+        <v>0</v>
+      </c>
+      <c r="P324">
+        <v>3.76</v>
+      </c>
+      <c r="Q324">
+        <v>23.66</v>
+      </c>
+      <c r="R324">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="S324">
+        <v>23</v>
+      </c>
+      <c r="T324">
+        <v>7</v>
+      </c>
+      <c r="U324">
+        <v>10</v>
+      </c>
+      <c r="V324">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A325" t="s">
+        <v>21</v>
+      </c>
+      <c r="B325" s="1">
+        <v>46262</v>
+      </c>
+      <c r="C325" t="s">
+        <v>19</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E325" t="s">
+        <v>165</v>
+      </c>
+      <c r="F325" t="s">
+        <v>100</v>
+      </c>
+      <c r="G325" t="s">
+        <v>363</v>
+      </c>
+      <c r="H325">
+        <v>5.56</v>
+      </c>
+      <c r="I325">
+        <v>0.36</v>
+      </c>
+      <c r="J325">
+        <v>5.19</v>
+      </c>
+      <c r="K325">
+        <v>0.24</v>
+      </c>
+      <c r="L325">
+        <v>0.09</v>
+      </c>
+      <c r="M325">
+        <v>0.02</v>
+      </c>
+      <c r="N325">
+        <v>0.01</v>
+      </c>
+      <c r="O325">
+        <v>3</v>
+      </c>
+      <c r="P325">
+        <v>3.41</v>
+      </c>
+      <c r="Q325">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="R325">
+        <v>4.45</v>
+      </c>
+      <c r="S325">
+        <v>14</v>
+      </c>
+      <c r="T325">
+        <v>2</v>
+      </c>
+      <c r="U325">
+        <v>12</v>
+      </c>
+      <c r="V325">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>21</v>
+      </c>
+      <c r="B326" s="1">
+        <v>46262</v>
+      </c>
+      <c r="C326" t="s">
+        <v>19</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E326" t="s">
+        <v>30</v>
+      </c>
+      <c r="F326" t="s">
+        <v>27</v>
+      </c>
+      <c r="G326" t="s">
+        <v>362</v>
+      </c>
+      <c r="H326">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="I326">
+        <v>0.43</v>
+      </c>
+      <c r="J326">
+        <v>4.42</v>
+      </c>
+      <c r="K326">
+        <v>0.23</v>
+      </c>
+      <c r="L326">
+        <v>0.16</v>
+      </c>
+      <c r="M326">
+        <v>0.04</v>
+      </c>
+      <c r="N326">
+        <v>0.01</v>
+      </c>
+      <c r="O326">
+        <v>3</v>
+      </c>
+      <c r="P326">
+        <v>3.88</v>
+      </c>
+      <c r="Q326">
+        <v>30.45</v>
+      </c>
+      <c r="R326">
+        <v>4.41</v>
+      </c>
+      <c r="S326">
+        <v>10</v>
+      </c>
+      <c r="T326">
+        <v>6</v>
+      </c>
+      <c r="U326">
+        <v>15</v>
+      </c>
+      <c r="V326">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>370</v>
+      </c>
+      <c r="B327" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C327" t="s">
+        <v>19</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E327" t="s">
+        <v>31</v>
+      </c>
+      <c r="F327" t="s">
+        <v>26</v>
+      </c>
+      <c r="G327" t="s">
+        <v>365</v>
+      </c>
+      <c r="H327">
+        <v>11.76</v>
+      </c>
+      <c r="I327">
+        <v>1.68</v>
+      </c>
+      <c r="J327">
+        <v>10.06</v>
+      </c>
+      <c r="K327">
+        <v>1.37</v>
+      </c>
+      <c r="L327">
+        <v>0.32</v>
+      </c>
+      <c r="M327">
+        <v>0.01</v>
+      </c>
+      <c r="N327">
+        <v>0</v>
+      </c>
+      <c r="O327">
+        <v>1</v>
+      </c>
+      <c r="P327">
+        <v>7.04</v>
+      </c>
+      <c r="Q327">
+        <v>25.91</v>
+      </c>
+      <c r="R327">
+        <v>4.16</v>
+      </c>
+      <c r="S327">
+        <v>38</v>
+      </c>
+      <c r="T327">
+        <v>2</v>
+      </c>
+      <c r="U327">
+        <v>26</v>
+      </c>
+      <c r="V327">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>370</v>
+      </c>
+      <c r="B328" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C328" t="s">
+        <v>19</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E328" t="s">
+        <v>165</v>
+      </c>
+      <c r="F328" t="s">
+        <v>100</v>
+      </c>
+      <c r="G328" t="s">
+        <v>366</v>
+      </c>
+      <c r="H328">
+        <v>8.1</v>
+      </c>
+      <c r="I328">
+        <v>1.38</v>
+      </c>
+      <c r="J328">
+        <v>6.7</v>
+      </c>
+      <c r="K328">
+        <v>0.87</v>
+      </c>
+      <c r="L328">
+        <v>0.39</v>
+      </c>
+      <c r="M328">
+        <v>0.12</v>
+      </c>
+      <c r="N328">
+        <v>0.02</v>
+      </c>
+      <c r="O328">
+        <v>9</v>
+      </c>
+      <c r="P328">
+        <v>6.29</v>
+      </c>
+      <c r="Q328">
+        <v>32.659999999999997</v>
+      </c>
+      <c r="R328">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="S328">
+        <v>32</v>
+      </c>
+      <c r="T328">
+        <v>5</v>
+      </c>
+      <c r="U328">
+        <v>21</v>
+      </c>
+      <c r="V328">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="329" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>370</v>
+      </c>
+      <c r="B329" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C329" t="s">
+        <v>19</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E329" t="s">
+        <v>88</v>
+      </c>
+      <c r="F329" t="s">
+        <v>23</v>
+      </c>
+      <c r="G329" t="s">
+        <v>367</v>
+      </c>
+      <c r="H329">
+        <v>9.17</v>
+      </c>
+      <c r="I329">
+        <v>0.92</v>
+      </c>
+      <c r="J329">
+        <v>8.23</v>
+      </c>
+      <c r="K329">
+        <v>0.59</v>
+      </c>
+      <c r="L329">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M329">
+        <v>0.06</v>
+      </c>
+      <c r="N329">
+        <v>0</v>
+      </c>
+      <c r="O329">
+        <v>7</v>
+      </c>
+      <c r="P329">
+        <v>5.5</v>
+      </c>
+      <c r="Q329">
+        <v>27.88</v>
+      </c>
+      <c r="R329">
+        <v>4.62</v>
+      </c>
+      <c r="S329">
+        <v>21</v>
+      </c>
+      <c r="T329">
+        <v>1</v>
+      </c>
+      <c r="U329">
+        <v>21</v>
+      </c>
+      <c r="V329">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="330" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>370</v>
+      </c>
+      <c r="B330" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C330" t="s">
+        <v>19</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E330" t="s">
+        <v>81</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G330" t="s">
+        <v>368</v>
+      </c>
+      <c r="H330">
+        <v>7.25</v>
+      </c>
+      <c r="I330">
+        <v>1.47</v>
+      </c>
+      <c r="J330">
+        <v>5.76</v>
+      </c>
+      <c r="K330">
+        <v>1.06</v>
+      </c>
+      <c r="L330">
+        <v>0.37</v>
+      </c>
+      <c r="M330">
+        <v>0.05</v>
+      </c>
+      <c r="N330">
+        <v>0</v>
+      </c>
+      <c r="O330">
+        <v>5</v>
+      </c>
+      <c r="P330">
+        <v>7.07</v>
+      </c>
+      <c r="Q330">
+        <v>27.91</v>
+      </c>
+      <c r="R330">
+        <v>4.34</v>
+      </c>
+      <c r="S330">
+        <v>30</v>
+      </c>
+      <c r="T330">
+        <v>3</v>
+      </c>
+      <c r="U330">
+        <v>27</v>
+      </c>
+      <c r="V330">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="331" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>370</v>
+      </c>
+      <c r="B331" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C331" t="s">
+        <v>19</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E331" t="s">
+        <v>183</v>
+      </c>
+      <c r="F331" t="s">
+        <v>23</v>
+      </c>
+      <c r="G331" t="s">
+        <v>369</v>
+      </c>
+      <c r="H331">
+        <v>7.75</v>
+      </c>
+      <c r="I331">
+        <v>0.84</v>
+      </c>
+      <c r="J331">
+        <v>6.9</v>
+      </c>
+      <c r="K331">
+        <v>0.64</v>
+      </c>
+      <c r="L331">
+        <v>0.15</v>
+      </c>
+      <c r="M331">
+        <v>0.06</v>
+      </c>
+      <c r="N331">
+        <v>0</v>
+      </c>
+      <c r="O331">
+        <v>6</v>
+      </c>
+      <c r="P331">
+        <v>6.18</v>
+      </c>
+      <c r="Q331">
+        <v>29.51</v>
+      </c>
+      <c r="R331">
+        <v>4.38</v>
+      </c>
+      <c r="S331">
+        <v>22</v>
+      </c>
+      <c r="T331">
+        <v>4</v>
+      </c>
+      <c r="U331">
+        <v>24</v>
+      </c>
+      <c r="V331">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>21</v>
+      </c>
+      <c r="B332" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C332" t="s">
+        <v>19</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E332" t="s">
+        <v>37</v>
+      </c>
+      <c r="F332" t="s">
+        <v>26</v>
+      </c>
+      <c r="G332" t="s">
+        <v>371</v>
+      </c>
+      <c r="H332">
+        <v>5.94</v>
+      </c>
+      <c r="I332">
+        <v>1.9</v>
+      </c>
+      <c r="J332">
+        <v>4.04</v>
+      </c>
+      <c r="K332">
+        <v>1.25</v>
+      </c>
+      <c r="L332">
+        <v>0.66</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
+      </c>
+      <c r="N332">
+        <v>0</v>
+      </c>
+      <c r="O332">
+        <v>0</v>
+      </c>
+      <c r="P332">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="Q332">
+        <v>22.97</v>
+      </c>
+      <c r="R332">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="S332">
+        <v>39</v>
+      </c>
+      <c r="T332">
+        <v>5</v>
+      </c>
+      <c r="U332">
+        <v>12</v>
+      </c>
+      <c r="V332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>21</v>
+      </c>
+      <c r="B333" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C333" t="s">
+        <v>19</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E333" t="s">
+        <v>30</v>
+      </c>
+      <c r="F333" t="s">
+        <v>27</v>
+      </c>
+      <c r="G333" t="s">
+        <v>372</v>
+      </c>
+      <c r="H333">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I333">
+        <v>0.16</v>
+      </c>
+      <c r="J333">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="K333">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L333">
+        <v>0.03</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>0</v>
+      </c>
+      <c r="O333">
+        <v>0</v>
+      </c>
+      <c r="P333">
+        <v>3.64</v>
+      </c>
+      <c r="Q333">
+        <v>23.86</v>
+      </c>
+      <c r="R333">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="S333">
+        <v>17</v>
+      </c>
+      <c r="T333">
+        <v>4</v>
+      </c>
+      <c r="U333">
+        <v>11</v>
+      </c>
+      <c r="V333">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>21</v>
+      </c>
+      <c r="B334" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C334" t="s">
+        <v>19</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E334" t="s">
+        <v>90</v>
+      </c>
+      <c r="F334" t="s">
+        <v>100</v>
+      </c>
+      <c r="G334" t="s">
+        <v>373</v>
+      </c>
+      <c r="H334">
+        <v>5.71</v>
+      </c>
+      <c r="I334">
+        <v>1.08</v>
+      </c>
+      <c r="J334">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="K334">
+        <v>1.03</v>
+      </c>
+      <c r="L334">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M334">
+        <v>0</v>
+      </c>
+      <c r="N334">
+        <v>0</v>
+      </c>
+      <c r="O334">
+        <v>0</v>
+      </c>
+      <c r="P334">
+        <v>3.59</v>
+      </c>
+      <c r="Q334">
+        <v>22.59</v>
+      </c>
+      <c r="R334">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="S334">
+        <v>53</v>
+      </c>
+      <c r="T334">
+        <v>14</v>
+      </c>
+      <c r="U334">
+        <v>20</v>
+      </c>
+      <c r="V334">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="335" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C335" t="s">
+        <v>19</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E335" t="s">
+        <v>34</v>
+      </c>
+      <c r="F335" t="s">
+        <v>26</v>
+      </c>
+      <c r="G335" t="s">
+        <v>374</v>
+      </c>
+      <c r="H335">
+        <v>5.55</v>
+      </c>
+      <c r="I335">
+        <v>1.71</v>
+      </c>
+      <c r="J335">
+        <v>3.84</v>
+      </c>
+      <c r="K335">
+        <v>1.3</v>
+      </c>
+      <c r="L335">
+        <v>0.41</v>
+      </c>
+      <c r="M335">
+        <v>0</v>
+      </c>
+      <c r="N335">
+        <v>0</v>
+      </c>
+      <c r="O335">
+        <v>0</v>
+      </c>
+      <c r="P335">
+        <v>3.97</v>
+      </c>
+      <c r="Q335">
+        <v>22.29</v>
+      </c>
+      <c r="R335">
+        <v>4.12</v>
+      </c>
+      <c r="S335">
+        <v>26</v>
+      </c>
+      <c r="T335">
+        <v>5</v>
+      </c>
+      <c r="U335">
+        <v>8</v>
+      </c>
+      <c r="V335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>21</v>
+      </c>
+      <c r="B336" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C336" t="s">
+        <v>19</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E336" t="s">
+        <v>165</v>
+      </c>
+      <c r="F336" t="s">
+        <v>100</v>
+      </c>
+      <c r="G336" t="s">
+        <v>375</v>
+      </c>
+      <c r="H336">
+        <v>4.58</v>
+      </c>
+      <c r="I336">
+        <v>0.03</v>
+      </c>
+      <c r="J336">
+        <v>4.55</v>
+      </c>
+      <c r="K336">
+        <v>0.03</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336">
+        <v>0</v>
+      </c>
+      <c r="N336">
+        <v>0</v>
+      </c>
+      <c r="O336">
+        <v>0</v>
+      </c>
+      <c r="P336">
+        <v>3.3</v>
+      </c>
+      <c r="Q336">
+        <v>20.36</v>
+      </c>
+      <c r="R336">
+        <v>5.2</v>
+      </c>
+      <c r="S336">
+        <v>18</v>
+      </c>
+      <c r="T336">
+        <v>2</v>
+      </c>
+      <c r="U336">
+        <v>12</v>
+      </c>
+      <c r="V336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>21</v>
+      </c>
+      <c r="B337" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C337" t="s">
+        <v>19</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E337" t="s">
+        <v>88</v>
+      </c>
+      <c r="F337" t="s">
+        <v>23</v>
+      </c>
+      <c r="G337" t="s">
+        <v>376</v>
+      </c>
+      <c r="H337">
+        <v>2.77</v>
+      </c>
+      <c r="I337">
+        <v>0.04</v>
+      </c>
+      <c r="J337">
+        <v>2.73</v>
+      </c>
+      <c r="K337">
+        <v>0.04</v>
+      </c>
+      <c r="L337">
+        <v>0.01</v>
+      </c>
+      <c r="M337">
+        <v>0</v>
+      </c>
+      <c r="N337">
+        <v>0</v>
+      </c>
+      <c r="O337">
+        <v>0</v>
+      </c>
+      <c r="P337">
+        <v>2.41</v>
+      </c>
+      <c r="Q337">
+        <v>20.82</v>
+      </c>
+      <c r="R337">
+        <v>3.96</v>
+      </c>
+      <c r="S337">
+        <v>9</v>
+      </c>
+      <c r="T337">
+        <v>0</v>
+      </c>
+      <c r="U337">
+        <v>7</v>
+      </c>
+      <c r="V337">
         <v>0</v>
       </c>
     </row>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EABADD-8741-CD4E-9B7C-545877866B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C8E72B-71CB-6C49-8B59-515396E86922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="384">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1169,6 +1169,24 @@
   </si>
   <si>
     <t>J+2</t>
+  </si>
+  <si>
+    <t>01:28:21</t>
+  </si>
+  <si>
+    <t>01:24:56</t>
+  </si>
+  <si>
+    <t>01:34:19</t>
+  </si>
+  <si>
+    <t>01:38:03</t>
+  </si>
+  <si>
+    <t>01:28:30</t>
+  </si>
+  <si>
+    <t>01:23:14</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V337"/>
+  <dimension ref="A1:V344"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -23565,6 +23583,482 @@
         <v>0</v>
       </c>
     </row>
+    <row r="338" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>21</v>
+      </c>
+      <c r="B338" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C338" t="s">
+        <v>19</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E338" t="s">
+        <v>90</v>
+      </c>
+      <c r="F338" t="s">
+        <v>100</v>
+      </c>
+      <c r="G338" t="s">
+        <v>378</v>
+      </c>
+      <c r="H338">
+        <v>4.57</v>
+      </c>
+      <c r="I338">
+        <v>0.1</v>
+      </c>
+      <c r="J338">
+        <v>4.46</v>
+      </c>
+      <c r="K338">
+        <v>0.1</v>
+      </c>
+      <c r="L338">
+        <v>0.01</v>
+      </c>
+      <c r="M338">
+        <v>0</v>
+      </c>
+      <c r="N338">
+        <v>0</v>
+      </c>
+      <c r="O338">
+        <v>0</v>
+      </c>
+      <c r="P338">
+        <v>2.54</v>
+      </c>
+      <c r="Q338">
+        <v>23.1</v>
+      </c>
+      <c r="R338">
+        <v>5.2</v>
+      </c>
+      <c r="S338">
+        <v>38</v>
+      </c>
+      <c r="T338">
+        <v>10</v>
+      </c>
+      <c r="U338">
+        <v>22</v>
+      </c>
+      <c r="V338">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="339" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>21</v>
+      </c>
+      <c r="B339" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C339" t="s">
+        <v>19</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E339" t="s">
+        <v>88</v>
+      </c>
+      <c r="F339" t="s">
+        <v>23</v>
+      </c>
+      <c r="G339" t="s">
+        <v>379</v>
+      </c>
+      <c r="H339">
+        <v>3.93</v>
+      </c>
+      <c r="I339">
+        <v>0.05</v>
+      </c>
+      <c r="J339">
+        <v>3.88</v>
+      </c>
+      <c r="K339">
+        <v>0.04</v>
+      </c>
+      <c r="L339">
+        <v>0</v>
+      </c>
+      <c r="M339">
+        <v>0</v>
+      </c>
+      <c r="N339">
+        <v>0</v>
+      </c>
+      <c r="O339">
+        <v>0</v>
+      </c>
+      <c r="P339">
+        <v>2.5</v>
+      </c>
+      <c r="Q339">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="R339">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="S339">
+        <v>8</v>
+      </c>
+      <c r="T339">
+        <v>1</v>
+      </c>
+      <c r="U339">
+        <v>6</v>
+      </c>
+      <c r="V339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>21</v>
+      </c>
+      <c r="B340" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C340" t="s">
+        <v>19</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E340" t="s">
+        <v>165</v>
+      </c>
+      <c r="F340" t="s">
+        <v>100</v>
+      </c>
+      <c r="G340" t="s">
+        <v>380</v>
+      </c>
+      <c r="H340">
+        <v>5.58</v>
+      </c>
+      <c r="I340">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J340">
+        <v>5.5</v>
+      </c>
+      <c r="K340">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L340">
+        <v>0.01</v>
+      </c>
+      <c r="M340">
+        <v>0</v>
+      </c>
+      <c r="N340">
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <v>2.68</v>
+      </c>
+      <c r="Q340">
+        <v>21.33</v>
+      </c>
+      <c r="R340">
+        <v>4.16</v>
+      </c>
+      <c r="S340">
+        <v>30</v>
+      </c>
+      <c r="T340">
+        <v>4</v>
+      </c>
+      <c r="U340">
+        <v>18</v>
+      </c>
+      <c r="V340">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>21</v>
+      </c>
+      <c r="B341" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C341" t="s">
+        <v>19</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E341" t="s">
+        <v>30</v>
+      </c>
+      <c r="F341" t="s">
+        <v>27</v>
+      </c>
+      <c r="G341" t="s">
+        <v>381</v>
+      </c>
+      <c r="H341">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="I341">
+        <v>0.13</v>
+      </c>
+      <c r="J341">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="K341">
+        <v>0.13</v>
+      </c>
+      <c r="L341">
+        <v>0.01</v>
+      </c>
+      <c r="M341">
+        <v>0</v>
+      </c>
+      <c r="N341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>2.87</v>
+      </c>
+      <c r="Q341">
+        <v>21.8</v>
+      </c>
+      <c r="R341">
+        <v>4.54</v>
+      </c>
+      <c r="S341">
+        <v>18</v>
+      </c>
+      <c r="T341">
+        <v>3</v>
+      </c>
+      <c r="U341">
+        <v>14</v>
+      </c>
+      <c r="V341">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>21</v>
+      </c>
+      <c r="B342" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C342" t="s">
+        <v>19</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E342" t="s">
+        <v>29</v>
+      </c>
+      <c r="F342" t="s">
+        <v>25</v>
+      </c>
+      <c r="G342" t="s">
+        <v>382</v>
+      </c>
+      <c r="H342">
+        <v>6.19</v>
+      </c>
+      <c r="I342">
+        <v>0.15</v>
+      </c>
+      <c r="J342">
+        <v>6.04</v>
+      </c>
+      <c r="K342">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L342">
+        <v>0.01</v>
+      </c>
+      <c r="M342">
+        <v>0</v>
+      </c>
+      <c r="N342">
+        <v>0</v>
+      </c>
+      <c r="O342">
+        <v>0</v>
+      </c>
+      <c r="P342">
+        <v>2.73</v>
+      </c>
+      <c r="Q342">
+        <v>23.97</v>
+      </c>
+      <c r="R342">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="S342">
+        <v>32</v>
+      </c>
+      <c r="T342">
+        <v>5</v>
+      </c>
+      <c r="U342">
+        <v>20</v>
+      </c>
+      <c r="V342">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>21</v>
+      </c>
+      <c r="B343" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C343" t="s">
+        <v>19</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E343" t="s">
+        <v>34</v>
+      </c>
+      <c r="F343" t="s">
+        <v>26</v>
+      </c>
+      <c r="G343" t="s">
+        <v>383</v>
+      </c>
+      <c r="H343">
+        <v>3.8</v>
+      </c>
+      <c r="I343">
+        <v>0.08</v>
+      </c>
+      <c r="J343">
+        <v>3.72</v>
+      </c>
+      <c r="K343">
+        <v>0.09</v>
+      </c>
+      <c r="L343">
+        <v>0</v>
+      </c>
+      <c r="M343">
+        <v>0</v>
+      </c>
+      <c r="N343">
+        <v>0</v>
+      </c>
+      <c r="O343">
+        <v>0</v>
+      </c>
+      <c r="P343">
+        <v>2.59</v>
+      </c>
+      <c r="Q343">
+        <v>19.25</v>
+      </c>
+      <c r="R343">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="S343">
+        <v>18</v>
+      </c>
+      <c r="T343">
+        <v>3</v>
+      </c>
+      <c r="U343">
+        <v>14</v>
+      </c>
+      <c r="V343">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="344" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>21</v>
+      </c>
+      <c r="B344" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C344" t="s">
+        <v>19</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E344" t="s">
+        <v>37</v>
+      </c>
+      <c r="F344" t="s">
+        <v>26</v>
+      </c>
+      <c r="G344" t="s">
+        <v>373</v>
+      </c>
+      <c r="H344">
+        <v>4.59</v>
+      </c>
+      <c r="I344">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J344">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="K344">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L344">
+        <v>0</v>
+      </c>
+      <c r="M344">
+        <v>0</v>
+      </c>
+      <c r="N344">
+        <v>0</v>
+      </c>
+      <c r="O344">
+        <v>0</v>
+      </c>
+      <c r="P344">
+        <v>2.61</v>
+      </c>
+      <c r="Q344">
+        <v>21.07</v>
+      </c>
+      <c r="R344">
+        <v>5.35</v>
+      </c>
+      <c r="S344">
+        <v>31</v>
+      </c>
+      <c r="T344">
+        <v>8</v>
+      </c>
+      <c r="U344">
+        <v>23</v>
+      </c>
+      <c r="V344">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C8E72B-71CB-6C49-8B59-515396E86922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79969A-D7C4-CF48-B5B6-B89D1A10148D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="388">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1187,6 +1187,18 @@
   </si>
   <si>
     <t>01:23:14</t>
+  </si>
+  <si>
+    <t>01:24:38</t>
+  </si>
+  <si>
+    <t>01:24:59</t>
+  </si>
+  <si>
+    <t>01:13:47</t>
+  </si>
+  <si>
+    <t>01:24:52</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V344"/>
+  <dimension ref="A1:V350"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -24059,6 +24071,414 @@
         <v>4</v>
       </c>
     </row>
+    <row r="345" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>21</v>
+      </c>
+      <c r="B345" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C345" t="s">
+        <v>19</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E345" t="s">
+        <v>90</v>
+      </c>
+      <c r="F345" t="s">
+        <v>100</v>
+      </c>
+      <c r="G345" t="s">
+        <v>384</v>
+      </c>
+      <c r="H345">
+        <v>6.25</v>
+      </c>
+      <c r="I345">
+        <v>0.72</v>
+      </c>
+      <c r="J345">
+        <v>5.51</v>
+      </c>
+      <c r="K345">
+        <v>0.54</v>
+      </c>
+      <c r="L345">
+        <v>0.17</v>
+      </c>
+      <c r="M345">
+        <v>0.03</v>
+      </c>
+      <c r="N345">
+        <v>0</v>
+      </c>
+      <c r="O345">
+        <v>4</v>
+      </c>
+      <c r="P345">
+        <v>3.95</v>
+      </c>
+      <c r="Q345">
+        <v>28.06</v>
+      </c>
+      <c r="R345">
+        <v>6.46</v>
+      </c>
+      <c r="S345">
+        <v>60</v>
+      </c>
+      <c r="T345">
+        <v>24</v>
+      </c>
+      <c r="U345">
+        <v>52</v>
+      </c>
+      <c r="V345">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="346" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>21</v>
+      </c>
+      <c r="B346" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C346" t="s">
+        <v>19</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E346" t="s">
+        <v>29</v>
+      </c>
+      <c r="F346" t="s">
+        <v>25</v>
+      </c>
+      <c r="G346" t="s">
+        <v>385</v>
+      </c>
+      <c r="H346">
+        <v>6.45</v>
+      </c>
+      <c r="I346">
+        <v>1</v>
+      </c>
+      <c r="J346">
+        <v>5.44</v>
+      </c>
+      <c r="K346">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L346">
+        <v>0.38</v>
+      </c>
+      <c r="M346">
+        <v>0.05</v>
+      </c>
+      <c r="N346">
+        <v>0</v>
+      </c>
+      <c r="O346">
+        <v>6</v>
+      </c>
+      <c r="P346">
+        <v>4.5</v>
+      </c>
+      <c r="Q346">
+        <v>27.32</v>
+      </c>
+      <c r="R346">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S346">
+        <v>35</v>
+      </c>
+      <c r="T346">
+        <v>7</v>
+      </c>
+      <c r="U346">
+        <v>30</v>
+      </c>
+      <c r="V346">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="347" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>21</v>
+      </c>
+      <c r="B347" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C347" t="s">
+        <v>19</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E347" t="s">
+        <v>30</v>
+      </c>
+      <c r="F347" t="s">
+        <v>27</v>
+      </c>
+      <c r="G347" t="s">
+        <v>385</v>
+      </c>
+      <c r="H347">
+        <v>6.96</v>
+      </c>
+      <c r="I347">
+        <v>0.82</v>
+      </c>
+      <c r="J347">
+        <v>6.12</v>
+      </c>
+      <c r="K347">
+        <v>0.49</v>
+      </c>
+      <c r="L347">
+        <v>0.23</v>
+      </c>
+      <c r="M347">
+        <v>0.1</v>
+      </c>
+      <c r="N347">
+        <v>0.02</v>
+      </c>
+      <c r="O347">
+        <v>5</v>
+      </c>
+      <c r="P347">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="Q347">
+        <v>30.69</v>
+      </c>
+      <c r="R347">
+        <v>4.67</v>
+      </c>
+      <c r="S347">
+        <v>13</v>
+      </c>
+      <c r="T347">
+        <v>3</v>
+      </c>
+      <c r="U347">
+        <v>14</v>
+      </c>
+      <c r="V347">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A348" t="s">
+        <v>21</v>
+      </c>
+      <c r="B348" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C348" t="s">
+        <v>19</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E348" t="s">
+        <v>165</v>
+      </c>
+      <c r="F348" t="s">
+        <v>100</v>
+      </c>
+      <c r="G348" t="s">
+        <v>386</v>
+      </c>
+      <c r="H348">
+        <v>5.28</v>
+      </c>
+      <c r="I348">
+        <v>0.6</v>
+      </c>
+      <c r="J348">
+        <v>4.67</v>
+      </c>
+      <c r="K348">
+        <v>0.38</v>
+      </c>
+      <c r="L348">
+        <v>0.2</v>
+      </c>
+      <c r="M348">
+        <v>0.02</v>
+      </c>
+      <c r="N348">
+        <v>0</v>
+      </c>
+      <c r="O348">
+        <v>6</v>
+      </c>
+      <c r="P348">
+        <v>3.78</v>
+      </c>
+      <c r="Q348">
+        <v>25.98</v>
+      </c>
+      <c r="R348">
+        <v>5.05</v>
+      </c>
+      <c r="S348">
+        <v>32</v>
+      </c>
+      <c r="T348">
+        <v>11</v>
+      </c>
+      <c r="U348">
+        <v>38</v>
+      </c>
+      <c r="V348">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="349" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>21</v>
+      </c>
+      <c r="B349" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C349" t="s">
+        <v>19</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E349" t="s">
+        <v>88</v>
+      </c>
+      <c r="F349" t="s">
+        <v>23</v>
+      </c>
+      <c r="G349" t="s">
+        <v>387</v>
+      </c>
+      <c r="H349">
+        <v>5.45</v>
+      </c>
+      <c r="I349">
+        <v>0.41</v>
+      </c>
+      <c r="J349">
+        <v>5.04</v>
+      </c>
+      <c r="K349">
+        <v>0.35</v>
+      </c>
+      <c r="L349">
+        <v>0.05</v>
+      </c>
+      <c r="M349">
+        <v>0.01</v>
+      </c>
+      <c r="N349">
+        <v>0</v>
+      </c>
+      <c r="O349">
+        <v>2</v>
+      </c>
+      <c r="P349">
+        <v>3.75</v>
+      </c>
+      <c r="Q349">
+        <v>27.31</v>
+      </c>
+      <c r="R349">
+        <v>4.17</v>
+      </c>
+      <c r="S349">
+        <v>12</v>
+      </c>
+      <c r="T349">
+        <v>2</v>
+      </c>
+      <c r="U349">
+        <v>13</v>
+      </c>
+      <c r="V349">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>21</v>
+      </c>
+      <c r="B350" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C350" t="s">
+        <v>19</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E350" t="s">
+        <v>37</v>
+      </c>
+      <c r="F350" t="s">
+        <v>26</v>
+      </c>
+      <c r="G350" t="s">
+        <v>387</v>
+      </c>
+      <c r="H350">
+        <v>6.71</v>
+      </c>
+      <c r="I350">
+        <v>0.82</v>
+      </c>
+      <c r="J350">
+        <v>5.88</v>
+      </c>
+      <c r="K350">
+        <v>0.61</v>
+      </c>
+      <c r="L350">
+        <v>0.21</v>
+      </c>
+      <c r="M350">
+        <v>0.02</v>
+      </c>
+      <c r="N350">
+        <v>0</v>
+      </c>
+      <c r="O350">
+        <v>4</v>
+      </c>
+      <c r="P350">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="Q350">
+        <v>26.12</v>
+      </c>
+      <c r="R350">
+        <v>4.51</v>
+      </c>
+      <c r="S350">
+        <v>32</v>
+      </c>
+      <c r="T350">
+        <v>3</v>
+      </c>
+      <c r="U350">
+        <v>28</v>
+      </c>
+      <c r="V350">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79969A-D7C4-CF48-B5B6-B89D1A10148D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85635FF-66E4-8D4D-995D-81F2A3E59F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="389">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1199,6 +1199,9 @@
   </si>
   <si>
     <t>01:24:52</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
 </sst>
 </file>
@@ -1583,6 +1586,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>388</v>
+      </c>
       <c r="B1" t="s">
         <v>17</v>
       </c>

--- a/data/2026-2027/DonneesGPSPropres.xlsx
+++ b/data/2026-2027/DonneesGPSPropres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85635FF-66E4-8D4D-995D-81F2A3E59F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B094524D-17FB-F244-BC68-5DD3024AE686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{D839DFFF-AA38-2145-9D48-3C82EEA1EE91}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="392">
   <si>
     <t>Temps joué</t>
   </si>
@@ -1202,6 +1202,15 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>01:17:46</t>
+  </si>
+  <si>
+    <t>01:16:45</t>
+  </si>
+  <si>
+    <t>01:23:38</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE8228-0F81-ED4B-A4A4-4C340123FE2A}">
-  <dimension ref="A1:V350"/>
+  <dimension ref="A1:V355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -24485,6 +24494,346 @@
         <v>11</v>
       </c>
     </row>
+    <row r="351" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" s="1">
+        <v>46268</v>
+      </c>
+      <c r="C351" t="s">
+        <v>19</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E351" t="s">
+        <v>30</v>
+      </c>
+      <c r="F351" t="s">
+        <v>27</v>
+      </c>
+      <c r="G351" t="s">
+        <v>389</v>
+      </c>
+      <c r="H351">
+        <v>4.68</v>
+      </c>
+      <c r="I351">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J351">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K351">
+        <v>0.33</v>
+      </c>
+      <c r="L351">
+        <v>0.13</v>
+      </c>
+      <c r="M351">
+        <v>0.1</v>
+      </c>
+      <c r="N351">
+        <v>0.02</v>
+      </c>
+      <c r="O351">
+        <v>6</v>
+      </c>
+      <c r="P351">
+        <v>3.5</v>
+      </c>
+      <c r="Q351">
+        <v>31.67</v>
+      </c>
+      <c r="R351">
+        <v>5.56</v>
+      </c>
+      <c r="S351">
+        <v>11</v>
+      </c>
+      <c r="T351">
+        <v>13</v>
+      </c>
+      <c r="U351">
+        <v>19</v>
+      </c>
+      <c r="V351">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>21</v>
+      </c>
+      <c r="B352" s="1">
+        <v>46268</v>
+      </c>
+      <c r="C352" t="s">
+        <v>19</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E352" t="s">
+        <v>45</v>
+      </c>
+      <c r="F352" t="s">
+        <v>23</v>
+      </c>
+      <c r="G352" t="s">
+        <v>176</v>
+      </c>
+      <c r="H352">
+        <v>4.25</v>
+      </c>
+      <c r="I352">
+        <v>0.48</v>
+      </c>
+      <c r="J352">
+        <v>3.76</v>
+      </c>
+      <c r="K352">
+        <v>0.21</v>
+      </c>
+      <c r="L352">
+        <v>0.12</v>
+      </c>
+      <c r="M352">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N352">
+        <v>0.02</v>
+      </c>
+      <c r="O352">
+        <v>8</v>
+      </c>
+      <c r="P352">
+        <v>2.89</v>
+      </c>
+      <c r="Q352">
+        <v>32.090000000000003</v>
+      </c>
+      <c r="R352">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="S352">
+        <v>12</v>
+      </c>
+      <c r="T352">
+        <v>4</v>
+      </c>
+      <c r="U352">
+        <v>6</v>
+      </c>
+      <c r="V352">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>21</v>
+      </c>
+      <c r="B353" s="1">
+        <v>46268</v>
+      </c>
+      <c r="C353" t="s">
+        <v>19</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E353" t="s">
+        <v>90</v>
+      </c>
+      <c r="F353" t="s">
+        <v>100</v>
+      </c>
+      <c r="G353" t="s">
+        <v>390</v>
+      </c>
+      <c r="H353">
+        <v>5.01</v>
+      </c>
+      <c r="I353">
+        <v>0.8</v>
+      </c>
+      <c r="J353">
+        <v>4.2</v>
+      </c>
+      <c r="K353">
+        <v>0.35</v>
+      </c>
+      <c r="L353">
+        <v>0.32</v>
+      </c>
+      <c r="M353">
+        <v>0.11</v>
+      </c>
+      <c r="N353">
+        <v>0.04</v>
+      </c>
+      <c r="O353">
+        <v>16</v>
+      </c>
+      <c r="P353">
+        <v>3.45</v>
+      </c>
+      <c r="Q353">
+        <v>32.9</v>
+      </c>
+      <c r="R353">
+        <v>5.83</v>
+      </c>
+      <c r="S353">
+        <v>40</v>
+      </c>
+      <c r="T353">
+        <v>18</v>
+      </c>
+      <c r="U353">
+        <v>32</v>
+      </c>
+      <c r="V353">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>21</v>
+      </c>
+      <c r="B354" s="1">
+        <v>46268</v>
+      </c>
+      <c r="C354" t="s">
+        <v>19</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E354" t="s">
+        <v>29</v>
+      </c>
+      <c r="F354" t="s">
+        <v>25</v>
+      </c>
+      <c r="G354" t="s">
+        <v>240</v>
+      </c>
+      <c r="H354">
+        <v>4.74</v>
+      </c>
+      <c r="I354">
+        <v>0.9</v>
+      </c>
+      <c r="J354">
+        <v>3.83</v>
+      </c>
+      <c r="K354">
+        <v>0.53</v>
+      </c>
+      <c r="L354">
+        <v>0.26</v>
+      </c>
+      <c r="M354">
+        <v>0.1</v>
+      </c>
+      <c r="N354">
+        <v>0.02</v>
+      </c>
+      <c r="O354">
+        <v>6</v>
+      </c>
+      <c r="P354">
+        <v>3.46</v>
+      </c>
+      <c r="Q354">
+        <v>31.58</v>
+      </c>
+      <c r="R354">
+        <v>5.54</v>
+      </c>
+      <c r="S354">
+        <v>32</v>
+      </c>
+      <c r="T354">
+        <v>11</v>
+      </c>
+      <c r="U354">
+        <v>12</v>
+      </c>
+      <c r="V354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>21</v>
+      </c>
+      <c r="B355" s="1">
+        <v>46268</v>
+      </c>
+      <c r="C355" t="s">
+        <v>19</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E355" t="s">
+        <v>37</v>
+      </c>
+      <c r="F355" t="s">
+        <v>26</v>
+      </c>
+      <c r="G355" t="s">
+        <v>391</v>
+      </c>
+      <c r="H355">
+        <v>5.55</v>
+      </c>
+      <c r="I355">
+        <v>0.72</v>
+      </c>
+      <c r="J355">
+        <v>4.82</v>
+      </c>
+      <c r="K355">
+        <v>0.46</v>
+      </c>
+      <c r="L355">
+        <v>0.17</v>
+      </c>
+      <c r="M355">
+        <v>0.1</v>
+      </c>
+      <c r="N355">
+        <v>0</v>
+      </c>
+      <c r="O355">
+        <v>7</v>
+      </c>
+      <c r="P355">
+        <v>3.68</v>
+      </c>
+      <c r="Q355">
+        <v>30.27</v>
+      </c>
+      <c r="R355">
+        <v>5.4</v>
+      </c>
+      <c r="S355">
+        <v>36</v>
+      </c>
+      <c r="T355">
+        <v>30</v>
+      </c>
+      <c r="U355">
+        <v>40</v>
+      </c>
+      <c r="V355">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
